--- a/progress/megatrends_RF.xlsx
+++ b/progress/megatrends_RF.xlsx
@@ -3,11 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Political stringency" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Color code" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Political stringency'!$A$1:$N$25</definedName>
+  </definedNames>
   <calcPr/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
@@ -16,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <si>
     <t>Calcul</t>
   </si>
@@ -79,7 +83,7 @@
 AES, HVE, bio</t>
   </si>
   <si>
-    <t>PS01_GREEN_AREA</t>
+    <t>PS_GREEN_AREA</t>
   </si>
   <si>
     <t>%</t>
@@ -112,7 +116,7 @@
     <t xml:space="preserve">Ministère de l'Agriculture et de l'Alimentation</t>
   </si>
   <si>
-    <t>PS02_GREEN_SUBS</t>
+    <t>PS_GREEN_SUBS</t>
   </si>
   <si>
     <t>EUR</t>
@@ -145,10 +149,7 @@
 build on indicator 1?</t>
   </si>
   <si>
-    <t>PS03_CLIMATE_AREA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a tester</t>
+    <t>PS_CLIMATE_AREA</t>
   </si>
   <si>
     <t xml:space="preserve">% grassland</t>
@@ -168,14 +169,24 @@
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">
-P_GRA_CROP → % of grassland relative to the total agricultural area (standardized by agricultural area)</t>
+P_GRA_CROP → % of grassland relative to the total agricultural area (standardized by agricultural area)
+</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="2"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+Not all grassland in RPG... How to define grassland in RPG?</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">IGN RPG</t>
   </si>
   <si>
-    <t>PS04_GRASS_AREA</t>
+    <t>PS_GRASS_AREA</t>
   </si>
   <si>
     <t>https://geoservices.ign.fr/rpg</t>
@@ -221,7 +232,7 @@
 BD TOPO? OSO?</t>
   </si>
   <si>
-    <t>PS05_FOREST_AREA</t>
+    <t>PS_FOREST_AREA</t>
   </si>
   <si>
     <t>https://geoservices.ign.fr/bdforet</t>
@@ -239,7 +250,7 @@
     <t>PAUL</t>
   </si>
   <si>
-    <t>PS06_AGROFST_AREA</t>
+    <t>PS_AGROFST_AREA</t>
   </si>
   <si>
     <t>Farm</t>
@@ -269,7 +280,7 @@
     </r>
   </si>
   <si>
-    <t>PS07_NB_HVE</t>
+    <t>PS_NB_HVE</t>
   </si>
   <si>
     <t>/</t>
@@ -303,14 +314,14 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="8" tint="0"/>
+        <color indexed="2"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">Cartobio (already processed)</t>
+      <t xml:space="preserve">or Cartobio (already processed)?</t>
     </r>
   </si>
   <si>
-    <t>PS08_ORG_AREA</t>
+    <t>PS_ORG_AREA</t>
   </si>
   <si>
     <t>https://www.data.gouv.fr/fr/datasets/parcelles-en-agriculture-biologique-ab-declarees-a-la-pac/</t>
@@ -349,7 +360,7 @@
     </r>
   </si>
   <si>
-    <t>PS09_FALLOW_AREA</t>
+    <t>PS_FALLOW_AREA</t>
   </si>
   <si>
     <t xml:space="preserve">Fertilizer use reduction</t>
@@ -361,6 +372,9 @@
     <t xml:space="preserve">légumineuses (pas d'apport d'azote nécessaire); présence de légumineuses dans les rotations culturales; surfaces cultivées en bio, RNN, MAEC, rammsar, BCAE 4 - Bandes tampons des cours d'eau (5m)</t>
   </si>
   <si>
+    <t xml:space="preserve">based on RPG?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fertilizer sales</t>
   </si>
   <si>
@@ -370,15 +384,31 @@
     <t xml:space="preserve">Nitrate levels at water intake points</t>
   </si>
   <si>
-    <t xml:space="preserve">ND_GW_2024 →  Average nitrate concentrations (mg/L) in groundwater in 2024
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">ND_GW_2024 →  Average nitrate concentrations (mg/L) in groundwater in 2024
 ND_SW_2024 → Average nitrate concentrations (mg/L)  in surface waters in 2024
-interpolation (IDW) of nitrate measurements from groundwater monitoring stations</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="2"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">interpolation (IDW) of nitrate measurements from groundwater monitoring stations
+how to interpolate? along rivers?</t>
+    </r>
   </si>
   <si>
     <t>Eaufrance</t>
   </si>
   <si>
-    <t xml:space="preserve">ND_GW_2024; ND_SW_2024</t>
+    <t xml:space="preserve">PS_NI_GW_2024
+PS_NI_SW_2024</t>
   </si>
   <si>
     <r>
@@ -416,13 +446,16 @@
     <t>Station</t>
   </si>
   <si>
+    <t xml:space="preserve">a tester</t>
+  </si>
+  <si>
     <t xml:space="preserve">Crop type</t>
   </si>
   <si>
     <t xml:space="preserve">Dominant crop by municipality in term of surface area</t>
   </si>
   <si>
-    <t>PS13_CROP_TYPE</t>
+    <t>PS_CROP_TYPE</t>
   </si>
   <si>
     <t xml:space="preserve">Pesticide use reduction</t>
@@ -435,7 +468,23 @@
 PEST_EVO → Change in active substance use (kg) between 2015 and 2020 per municipality</t>
   </si>
   <si>
-    <t xml:space="preserve">Lungarska, Anna; Poméon, Thomas; Lision, Olivier; Ramalanjaona, Lovasoa; Cantelaube, Pierre; Lardot, Benjamin, 2024, "Extraction à la commune des données de la BNV-D spatialisée 2015 - 2020 (csv)", https://doi.org/10.57745/PCUA3B, Recherche Data Gouv, V1</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Lungarska, et al. 2024, https://doi.org/10.57745/PCUA3B
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="2"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">or
+Rigal and Perrot 2025 https://doi.org/10.5061/dryad.g4f4qrg0p</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">PEST_tot, PEST_EVO</t>
@@ -464,14 +513,14 @@
     <t xml:space="preserve">dominant crop by municipality”</t>
   </si>
   <si>
-    <t xml:space="preserve">same as PS13_CROP_TYPE?</t>
+    <t xml:space="preserve">same as PS_CROP_TYPE?</t>
   </si>
   <si>
     <t xml:space="preserve">P_GRA → % of grassland relative to the total area of the municipality (standardized by municipality size)
 P_GRA_CROP → % of grassland relative to the total agricultural area (standardized by agricultural area)</t>
   </si>
   <si>
-    <t xml:space="preserve">same as PS04_GRASS_AREA?</t>
+    <t xml:space="preserve">same as PS_GRASS_AREA?</t>
   </si>
   <si>
     <t xml:space="preserve">P_FOR→ % of forest relative to the total area of the municipality (standardized by municipality size)</t>
@@ -480,7 +529,7 @@
     <t xml:space="preserve">IGN BD TOPO</t>
   </si>
   <si>
-    <t xml:space="preserve">same as PS05_FOREST_AREA?</t>
+    <t xml:space="preserve">same as PS_FOREST_AREA?</t>
   </si>
   <si>
     <t>https://geoservices.ign.fr/documentation/donnees/vecteur/bdforet</t>
@@ -489,7 +538,7 @@
     <t xml:space="preserve">Agence Bio</t>
   </si>
   <si>
-    <t xml:space="preserve">same as PS08_ORG_AREA?</t>
+    <t xml:space="preserve">same as PS_ORG_AREA?</t>
   </si>
   <si>
     <t xml:space="preserve">Antibiotic use reduction</t>
@@ -499,6 +548,9 @@
   </si>
   <si>
     <t xml:space="preserve">Disease frequency or occurence</t>
+  </si>
+  <si>
+    <t>ok</t>
   </si>
   <si>
     <t xml:space="preserve">Protected area</t>
@@ -524,11 +576,11 @@
         <color indexed="2"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>WDPA?</t>
+      <t xml:space="preserve">or WDPA?</t>
     </r>
   </si>
   <si>
-    <t>PS21_PROTECTED_AREA</t>
+    <t>PS_PROT_AREA</t>
   </si>
   <si>
     <t>https://inpn.mnhn.fr/telechargement/cartes-et-information-geographique/nat/natura</t>
@@ -539,13 +591,13 @@
   <si>
     <t xml:space="preserve">to be defined
 on how many years? crop type?
-there are180 indicators available </t>
+there are 180 indicators available </t>
   </si>
   <si>
     <t xml:space="preserve">INRAE successions culturales</t>
   </si>
   <si>
-    <t>PS22_NCROP</t>
+    <t>PS_NCROP</t>
   </si>
   <si>
     <t>https://entrepot.recherche.data.gouv.fr/dataset.xhtml?persistentId=doi:10.57745/DPSBYA</t>
@@ -557,7 +609,7 @@
     <t>2015-2022</t>
   </si>
   <si>
-    <t xml:space="preserve">same as PS22_NCROP?</t>
+    <t xml:space="preserve">same as PS_NCROP?</t>
   </si>
   <si>
     <t xml:space="preserve">Crop diversity</t>
@@ -581,14 +633,38 @@
     </r>
   </si>
   <si>
-    <t>PS24_CROP_DIV</t>
+    <t>PS_CROP_DIV</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data is available, calculations are clear and feasible =&gt; indicator calculated or under reach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">few details have to be discussed, but it shouldn't be too difficult to get an indicator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">some important information missing before getting an indicator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data not identified properly or calculations not defined. Hard to imagine an indicator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indicator that seems duplicated with another one (to be deleted from the list?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">out of my reach</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -647,6 +723,13 @@
       <color theme="10"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -681,26 +764,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor theme="7" tint="0.39997558519241921"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor theme="9" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor theme="7" tint="-0.249977111117893"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFD9"/>
-        <bgColor rgb="FFE2EFD9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFCB8B8"/>
+        <bgColor rgb="FFFCB8B8"/>
       </patternFill>
     </fill>
   </fills>
@@ -716,7 +799,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -775,6 +858,9 @@
     <xf fontId="3" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="7" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="6" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -785,15 +871,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="6" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="6" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -804,28 +896,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="6" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="4" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="8" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -847,6 +931,8 @@
     <xf fontId="10" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="11" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1351,7 +1437,7 @@
     <col customWidth="1" min="3" max="3" width="19.8515625"/>
     <col customWidth="1" min="4" max="4" width="16.28125"/>
     <col customWidth="1" min="5" max="5" width="31.57421875"/>
-    <col customWidth="1" min="6" max="6" width="36.421875"/>
+    <col customWidth="1" min="6" max="6" width="45.8515625"/>
     <col customWidth="1" min="7" max="7" width="32.140625"/>
     <col customWidth="1" min="8" max="8" width="34.421875"/>
     <col customWidth="1" min="10" max="10" width="32.00390625"/>
@@ -1361,7 +1447,7 @@
     <col customWidth="1" min="14" max="14" width="25.421875"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="38.25">
+    <row r="1" s="1" customFormat="1" ht="25.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1475,7 +1561,7 @@
       <c r="AF2" s="9"/>
       <c r="AG2" s="10"/>
     </row>
-    <row r="3" s="11" customFormat="1" ht="102">
+    <row r="3" s="11" customFormat="1" ht="76.5">
       <c r="A3" s="12" t="s">
         <v>22</v>
       </c>
@@ -1591,129 +1677,129 @@
       <c r="AF4" s="9"/>
       <c r="AG4" s="10"/>
     </row>
-    <row r="5" s="17" customFormat="1" ht="89.25">
-      <c r="A5" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="18" t="str">
+    <row r="5" s="11" customFormat="1" ht="102">
+      <c r="A5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="12" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="G5" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="H5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="I5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="19" t="s">
+      <c r="K5" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="L5" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="M5" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="18" t="s">
+      <c r="N5" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15"/>
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" s="15"/>
+      <c r="AC5" s="15"/>
+      <c r="AD5" s="15"/>
+      <c r="AE5" s="15"/>
+      <c r="AF5" s="15"/>
+      <c r="AG5" s="16"/>
+    </row>
+    <row r="6" s="17" customFormat="1" ht="38.25">
+      <c r="A6" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18"/>
-      <c r="S5" s="18"/>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="20"/>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="20"/>
-      <c r="AB5" s="20"/>
-      <c r="AC5" s="20"/>
-      <c r="AD5" s="20"/>
-      <c r="AE5" s="20"/>
-      <c r="AF5" s="20"/>
-      <c r="AG5" s="21"/>
-    </row>
-    <row r="6" s="22" customFormat="1" ht="51">
-      <c r="A6" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="23" t="str">
+      <c r="B6" s="18" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="G6" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="H6" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="I6" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="25" t="s">
+      <c r="K6" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="23" t="s">
+      <c r="L6" s="18"/>
+      <c r="M6" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="26"/>
-      <c r="V6" s="26"/>
-      <c r="W6" s="26"/>
-      <c r="X6" s="26"/>
-      <c r="Y6" s="26"/>
-      <c r="Z6" s="26"/>
-      <c r="AA6" s="26"/>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
-      <c r="AD6" s="26"/>
-      <c r="AE6" s="26"/>
-      <c r="AF6" s="26"/>
-      <c r="AG6" s="27"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="21"/>
+      <c r="W6" s="21"/>
+      <c r="X6" s="21"/>
+      <c r="Y6" s="21"/>
+      <c r="Z6" s="21"/>
+      <c r="AA6" s="21"/>
+      <c r="AB6" s="21"/>
+      <c r="AC6" s="21"/>
+      <c r="AD6" s="21"/>
+      <c r="AE6" s="21"/>
+      <c r="AF6" s="21"/>
+      <c r="AG6" s="22"/>
     </row>
     <row r="7" s="7" customFormat="1" ht="38.25">
       <c r="A7" s="8" t="s">
@@ -1730,32 +1816,32 @@
         <v>33</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>56</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>44</v>
-      </c>
       <c r="M7" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N7" s="28" t="s">
-        <v>46</v>
+        <v>57</v>
+      </c>
+      <c r="N7" s="23" t="s">
+        <v>45</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -1782,7 +1868,7 @@
         <v>22</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>16</v>
@@ -1791,28 +1877,28 @@
         <v>33</v>
       </c>
       <c r="E8" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>60</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>61</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>25</v>
       </c>
       <c r="H8" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="J8" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="J8" s="30" t="s">
+      <c r="K8" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="L8" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>66</v>
       </c>
       <c r="M8" s="12" t="s">
         <v>31</v>
@@ -1838,71 +1924,71 @@
       <c r="AF8" s="15"/>
       <c r="AG8" s="16"/>
     </row>
-    <row r="9" s="11" customFormat="1" ht="89.25">
-      <c r="A9" s="12" t="s">
+    <row r="9" s="26" customFormat="1" ht="76.5">
+      <c r="A9" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="G9" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="H9" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="I9" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="14" t="s">
+      <c r="K9" s="27"/>
+      <c r="L9" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="M9" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="15"/>
-      <c r="Y9" s="15"/>
-      <c r="Z9" s="15"/>
-      <c r="AA9" s="15"/>
-      <c r="AB9" s="15"/>
-      <c r="AC9" s="15"/>
-      <c r="AD9" s="15"/>
-      <c r="AE9" s="15"/>
-      <c r="AF9" s="15"/>
-      <c r="AG9" s="16"/>
-    </row>
-    <row r="10" s="11" customFormat="1" ht="114.75">
+      <c r="M9" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="29"/>
+      <c r="AC9" s="29"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="29"/>
+      <c r="AF9" s="29"/>
+      <c r="AG9" s="30"/>
+    </row>
+    <row r="10" s="11" customFormat="1" ht="89.25">
       <c r="A10" s="12" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>16</v>
@@ -1911,34 +1997,34 @@
         <v>33</v>
       </c>
       <c r="E10" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="G10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J10" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="L10" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="M10" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="N10" s="14" t="s">
         <v>45</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>46</v>
       </c>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
@@ -1960,226 +2046,228 @@
       <c r="AF10" s="15"/>
       <c r="AG10" s="16"/>
     </row>
-    <row r="11" s="22" customFormat="1" ht="76.5">
-      <c r="A11" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="23" t="str">
+    <row r="11" s="17" customFormat="1" ht="63.75">
+      <c r="A11" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="18" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="F11" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="G11" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="26"/>
-      <c r="W11" s="26"/>
-      <c r="X11" s="26"/>
-      <c r="Y11" s="26"/>
-      <c r="Z11" s="26"/>
-      <c r="AA11" s="26"/>
-      <c r="AB11" s="26"/>
-      <c r="AC11" s="26"/>
-      <c r="AD11" s="26"/>
-      <c r="AE11" s="26"/>
-      <c r="AF11" s="26"/>
-      <c r="AG11" s="27"/>
-    </row>
-    <row r="12" s="22" customFormat="1" ht="25.5">
-      <c r="A12" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="23" t="str">
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="21"/>
+      <c r="W11" s="21"/>
+      <c r="X11" s="21"/>
+      <c r="Y11" s="21"/>
+      <c r="Z11" s="21"/>
+      <c r="AA11" s="21"/>
+      <c r="AB11" s="21"/>
+      <c r="AC11" s="21"/>
+      <c r="AD11" s="21"/>
+      <c r="AE11" s="21"/>
+      <c r="AF11" s="21"/>
+      <c r="AG11" s="22"/>
+    </row>
+    <row r="12" s="31" customFormat="1" ht="25.5">
+      <c r="A12" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="32" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" s="23" t="s">
+      <c r="D12" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="26"/>
-      <c r="W12" s="26"/>
-      <c r="X12" s="26"/>
-      <c r="Y12" s="26"/>
-      <c r="Z12" s="26"/>
-      <c r="AA12" s="26"/>
-      <c r="AB12" s="26"/>
-      <c r="AC12" s="26"/>
-      <c r="AD12" s="26"/>
-      <c r="AE12" s="26"/>
-      <c r="AF12" s="26"/>
-      <c r="AG12" s="27"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="114.75">
-      <c r="A13" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="31" t="s">
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="32"/>
+      <c r="S12" s="32"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="33"/>
+      <c r="V12" s="33"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="33"/>
+      <c r="Y12" s="33"/>
+      <c r="Z12" s="33"/>
+      <c r="AA12" s="33"/>
+      <c r="AB12" s="33"/>
+      <c r="AC12" s="33"/>
+      <c r="AD12" s="33"/>
+      <c r="AE12" s="33"/>
+      <c r="AF12" s="33"/>
+      <c r="AG12" s="34"/>
+    </row>
+    <row r="13" s="17" customFormat="1" ht="89.25">
+      <c r="A13" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" s="31" t="s">
+      <c r="D13" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="H13" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="I13" s="32"/>
-      <c r="J13" s="33" t="s">
+      <c r="I13" s="18"/>
+      <c r="J13" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="K13" s="32" t="s">
+      <c r="K13" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="L13" s="32" t="s">
+      <c r="L13" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="32" t="s">
+      <c r="M13" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="32"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="34"/>
-      <c r="W13" s="34"/>
-      <c r="X13" s="34"/>
-      <c r="Y13" s="34"/>
-      <c r="Z13" s="34"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="34"/>
-      <c r="AC13" s="34"/>
-      <c r="AD13" s="34"/>
-      <c r="AE13" s="34"/>
-      <c r="AF13" s="34"/>
-      <c r="AG13" s="6"/>
-    </row>
-    <row r="14" s="17" customFormat="1" ht="38.25">
-      <c r="A14" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="18" t="str">
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="18"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="21"/>
+      <c r="AA13" s="21"/>
+      <c r="AB13" s="21"/>
+      <c r="AC13" s="21"/>
+      <c r="AD13" s="21"/>
+      <c r="AE13" s="21"/>
+      <c r="AF13" s="21"/>
+      <c r="AG13" s="22"/>
+    </row>
+    <row r="14" s="26" customFormat="1" ht="38.25">
+      <c r="A14" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="27" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="18" t="s">
+      <c r="D14" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="G14" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="H14" s="18" t="s">
+      <c r="F14" s="27" t="s">
         <v>91</v>
       </c>
+      <c r="G14" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>92</v>
+      </c>
       <c r="I14" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="J14" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="K14" s="18" t="s">
+      <c r="L14" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="L14" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="M14" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="N14" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="20"/>
-      <c r="U14" s="20"/>
-      <c r="V14" s="20"/>
-      <c r="W14" s="20"/>
-      <c r="X14" s="20"/>
-      <c r="Y14" s="20"/>
-      <c r="Z14" s="20"/>
-      <c r="AA14" s="20"/>
-      <c r="AB14" s="20"/>
-      <c r="AC14" s="20"/>
-      <c r="AD14" s="20"/>
-      <c r="AE14" s="20"/>
-      <c r="AF14" s="20"/>
-      <c r="AG14" s="21"/>
-    </row>
-    <row r="15" s="11" customFormat="1" ht="165.75">
+      <c r="M14" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="29"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="29"/>
+      <c r="AF14" s="29"/>
+      <c r="AG14" s="30"/>
+    </row>
+    <row r="15" s="11" customFormat="1" ht="140.25">
       <c r="A15" s="12" t="s">
         <v>22</v>
       </c>
@@ -2191,34 +2279,34 @@
         <v>16</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="I15" s="29" t="s">
         <v>97</v>
       </c>
+      <c r="I15" s="24" t="s">
+        <v>98</v>
+      </c>
       <c r="J15" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N15" s="12"/>
       <c r="O15" s="12"/>
@@ -2243,7 +2331,7 @@
     </row>
     <row r="16" s="36" customFormat="1" ht="38.25">
       <c r="A16" s="37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B16" s="37" t="str">
         <f t="shared" si="0"/>
@@ -2253,37 +2341,37 @@
         <v>16</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J16" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="K16" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="K16" s="37" t="s">
+      <c r="L16" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="L16" s="37" t="s">
-        <v>44</v>
-      </c>
       <c r="M16" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N16" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O16" s="37"/>
       <c r="P16" s="37"/>
@@ -2305,9 +2393,9 @@
       <c r="AF16" s="39"/>
       <c r="AG16" s="40"/>
     </row>
-    <row r="17" s="36" customFormat="1" ht="89.25">
+    <row r="17" s="36" customFormat="1" ht="63.75">
       <c r="A17" s="37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B17" s="37" t="str">
         <f t="shared" si="0"/>
@@ -2317,37 +2405,37 @@
         <v>16</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I17" s="37" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="K17" s="37" t="s">
+      <c r="L17" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="L17" s="37" t="s">
-        <v>44</v>
-      </c>
       <c r="M17" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N17" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O17" s="37"/>
       <c r="P17" s="37"/>
@@ -2371,7 +2459,7 @@
     </row>
     <row r="18" s="36" customFormat="1" ht="38.25">
       <c r="A18" s="37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B18" s="37" t="str">
         <f t="shared" si="0"/>
@@ -2381,33 +2469,33 @@
         <v>16</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I18" s="37" t="s">
         <v>21</v>
       </c>
       <c r="J18" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="37" t="s">
         <v>52</v>
-      </c>
-      <c r="K18" s="37" t="s">
-        <v>53</v>
       </c>
       <c r="L18" s="37"/>
       <c r="M18" s="37"/>
       <c r="N18" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O18" s="37"/>
       <c r="P18" s="37"/>
@@ -2429,9 +2517,9 @@
       <c r="AF18" s="39"/>
       <c r="AG18" s="40"/>
     </row>
-    <row r="19" s="36" customFormat="1" ht="89.25">
+    <row r="19" s="36" customFormat="1" ht="76.5">
       <c r="A19" s="37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B19" s="37" t="str">
         <f t="shared" si="0"/>
@@ -2441,32 +2529,32 @@
         <v>16</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E19" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="37" t="s">
-        <v>68</v>
-      </c>
       <c r="G19" s="37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I19" s="37" t="s">
         <v>21</v>
       </c>
       <c r="J19" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K19" s="37"/>
       <c r="L19" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M19" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N19" s="37"/>
       <c r="O19" s="37"/>
@@ -2489,194 +2577,194 @@
       <c r="AF19" s="39"/>
       <c r="AG19" s="40"/>
     </row>
-    <row r="20" s="22" customFormat="1" ht="25.5">
-      <c r="A20" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="23" t="str">
+    <row r="20" s="31" customFormat="1" ht="25.5">
+      <c r="A20" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="32" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" s="23" t="s">
+      <c r="D20" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="E20" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="26"/>
-      <c r="V20" s="26"/>
-      <c r="W20" s="26"/>
-      <c r="X20" s="26"/>
-      <c r="Y20" s="26"/>
-      <c r="Z20" s="26"/>
-      <c r="AA20" s="26"/>
-      <c r="AB20" s="26"/>
-      <c r="AC20" s="26"/>
-      <c r="AD20" s="26"/>
-      <c r="AE20" s="26"/>
-      <c r="AF20" s="26"/>
-      <c r="AG20" s="27"/>
-    </row>
-    <row r="21" s="22" customFormat="1" ht="25.5">
-      <c r="A21" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="23" t="str">
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="33"/>
+      <c r="U20" s="33"/>
+      <c r="V20" s="33"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="33"/>
+      <c r="Y20" s="33"/>
+      <c r="Z20" s="33"/>
+      <c r="AA20" s="33"/>
+      <c r="AB20" s="33"/>
+      <c r="AC20" s="33"/>
+      <c r="AD20" s="33"/>
+      <c r="AE20" s="33"/>
+      <c r="AF20" s="33"/>
+      <c r="AG20" s="34"/>
+    </row>
+    <row r="21" s="31" customFormat="1" ht="25.5">
+      <c r="A21" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="32" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="F21" s="23" t="s">
+      <c r="D21" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="26"/>
-      <c r="V21" s="26"/>
-      <c r="W21" s="26"/>
-      <c r="X21" s="26"/>
-      <c r="Y21" s="26"/>
-      <c r="Z21" s="26"/>
-      <c r="AA21" s="26"/>
-      <c r="AB21" s="26"/>
-      <c r="AC21" s="26"/>
-      <c r="AD21" s="26"/>
-      <c r="AE21" s="26"/>
-      <c r="AF21" s="26"/>
-      <c r="AG21" s="27"/>
-    </row>
-    <row r="22" s="11" customFormat="1" ht="38.25">
-      <c r="A22" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="12" t="str">
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="33"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="33"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="33"/>
+      <c r="AB21" s="33"/>
+      <c r="AC21" s="33"/>
+      <c r="AD21" s="33"/>
+      <c r="AE21" s="33"/>
+      <c r="AF21" s="33"/>
+      <c r="AG21" s="34"/>
+    </row>
+    <row r="22" s="26" customFormat="1" ht="38.25">
+      <c r="A22" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="27" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="F22" s="12" t="s">
+      <c r="D22" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="E22" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="F22" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="G22" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="I22" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="J22" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="K22" s="29"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="15"/>
-      <c r="U22" s="15"/>
-      <c r="V22" s="15"/>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="15"/>
-      <c r="AA22" s="15"/>
-      <c r="AB22" s="15"/>
-      <c r="AC22" s="15"/>
-      <c r="AD22" s="15"/>
-      <c r="AE22" s="15"/>
-      <c r="AF22" s="15"/>
-      <c r="AG22" s="16"/>
+      <c r="J22" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="K22" s="35"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="27"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+      <c r="W22" s="29"/>
+      <c r="X22" s="29"/>
+      <c r="Y22" s="29"/>
+      <c r="Z22" s="29"/>
+      <c r="AA22" s="29"/>
+      <c r="AB22" s="29"/>
+      <c r="AC22" s="29"/>
+      <c r="AD22" s="29"/>
+      <c r="AE22" s="29"/>
+      <c r="AF22" s="29"/>
+      <c r="AG22" s="30"/>
     </row>
     <row r="23" s="11" customFormat="1" ht="42.75">
       <c r="A23" s="12" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I23" s="12"/>
       <c r="J23" s="41" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>31</v>
@@ -2704,28 +2792,28 @@
     </row>
     <row r="24" s="36" customFormat="1" ht="25.5">
       <c r="A24" s="37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C24" s="39" t="s">
         <v>16</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E24" s="39" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I24" s="37"/>
       <c r="J24" s="37"/>
@@ -2758,7 +2846,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>16</v>
@@ -2767,34 +2855,34 @@
         <v>17</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J25" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K25" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K25" s="12" t="s">
+      <c r="L25" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L25" s="12" t="s">
-        <v>44</v>
-      </c>
       <c r="M25" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N25" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O25" s="12"/>
       <c r="P25" s="12"/>
@@ -2817,6 +2905,7 @@
       <c r="AG25" s="16"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N25"/>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="J3"/>
     <hyperlink r:id="rId2" ref="N3"/>
@@ -2850,4 +2939,63 @@
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="2" max="2" width="62.57421875"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" s="27"/>
+      <c r="B2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" s="12"/>
+      <c r="B3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" s="18"/>
+      <c r="B4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="32"/>
+      <c r="B5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="37"/>
+      <c r="B6" s="43" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="8"/>
+      <c r="B7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/progress/megatrends_RF.xlsx
+++ b/progress/megatrends_RF.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Political stringency" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Color code" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Political stringency'!$A$1:$N$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Political stringency'!$A$1:$N$25</definedName>
   </definedNames>
   <calcPr/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <si>
     <t>Calcul</t>
   </si>
@@ -89,7 +90,7 @@
     <t>%</t>
   </si>
   <si>
-    <t>questions</t>
+    <t xml:space="preserve">a tester</t>
   </si>
   <si>
     <t xml:space="preserve">amount of allocations received for greening practices</t>
@@ -150,6 +151,9 @@
   </si>
   <si>
     <t>PS_CLIMATE_AREA</t>
+  </si>
+  <si>
+    <t>questions</t>
   </si>
   <si>
     <t xml:space="preserve">% grassland</t>
@@ -256,6 +260,9 @@
     <t>Farm</t>
   </si>
   <si>
+    <t>ok</t>
+  </si>
+  <si>
     <t>V2</t>
   </si>
   <si>
@@ -299,35 +306,16 @@
     <t xml:space="preserve">% organic farming</t>
   </si>
   <si>
-    <t xml:space="preserve">P_ORG → % of organic crop relative to the total area of the municipality (standardized by municipality size)
-P_ORG_CROP → % of organic crop relative to the total agricultural area (standardized by agricultural area)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Agence Bio
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="2"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">or Cartobio (already processed)?</t>
-    </r>
+    <t xml:space="preserve">PS_ORG_AREA : % of organic crop relative to the municipality area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agence Bio (Cartobio)</t>
   </si>
   <si>
     <t>PS_ORG_AREA</t>
   </si>
   <si>
-    <t>https://www.data.gouv.fr/fr/datasets/parcelles-en-agriculture-biologique-ab-declarees-a-la-pac/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019 - 2022</t>
+    <t>https://www.data.gouv.fr/datasets/parcelles-certifiees-en-agriculture-biologique-sur-cartobio</t>
   </si>
   <si>
     <t xml:space="preserve">% fallow land</t>
@@ -446,9 +434,6 @@
     <t>Station</t>
   </si>
   <si>
-    <t xml:space="preserve">a tester</t>
-  </si>
-  <si>
     <t xml:space="preserve">Crop type</t>
   </si>
   <si>
@@ -456,6 +441,9 @@
   </si>
   <si>
     <t>PS_CROP_TYPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">à tester</t>
   </si>
   <si>
     <t xml:space="preserve">Pesticide use reduction</t>
@@ -535,12 +523,22 @@
     <t>https://geoservices.ign.fr/documentation/donnees/vecteur/bdforet</t>
   </si>
   <si>
+    <t xml:space="preserve">P_ORG → % of organic crop relative to the total area of the municipality (standardized by municipality size)
+P_ORG_CROP → % of organic crop relative to the total agricultural area (standardized by agricultural area)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Agence Bio</t>
   </si>
   <si>
     <t xml:space="preserve">same as PS_ORG_AREA?</t>
   </si>
   <si>
+    <t>https://www.data.gouv.fr/fr/datasets/parcelles-en-agriculture-biologique-ab-declarees-a-la-pac/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019 - 2022</t>
+  </si>
+  <si>
     <t xml:space="preserve">Antibiotic use reduction</t>
   </si>
   <si>
@@ -548,9 +546,6 @@
   </si>
   <si>
     <t xml:space="preserve">Disease frequency or occurence</t>
-  </si>
-  <si>
-    <t>ok</t>
   </si>
   <si>
     <t xml:space="preserve">Protected area</t>
@@ -764,14 +759,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor theme="7" tint="0.39997558519241921"/>
       </patternFill>
     </fill>
     <fill>
@@ -799,7 +794,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -836,6 +831,9 @@
     <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="3" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="3" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -852,64 +850,64 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="6" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="6" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="7" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf fontId="8" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="10" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="6" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="6" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="8" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="8" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1565,65 +1563,65 @@
       <c r="A3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="12" t="str">
+      <c r="B3" s="13" t="str">
         <f t="shared" ref="B3:B22" si="0">$B$2</f>
         <v>V1</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="N3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="15"/>
-      <c r="Y3" s="15"/>
-      <c r="Z3" s="15"/>
-      <c r="AA3" s="15"/>
-      <c r="AB3" s="15"/>
-      <c r="AC3" s="15"/>
-      <c r="AD3" s="15"/>
-      <c r="AE3" s="15"/>
-      <c r="AF3" s="15"/>
-      <c r="AG3" s="16"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="17"/>
     </row>
     <row r="4" s="7" customFormat="1" ht="55.5" customHeight="1">
       <c r="A4" s="8" t="s">
@@ -1678,128 +1676,128 @@
       <c r="AG4" s="10"/>
     </row>
     <row r="5" s="11" customFormat="1" ht="102">
-      <c r="A5" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="12" t="str">
+      <c r="A5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="13" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="12" t="s">
+      <c r="E5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="F5" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="G5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="H5" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="12" t="s">
+      <c r="J5" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="K5" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="L5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="M5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="15"/>
-      <c r="Y5" s="15"/>
-      <c r="Z5" s="15"/>
-      <c r="AA5" s="15"/>
-      <c r="AB5" s="15"/>
-      <c r="AC5" s="15"/>
-      <c r="AD5" s="15"/>
-      <c r="AE5" s="15"/>
-      <c r="AF5" s="15"/>
-      <c r="AG5" s="16"/>
-    </row>
-    <row r="6" s="17" customFormat="1" ht="38.25">
-      <c r="A6" s="18" t="s">
+      <c r="N5" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="18" t="str">
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AC5" s="16"/>
+      <c r="AD5" s="16"/>
+      <c r="AE5" s="16"/>
+      <c r="AF5" s="16"/>
+      <c r="AG5" s="17"/>
+    </row>
+    <row r="6" s="18" customFormat="1" ht="38.25">
+      <c r="A6" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="19" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="18" t="s">
+      <c r="E6" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="F6" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="G6" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="H6" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="K6" s="18" t="s">
+      <c r="J6" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18" t="s">
+      <c r="K6" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="21"/>
-      <c r="V6" s="21"/>
-      <c r="W6" s="21"/>
-      <c r="X6" s="21"/>
-      <c r="Y6" s="21"/>
-      <c r="Z6" s="21"/>
-      <c r="AA6" s="21"/>
-      <c r="AB6" s="21"/>
-      <c r="AC6" s="21"/>
-      <c r="AD6" s="21"/>
-      <c r="AE6" s="21"/>
-      <c r="AF6" s="21"/>
-      <c r="AG6" s="22"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+      <c r="AC6" s="22"/>
+      <c r="AD6" s="22"/>
+      <c r="AE6" s="22"/>
+      <c r="AF6" s="22"/>
+      <c r="AG6" s="23"/>
     </row>
     <row r="7" s="7" customFormat="1" ht="38.25">
       <c r="A7" s="8" t="s">
@@ -1816,32 +1814,32 @@
         <v>33</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="23" t="s">
-        <v>41</v>
+      <c r="J7" s="24" t="s">
+        <v>42</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" s="23" t="s">
-        <v>45</v>
+        <v>58</v>
+      </c>
+      <c r="N7" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -1863,12 +1861,12 @@
       <c r="AF7" s="9"/>
       <c r="AG7" s="10"/>
     </row>
-    <row r="8" s="11" customFormat="1" ht="38.25">
+    <row r="8" s="25" customFormat="1" ht="38.25">
       <c r="A8" s="12" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>16</v>
@@ -1877,28 +1875,28 @@
         <v>33</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>25</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="25" t="s">
         <v>63</v>
       </c>
+      <c r="I8" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="27" t="s">
+        <v>65</v>
+      </c>
       <c r="K8" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M8" s="12" t="s">
         <v>31</v>
@@ -1909,196 +1907,196 @@
       <c r="Q8" s="12"/>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="15"/>
-      <c r="Z8" s="15"/>
-      <c r="AA8" s="15"/>
-      <c r="AB8" s="15"/>
-      <c r="AC8" s="15"/>
-      <c r="AD8" s="15"/>
-      <c r="AE8" s="15"/>
-      <c r="AF8" s="15"/>
-      <c r="AG8" s="16"/>
-    </row>
-    <row r="9" s="26" customFormat="1" ht="76.5">
-      <c r="A9" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="27" t="s">
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="28"/>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="28"/>
+      <c r="AD8" s="28"/>
+      <c r="AE8" s="28"/>
+      <c r="AF8" s="28"/>
+      <c r="AG8" s="29"/>
+    </row>
+    <row r="9" s="25" customFormat="1" ht="76.5">
+      <c r="A9" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="27" t="s">
+      <c r="E9" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="F9" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="27" t="s">
+      <c r="G9" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="M9" s="27" t="s">
+      <c r="J9" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12">
+        <v>2024</v>
+      </c>
+      <c r="M9" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="29"/>
+    </row>
+    <row r="10" s="11" customFormat="1" ht="89.25">
+      <c r="A10" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="29"/>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="29"/>
-      <c r="AG9" s="30"/>
-    </row>
-    <row r="10" s="11" customFormat="1" ht="89.25">
-      <c r="A10" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="N10" s="14" t="s">
+      <c r="M10" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="15"/>
-      <c r="X10" s="15"/>
-      <c r="Y10" s="15"/>
-      <c r="Z10" s="15"/>
-      <c r="AA10" s="15"/>
-      <c r="AB10" s="15"/>
-      <c r="AC10" s="15"/>
-      <c r="AD10" s="15"/>
-      <c r="AE10" s="15"/>
-      <c r="AF10" s="15"/>
-      <c r="AG10" s="16"/>
-    </row>
-    <row r="11" s="17" customFormat="1" ht="63.75">
-      <c r="A11" s="18" t="s">
+      <c r="N10" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="18" t="str">
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="16"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
+      <c r="AF10" s="16"/>
+      <c r="AG10" s="17"/>
+    </row>
+    <row r="11" s="18" customFormat="1" ht="63.75">
+      <c r="A11" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="19" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="E11" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="F11" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="21"/>
-      <c r="Z11" s="21"/>
-      <c r="AA11" s="21"/>
-      <c r="AB11" s="21"/>
-      <c r="AC11" s="21"/>
-      <c r="AD11" s="21"/>
-      <c r="AE11" s="21"/>
-      <c r="AF11" s="21"/>
-      <c r="AG11" s="22"/>
+      <c r="G11" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="22"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="22"/>
+      <c r="AE11" s="22"/>
+      <c r="AF11" s="22"/>
+      <c r="AG11" s="23"/>
     </row>
     <row r="12" s="31" customFormat="1" ht="25.5">
       <c r="A12" s="32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="32" t="str">
         <f t="shared" si="0"/>
@@ -2108,13 +2106,13 @@
         <v>16</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
@@ -2144,442 +2142,442 @@
       <c r="AF12" s="33"/>
       <c r="AG12" s="34"/>
     </row>
-    <row r="13" s="17" customFormat="1" ht="89.25">
-      <c r="A13" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="18" t="s">
+    <row r="13" s="18" customFormat="1" ht="89.25">
+      <c r="A13" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" s="18" t="s">
+      <c r="D13" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="F13" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="G13" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="I13" s="18"/>
-      <c r="J13" s="20" t="s">
+      <c r="H13" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="I13" s="19"/>
+      <c r="J13" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="L13" s="18" t="s">
+      <c r="K13" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="18" t="s">
+      <c r="L13" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="18"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="22"/>
-    </row>
-    <row r="14" s="26" customFormat="1" ht="38.25">
-      <c r="A14" s="27" t="s">
+      <c r="M13" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="27" t="str">
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+      <c r="AG13" s="23"/>
+    </row>
+    <row r="14" s="25" customFormat="1" ht="38.25">
+      <c r="A14" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="12" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="27" t="s">
+      <c r="D14" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G14" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="27" t="s">
+      <c r="G14" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="J14" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="K14" s="27" t="s">
+      <c r="I14" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="L14" s="27" t="s">
+      <c r="K14" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="M14" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="N14" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27"/>
-      <c r="S14" s="27"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29"/>
-      <c r="Y14" s="29"/>
-      <c r="Z14" s="29"/>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="29"/>
-      <c r="AC14" s="29"/>
-      <c r="AD14" s="29"/>
-      <c r="AE14" s="29"/>
-      <c r="AF14" s="29"/>
-      <c r="AG14" s="30"/>
+      <c r="L14" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="N14" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="28"/>
+      <c r="U14" s="28"/>
+      <c r="V14" s="28"/>
+      <c r="W14" s="28"/>
+      <c r="X14" s="28"/>
+      <c r="Y14" s="28"/>
+      <c r="Z14" s="28"/>
+      <c r="AA14" s="28"/>
+      <c r="AB14" s="28"/>
+      <c r="AC14" s="28"/>
+      <c r="AD14" s="28"/>
+      <c r="AE14" s="28"/>
+      <c r="AF14" s="28"/>
+      <c r="AG14" s="29"/>
     </row>
     <row r="15" s="11" customFormat="1" ht="140.25">
-      <c r="A15" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="12" t="str">
+      <c r="A15" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="13" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="E15" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="F15" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="G15" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="I15" s="24" t="s">
+      <c r="H15" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="I15" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="K15" s="12" t="s">
+      <c r="J15" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="12" t="s">
+      <c r="K15" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="12" t="s">
+      <c r="L15" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="15"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="15"/>
-      <c r="X15" s="15"/>
-      <c r="Y15" s="15"/>
-      <c r="Z15" s="15"/>
-      <c r="AA15" s="15"/>
-      <c r="AB15" s="15"/>
-      <c r="AC15" s="15"/>
-      <c r="AD15" s="15"/>
-      <c r="AE15" s="15"/>
-      <c r="AF15" s="15"/>
-      <c r="AG15" s="16"/>
-    </row>
-    <row r="16" s="36" customFormat="1" ht="38.25">
-      <c r="A16" s="37" t="s">
+      <c r="M15" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="37" t="str">
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
+      <c r="Z15" s="16"/>
+      <c r="AA15" s="16"/>
+      <c r="AB15" s="16"/>
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="16"/>
+      <c r="AF15" s="16"/>
+      <c r="AG15" s="17"/>
+    </row>
+    <row r="16" s="37" customFormat="1" ht="38.25">
+      <c r="A16" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="38" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" s="37" t="s">
+      <c r="D16" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="K16" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="L16" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="M16" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="40"/>
+      <c r="W16" s="40"/>
+      <c r="X16" s="40"/>
+      <c r="Y16" s="40"/>
+      <c r="Z16" s="40"/>
+      <c r="AA16" s="40"/>
+      <c r="AB16" s="40"/>
+      <c r="AC16" s="40"/>
+      <c r="AD16" s="40"/>
+      <c r="AE16" s="40"/>
+      <c r="AF16" s="40"/>
+      <c r="AG16" s="41"/>
+    </row>
+    <row r="17" s="37" customFormat="1" ht="63.75">
+      <c r="A17" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="G16" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="I16" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="J16" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="L16" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="M16" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="N16" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
-      <c r="S16" s="37"/>
-      <c r="T16" s="39"/>
-      <c r="U16" s="39"/>
-      <c r="V16" s="39"/>
-      <c r="W16" s="39"/>
-      <c r="X16" s="39"/>
-      <c r="Y16" s="39"/>
-      <c r="Z16" s="39"/>
-      <c r="AA16" s="39"/>
-      <c r="AB16" s="39"/>
-      <c r="AC16" s="39"/>
-      <c r="AD16" s="39"/>
-      <c r="AE16" s="39"/>
-      <c r="AF16" s="39"/>
-      <c r="AG16" s="40"/>
-    </row>
-    <row r="17" s="36" customFormat="1" ht="63.75">
-      <c r="A17" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="37" t="str">
+      <c r="B17" s="38" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="F17" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="G17" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="H17" s="37" t="s">
+      <c r="D17" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="I17" s="37" t="s">
+      <c r="G17" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" s="37" t="s">
+      <c r="J17" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="L17" s="37" t="s">
+      <c r="K17" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="M17" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="N17" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
-      <c r="S17" s="37"/>
-      <c r="T17" s="39"/>
-      <c r="U17" s="39"/>
-      <c r="V17" s="39"/>
-      <c r="W17" s="39"/>
-      <c r="X17" s="39"/>
-      <c r="Y17" s="39"/>
-      <c r="Z17" s="39"/>
-      <c r="AA17" s="39"/>
-      <c r="AB17" s="39"/>
-      <c r="AC17" s="39"/>
-      <c r="AD17" s="39"/>
-      <c r="AE17" s="39"/>
-      <c r="AF17" s="39"/>
-      <c r="AG17" s="40"/>
-    </row>
-    <row r="18" s="36" customFormat="1" ht="38.25">
-      <c r="A18" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="37" t="str">
+      <c r="L17" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="M17" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="38"/>
+      <c r="T17" s="40"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="40"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="40"/>
+      <c r="Y17" s="40"/>
+      <c r="Z17" s="40"/>
+      <c r="AA17" s="40"/>
+      <c r="AB17" s="40"/>
+      <c r="AC17" s="40"/>
+      <c r="AD17" s="40"/>
+      <c r="AE17" s="40"/>
+      <c r="AF17" s="40"/>
+      <c r="AG17" s="41"/>
+    </row>
+    <row r="18" s="37" customFormat="1" ht="38.25">
+      <c r="A18" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="38" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="G18" s="37" t="s">
+      <c r="D18" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="H18" s="37" t="s">
+      <c r="G18" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="I18" s="37" t="s">
+      <c r="H18" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="I18" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="K18" s="37" t="s">
+      <c r="J18" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
-      <c r="S18" s="37"/>
-      <c r="T18" s="39"/>
-      <c r="U18" s="39"/>
-      <c r="V18" s="39"/>
-      <c r="W18" s="39"/>
-      <c r="X18" s="39"/>
-      <c r="Y18" s="39"/>
-      <c r="Z18" s="39"/>
-      <c r="AA18" s="39"/>
-      <c r="AB18" s="39"/>
-      <c r="AC18" s="39"/>
-      <c r="AD18" s="39"/>
-      <c r="AE18" s="39"/>
-      <c r="AF18" s="39"/>
-      <c r="AG18" s="40"/>
-    </row>
-    <row r="19" s="36" customFormat="1" ht="76.5">
-      <c r="A19" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="37" t="str">
+      <c r="K18" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="38"/>
+      <c r="T18" s="40"/>
+      <c r="U18" s="40"/>
+      <c r="V18" s="40"/>
+      <c r="W18" s="40"/>
+      <c r="X18" s="40"/>
+      <c r="Y18" s="40"/>
+      <c r="Z18" s="40"/>
+      <c r="AA18" s="40"/>
+      <c r="AB18" s="40"/>
+      <c r="AC18" s="40"/>
+      <c r="AD18" s="40"/>
+      <c r="AE18" s="40"/>
+      <c r="AF18" s="40"/>
+      <c r="AG18" s="41"/>
+    </row>
+    <row r="19" s="37" customFormat="1" ht="76.5">
+      <c r="A19" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="38" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="H19" s="37" t="s">
+      <c r="D19" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="I19" s="37" t="s">
+      <c r="G19" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="H19" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="I19" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="J19" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
-      <c r="S19" s="37"/>
-      <c r="T19" s="39"/>
-      <c r="U19" s="39"/>
-      <c r="V19" s="39"/>
-      <c r="W19" s="39"/>
-      <c r="X19" s="39"/>
-      <c r="Y19" s="39"/>
-      <c r="Z19" s="39"/>
-      <c r="AA19" s="39"/>
-      <c r="AB19" s="39"/>
-      <c r="AC19" s="39"/>
-      <c r="AD19" s="39"/>
-      <c r="AE19" s="39"/>
-      <c r="AF19" s="39"/>
-      <c r="AG19" s="40"/>
+      <c r="J19" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="M19" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="40"/>
+      <c r="U19" s="40"/>
+      <c r="V19" s="40"/>
+      <c r="W19" s="40"/>
+      <c r="X19" s="40"/>
+      <c r="Y19" s="40"/>
+      <c r="Z19" s="40"/>
+      <c r="AA19" s="40"/>
+      <c r="AB19" s="40"/>
+      <c r="AC19" s="40"/>
+      <c r="AD19" s="40"/>
+      <c r="AE19" s="40"/>
+      <c r="AF19" s="40"/>
+      <c r="AG19" s="41"/>
     </row>
     <row r="20" s="31" customFormat="1" ht="25.5">
       <c r="A20" s="32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="32" t="str">
         <f t="shared" si="0"/>
@@ -2589,13 +2587,13 @@
         <v>16</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F20" s="32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
@@ -2627,7 +2625,7 @@
     </row>
     <row r="21" s="31" customFormat="1" ht="25.5">
       <c r="A21" s="32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B21" s="32" t="str">
         <f t="shared" si="0"/>
@@ -2637,13 +2635,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
@@ -2673,236 +2671,236 @@
       <c r="AF21" s="33"/>
       <c r="AG21" s="34"/>
     </row>
-    <row r="22" s="26" customFormat="1" ht="38.25">
-      <c r="A22" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B22" s="27" t="str">
+    <row r="22" s="25" customFormat="1" ht="38.25">
+      <c r="A22" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="12" t="str">
         <f t="shared" si="0"/>
         <v>V1</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="F22" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="G22" s="27" t="s">
+      <c r="D22" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H22" s="27" t="s">
+      <c r="E22" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="I22" s="27" t="s">
+      <c r="F22" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="I22" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J22" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="K22" s="35"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="29"/>
-      <c r="W22" s="29"/>
-      <c r="X22" s="29"/>
-      <c r="Y22" s="29"/>
-      <c r="Z22" s="29"/>
-      <c r="AA22" s="29"/>
-      <c r="AB22" s="29"/>
-      <c r="AC22" s="29"/>
-      <c r="AD22" s="29"/>
-      <c r="AE22" s="29"/>
-      <c r="AF22" s="29"/>
-      <c r="AG22" s="30"/>
+      <c r="J22" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="K22" s="26"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28"/>
+      <c r="V22" s="28"/>
+      <c r="W22" s="28"/>
+      <c r="X22" s="28"/>
+      <c r="Y22" s="28"/>
+      <c r="Z22" s="28"/>
+      <c r="AA22" s="28"/>
+      <c r="AB22" s="28"/>
+      <c r="AC22" s="28"/>
+      <c r="AD22" s="28"/>
+      <c r="AE22" s="28"/>
+      <c r="AF22" s="28"/>
+      <c r="AG22" s="29"/>
     </row>
     <row r="23" s="11" customFormat="1" ht="42.75">
-      <c r="A23" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="12" t="s">
+      <c r="A23" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="I23" s="13"/>
+      <c r="J23" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="15"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="16"/>
+      <c r="V23" s="16"/>
+      <c r="W23" s="16"/>
+      <c r="X23" s="16"/>
+      <c r="Y23" s="16"/>
+      <c r="Z23" s="16"/>
+      <c r="AA23" s="16"/>
+      <c r="AB23" s="16"/>
+      <c r="AC23" s="16"/>
+      <c r="AD23" s="16"/>
+      <c r="AE23" s="16"/>
+      <c r="AF23" s="16"/>
+      <c r="AG23" s="17"/>
+    </row>
+    <row r="24" s="37" customFormat="1" ht="25.5">
+      <c r="A24" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="38"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="40"/>
+      <c r="V24" s="40"/>
+      <c r="W24" s="40"/>
+      <c r="X24" s="40"/>
+      <c r="Y24" s="40"/>
+      <c r="Z24" s="40"/>
+      <c r="AA24" s="40"/>
+      <c r="AB24" s="40"/>
+      <c r="AC24" s="40"/>
+      <c r="AD24" s="40"/>
+      <c r="AE24" s="40"/>
+      <c r="AF24" s="40"/>
+      <c r="AG24" s="41"/>
+    </row>
+    <row r="25" s="11" customFormat="1" ht="38.25">
+      <c r="A25" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="M25" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="I23" s="12"/>
-      <c r="J23" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="K23" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="M23" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="N23" s="14"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="15"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="15"/>
-      <c r="AA23" s="15"/>
-      <c r="AB23" s="15"/>
-      <c r="AC23" s="15"/>
-      <c r="AD23" s="15"/>
-      <c r="AE23" s="15"/>
-      <c r="AF23" s="15"/>
-      <c r="AG23" s="16"/>
-    </row>
-    <row r="24" s="36" customFormat="1" ht="25.5">
-      <c r="A24" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="F24" s="37" t="s">
+      <c r="N25" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="37"/>
-      <c r="L24" s="37"/>
-      <c r="M24" s="37"/>
-      <c r="N24" s="37"/>
-      <c r="O24" s="37"/>
-      <c r="P24" s="37"/>
-      <c r="Q24" s="37"/>
-      <c r="R24" s="37"/>
-      <c r="S24" s="37"/>
-      <c r="T24" s="39"/>
-      <c r="U24" s="39"/>
-      <c r="V24" s="39"/>
-      <c r="W24" s="39"/>
-      <c r="X24" s="39"/>
-      <c r="Y24" s="39"/>
-      <c r="Z24" s="39"/>
-      <c r="AA24" s="39"/>
-      <c r="AB24" s="39"/>
-      <c r="AC24" s="39"/>
-      <c r="AD24" s="39"/>
-      <c r="AE24" s="39"/>
-      <c r="AF24" s="39"/>
-      <c r="AG24" s="40"/>
-    </row>
-    <row r="25" s="11" customFormat="1" ht="38.25">
-      <c r="A25" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="K25" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="M25" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="N25" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="12"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="15"/>
-      <c r="AB25" s="15"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
-      <c r="AE25" s="15"/>
-      <c r="AF25" s="15"/>
-      <c r="AG25" s="16"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="13"/>
+      <c r="T25" s="16"/>
+      <c r="U25" s="16"/>
+      <c r="V25" s="16"/>
+      <c r="W25" s="16"/>
+      <c r="X25" s="16"/>
+      <c r="Y25" s="16"/>
+      <c r="Z25" s="16"/>
+      <c r="AA25" s="16"/>
+      <c r="AB25" s="16"/>
+      <c r="AC25" s="16"/>
+      <c r="AD25" s="16"/>
+      <c r="AE25" s="16"/>
+      <c r="AF25" s="16"/>
+      <c r="AG25" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N25"/>
@@ -2928,9 +2926,9 @@
     <hyperlink r:id="rId4" ref="N17"/>
     <hyperlink r:id="rId5" ref="J18"/>
     <hyperlink r:id="rId10" ref="N18"/>
-    <hyperlink r:id="rId7" ref="J19"/>
-    <hyperlink r:id="rId11" ref="J22"/>
-    <hyperlink r:id="rId12" ref="J23"/>
+    <hyperlink r:id="rId11" ref="J19"/>
+    <hyperlink r:id="rId12" ref="J22"/>
+    <hyperlink r:id="rId13" ref="J23"/>
     <hyperlink r:id="rId3" ref="J25"/>
     <hyperlink r:id="rId4" ref="N25"/>
   </hyperlinks>
@@ -2949,47 +2947,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="B1" s="42" t="s">
-        <v>136</v>
+      <c r="A1" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="27"/>
+      <c r="A2" s="12"/>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="12"/>
+      <c r="A3" s="13"/>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="18"/>
+      <c r="A4" s="19"/>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="32"/>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="37"/>
-      <c r="B6" s="43" t="s">
-        <v>141</v>
+      <c r="A6" s="38"/>
+      <c r="B6" s="44" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="8"/>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/progress/megatrends_RF.xlsx
+++ b/progress/megatrends_RF.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
   <si>
     <t>Calcul</t>
   </si>
@@ -305,9 +305,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">1. almost</t>
-  </si>
-  <si>
     <t xml:space="preserve">Demographic change</t>
   </si>
   <si>
@@ -327,16 +324,69 @@
     <t>FIELD_SIZE</t>
   </si>
   <si>
+    <t>ha</t>
+  </si>
+  <si>
     <t>https://geoservices.ign.fr/rpg</t>
   </si>
   <si>
-    <t>IGNF_RPG_2-1</t>
+    <t>RPG_2-2_2023_PARCELLES_GRAPHIQUES.gpkg</t>
   </si>
   <si>
     <t>2015-2024</t>
   </si>
   <si>
-    <t>https://geoservices.ign.fr/sites/default/files/2023-11/IGNF_RPG_2-1.html</t>
+    <t>02g_get_rpg.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHG emissions reduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% fallow land</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of fallow relative to the total area of the municipality (standardized by municipality size)
+</t>
+  </si>
+  <si>
+    <t>FALLOW_AREA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007 to 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pesticide + Fertilizer use reduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crop type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominant crop by municipality in term of surface area</t>
+  </si>
+  <si>
+    <t>DOMINANT_CROP</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP subsidies 
+Changes in farming practices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crop diversity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shannon index</t>
+  </si>
+  <si>
+    <t>CROP_DIV_SHANNON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. almost</t>
   </si>
   <si>
     <t xml:space="preserve">Changes in farmer population structure</t>
@@ -473,52 +523,6 @@
     <t>linear</t>
   </si>
   <si>
-    <t xml:space="preserve">GHG emissions reduction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% fallow land</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="8" tint="0"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">P_FAL→ % of fallow relative to the total area of the municipality (standardized by municipality size)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-P_FAL_CROP → % of fallow relative to the total agricultural area (standardized by agricultural area)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="2"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">how to define fallow land cover in RPG?</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">IGN RPG
-2024</t>
-  </si>
-  <si>
-    <t>PS_FALLOW_AREA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2007 to 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pesticide + Fertilizer use reduction</t>
-  </si>
-  <si>
     <t xml:space="preserve">Crop rotation</t>
   </si>
   <si>
@@ -545,55 +549,6 @@
 Dimension reduction?</t>
   </si>
   <si>
-    <t xml:space="preserve">Crop type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominant crop by municipality in term of surface area</t>
-  </si>
-  <si>
-    <t>PS_CROP_TYPE</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>Farm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wait for other RPG calculation to be decided</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP subsidies 
-Changes in farming practices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crop diversity</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Shannon index
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="2"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">how to standardize per crop area / municipality area ?</t>
-    </r>
-  </si>
-  <si>
-    <t>PS_CROP_DIV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How to group crop in meaningfull way?</t>
-  </si>
-  <si>
     <t xml:space="preserve">2. details</t>
   </si>
   <si>
@@ -645,9 +600,6 @@
     <t xml:space="preserve">Average farm size per commune</t>
   </si>
   <si>
-    <t>ha</t>
-  </si>
-  <si>
     <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=raanc2.saumoyaa&amp;s=2010&amp;t=A02&amp;view=map1</t>
   </si>
   <si>
@@ -673,6 +625,9 @@
   </si>
   <si>
     <t xml:space="preserve">Market value/demand for organic products/local products</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
   <si>
     <t xml:space="preserve">Sensitivity to nature protection</t>
@@ -748,6 +703,9 @@
   </si>
   <si>
     <t>PS_GRASS_AREA</t>
+  </si>
+  <si>
+    <t>IGNF_RPG_2-1</t>
   </si>
   <si>
     <t xml:space="preserve">4. no idea</t>
@@ -986,14 +944,14 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10.000000"/>
+      <color theme="8" tint="0"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="10.000000"/>
       <color indexed="2"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.000000"/>
-      <color theme="8" tint="0"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1100,7 +1058,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="76">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1143,7 +1101,19 @@
     <xf fontId="3" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf fontId="2" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="7" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="7" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1153,38 +1123,35 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="4" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="4" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="7" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="3" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="8" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="9" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="5" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="9" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="8" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="5" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1202,7 +1169,7 @@
     <xf fontId="3" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="8" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="9" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="10" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1293,9 +1260,6 @@
     </xf>
     <xf fontId="2" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="17" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1810,7 +1774,7 @@
     <col customWidth="1" min="6" max="6" width="32.140625"/>
     <col customWidth="1" min="7" max="7" width="34.421875"/>
     <col customWidth="1" min="9" max="9" width="32.00390625"/>
-    <col customWidth="1" min="10" max="10" width="30.57421875"/>
+    <col customWidth="1" min="10" max="10" width="32.28125"/>
     <col customWidth="1" min="11" max="11" width="24.00390625"/>
     <col customWidth="1" min="12" max="12" width="12.140625"/>
     <col customWidth="1" min="13" max="13" width="16.8515625"/>
@@ -2121,7 +2085,7 @@
       <c r="JM1"/>
       <c r="JN1"/>
     </row>
-    <row r="2" s="4" customFormat="1" ht="51">
+    <row r="2" s="4" customFormat="1" ht="42.75">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -2423,7 +2387,7 @@
       <c r="JM2" s="7"/>
       <c r="JN2" s="7"/>
     </row>
-    <row r="3" s="4" customFormat="1" ht="42.75">
+    <row r="3" s="4" customFormat="1" ht="38.25">
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
@@ -2727,7 +2691,7 @@
       <c r="JM3" s="7"/>
       <c r="JN3" s="7"/>
     </row>
-    <row r="4" s="4" customFormat="1" ht="38.25">
+    <row r="4" s="4" customFormat="1" ht="51">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
@@ -3637,7 +3601,7 @@
       <c r="JM6" s="13"/>
       <c r="JN6" s="13"/>
     </row>
-    <row r="7" s="11" customFormat="1" ht="25.5">
+    <row r="7" s="11" customFormat="1" ht="63.75">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
@@ -3941,345 +3905,349 @@
       <c r="JM7" s="13"/>
       <c r="JN7" s="13"/>
     </row>
-    <row r="8" s="16" customFormat="1" ht="25.5">
-      <c r="A8" s="17" t="s">
+    <row r="8" s="4" customFormat="1" ht="63.75">
+      <c r="A8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="C8" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="D8" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="E8" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="F8" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="G8" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="H8" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="L8" s="17" t="s">
+      <c r="L8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="20" t="s">
+      <c r="M8" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="21"/>
-      <c r="V8" s="21"/>
-      <c r="W8" s="21"/>
-      <c r="X8" s="21"/>
-      <c r="Y8" s="21"/>
-      <c r="Z8" s="21"/>
-      <c r="AA8" s="21"/>
-      <c r="AB8" s="21"/>
-      <c r="AC8" s="21"/>
-      <c r="AD8" s="21"/>
-      <c r="AE8" s="21"/>
-      <c r="AF8" s="21"/>
-      <c r="AG8" s="21"/>
-      <c r="AH8" s="21"/>
-      <c r="AI8" s="21"/>
-      <c r="AJ8" s="21"/>
-      <c r="AK8" s="21"/>
-      <c r="AL8" s="21"/>
-      <c r="AM8" s="21"/>
-      <c r="AN8" s="21"/>
-      <c r="AO8" s="21"/>
-      <c r="AP8" s="21"/>
-      <c r="AQ8" s="21"/>
-      <c r="AR8" s="21"/>
-      <c r="AS8" s="21"/>
-      <c r="AT8" s="21"/>
-      <c r="AU8" s="21"/>
-      <c r="AV8" s="21"/>
-      <c r="AW8" s="21"/>
-      <c r="AX8" s="21"/>
-      <c r="AY8" s="21"/>
-      <c r="AZ8" s="21"/>
-      <c r="BA8" s="21"/>
-      <c r="BB8" s="21"/>
-      <c r="BC8" s="21"/>
-      <c r="BD8" s="21"/>
-      <c r="BE8" s="21"/>
-      <c r="BF8" s="21"/>
-      <c r="BG8" s="21"/>
-      <c r="BH8" s="21"/>
-      <c r="BI8" s="21"/>
-      <c r="BJ8" s="21"/>
-      <c r="BK8" s="21"/>
-      <c r="BL8" s="21"/>
-      <c r="BM8" s="21"/>
-      <c r="BN8" s="21"/>
-      <c r="BO8" s="21"/>
-      <c r="BP8" s="21"/>
-      <c r="BQ8" s="21"/>
-      <c r="BR8" s="21"/>
-      <c r="BS8" s="21"/>
-      <c r="BT8" s="21"/>
-      <c r="BU8" s="21"/>
-      <c r="BV8" s="21"/>
-      <c r="BW8" s="21"/>
-      <c r="BX8" s="21"/>
-      <c r="BY8" s="21"/>
-      <c r="BZ8" s="21"/>
-      <c r="CA8" s="21"/>
-      <c r="CB8" s="21"/>
-      <c r="CC8" s="21"/>
-      <c r="CD8" s="21"/>
-      <c r="CE8" s="21"/>
-      <c r="CF8" s="21"/>
-      <c r="CG8" s="21"/>
-      <c r="CH8" s="21"/>
-      <c r="CI8" s="21"/>
-      <c r="CJ8" s="21"/>
-      <c r="CK8" s="21"/>
-      <c r="CL8" s="21"/>
-      <c r="CM8" s="21"/>
-      <c r="CN8" s="21"/>
-      <c r="CO8" s="21"/>
-      <c r="CP8" s="21"/>
-      <c r="CQ8" s="21"/>
-      <c r="CR8" s="21"/>
-      <c r="CS8" s="21"/>
-      <c r="CT8" s="21"/>
-      <c r="CU8" s="21"/>
-      <c r="CV8" s="21"/>
-      <c r="CW8" s="21"/>
-      <c r="CX8" s="21"/>
-      <c r="CY8" s="21"/>
-      <c r="CZ8" s="21"/>
-      <c r="DA8" s="21"/>
-      <c r="DB8" s="21"/>
-      <c r="DC8" s="21"/>
-      <c r="DD8" s="21"/>
-      <c r="DE8" s="21"/>
-      <c r="DF8" s="21"/>
-      <c r="DG8" s="21"/>
-      <c r="DH8" s="21"/>
-      <c r="DI8" s="21"/>
-      <c r="DJ8" s="21"/>
-      <c r="DK8" s="21"/>
-      <c r="DL8" s="21"/>
-      <c r="DM8" s="21"/>
-      <c r="DN8" s="21"/>
-      <c r="DO8" s="21"/>
-      <c r="DP8" s="21"/>
-      <c r="DQ8" s="21"/>
-      <c r="DR8" s="21"/>
-      <c r="DS8" s="21"/>
-      <c r="DT8" s="21"/>
-      <c r="DU8" s="21"/>
-      <c r="DV8" s="21"/>
-      <c r="DW8" s="21"/>
-      <c r="DX8" s="21"/>
-      <c r="DY8" s="21"/>
-      <c r="DZ8" s="21"/>
-      <c r="EA8" s="21"/>
-      <c r="EB8" s="21"/>
-      <c r="EC8" s="21"/>
-      <c r="ED8" s="21"/>
-      <c r="EE8" s="21"/>
-      <c r="EF8" s="21"/>
-      <c r="EG8" s="21"/>
-      <c r="EH8" s="21"/>
-      <c r="EI8" s="21"/>
-      <c r="EJ8" s="21"/>
-      <c r="EK8" s="21"/>
-      <c r="EL8" s="21"/>
-      <c r="EM8" s="21"/>
-      <c r="EN8" s="21"/>
-      <c r="EO8" s="21"/>
-      <c r="EP8" s="21"/>
-      <c r="EQ8" s="21"/>
-      <c r="ER8" s="21"/>
-      <c r="ES8" s="21"/>
-      <c r="ET8" s="21"/>
-      <c r="EU8" s="21"/>
-      <c r="EV8" s="21"/>
-      <c r="EW8" s="21"/>
-      <c r="EX8" s="21"/>
-      <c r="EY8" s="21"/>
-      <c r="EZ8" s="21"/>
-      <c r="FA8" s="21"/>
-      <c r="FB8" s="21"/>
-      <c r="FC8" s="21"/>
-      <c r="FD8" s="21"/>
-      <c r="FE8" s="21"/>
-      <c r="FF8" s="21"/>
-      <c r="FG8" s="21"/>
-      <c r="FH8" s="21"/>
-      <c r="FI8" s="21"/>
-      <c r="FJ8" s="21"/>
-      <c r="FK8" s="21"/>
-      <c r="FL8" s="21"/>
-      <c r="FM8" s="21"/>
-      <c r="FN8" s="21"/>
-      <c r="FO8" s="21"/>
-      <c r="FP8" s="21"/>
-      <c r="FQ8" s="21"/>
-      <c r="FR8" s="21"/>
-      <c r="FS8" s="21"/>
-      <c r="FT8" s="21"/>
-      <c r="FU8" s="21"/>
-      <c r="FV8" s="21"/>
-      <c r="FW8" s="21"/>
-      <c r="FX8" s="21"/>
-      <c r="FY8" s="21"/>
-      <c r="FZ8" s="21"/>
-      <c r="GA8" s="21"/>
-      <c r="GB8" s="21"/>
-      <c r="GC8" s="21"/>
-      <c r="GD8" s="21"/>
-      <c r="GE8" s="21"/>
-      <c r="GF8" s="21"/>
-      <c r="GG8" s="21"/>
-      <c r="GH8" s="21"/>
-      <c r="GI8" s="21"/>
-      <c r="GJ8" s="21"/>
-      <c r="GK8" s="21"/>
-      <c r="GL8" s="21"/>
-      <c r="GM8" s="21"/>
-      <c r="GN8" s="21"/>
-      <c r="GO8" s="21"/>
-      <c r="GP8" s="21"/>
-      <c r="GQ8" s="21"/>
-      <c r="GR8" s="21"/>
-      <c r="GS8" s="21"/>
-      <c r="GT8" s="21"/>
-      <c r="GU8" s="21"/>
-      <c r="GV8" s="21"/>
-      <c r="GW8" s="21"/>
-      <c r="GX8" s="21"/>
-      <c r="GY8" s="21"/>
-      <c r="GZ8" s="21"/>
-      <c r="HA8" s="21"/>
-      <c r="HB8" s="21"/>
-      <c r="HC8" s="21"/>
-      <c r="HD8" s="21"/>
-      <c r="HE8" s="21"/>
-      <c r="HF8" s="21"/>
-      <c r="HG8" s="21"/>
-      <c r="HH8" s="21"/>
-      <c r="HI8" s="21"/>
-      <c r="HJ8" s="21"/>
-      <c r="HK8" s="21"/>
-      <c r="HL8" s="21"/>
-      <c r="HM8" s="21"/>
-      <c r="HN8" s="21"/>
-      <c r="HO8" s="21"/>
-      <c r="HP8" s="21"/>
-      <c r="HQ8" s="21"/>
-      <c r="HR8" s="21"/>
-      <c r="HS8" s="21"/>
-      <c r="HT8" s="21"/>
-      <c r="HU8" s="21"/>
-      <c r="HV8" s="21"/>
-      <c r="HW8" s="21"/>
-      <c r="HX8" s="21"/>
-      <c r="HY8" s="21"/>
-      <c r="HZ8" s="21"/>
-      <c r="IA8" s="21"/>
-      <c r="IB8" s="21"/>
-      <c r="IC8" s="21"/>
-      <c r="ID8" s="21"/>
-      <c r="IE8" s="21"/>
-      <c r="IF8" s="21"/>
-      <c r="IG8" s="21"/>
-      <c r="IH8" s="21"/>
-      <c r="II8" s="21"/>
-      <c r="IJ8" s="21"/>
-      <c r="IK8" s="21"/>
-      <c r="IL8" s="21"/>
-      <c r="IM8" s="21"/>
-      <c r="IN8" s="21"/>
-      <c r="IO8" s="21"/>
-      <c r="IP8" s="21"/>
-      <c r="IQ8" s="21"/>
-      <c r="IR8" s="21"/>
-      <c r="IS8" s="21"/>
-      <c r="IT8" s="21"/>
-      <c r="IU8" s="21"/>
-      <c r="IV8" s="21"/>
-      <c r="IW8" s="21"/>
-      <c r="IX8" s="21"/>
-      <c r="IY8" s="21"/>
-      <c r="IZ8" s="21"/>
-      <c r="JA8" s="21"/>
-      <c r="JB8" s="21"/>
-      <c r="JC8" s="21"/>
-      <c r="JD8" s="21"/>
-      <c r="JE8" s="21"/>
-      <c r="JF8" s="21"/>
-      <c r="JG8" s="21"/>
-      <c r="JH8" s="21"/>
-      <c r="JI8" s="21"/>
-      <c r="JJ8" s="21"/>
-      <c r="JK8" s="21"/>
-      <c r="JL8" s="21"/>
-      <c r="JM8" s="21"/>
-      <c r="JN8" s="21"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="7"/>
+      <c r="AF8" s="7"/>
+      <c r="AG8" s="7"/>
+      <c r="AH8" s="7"/>
+      <c r="AI8" s="7"/>
+      <c r="AJ8" s="7"/>
+      <c r="AK8" s="7"/>
+      <c r="AL8" s="7"/>
+      <c r="AM8" s="7"/>
+      <c r="AN8" s="7"/>
+      <c r="AO8" s="7"/>
+      <c r="AP8" s="7"/>
+      <c r="AQ8" s="7"/>
+      <c r="AR8" s="7"/>
+      <c r="AS8" s="7"/>
+      <c r="AT8" s="7"/>
+      <c r="AU8" s="7"/>
+      <c r="AV8" s="7"/>
+      <c r="AW8" s="7"/>
+      <c r="AX8" s="7"/>
+      <c r="AY8" s="7"/>
+      <c r="AZ8" s="7"/>
+      <c r="BA8" s="7"/>
+      <c r="BB8" s="7"/>
+      <c r="BC8" s="7"/>
+      <c r="BD8" s="7"/>
+      <c r="BE8" s="7"/>
+      <c r="BF8" s="7"/>
+      <c r="BG8" s="7"/>
+      <c r="BH8" s="7"/>
+      <c r="BI8" s="7"/>
+      <c r="BJ8" s="7"/>
+      <c r="BK8" s="7"/>
+      <c r="BL8" s="7"/>
+      <c r="BM8" s="7"/>
+      <c r="BN8" s="7"/>
+      <c r="BO8" s="7"/>
+      <c r="BP8" s="7"/>
+      <c r="BQ8" s="7"/>
+      <c r="BR8" s="7"/>
+      <c r="BS8" s="7"/>
+      <c r="BT8" s="7"/>
+      <c r="BU8" s="7"/>
+      <c r="BV8" s="7"/>
+      <c r="BW8" s="7"/>
+      <c r="BX8" s="7"/>
+      <c r="BY8" s="7"/>
+      <c r="BZ8" s="7"/>
+      <c r="CA8" s="7"/>
+      <c r="CB8" s="7"/>
+      <c r="CC8" s="7"/>
+      <c r="CD8" s="7"/>
+      <c r="CE8" s="7"/>
+      <c r="CF8" s="7"/>
+      <c r="CG8" s="7"/>
+      <c r="CH8" s="7"/>
+      <c r="CI8" s="7"/>
+      <c r="CJ8" s="7"/>
+      <c r="CK8" s="7"/>
+      <c r="CL8" s="7"/>
+      <c r="CM8" s="7"/>
+      <c r="CN8" s="7"/>
+      <c r="CO8" s="7"/>
+      <c r="CP8" s="7"/>
+      <c r="CQ8" s="7"/>
+      <c r="CR8" s="7"/>
+      <c r="CS8" s="7"/>
+      <c r="CT8" s="7"/>
+      <c r="CU8" s="7"/>
+      <c r="CV8" s="7"/>
+      <c r="CW8" s="7"/>
+      <c r="CX8" s="7"/>
+      <c r="CY8" s="7"/>
+      <c r="CZ8" s="7"/>
+      <c r="DA8" s="7"/>
+      <c r="DB8" s="7"/>
+      <c r="DC8" s="7"/>
+      <c r="DD8" s="7"/>
+      <c r="DE8" s="7"/>
+      <c r="DF8" s="7"/>
+      <c r="DG8" s="7"/>
+      <c r="DH8" s="7"/>
+      <c r="DI8" s="7"/>
+      <c r="DJ8" s="7"/>
+      <c r="DK8" s="7"/>
+      <c r="DL8" s="7"/>
+      <c r="DM8" s="7"/>
+      <c r="DN8" s="7"/>
+      <c r="DO8" s="7"/>
+      <c r="DP8" s="7"/>
+      <c r="DQ8" s="7"/>
+      <c r="DR8" s="7"/>
+      <c r="DS8" s="7"/>
+      <c r="DT8" s="7"/>
+      <c r="DU8" s="7"/>
+      <c r="DV8" s="7"/>
+      <c r="DW8" s="7"/>
+      <c r="DX8" s="7"/>
+      <c r="DY8" s="7"/>
+      <c r="DZ8" s="7"/>
+      <c r="EA8" s="7"/>
+      <c r="EB8" s="7"/>
+      <c r="EC8" s="7"/>
+      <c r="ED8" s="7"/>
+      <c r="EE8" s="7"/>
+      <c r="EF8" s="7"/>
+      <c r="EG8" s="7"/>
+      <c r="EH8" s="7"/>
+      <c r="EI8" s="7"/>
+      <c r="EJ8" s="7"/>
+      <c r="EK8" s="7"/>
+      <c r="EL8" s="7"/>
+      <c r="EM8" s="7"/>
+      <c r="EN8" s="7"/>
+      <c r="EO8" s="7"/>
+      <c r="EP8" s="7"/>
+      <c r="EQ8" s="7"/>
+      <c r="ER8" s="7"/>
+      <c r="ES8" s="7"/>
+      <c r="ET8" s="7"/>
+      <c r="EU8" s="7"/>
+      <c r="EV8" s="7"/>
+      <c r="EW8" s="7"/>
+      <c r="EX8" s="7"/>
+      <c r="EY8" s="7"/>
+      <c r="EZ8" s="7"/>
+      <c r="FA8" s="7"/>
+      <c r="FB8" s="7"/>
+      <c r="FC8" s="7"/>
+      <c r="FD8" s="7"/>
+      <c r="FE8" s="7"/>
+      <c r="FF8" s="7"/>
+      <c r="FG8" s="7"/>
+      <c r="FH8" s="7"/>
+      <c r="FI8" s="7"/>
+      <c r="FJ8" s="7"/>
+      <c r="FK8" s="7"/>
+      <c r="FL8" s="7"/>
+      <c r="FM8" s="7"/>
+      <c r="FN8" s="7"/>
+      <c r="FO8" s="7"/>
+      <c r="FP8" s="7"/>
+      <c r="FQ8" s="7"/>
+      <c r="FR8" s="7"/>
+      <c r="FS8" s="7"/>
+      <c r="FT8" s="7"/>
+      <c r="FU8" s="7"/>
+      <c r="FV8" s="7"/>
+      <c r="FW8" s="7"/>
+      <c r="FX8" s="7"/>
+      <c r="FY8" s="7"/>
+      <c r="FZ8" s="7"/>
+      <c r="GA8" s="7"/>
+      <c r="GB8" s="7"/>
+      <c r="GC8" s="7"/>
+      <c r="GD8" s="7"/>
+      <c r="GE8" s="7"/>
+      <c r="GF8" s="7"/>
+      <c r="GG8" s="7"/>
+      <c r="GH8" s="7"/>
+      <c r="GI8" s="7"/>
+      <c r="GJ8" s="7"/>
+      <c r="GK8" s="7"/>
+      <c r="GL8" s="7"/>
+      <c r="GM8" s="7"/>
+      <c r="GN8" s="7"/>
+      <c r="GO8" s="7"/>
+      <c r="GP8" s="7"/>
+      <c r="GQ8" s="7"/>
+      <c r="GR8" s="7"/>
+      <c r="GS8" s="7"/>
+      <c r="GT8" s="7"/>
+      <c r="GU8" s="7"/>
+      <c r="GV8" s="7"/>
+      <c r="GW8" s="7"/>
+      <c r="GX8" s="7"/>
+      <c r="GY8" s="7"/>
+      <c r="GZ8" s="7"/>
+      <c r="HA8" s="7"/>
+      <c r="HB8" s="7"/>
+      <c r="HC8" s="7"/>
+      <c r="HD8" s="7"/>
+      <c r="HE8" s="7"/>
+      <c r="HF8" s="7"/>
+      <c r="HG8" s="7"/>
+      <c r="HH8" s="7"/>
+      <c r="HI8" s="7"/>
+      <c r="HJ8" s="7"/>
+      <c r="HK8" s="7"/>
+      <c r="HL8" s="7"/>
+      <c r="HM8" s="7"/>
+      <c r="HN8" s="7"/>
+      <c r="HO8" s="7"/>
+      <c r="HP8" s="7"/>
+      <c r="HQ8" s="7"/>
+      <c r="HR8" s="7"/>
+      <c r="HS8" s="7"/>
+      <c r="HT8" s="7"/>
+      <c r="HU8" s="7"/>
+      <c r="HV8" s="7"/>
+      <c r="HW8" s="7"/>
+      <c r="HX8" s="7"/>
+      <c r="HY8" s="7"/>
+      <c r="HZ8" s="7"/>
+      <c r="IA8" s="7"/>
+      <c r="IB8" s="7"/>
+      <c r="IC8" s="7"/>
+      <c r="ID8" s="7"/>
+      <c r="IE8" s="7"/>
+      <c r="IF8" s="7"/>
+      <c r="IG8" s="7"/>
+      <c r="IH8" s="7"/>
+      <c r="II8" s="7"/>
+      <c r="IJ8" s="7"/>
+      <c r="IK8" s="7"/>
+      <c r="IL8" s="7"/>
+      <c r="IM8" s="7"/>
+      <c r="IN8" s="7"/>
+      <c r="IO8" s="7"/>
+      <c r="IP8" s="7"/>
+      <c r="IQ8" s="7"/>
+      <c r="IR8" s="7"/>
+      <c r="IS8" s="7"/>
+      <c r="IT8" s="7"/>
+      <c r="IU8" s="7"/>
+      <c r="IV8" s="7"/>
+      <c r="IW8" s="7"/>
+      <c r="IX8" s="7"/>
+      <c r="IY8" s="7"/>
+      <c r="IZ8" s="7"/>
+      <c r="JA8" s="7"/>
+      <c r="JB8" s="7"/>
+      <c r="JC8" s="7"/>
+      <c r="JD8" s="7"/>
+      <c r="JE8" s="7"/>
+      <c r="JF8" s="7"/>
+      <c r="JG8" s="7"/>
+      <c r="JH8" s="7"/>
+      <c r="JI8" s="7"/>
+      <c r="JJ8" s="7"/>
+      <c r="JK8" s="7"/>
+      <c r="JL8" s="7"/>
+      <c r="JM8" s="7"/>
+      <c r="JN8" s="7"/>
     </row>
     <row r="9" s="11" customFormat="1" ht="38.25">
-      <c r="A9" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="17" t="s">
+      <c r="A9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="H9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H9" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="I9" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="K9" s="17">
-        <v>2020</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="M9" s="17"/>
-      <c r="N9" s="13"/>
+      <c r="L9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="N9" s="5"/>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
@@ -4542,44 +4510,46 @@
       <c r="JN9" s="13"/>
     </row>
     <row r="10" s="11" customFormat="1" ht="38.25">
-      <c r="A10" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="17" t="s">
+      <c r="A10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="H10" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="I10" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="J10" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="M10" s="17"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="N10" s="5"/>
       <c r="O10" s="13"/>
       <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
@@ -4841,43 +4811,47 @@
       <c r="JM10" s="13"/>
       <c r="JN10" s="13"/>
     </row>
-    <row r="11" s="11" customFormat="1" ht="63.75">
-      <c r="A11" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="J11" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="K11" s="25">
-        <v>2010</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="M11" s="17"/>
-      <c r="N11" s="13"/>
+    <row r="11" s="11" customFormat="1" ht="25.5">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="N11" s="5"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
@@ -5139,43 +5113,45 @@
       <c r="JM11" s="7"/>
       <c r="JN11" s="7"/>
     </row>
-    <row r="12" s="4" customFormat="1" ht="114.75">
-      <c r="A12" s="17" t="s">
+    <row r="12" s="4" customFormat="1" ht="25.5">
+      <c r="A12" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="I12" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="J12" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="F12" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="J12" s="26"/>
-      <c r="K12" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="L12" s="17" t="s">
+      <c r="K12" s="21">
+        <v>2020</v>
+      </c>
+      <c r="L12" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="M12" s="17"/>
-      <c r="N12" s="13" t="s">
-        <v>119</v>
-      </c>
+      <c r="M12" s="21"/>
+      <c r="N12" s="13"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
@@ -5437,3162 +5413,3156 @@
       <c r="JM12" s="7"/>
       <c r="JN12" s="7"/>
     </row>
-    <row r="13" s="16" customFormat="1" ht="38.25">
-      <c r="A13" s="17" t="s">
+    <row r="13" s="24" customFormat="1" ht="38.25">
+      <c r="A13" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="C13" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="I13" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="J13" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="F13" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G13" s="17" t="s">
+      <c r="K13" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="L13" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="M13" s="21"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="26"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="26"/>
+      <c r="U13" s="26"/>
+      <c r="V13" s="26"/>
+      <c r="W13" s="26"/>
+      <c r="X13" s="26"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="26"/>
+      <c r="AA13" s="26"/>
+      <c r="AB13" s="26"/>
+      <c r="AC13" s="26"/>
+      <c r="AD13" s="26"/>
+      <c r="AE13" s="26"/>
+      <c r="AF13" s="26"/>
+      <c r="AG13" s="26"/>
+      <c r="AH13" s="26"/>
+      <c r="AI13" s="26"/>
+      <c r="AJ13" s="26"/>
+      <c r="AK13" s="26"/>
+      <c r="AL13" s="26"/>
+      <c r="AM13" s="26"/>
+      <c r="AN13" s="26"/>
+      <c r="AO13" s="26"/>
+      <c r="AP13" s="26"/>
+      <c r="AQ13" s="26"/>
+      <c r="AR13" s="26"/>
+      <c r="AS13" s="26"/>
+      <c r="AT13" s="26"/>
+      <c r="AU13" s="26"/>
+      <c r="AV13" s="26"/>
+      <c r="AW13" s="26"/>
+      <c r="AX13" s="26"/>
+      <c r="AY13" s="26"/>
+      <c r="AZ13" s="26"/>
+      <c r="BA13" s="26"/>
+      <c r="BB13" s="26"/>
+      <c r="BC13" s="26"/>
+      <c r="BD13" s="26"/>
+      <c r="BE13" s="26"/>
+      <c r="BF13" s="26"/>
+      <c r="BG13" s="26"/>
+      <c r="BH13" s="26"/>
+      <c r="BI13" s="26"/>
+      <c r="BJ13" s="26"/>
+      <c r="BK13" s="26"/>
+      <c r="BL13" s="26"/>
+      <c r="BM13" s="26"/>
+      <c r="BN13" s="26"/>
+      <c r="BO13" s="26"/>
+      <c r="BP13" s="26"/>
+      <c r="BQ13" s="26"/>
+      <c r="BR13" s="26"/>
+      <c r="BS13" s="26"/>
+      <c r="BT13" s="26"/>
+      <c r="BU13" s="26"/>
+      <c r="BV13" s="26"/>
+      <c r="BW13" s="26"/>
+      <c r="BX13" s="26"/>
+      <c r="BY13" s="26"/>
+      <c r="BZ13" s="26"/>
+      <c r="CA13" s="26"/>
+      <c r="CB13" s="26"/>
+      <c r="CC13" s="26"/>
+      <c r="CD13" s="26"/>
+      <c r="CE13" s="26"/>
+      <c r="CF13" s="26"/>
+      <c r="CG13" s="26"/>
+      <c r="CH13" s="26"/>
+      <c r="CI13" s="26"/>
+      <c r="CJ13" s="26"/>
+      <c r="CK13" s="26"/>
+      <c r="CL13" s="26"/>
+      <c r="CM13" s="26"/>
+      <c r="CN13" s="26"/>
+      <c r="CO13" s="26"/>
+      <c r="CP13" s="26"/>
+      <c r="CQ13" s="26"/>
+      <c r="CR13" s="26"/>
+      <c r="CS13" s="26"/>
+      <c r="CT13" s="26"/>
+      <c r="CU13" s="26"/>
+      <c r="CV13" s="26"/>
+      <c r="CW13" s="26"/>
+      <c r="CX13" s="26"/>
+      <c r="CY13" s="26"/>
+      <c r="CZ13" s="26"/>
+      <c r="DA13" s="26"/>
+      <c r="DB13" s="26"/>
+      <c r="DC13" s="26"/>
+      <c r="DD13" s="26"/>
+      <c r="DE13" s="26"/>
+      <c r="DF13" s="26"/>
+      <c r="DG13" s="26"/>
+      <c r="DH13" s="26"/>
+      <c r="DI13" s="26"/>
+      <c r="DJ13" s="26"/>
+      <c r="DK13" s="26"/>
+      <c r="DL13" s="26"/>
+      <c r="DM13" s="26"/>
+      <c r="DN13" s="26"/>
+      <c r="DO13" s="26"/>
+      <c r="DP13" s="26"/>
+      <c r="DQ13" s="26"/>
+      <c r="DR13" s="26"/>
+      <c r="DS13" s="26"/>
+      <c r="DT13" s="26"/>
+      <c r="DU13" s="26"/>
+      <c r="DV13" s="26"/>
+      <c r="DW13" s="26"/>
+      <c r="DX13" s="26"/>
+      <c r="DY13" s="26"/>
+      <c r="DZ13" s="26"/>
+      <c r="EA13" s="26"/>
+      <c r="EB13" s="26"/>
+      <c r="EC13" s="26"/>
+      <c r="ED13" s="26"/>
+      <c r="EE13" s="26"/>
+      <c r="EF13" s="26"/>
+      <c r="EG13" s="26"/>
+      <c r="EH13" s="26"/>
+      <c r="EI13" s="26"/>
+      <c r="EJ13" s="26"/>
+      <c r="EK13" s="26"/>
+      <c r="EL13" s="26"/>
+      <c r="EM13" s="26"/>
+      <c r="EN13" s="26"/>
+      <c r="EO13" s="26"/>
+      <c r="EP13" s="26"/>
+      <c r="EQ13" s="26"/>
+      <c r="ER13" s="26"/>
+      <c r="ES13" s="26"/>
+      <c r="ET13" s="26"/>
+      <c r="EU13" s="26"/>
+      <c r="EV13" s="26"/>
+      <c r="EW13" s="26"/>
+      <c r="EX13" s="26"/>
+      <c r="EY13" s="26"/>
+      <c r="EZ13" s="26"/>
+      <c r="FA13" s="26"/>
+      <c r="FB13" s="26"/>
+      <c r="FC13" s="26"/>
+      <c r="FD13" s="26"/>
+      <c r="FE13" s="26"/>
+      <c r="FF13" s="26"/>
+      <c r="FG13" s="26"/>
+      <c r="FH13" s="26"/>
+      <c r="FI13" s="26"/>
+      <c r="FJ13" s="26"/>
+      <c r="FK13" s="26"/>
+      <c r="FL13" s="26"/>
+      <c r="FM13" s="26"/>
+      <c r="FN13" s="26"/>
+      <c r="FO13" s="26"/>
+      <c r="FP13" s="26"/>
+      <c r="FQ13" s="26"/>
+      <c r="FR13" s="26"/>
+      <c r="FS13" s="26"/>
+      <c r="FT13" s="26"/>
+      <c r="FU13" s="26"/>
+      <c r="FV13" s="26"/>
+      <c r="FW13" s="26"/>
+      <c r="FX13" s="26"/>
+      <c r="FY13" s="26"/>
+      <c r="FZ13" s="26"/>
+      <c r="GA13" s="26"/>
+      <c r="GB13" s="26"/>
+      <c r="GC13" s="26"/>
+      <c r="GD13" s="26"/>
+      <c r="GE13" s="26"/>
+      <c r="GF13" s="26"/>
+      <c r="GG13" s="26"/>
+      <c r="GH13" s="26"/>
+      <c r="GI13" s="26"/>
+      <c r="GJ13" s="26"/>
+      <c r="GK13" s="26"/>
+      <c r="GL13" s="26"/>
+      <c r="GM13" s="26"/>
+      <c r="GN13" s="26"/>
+      <c r="GO13" s="26"/>
+      <c r="GP13" s="26"/>
+      <c r="GQ13" s="26"/>
+      <c r="GR13" s="26"/>
+      <c r="GS13" s="26"/>
+      <c r="GT13" s="26"/>
+      <c r="GU13" s="26"/>
+      <c r="GV13" s="26"/>
+      <c r="GW13" s="26"/>
+      <c r="GX13" s="26"/>
+      <c r="GY13" s="26"/>
+      <c r="GZ13" s="26"/>
+      <c r="HA13" s="26"/>
+      <c r="HB13" s="26"/>
+      <c r="HC13" s="26"/>
+      <c r="HD13" s="26"/>
+      <c r="HE13" s="26"/>
+      <c r="HF13" s="26"/>
+      <c r="HG13" s="26"/>
+      <c r="HH13" s="26"/>
+      <c r="HI13" s="26"/>
+      <c r="HJ13" s="26"/>
+      <c r="HK13" s="26"/>
+      <c r="HL13" s="26"/>
+      <c r="HM13" s="26"/>
+      <c r="HN13" s="26"/>
+      <c r="HO13" s="26"/>
+      <c r="HP13" s="26"/>
+      <c r="HQ13" s="26"/>
+      <c r="HR13" s="26"/>
+      <c r="HS13" s="26"/>
+      <c r="HT13" s="26"/>
+      <c r="HU13" s="26"/>
+      <c r="HV13" s="26"/>
+      <c r="HW13" s="26"/>
+      <c r="HX13" s="26"/>
+      <c r="HY13" s="26"/>
+      <c r="HZ13" s="26"/>
+      <c r="IA13" s="26"/>
+      <c r="IB13" s="26"/>
+      <c r="IC13" s="26"/>
+      <c r="ID13" s="26"/>
+      <c r="IE13" s="26"/>
+      <c r="IF13" s="26"/>
+      <c r="IG13" s="26"/>
+      <c r="IH13" s="26"/>
+      <c r="II13" s="26"/>
+      <c r="IJ13" s="26"/>
+      <c r="IK13" s="26"/>
+      <c r="IL13" s="26"/>
+      <c r="IM13" s="26"/>
+      <c r="IN13" s="26"/>
+      <c r="IO13" s="26"/>
+      <c r="IP13" s="26"/>
+      <c r="IQ13" s="26"/>
+      <c r="IR13" s="26"/>
+      <c r="IS13" s="26"/>
+      <c r="IT13" s="26"/>
+      <c r="IU13" s="26"/>
+      <c r="IV13" s="26"/>
+      <c r="IW13" s="26"/>
+      <c r="IX13" s="26"/>
+      <c r="IY13" s="26"/>
+      <c r="IZ13" s="26"/>
+      <c r="JA13" s="26"/>
+      <c r="JB13" s="26"/>
+      <c r="JC13" s="26"/>
+      <c r="JD13" s="26"/>
+      <c r="JE13" s="26"/>
+      <c r="JF13" s="26"/>
+      <c r="JG13" s="26"/>
+      <c r="JH13" s="26"/>
+      <c r="JI13" s="26"/>
+      <c r="JJ13" s="26"/>
+      <c r="JK13" s="26"/>
+      <c r="JL13" s="26"/>
+      <c r="JM13" s="26"/>
+      <c r="JN13" s="26"/>
+    </row>
+    <row r="14" s="24" customFormat="1" ht="25.5">
+      <c r="A14" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="J13" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="K13" s="17">
+      <c r="E14" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="K14" s="28">
+        <v>2010</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14" s="21"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
+      <c r="U14" s="26"/>
+      <c r="V14" s="26"/>
+      <c r="W14" s="26"/>
+      <c r="X14" s="26"/>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="26"/>
+      <c r="AA14" s="26"/>
+      <c r="AB14" s="26"/>
+      <c r="AC14" s="26"/>
+      <c r="AD14" s="26"/>
+      <c r="AE14" s="26"/>
+      <c r="AF14" s="26"/>
+      <c r="AG14" s="26"/>
+      <c r="AH14" s="26"/>
+      <c r="AI14" s="26"/>
+      <c r="AJ14" s="26"/>
+      <c r="AK14" s="26"/>
+      <c r="AL14" s="26"/>
+      <c r="AM14" s="26"/>
+      <c r="AN14" s="26"/>
+      <c r="AO14" s="26"/>
+      <c r="AP14" s="26"/>
+      <c r="AQ14" s="26"/>
+      <c r="AR14" s="26"/>
+      <c r="AS14" s="26"/>
+      <c r="AT14" s="26"/>
+      <c r="AU14" s="26"/>
+      <c r="AV14" s="26"/>
+      <c r="AW14" s="26"/>
+      <c r="AX14" s="26"/>
+      <c r="AY14" s="26"/>
+      <c r="AZ14" s="26"/>
+      <c r="BA14" s="26"/>
+      <c r="BB14" s="26"/>
+      <c r="BC14" s="26"/>
+      <c r="BD14" s="26"/>
+      <c r="BE14" s="26"/>
+      <c r="BF14" s="26"/>
+      <c r="BG14" s="26"/>
+      <c r="BH14" s="26"/>
+      <c r="BI14" s="26"/>
+      <c r="BJ14" s="26"/>
+      <c r="BK14" s="26"/>
+      <c r="BL14" s="26"/>
+      <c r="BM14" s="26"/>
+      <c r="BN14" s="26"/>
+      <c r="BO14" s="26"/>
+      <c r="BP14" s="26"/>
+      <c r="BQ14" s="26"/>
+      <c r="BR14" s="26"/>
+      <c r="BS14" s="26"/>
+      <c r="BT14" s="26"/>
+      <c r="BU14" s="26"/>
+      <c r="BV14" s="26"/>
+      <c r="BW14" s="26"/>
+      <c r="BX14" s="26"/>
+      <c r="BY14" s="26"/>
+      <c r="BZ14" s="26"/>
+      <c r="CA14" s="26"/>
+      <c r="CB14" s="26"/>
+      <c r="CC14" s="26"/>
+      <c r="CD14" s="26"/>
+      <c r="CE14" s="26"/>
+      <c r="CF14" s="26"/>
+      <c r="CG14" s="26"/>
+      <c r="CH14" s="26"/>
+      <c r="CI14" s="26"/>
+      <c r="CJ14" s="26"/>
+      <c r="CK14" s="26"/>
+      <c r="CL14" s="26"/>
+      <c r="CM14" s="26"/>
+      <c r="CN14" s="26"/>
+      <c r="CO14" s="26"/>
+      <c r="CP14" s="26"/>
+      <c r="CQ14" s="26"/>
+      <c r="CR14" s="26"/>
+      <c r="CS14" s="26"/>
+      <c r="CT14" s="26"/>
+      <c r="CU14" s="26"/>
+      <c r="CV14" s="26"/>
+      <c r="CW14" s="26"/>
+      <c r="CX14" s="26"/>
+      <c r="CY14" s="26"/>
+      <c r="CZ14" s="26"/>
+      <c r="DA14" s="26"/>
+      <c r="DB14" s="26"/>
+      <c r="DC14" s="26"/>
+      <c r="DD14" s="26"/>
+      <c r="DE14" s="26"/>
+      <c r="DF14" s="26"/>
+      <c r="DG14" s="26"/>
+      <c r="DH14" s="26"/>
+      <c r="DI14" s="26"/>
+      <c r="DJ14" s="26"/>
+      <c r="DK14" s="26"/>
+      <c r="DL14" s="26"/>
+      <c r="DM14" s="26"/>
+      <c r="DN14" s="26"/>
+      <c r="DO14" s="26"/>
+      <c r="DP14" s="26"/>
+      <c r="DQ14" s="26"/>
+      <c r="DR14" s="26"/>
+      <c r="DS14" s="26"/>
+      <c r="DT14" s="26"/>
+      <c r="DU14" s="26"/>
+      <c r="DV14" s="26"/>
+      <c r="DW14" s="26"/>
+      <c r="DX14" s="26"/>
+      <c r="DY14" s="26"/>
+      <c r="DZ14" s="26"/>
+      <c r="EA14" s="26"/>
+      <c r="EB14" s="26"/>
+      <c r="EC14" s="26"/>
+      <c r="ED14" s="26"/>
+      <c r="EE14" s="26"/>
+      <c r="EF14" s="26"/>
+      <c r="EG14" s="26"/>
+      <c r="EH14" s="26"/>
+      <c r="EI14" s="26"/>
+      <c r="EJ14" s="26"/>
+      <c r="EK14" s="26"/>
+      <c r="EL14" s="26"/>
+      <c r="EM14" s="26"/>
+      <c r="EN14" s="26"/>
+      <c r="EO14" s="26"/>
+      <c r="EP14" s="26"/>
+      <c r="EQ14" s="26"/>
+      <c r="ER14" s="26"/>
+      <c r="ES14" s="26"/>
+      <c r="ET14" s="26"/>
+      <c r="EU14" s="26"/>
+      <c r="EV14" s="26"/>
+      <c r="EW14" s="26"/>
+      <c r="EX14" s="26"/>
+      <c r="EY14" s="26"/>
+      <c r="EZ14" s="26"/>
+      <c r="FA14" s="26"/>
+      <c r="FB14" s="26"/>
+      <c r="FC14" s="26"/>
+      <c r="FD14" s="26"/>
+      <c r="FE14" s="26"/>
+      <c r="FF14" s="26"/>
+      <c r="FG14" s="26"/>
+      <c r="FH14" s="26"/>
+      <c r="FI14" s="26"/>
+      <c r="FJ14" s="26"/>
+      <c r="FK14" s="26"/>
+      <c r="FL14" s="26"/>
+      <c r="FM14" s="26"/>
+      <c r="FN14" s="26"/>
+      <c r="FO14" s="26"/>
+      <c r="FP14" s="26"/>
+      <c r="FQ14" s="26"/>
+      <c r="FR14" s="26"/>
+      <c r="FS14" s="26"/>
+      <c r="FT14" s="26"/>
+      <c r="FU14" s="26"/>
+      <c r="FV14" s="26"/>
+      <c r="FW14" s="26"/>
+      <c r="FX14" s="26"/>
+      <c r="FY14" s="26"/>
+      <c r="FZ14" s="26"/>
+      <c r="GA14" s="26"/>
+      <c r="GB14" s="26"/>
+      <c r="GC14" s="26"/>
+      <c r="GD14" s="26"/>
+      <c r="GE14" s="26"/>
+      <c r="GF14" s="26"/>
+      <c r="GG14" s="26"/>
+      <c r="GH14" s="26"/>
+      <c r="GI14" s="26"/>
+      <c r="GJ14" s="26"/>
+      <c r="GK14" s="26"/>
+      <c r="GL14" s="26"/>
+      <c r="GM14" s="26"/>
+      <c r="GN14" s="26"/>
+      <c r="GO14" s="26"/>
+      <c r="GP14" s="26"/>
+      <c r="GQ14" s="26"/>
+      <c r="GR14" s="26"/>
+      <c r="GS14" s="26"/>
+      <c r="GT14" s="26"/>
+      <c r="GU14" s="26"/>
+      <c r="GV14" s="26"/>
+      <c r="GW14" s="26"/>
+      <c r="GX14" s="26"/>
+      <c r="GY14" s="26"/>
+      <c r="GZ14" s="26"/>
+      <c r="HA14" s="26"/>
+      <c r="HB14" s="26"/>
+      <c r="HC14" s="26"/>
+      <c r="HD14" s="26"/>
+      <c r="HE14" s="26"/>
+      <c r="HF14" s="26"/>
+      <c r="HG14" s="26"/>
+      <c r="HH14" s="26"/>
+      <c r="HI14" s="26"/>
+      <c r="HJ14" s="26"/>
+      <c r="HK14" s="26"/>
+      <c r="HL14" s="26"/>
+      <c r="HM14" s="26"/>
+      <c r="HN14" s="26"/>
+      <c r="HO14" s="26"/>
+      <c r="HP14" s="26"/>
+      <c r="HQ14" s="26"/>
+      <c r="HR14" s="26"/>
+      <c r="HS14" s="26"/>
+      <c r="HT14" s="26"/>
+      <c r="HU14" s="26"/>
+      <c r="HV14" s="26"/>
+      <c r="HW14" s="26"/>
+      <c r="HX14" s="26"/>
+      <c r="HY14" s="26"/>
+      <c r="HZ14" s="26"/>
+      <c r="IA14" s="26"/>
+      <c r="IB14" s="26"/>
+      <c r="IC14" s="26"/>
+      <c r="ID14" s="26"/>
+      <c r="IE14" s="26"/>
+      <c r="IF14" s="26"/>
+      <c r="IG14" s="26"/>
+      <c r="IH14" s="26"/>
+      <c r="II14" s="26"/>
+      <c r="IJ14" s="26"/>
+      <c r="IK14" s="26"/>
+      <c r="IL14" s="26"/>
+      <c r="IM14" s="26"/>
+      <c r="IN14" s="26"/>
+      <c r="IO14" s="26"/>
+      <c r="IP14" s="26"/>
+      <c r="IQ14" s="26"/>
+      <c r="IR14" s="26"/>
+      <c r="IS14" s="26"/>
+      <c r="IT14" s="26"/>
+      <c r="IU14" s="26"/>
+      <c r="IV14" s="26"/>
+      <c r="IW14" s="26"/>
+      <c r="IX14" s="26"/>
+      <c r="IY14" s="26"/>
+      <c r="IZ14" s="26"/>
+      <c r="JA14" s="26"/>
+      <c r="JB14" s="26"/>
+      <c r="JC14" s="26"/>
+      <c r="JD14" s="26"/>
+      <c r="JE14" s="26"/>
+      <c r="JF14" s="26"/>
+      <c r="JG14" s="26"/>
+      <c r="JH14" s="26"/>
+      <c r="JI14" s="26"/>
+      <c r="JJ14" s="26"/>
+      <c r="JK14" s="26"/>
+      <c r="JL14" s="26"/>
+      <c r="JM14" s="26"/>
+      <c r="JN14" s="26"/>
+    </row>
+    <row r="15" s="29" customFormat="1" ht="89.25">
+      <c r="A15" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="H15" s="21"/>
+      <c r="I15" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="J15" s="31"/>
+      <c r="K15" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="21"/>
+      <c r="N15" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="32"/>
+      <c r="X15" s="32"/>
+      <c r="Y15" s="32"/>
+      <c r="Z15" s="32"/>
+      <c r="AA15" s="32"/>
+      <c r="AB15" s="32"/>
+      <c r="AC15" s="32"/>
+      <c r="AD15" s="32"/>
+      <c r="AE15" s="32"/>
+      <c r="AF15" s="32"/>
+      <c r="AG15" s="32"/>
+      <c r="AH15" s="32"/>
+      <c r="AI15" s="32"/>
+      <c r="AJ15" s="32"/>
+      <c r="AK15" s="32"/>
+      <c r="AL15" s="32"/>
+      <c r="AM15" s="32"/>
+      <c r="AN15" s="32"/>
+      <c r="AO15" s="32"/>
+      <c r="AP15" s="32"/>
+      <c r="AQ15" s="32"/>
+      <c r="AR15" s="32"/>
+      <c r="AS15" s="32"/>
+      <c r="AT15" s="32"/>
+      <c r="AU15" s="32"/>
+      <c r="AV15" s="32"/>
+      <c r="AW15" s="32"/>
+      <c r="AX15" s="32"/>
+      <c r="AY15" s="32"/>
+      <c r="AZ15" s="32"/>
+      <c r="BA15" s="32"/>
+      <c r="BB15" s="32"/>
+      <c r="BC15" s="32"/>
+      <c r="BD15" s="32"/>
+      <c r="BE15" s="32"/>
+      <c r="BF15" s="32"/>
+      <c r="BG15" s="32"/>
+      <c r="BH15" s="32"/>
+      <c r="BI15" s="32"/>
+      <c r="BJ15" s="32"/>
+      <c r="BK15" s="32"/>
+      <c r="BL15" s="32"/>
+      <c r="BM15" s="32"/>
+      <c r="BN15" s="32"/>
+      <c r="BO15" s="32"/>
+      <c r="BP15" s="32"/>
+      <c r="BQ15" s="32"/>
+      <c r="BR15" s="32"/>
+      <c r="BS15" s="32"/>
+      <c r="BT15" s="32"/>
+      <c r="BU15" s="32"/>
+      <c r="BV15" s="32"/>
+      <c r="BW15" s="32"/>
+      <c r="BX15" s="32"/>
+      <c r="BY15" s="32"/>
+      <c r="BZ15" s="32"/>
+      <c r="CA15" s="32"/>
+      <c r="CB15" s="32"/>
+      <c r="CC15" s="32"/>
+      <c r="CD15" s="32"/>
+      <c r="CE15" s="32"/>
+      <c r="CF15" s="32"/>
+      <c r="CG15" s="32"/>
+      <c r="CH15" s="32"/>
+      <c r="CI15" s="32"/>
+      <c r="CJ15" s="32"/>
+      <c r="CK15" s="32"/>
+      <c r="CL15" s="32"/>
+      <c r="CM15" s="32"/>
+      <c r="CN15" s="32"/>
+      <c r="CO15" s="32"/>
+      <c r="CP15" s="32"/>
+      <c r="CQ15" s="32"/>
+      <c r="CR15" s="32"/>
+      <c r="CS15" s="32"/>
+      <c r="CT15" s="32"/>
+      <c r="CU15" s="32"/>
+      <c r="CV15" s="32"/>
+      <c r="CW15" s="32"/>
+      <c r="CX15" s="32"/>
+      <c r="CY15" s="32"/>
+      <c r="CZ15" s="32"/>
+      <c r="DA15" s="32"/>
+      <c r="DB15" s="32"/>
+      <c r="DC15" s="32"/>
+      <c r="DD15" s="32"/>
+      <c r="DE15" s="32"/>
+      <c r="DF15" s="32"/>
+      <c r="DG15" s="32"/>
+      <c r="DH15" s="32"/>
+      <c r="DI15" s="32"/>
+      <c r="DJ15" s="32"/>
+      <c r="DK15" s="32"/>
+      <c r="DL15" s="32"/>
+      <c r="DM15" s="32"/>
+      <c r="DN15" s="32"/>
+      <c r="DO15" s="32"/>
+      <c r="DP15" s="32"/>
+      <c r="DQ15" s="32"/>
+      <c r="DR15" s="32"/>
+      <c r="DS15" s="32"/>
+      <c r="DT15" s="32"/>
+      <c r="DU15" s="32"/>
+      <c r="DV15" s="32"/>
+      <c r="DW15" s="32"/>
+      <c r="DX15" s="32"/>
+      <c r="DY15" s="32"/>
+      <c r="DZ15" s="32"/>
+      <c r="EA15" s="32"/>
+      <c r="EB15" s="32"/>
+      <c r="EC15" s="32"/>
+      <c r="ED15" s="32"/>
+      <c r="EE15" s="32"/>
+      <c r="EF15" s="32"/>
+      <c r="EG15" s="32"/>
+      <c r="EH15" s="32"/>
+      <c r="EI15" s="32"/>
+      <c r="EJ15" s="32"/>
+      <c r="EK15" s="32"/>
+      <c r="EL15" s="32"/>
+      <c r="EM15" s="32"/>
+      <c r="EN15" s="32"/>
+      <c r="EO15" s="32"/>
+      <c r="EP15" s="32"/>
+      <c r="EQ15" s="32"/>
+      <c r="ER15" s="32"/>
+      <c r="ES15" s="32"/>
+      <c r="ET15" s="32"/>
+      <c r="EU15" s="32"/>
+      <c r="EV15" s="32"/>
+      <c r="EW15" s="32"/>
+      <c r="EX15" s="32"/>
+      <c r="EY15" s="32"/>
+      <c r="EZ15" s="32"/>
+      <c r="FA15" s="32"/>
+      <c r="FB15" s="32"/>
+      <c r="FC15" s="32"/>
+      <c r="FD15" s="32"/>
+      <c r="FE15" s="32"/>
+      <c r="FF15" s="32"/>
+      <c r="FG15" s="32"/>
+      <c r="FH15" s="32"/>
+      <c r="FI15" s="32"/>
+      <c r="FJ15" s="32"/>
+      <c r="FK15" s="32"/>
+      <c r="FL15" s="32"/>
+      <c r="FM15" s="32"/>
+      <c r="FN15" s="32"/>
+      <c r="FO15" s="32"/>
+      <c r="FP15" s="32"/>
+      <c r="FQ15" s="32"/>
+      <c r="FR15" s="32"/>
+      <c r="FS15" s="32"/>
+      <c r="FT15" s="32"/>
+      <c r="FU15" s="32"/>
+      <c r="FV15" s="32"/>
+      <c r="FW15" s="32"/>
+      <c r="FX15" s="32"/>
+      <c r="FY15" s="32"/>
+      <c r="FZ15" s="32"/>
+      <c r="GA15" s="32"/>
+      <c r="GB15" s="32"/>
+      <c r="GC15" s="32"/>
+      <c r="GD15" s="32"/>
+      <c r="GE15" s="32"/>
+      <c r="GF15" s="32"/>
+      <c r="GG15" s="32"/>
+      <c r="GH15" s="32"/>
+      <c r="GI15" s="32"/>
+      <c r="GJ15" s="32"/>
+      <c r="GK15" s="32"/>
+      <c r="GL15" s="32"/>
+      <c r="GM15" s="32"/>
+      <c r="GN15" s="32"/>
+      <c r="GO15" s="32"/>
+      <c r="GP15" s="32"/>
+      <c r="GQ15" s="32"/>
+      <c r="GR15" s="32"/>
+      <c r="GS15" s="32"/>
+      <c r="GT15" s="32"/>
+      <c r="GU15" s="32"/>
+      <c r="GV15" s="32"/>
+      <c r="GW15" s="32"/>
+      <c r="GX15" s="32"/>
+      <c r="GY15" s="32"/>
+      <c r="GZ15" s="32"/>
+      <c r="HA15" s="32"/>
+      <c r="HB15" s="32"/>
+      <c r="HC15" s="32"/>
+      <c r="HD15" s="32"/>
+      <c r="HE15" s="32"/>
+      <c r="HF15" s="32"/>
+      <c r="HG15" s="32"/>
+      <c r="HH15" s="32"/>
+      <c r="HI15" s="32"/>
+      <c r="HJ15" s="32"/>
+      <c r="HK15" s="32"/>
+      <c r="HL15" s="32"/>
+      <c r="HM15" s="32"/>
+      <c r="HN15" s="32"/>
+      <c r="HO15" s="32"/>
+      <c r="HP15" s="32"/>
+      <c r="HQ15" s="32"/>
+      <c r="HR15" s="32"/>
+      <c r="HS15" s="32"/>
+      <c r="HT15" s="32"/>
+      <c r="HU15" s="32"/>
+      <c r="HV15" s="32"/>
+      <c r="HW15" s="32"/>
+      <c r="HX15" s="32"/>
+      <c r="HY15" s="32"/>
+      <c r="HZ15" s="32"/>
+      <c r="IA15" s="32"/>
+      <c r="IB15" s="32"/>
+      <c r="IC15" s="32"/>
+      <c r="ID15" s="32"/>
+      <c r="IE15" s="32"/>
+      <c r="IF15" s="32"/>
+      <c r="IG15" s="32"/>
+      <c r="IH15" s="32"/>
+      <c r="II15" s="32"/>
+      <c r="IJ15" s="32"/>
+      <c r="IK15" s="32"/>
+      <c r="IL15" s="32"/>
+      <c r="IM15" s="32"/>
+      <c r="IN15" s="32"/>
+      <c r="IO15" s="32"/>
+      <c r="IP15" s="32"/>
+      <c r="IQ15" s="32"/>
+      <c r="IR15" s="32"/>
+      <c r="IS15" s="32"/>
+      <c r="IT15" s="32"/>
+      <c r="IU15" s="32"/>
+      <c r="IV15" s="32"/>
+      <c r="IW15" s="32"/>
+      <c r="IX15" s="32"/>
+      <c r="IY15" s="32"/>
+      <c r="IZ15" s="32"/>
+      <c r="JA15" s="32"/>
+      <c r="JB15" s="32"/>
+      <c r="JC15" s="32"/>
+      <c r="JD15" s="32"/>
+      <c r="JE15" s="32"/>
+      <c r="JF15" s="32"/>
+      <c r="JG15" s="32"/>
+      <c r="JH15" s="32"/>
+      <c r="JI15" s="32"/>
+      <c r="JJ15" s="32"/>
+      <c r="JK15" s="32"/>
+      <c r="JL15" s="32"/>
+      <c r="JM15" s="32"/>
+      <c r="JN15" s="32"/>
+    </row>
+    <row r="16" s="4" customFormat="1" ht="89.25">
+      <c r="A16" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="J16" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="K16" s="21">
         <v>2020</v>
       </c>
-      <c r="L13" s="17" t="s">
+      <c r="L16" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="M13" s="17"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
-      <c r="AI13" s="21"/>
-      <c r="AJ13" s="21"/>
-      <c r="AK13" s="21"/>
-      <c r="AL13" s="21"/>
-      <c r="AM13" s="21"/>
-      <c r="AN13" s="21"/>
-      <c r="AO13" s="21"/>
-      <c r="AP13" s="21"/>
-      <c r="AQ13" s="21"/>
-      <c r="AR13" s="21"/>
-      <c r="AS13" s="21"/>
-      <c r="AT13" s="21"/>
-      <c r="AU13" s="21"/>
-      <c r="AV13" s="21"/>
-      <c r="AW13" s="21"/>
-      <c r="AX13" s="21"/>
-      <c r="AY13" s="21"/>
-      <c r="AZ13" s="21"/>
-      <c r="BA13" s="21"/>
-      <c r="BB13" s="21"/>
-      <c r="BC13" s="21"/>
-      <c r="BD13" s="21"/>
-      <c r="BE13" s="21"/>
-      <c r="BF13" s="21"/>
-      <c r="BG13" s="21"/>
-      <c r="BH13" s="21"/>
-      <c r="BI13" s="21"/>
-      <c r="BJ13" s="21"/>
-      <c r="BK13" s="21"/>
-      <c r="BL13" s="21"/>
-      <c r="BM13" s="21"/>
-      <c r="BN13" s="21"/>
-      <c r="BO13" s="21"/>
-      <c r="BP13" s="21"/>
-      <c r="BQ13" s="21"/>
-      <c r="BR13" s="21"/>
-      <c r="BS13" s="21"/>
-      <c r="BT13" s="21"/>
-      <c r="BU13" s="21"/>
-      <c r="BV13" s="21"/>
-      <c r="BW13" s="21"/>
-      <c r="BX13" s="21"/>
-      <c r="BY13" s="21"/>
-      <c r="BZ13" s="21"/>
-      <c r="CA13" s="21"/>
-      <c r="CB13" s="21"/>
-      <c r="CC13" s="21"/>
-      <c r="CD13" s="21"/>
-      <c r="CE13" s="21"/>
-      <c r="CF13" s="21"/>
-      <c r="CG13" s="21"/>
-      <c r="CH13" s="21"/>
-      <c r="CI13" s="21"/>
-      <c r="CJ13" s="21"/>
-      <c r="CK13" s="21"/>
-      <c r="CL13" s="21"/>
-      <c r="CM13" s="21"/>
-      <c r="CN13" s="21"/>
-      <c r="CO13" s="21"/>
-      <c r="CP13" s="21"/>
-      <c r="CQ13" s="21"/>
-      <c r="CR13" s="21"/>
-      <c r="CS13" s="21"/>
-      <c r="CT13" s="21"/>
-      <c r="CU13" s="21"/>
-      <c r="CV13" s="21"/>
-      <c r="CW13" s="21"/>
-      <c r="CX13" s="21"/>
-      <c r="CY13" s="21"/>
-      <c r="CZ13" s="21"/>
-      <c r="DA13" s="21"/>
-      <c r="DB13" s="21"/>
-      <c r="DC13" s="21"/>
-      <c r="DD13" s="21"/>
-      <c r="DE13" s="21"/>
-      <c r="DF13" s="21"/>
-      <c r="DG13" s="21"/>
-      <c r="DH13" s="21"/>
-      <c r="DI13" s="21"/>
-      <c r="DJ13" s="21"/>
-      <c r="DK13" s="21"/>
-      <c r="DL13" s="21"/>
-      <c r="DM13" s="21"/>
-      <c r="DN13" s="21"/>
-      <c r="DO13" s="21"/>
-      <c r="DP13" s="21"/>
-      <c r="DQ13" s="21"/>
-      <c r="DR13" s="21"/>
-      <c r="DS13" s="21"/>
-      <c r="DT13" s="21"/>
-      <c r="DU13" s="21"/>
-      <c r="DV13" s="21"/>
-      <c r="DW13" s="21"/>
-      <c r="DX13" s="21"/>
-      <c r="DY13" s="21"/>
-      <c r="DZ13" s="21"/>
-      <c r="EA13" s="21"/>
-      <c r="EB13" s="21"/>
-      <c r="EC13" s="21"/>
-      <c r="ED13" s="21"/>
-      <c r="EE13" s="21"/>
-      <c r="EF13" s="21"/>
-      <c r="EG13" s="21"/>
-      <c r="EH13" s="21"/>
-      <c r="EI13" s="21"/>
-      <c r="EJ13" s="21"/>
-      <c r="EK13" s="21"/>
-      <c r="EL13" s="21"/>
-      <c r="EM13" s="21"/>
-      <c r="EN13" s="21"/>
-      <c r="EO13" s="21"/>
-      <c r="EP13" s="21"/>
-      <c r="EQ13" s="21"/>
-      <c r="ER13" s="21"/>
-      <c r="ES13" s="21"/>
-      <c r="ET13" s="21"/>
-      <c r="EU13" s="21"/>
-      <c r="EV13" s="21"/>
-      <c r="EW13" s="21"/>
-      <c r="EX13" s="21"/>
-      <c r="EY13" s="21"/>
-      <c r="EZ13" s="21"/>
-      <c r="FA13" s="21"/>
-      <c r="FB13" s="21"/>
-      <c r="FC13" s="21"/>
-      <c r="FD13" s="21"/>
-      <c r="FE13" s="21"/>
-      <c r="FF13" s="21"/>
-      <c r="FG13" s="21"/>
-      <c r="FH13" s="21"/>
-      <c r="FI13" s="21"/>
-      <c r="FJ13" s="21"/>
-      <c r="FK13" s="21"/>
-      <c r="FL13" s="21"/>
-      <c r="FM13" s="21"/>
-      <c r="FN13" s="21"/>
-      <c r="FO13" s="21"/>
-      <c r="FP13" s="21"/>
-      <c r="FQ13" s="21"/>
-      <c r="FR13" s="21"/>
-      <c r="FS13" s="21"/>
-      <c r="FT13" s="21"/>
-      <c r="FU13" s="21"/>
-      <c r="FV13" s="21"/>
-      <c r="FW13" s="21"/>
-      <c r="FX13" s="21"/>
-      <c r="FY13" s="21"/>
-      <c r="FZ13" s="21"/>
-      <c r="GA13" s="21"/>
-      <c r="GB13" s="21"/>
-      <c r="GC13" s="21"/>
-      <c r="GD13" s="21"/>
-      <c r="GE13" s="21"/>
-      <c r="GF13" s="21"/>
-      <c r="GG13" s="21"/>
-      <c r="GH13" s="21"/>
-      <c r="GI13" s="21"/>
-      <c r="GJ13" s="21"/>
-      <c r="GK13" s="21"/>
-      <c r="GL13" s="21"/>
-      <c r="GM13" s="21"/>
-      <c r="GN13" s="21"/>
-      <c r="GO13" s="21"/>
-      <c r="GP13" s="21"/>
-      <c r="GQ13" s="21"/>
-      <c r="GR13" s="21"/>
-      <c r="GS13" s="21"/>
-      <c r="GT13" s="21"/>
-      <c r="GU13" s="21"/>
-      <c r="GV13" s="21"/>
-      <c r="GW13" s="21"/>
-      <c r="GX13" s="21"/>
-      <c r="GY13" s="21"/>
-      <c r="GZ13" s="21"/>
-      <c r="HA13" s="21"/>
-      <c r="HB13" s="21"/>
-      <c r="HC13" s="21"/>
-      <c r="HD13" s="21"/>
-      <c r="HE13" s="21"/>
-      <c r="HF13" s="21"/>
-      <c r="HG13" s="21"/>
-      <c r="HH13" s="21"/>
-      <c r="HI13" s="21"/>
-      <c r="HJ13" s="21"/>
-      <c r="HK13" s="21"/>
-      <c r="HL13" s="21"/>
-      <c r="HM13" s="21"/>
-      <c r="HN13" s="21"/>
-      <c r="HO13" s="21"/>
-      <c r="HP13" s="21"/>
-      <c r="HQ13" s="21"/>
-      <c r="HR13" s="21"/>
-      <c r="HS13" s="21"/>
-      <c r="HT13" s="21"/>
-      <c r="HU13" s="21"/>
-      <c r="HV13" s="21"/>
-      <c r="HW13" s="21"/>
-      <c r="HX13" s="21"/>
-      <c r="HY13" s="21"/>
-      <c r="HZ13" s="21"/>
-      <c r="IA13" s="21"/>
-      <c r="IB13" s="21"/>
-      <c r="IC13" s="21"/>
-      <c r="ID13" s="21"/>
-      <c r="IE13" s="21"/>
-      <c r="IF13" s="21"/>
-      <c r="IG13" s="21"/>
-      <c r="IH13" s="21"/>
-      <c r="II13" s="21"/>
-      <c r="IJ13" s="21"/>
-      <c r="IK13" s="21"/>
-      <c r="IL13" s="21"/>
-      <c r="IM13" s="21"/>
-      <c r="IN13" s="21"/>
-      <c r="IO13" s="21"/>
-      <c r="IP13" s="21"/>
-      <c r="IQ13" s="21"/>
-      <c r="IR13" s="21"/>
-      <c r="IS13" s="21"/>
-      <c r="IT13" s="21"/>
-      <c r="IU13" s="21"/>
-      <c r="IV13" s="21"/>
-      <c r="IW13" s="21"/>
-      <c r="IX13" s="21"/>
-      <c r="IY13" s="21"/>
-      <c r="IZ13" s="21"/>
-      <c r="JA13" s="21"/>
-      <c r="JB13" s="21"/>
-      <c r="JC13" s="21"/>
-      <c r="JD13" s="21"/>
-      <c r="JE13" s="21"/>
-      <c r="JF13" s="21"/>
-      <c r="JG13" s="21"/>
-      <c r="JH13" s="21"/>
-      <c r="JI13" s="21"/>
-      <c r="JJ13" s="21"/>
-      <c r="JK13" s="21"/>
-      <c r="JL13" s="21"/>
-      <c r="JM13" s="21"/>
-      <c r="JN13" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="7"/>
+      <c r="AG16" s="7"/>
+      <c r="AH16" s="7"/>
+      <c r="AI16" s="7"/>
+      <c r="AJ16" s="7"/>
+      <c r="AK16" s="7"/>
+      <c r="AL16" s="7"/>
+      <c r="AM16" s="7"/>
+      <c r="AN16" s="7"/>
+      <c r="AO16" s="7"/>
+      <c r="AP16" s="7"/>
+      <c r="AQ16" s="7"/>
+      <c r="AR16" s="7"/>
+      <c r="AS16" s="7"/>
+      <c r="AT16" s="7"/>
+      <c r="AU16" s="7"/>
+      <c r="AV16" s="7"/>
+      <c r="AW16" s="7"/>
+      <c r="AX16" s="7"/>
+      <c r="AY16" s="7"/>
+      <c r="AZ16" s="7"/>
+      <c r="BA16" s="7"/>
+      <c r="BB16" s="7"/>
+      <c r="BC16" s="7"/>
+      <c r="BD16" s="7"/>
+      <c r="BE16" s="7"/>
+      <c r="BF16" s="7"/>
+      <c r="BG16" s="7"/>
+      <c r="BH16" s="7"/>
+      <c r="BI16" s="7"/>
+      <c r="BJ16" s="7"/>
+      <c r="BK16" s="7"/>
+      <c r="BL16" s="7"/>
+      <c r="BM16" s="7"/>
+      <c r="BN16" s="7"/>
+      <c r="BO16" s="7"/>
+      <c r="BP16" s="7"/>
+      <c r="BQ16" s="7"/>
+      <c r="BR16" s="7"/>
+      <c r="BS16" s="7"/>
+      <c r="BT16" s="7"/>
+      <c r="BU16" s="7"/>
+      <c r="BV16" s="7"/>
+      <c r="BW16" s="7"/>
+      <c r="BX16" s="7"/>
+      <c r="BY16" s="7"/>
+      <c r="BZ16" s="7"/>
+      <c r="CA16" s="7"/>
+      <c r="CB16" s="7"/>
+      <c r="CC16" s="7"/>
+      <c r="CD16" s="7"/>
+      <c r="CE16" s="7"/>
+      <c r="CF16" s="7"/>
+      <c r="CG16" s="7"/>
+      <c r="CH16" s="7"/>
+      <c r="CI16" s="7"/>
+      <c r="CJ16" s="7"/>
+      <c r="CK16" s="7"/>
+      <c r="CL16" s="7"/>
+      <c r="CM16" s="7"/>
+      <c r="CN16" s="7"/>
+      <c r="CO16" s="7"/>
+      <c r="CP16" s="7"/>
+      <c r="CQ16" s="7"/>
+      <c r="CR16" s="7"/>
+      <c r="CS16" s="7"/>
+      <c r="CT16" s="7"/>
+      <c r="CU16" s="7"/>
+      <c r="CV16" s="7"/>
+      <c r="CW16" s="7"/>
+      <c r="CX16" s="7"/>
+      <c r="CY16" s="7"/>
+      <c r="CZ16" s="7"/>
+      <c r="DA16" s="7"/>
+      <c r="DB16" s="7"/>
+      <c r="DC16" s="7"/>
+      <c r="DD16" s="7"/>
+      <c r="DE16" s="7"/>
+      <c r="DF16" s="7"/>
+      <c r="DG16" s="7"/>
+      <c r="DH16" s="7"/>
+      <c r="DI16" s="7"/>
+      <c r="DJ16" s="7"/>
+      <c r="DK16" s="7"/>
+      <c r="DL16" s="7"/>
+      <c r="DM16" s="7"/>
+      <c r="DN16" s="7"/>
+      <c r="DO16" s="7"/>
+      <c r="DP16" s="7"/>
+      <c r="DQ16" s="7"/>
+      <c r="DR16" s="7"/>
+      <c r="DS16" s="7"/>
+      <c r="DT16" s="7"/>
+      <c r="DU16" s="7"/>
+      <c r="DV16" s="7"/>
+      <c r="DW16" s="7"/>
+      <c r="DX16" s="7"/>
+      <c r="DY16" s="7"/>
+      <c r="DZ16" s="7"/>
+      <c r="EA16" s="7"/>
+      <c r="EB16" s="7"/>
+      <c r="EC16" s="7"/>
+      <c r="ED16" s="7"/>
+      <c r="EE16" s="7"/>
+      <c r="EF16" s="7"/>
+      <c r="EG16" s="7"/>
+      <c r="EH16" s="7"/>
+      <c r="EI16" s="7"/>
+      <c r="EJ16" s="7"/>
+      <c r="EK16" s="7"/>
+      <c r="EL16" s="7"/>
+      <c r="EM16" s="7"/>
+      <c r="EN16" s="7"/>
+      <c r="EO16" s="7"/>
+      <c r="EP16" s="7"/>
+      <c r="EQ16" s="7"/>
+      <c r="ER16" s="7"/>
+      <c r="ES16" s="7"/>
+      <c r="ET16" s="7"/>
+      <c r="EU16" s="7"/>
+      <c r="EV16" s="7"/>
+      <c r="EW16" s="7"/>
+      <c r="EX16" s="7"/>
+      <c r="EY16" s="7"/>
+      <c r="EZ16" s="7"/>
+      <c r="FA16" s="7"/>
+      <c r="FB16" s="7"/>
+      <c r="FC16" s="7"/>
+      <c r="FD16" s="7"/>
+      <c r="FE16" s="7"/>
+      <c r="FF16" s="7"/>
+      <c r="FG16" s="7"/>
+      <c r="FH16" s="7"/>
+      <c r="FI16" s="7"/>
+      <c r="FJ16" s="7"/>
+      <c r="FK16" s="7"/>
+      <c r="FL16" s="7"/>
+      <c r="FM16" s="7"/>
+      <c r="FN16" s="7"/>
+      <c r="FO16" s="7"/>
+      <c r="FP16" s="7"/>
+      <c r="FQ16" s="7"/>
+      <c r="FR16" s="7"/>
+      <c r="FS16" s="7"/>
+      <c r="FT16" s="7"/>
+      <c r="FU16" s="7"/>
+      <c r="FV16" s="7"/>
+      <c r="FW16" s="7"/>
+      <c r="FX16" s="7"/>
+      <c r="FY16" s="7"/>
+      <c r="FZ16" s="7"/>
+      <c r="GA16" s="7"/>
+      <c r="GB16" s="7"/>
+      <c r="GC16" s="7"/>
+      <c r="GD16" s="7"/>
+      <c r="GE16" s="7"/>
+      <c r="GF16" s="7"/>
+      <c r="GG16" s="7"/>
+      <c r="GH16" s="7"/>
+      <c r="GI16" s="7"/>
+      <c r="GJ16" s="7"/>
+      <c r="GK16" s="7"/>
+      <c r="GL16" s="7"/>
+      <c r="GM16" s="7"/>
+      <c r="GN16" s="7"/>
+      <c r="GO16" s="7"/>
+      <c r="GP16" s="7"/>
+      <c r="GQ16" s="7"/>
+      <c r="GR16" s="7"/>
+      <c r="GS16" s="7"/>
+      <c r="GT16" s="7"/>
+      <c r="GU16" s="7"/>
+      <c r="GV16" s="7"/>
+      <c r="GW16" s="7"/>
+      <c r="GX16" s="7"/>
+      <c r="GY16" s="7"/>
+      <c r="GZ16" s="7"/>
+      <c r="HA16" s="7"/>
+      <c r="HB16" s="7"/>
+      <c r="HC16" s="7"/>
+      <c r="HD16" s="7"/>
+      <c r="HE16" s="7"/>
+      <c r="HF16" s="7"/>
+      <c r="HG16" s="7"/>
+      <c r="HH16" s="7"/>
+      <c r="HI16" s="7"/>
+      <c r="HJ16" s="7"/>
+      <c r="HK16" s="7"/>
+      <c r="HL16" s="7"/>
+      <c r="HM16" s="7"/>
+      <c r="HN16" s="7"/>
+      <c r="HO16" s="7"/>
+      <c r="HP16" s="7"/>
+      <c r="HQ16" s="7"/>
+      <c r="HR16" s="7"/>
+      <c r="HS16" s="7"/>
+      <c r="HT16" s="7"/>
+      <c r="HU16" s="7"/>
+      <c r="HV16" s="7"/>
+      <c r="HW16" s="7"/>
+      <c r="HX16" s="7"/>
+      <c r="HY16" s="7"/>
+      <c r="HZ16" s="7"/>
+      <c r="IA16" s="7"/>
+      <c r="IB16" s="7"/>
+      <c r="IC16" s="7"/>
+      <c r="ID16" s="7"/>
+      <c r="IE16" s="7"/>
+      <c r="IF16" s="7"/>
+      <c r="IG16" s="7"/>
+      <c r="IH16" s="7"/>
+      <c r="II16" s="7"/>
+      <c r="IJ16" s="7"/>
+      <c r="IK16" s="7"/>
+      <c r="IL16" s="7"/>
+      <c r="IM16" s="7"/>
+      <c r="IN16" s="7"/>
+      <c r="IO16" s="7"/>
+      <c r="IP16" s="7"/>
+      <c r="IQ16" s="7"/>
+      <c r="IR16" s="7"/>
+      <c r="IS16" s="7"/>
+      <c r="IT16" s="7"/>
+      <c r="IU16" s="7"/>
+      <c r="IV16" s="7"/>
+      <c r="IW16" s="7"/>
+      <c r="IX16" s="7"/>
+      <c r="IY16" s="7"/>
+      <c r="IZ16" s="7"/>
+      <c r="JA16" s="7"/>
+      <c r="JB16" s="7"/>
+      <c r="JC16" s="7"/>
+      <c r="JD16" s="7"/>
+      <c r="JE16" s="7"/>
+      <c r="JF16" s="7"/>
+      <c r="JG16" s="7"/>
+      <c r="JH16" s="7"/>
+      <c r="JI16" s="7"/>
+      <c r="JJ16" s="7"/>
+      <c r="JK16" s="7"/>
+      <c r="JL16" s="7"/>
+      <c r="JM16" s="7"/>
+      <c r="JN16" s="7"/>
     </row>
-    <row r="14" s="16" customFormat="1" ht="89.25">
-      <c r="A14" s="17" t="s">
+    <row r="17" s="29" customFormat="1" ht="42.75">
+      <c r="A17" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H14" s="17" t="s">
+      <c r="C17" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="H17" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="24" t="s">
+      <c r="I17" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="K17" s="21">
+        <v>2020</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="M17" s="21"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="32"/>
+      <c r="S17" s="32"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="32"/>
+      <c r="W17" s="32"/>
+      <c r="X17" s="32"/>
+      <c r="Y17" s="32"/>
+      <c r="Z17" s="32"/>
+      <c r="AA17" s="32"/>
+      <c r="AB17" s="32"/>
+      <c r="AC17" s="32"/>
+      <c r="AD17" s="32"/>
+      <c r="AE17" s="32"/>
+      <c r="AF17" s="32"/>
+      <c r="AG17" s="32"/>
+      <c r="AH17" s="32"/>
+      <c r="AI17" s="32"/>
+      <c r="AJ17" s="32"/>
+      <c r="AK17" s="32"/>
+      <c r="AL17" s="32"/>
+      <c r="AM17" s="32"/>
+      <c r="AN17" s="32"/>
+      <c r="AO17" s="32"/>
+      <c r="AP17" s="32"/>
+      <c r="AQ17" s="32"/>
+      <c r="AR17" s="32"/>
+      <c r="AS17" s="32"/>
+      <c r="AT17" s="32"/>
+      <c r="AU17" s="32"/>
+      <c r="AV17" s="32"/>
+      <c r="AW17" s="32"/>
+      <c r="AX17" s="32"/>
+      <c r="AY17" s="32"/>
+      <c r="AZ17" s="32"/>
+      <c r="BA17" s="32"/>
+      <c r="BB17" s="32"/>
+      <c r="BC17" s="32"/>
+      <c r="BD17" s="32"/>
+      <c r="BE17" s="32"/>
+      <c r="BF17" s="32"/>
+      <c r="BG17" s="32"/>
+      <c r="BH17" s="32"/>
+      <c r="BI17" s="32"/>
+      <c r="BJ17" s="32"/>
+      <c r="BK17" s="32"/>
+      <c r="BL17" s="32"/>
+      <c r="BM17" s="32"/>
+      <c r="BN17" s="32"/>
+      <c r="BO17" s="32"/>
+      <c r="BP17" s="32"/>
+      <c r="BQ17" s="32"/>
+      <c r="BR17" s="32"/>
+      <c r="BS17" s="32"/>
+      <c r="BT17" s="32"/>
+      <c r="BU17" s="32"/>
+      <c r="BV17" s="32"/>
+      <c r="BW17" s="32"/>
+      <c r="BX17" s="32"/>
+      <c r="BY17" s="32"/>
+      <c r="BZ17" s="32"/>
+      <c r="CA17" s="32"/>
+      <c r="CB17" s="32"/>
+      <c r="CC17" s="32"/>
+      <c r="CD17" s="32"/>
+      <c r="CE17" s="32"/>
+      <c r="CF17" s="32"/>
+      <c r="CG17" s="32"/>
+      <c r="CH17" s="32"/>
+      <c r="CI17" s="32"/>
+      <c r="CJ17" s="32"/>
+      <c r="CK17" s="32"/>
+      <c r="CL17" s="32"/>
+      <c r="CM17" s="32"/>
+      <c r="CN17" s="32"/>
+      <c r="CO17" s="32"/>
+      <c r="CP17" s="32"/>
+      <c r="CQ17" s="32"/>
+      <c r="CR17" s="32"/>
+      <c r="CS17" s="32"/>
+      <c r="CT17" s="32"/>
+      <c r="CU17" s="32"/>
+      <c r="CV17" s="32"/>
+      <c r="CW17" s="32"/>
+      <c r="CX17" s="32"/>
+      <c r="CY17" s="32"/>
+      <c r="CZ17" s="32"/>
+      <c r="DA17" s="32"/>
+      <c r="DB17" s="32"/>
+      <c r="DC17" s="32"/>
+      <c r="DD17" s="32"/>
+      <c r="DE17" s="32"/>
+      <c r="DF17" s="32"/>
+      <c r="DG17" s="32"/>
+      <c r="DH17" s="32"/>
+      <c r="DI17" s="32"/>
+      <c r="DJ17" s="32"/>
+      <c r="DK17" s="32"/>
+      <c r="DL17" s="32"/>
+      <c r="DM17" s="32"/>
+      <c r="DN17" s="32"/>
+      <c r="DO17" s="32"/>
+      <c r="DP17" s="32"/>
+      <c r="DQ17" s="32"/>
+      <c r="DR17" s="32"/>
+      <c r="DS17" s="32"/>
+      <c r="DT17" s="32"/>
+      <c r="DU17" s="32"/>
+      <c r="DV17" s="32"/>
+      <c r="DW17" s="32"/>
+      <c r="DX17" s="32"/>
+      <c r="DY17" s="32"/>
+      <c r="DZ17" s="32"/>
+      <c r="EA17" s="32"/>
+      <c r="EB17" s="32"/>
+      <c r="EC17" s="32"/>
+      <c r="ED17" s="32"/>
+      <c r="EE17" s="32"/>
+      <c r="EF17" s="32"/>
+      <c r="EG17" s="32"/>
+      <c r="EH17" s="32"/>
+      <c r="EI17" s="32"/>
+      <c r="EJ17" s="32"/>
+      <c r="EK17" s="32"/>
+      <c r="EL17" s="32"/>
+      <c r="EM17" s="32"/>
+      <c r="EN17" s="32"/>
+      <c r="EO17" s="32"/>
+      <c r="EP17" s="32"/>
+      <c r="EQ17" s="32"/>
+      <c r="ER17" s="32"/>
+      <c r="ES17" s="32"/>
+      <c r="ET17" s="32"/>
+      <c r="EU17" s="32"/>
+      <c r="EV17" s="32"/>
+      <c r="EW17" s="32"/>
+      <c r="EX17" s="32"/>
+      <c r="EY17" s="32"/>
+      <c r="EZ17" s="32"/>
+      <c r="FA17" s="32"/>
+      <c r="FB17" s="32"/>
+      <c r="FC17" s="32"/>
+      <c r="FD17" s="32"/>
+      <c r="FE17" s="32"/>
+      <c r="FF17" s="32"/>
+      <c r="FG17" s="32"/>
+      <c r="FH17" s="32"/>
+      <c r="FI17" s="32"/>
+      <c r="FJ17" s="32"/>
+      <c r="FK17" s="32"/>
+      <c r="FL17" s="32"/>
+      <c r="FM17" s="32"/>
+      <c r="FN17" s="32"/>
+      <c r="FO17" s="32"/>
+      <c r="FP17" s="32"/>
+      <c r="FQ17" s="32"/>
+      <c r="FR17" s="32"/>
+      <c r="FS17" s="32"/>
+      <c r="FT17" s="32"/>
+      <c r="FU17" s="32"/>
+      <c r="FV17" s="32"/>
+      <c r="FW17" s="32"/>
+      <c r="FX17" s="32"/>
+      <c r="FY17" s="32"/>
+      <c r="FZ17" s="32"/>
+      <c r="GA17" s="32"/>
+      <c r="GB17" s="32"/>
+      <c r="GC17" s="32"/>
+      <c r="GD17" s="32"/>
+      <c r="GE17" s="32"/>
+      <c r="GF17" s="32"/>
+      <c r="GG17" s="32"/>
+      <c r="GH17" s="32"/>
+      <c r="GI17" s="32"/>
+      <c r="GJ17" s="32"/>
+      <c r="GK17" s="32"/>
+      <c r="GL17" s="32"/>
+      <c r="GM17" s="32"/>
+      <c r="GN17" s="32"/>
+      <c r="GO17" s="32"/>
+      <c r="GP17" s="32"/>
+      <c r="GQ17" s="32"/>
+      <c r="GR17" s="32"/>
+      <c r="GS17" s="32"/>
+      <c r="GT17" s="32"/>
+      <c r="GU17" s="32"/>
+      <c r="GV17" s="32"/>
+      <c r="GW17" s="32"/>
+      <c r="GX17" s="32"/>
+      <c r="GY17" s="32"/>
+      <c r="GZ17" s="32"/>
+      <c r="HA17" s="32"/>
+      <c r="HB17" s="32"/>
+      <c r="HC17" s="32"/>
+      <c r="HD17" s="32"/>
+      <c r="HE17" s="32"/>
+      <c r="HF17" s="32"/>
+      <c r="HG17" s="32"/>
+      <c r="HH17" s="32"/>
+      <c r="HI17" s="32"/>
+      <c r="HJ17" s="32"/>
+      <c r="HK17" s="32"/>
+      <c r="HL17" s="32"/>
+      <c r="HM17" s="32"/>
+      <c r="HN17" s="32"/>
+      <c r="HO17" s="32"/>
+      <c r="HP17" s="32"/>
+      <c r="HQ17" s="32"/>
+      <c r="HR17" s="32"/>
+      <c r="HS17" s="32"/>
+      <c r="HT17" s="32"/>
+      <c r="HU17" s="32"/>
+      <c r="HV17" s="32"/>
+      <c r="HW17" s="32"/>
+      <c r="HX17" s="32"/>
+      <c r="HY17" s="32"/>
+      <c r="HZ17" s="32"/>
+      <c r="IA17" s="32"/>
+      <c r="IB17" s="32"/>
+      <c r="IC17" s="32"/>
+      <c r="ID17" s="32"/>
+      <c r="IE17" s="32"/>
+      <c r="IF17" s="32"/>
+      <c r="IG17" s="32"/>
+      <c r="IH17" s="32"/>
+      <c r="II17" s="32"/>
+      <c r="IJ17" s="32"/>
+      <c r="IK17" s="32"/>
+      <c r="IL17" s="32"/>
+      <c r="IM17" s="32"/>
+      <c r="IN17" s="32"/>
+      <c r="IO17" s="32"/>
+      <c r="IP17" s="32"/>
+      <c r="IQ17" s="32"/>
+      <c r="IR17" s="32"/>
+      <c r="IS17" s="32"/>
+      <c r="IT17" s="32"/>
+      <c r="IU17" s="32"/>
+      <c r="IV17" s="32"/>
+      <c r="IW17" s="32"/>
+      <c r="IX17" s="32"/>
+      <c r="IY17" s="32"/>
+      <c r="IZ17" s="32"/>
+      <c r="JA17" s="32"/>
+      <c r="JB17" s="32"/>
+      <c r="JC17" s="32"/>
+      <c r="JD17" s="32"/>
+      <c r="JE17" s="32"/>
+      <c r="JF17" s="32"/>
+      <c r="JG17" s="32"/>
+      <c r="JH17" s="32"/>
+      <c r="JI17" s="32"/>
+      <c r="JJ17" s="32"/>
+      <c r="JK17" s="32"/>
+      <c r="JL17" s="32"/>
+      <c r="JM17" s="32"/>
+      <c r="JN17" s="32"/>
+    </row>
+    <row r="18" s="4" customFormat="1" ht="25.5">
+      <c r="A18" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="J14" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="K14" s="17">
-        <v>2020</v>
-      </c>
-      <c r="L14" s="17" t="s">
+      <c r="D18" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="I18" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="J18" s="31"/>
+      <c r="K18" s="21">
+        <v>2025</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="M18" s="21"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="7"/>
+      <c r="AF18" s="7"/>
+      <c r="AG18" s="7"/>
+      <c r="AH18" s="7"/>
+      <c r="AI18" s="7"/>
+      <c r="AJ18" s="7"/>
+      <c r="AK18" s="7"/>
+      <c r="AL18" s="7"/>
+      <c r="AM18" s="7"/>
+      <c r="AN18" s="7"/>
+      <c r="AO18" s="7"/>
+      <c r="AP18" s="7"/>
+      <c r="AQ18" s="7"/>
+      <c r="AR18" s="7"/>
+      <c r="AS18" s="7"/>
+      <c r="AT18" s="7"/>
+      <c r="AU18" s="7"/>
+      <c r="AV18" s="7"/>
+      <c r="AW18" s="7"/>
+      <c r="AX18" s="7"/>
+      <c r="AY18" s="7"/>
+      <c r="AZ18" s="7"/>
+      <c r="BA18" s="7"/>
+      <c r="BB18" s="7"/>
+      <c r="BC18" s="7"/>
+      <c r="BD18" s="7"/>
+      <c r="BE18" s="7"/>
+      <c r="BF18" s="7"/>
+      <c r="BG18" s="7"/>
+      <c r="BH18" s="7"/>
+      <c r="BI18" s="7"/>
+      <c r="BJ18" s="7"/>
+      <c r="BK18" s="7"/>
+      <c r="BL18" s="7"/>
+      <c r="BM18" s="7"/>
+      <c r="BN18" s="7"/>
+      <c r="BO18" s="7"/>
+      <c r="BP18" s="7"/>
+      <c r="BQ18" s="7"/>
+      <c r="BR18" s="7"/>
+      <c r="BS18" s="7"/>
+      <c r="BT18" s="7"/>
+      <c r="BU18" s="7"/>
+      <c r="BV18" s="7"/>
+      <c r="BW18" s="7"/>
+      <c r="BX18" s="7"/>
+      <c r="BY18" s="7"/>
+      <c r="BZ18" s="7"/>
+      <c r="CA18" s="7"/>
+      <c r="CB18" s="7"/>
+      <c r="CC18" s="7"/>
+      <c r="CD18" s="7"/>
+      <c r="CE18" s="7"/>
+      <c r="CF18" s="7"/>
+      <c r="CG18" s="7"/>
+      <c r="CH18" s="7"/>
+      <c r="CI18" s="7"/>
+      <c r="CJ18" s="7"/>
+      <c r="CK18" s="7"/>
+      <c r="CL18" s="7"/>
+      <c r="CM18" s="7"/>
+      <c r="CN18" s="7"/>
+      <c r="CO18" s="7"/>
+      <c r="CP18" s="7"/>
+      <c r="CQ18" s="7"/>
+      <c r="CR18" s="7"/>
+      <c r="CS18" s="7"/>
+      <c r="CT18" s="7"/>
+      <c r="CU18" s="7"/>
+      <c r="CV18" s="7"/>
+      <c r="CW18" s="7"/>
+      <c r="CX18" s="7"/>
+      <c r="CY18" s="7"/>
+      <c r="CZ18" s="7"/>
+      <c r="DA18" s="7"/>
+      <c r="DB18" s="7"/>
+      <c r="DC18" s="7"/>
+      <c r="DD18" s="7"/>
+      <c r="DE18" s="7"/>
+      <c r="DF18" s="7"/>
+      <c r="DG18" s="7"/>
+      <c r="DH18" s="7"/>
+      <c r="DI18" s="7"/>
+      <c r="DJ18" s="7"/>
+      <c r="DK18" s="7"/>
+      <c r="DL18" s="7"/>
+      <c r="DM18" s="7"/>
+      <c r="DN18" s="7"/>
+      <c r="DO18" s="7"/>
+      <c r="DP18" s="7"/>
+      <c r="DQ18" s="7"/>
+      <c r="DR18" s="7"/>
+      <c r="DS18" s="7"/>
+      <c r="DT18" s="7"/>
+      <c r="DU18" s="7"/>
+      <c r="DV18" s="7"/>
+      <c r="DW18" s="7"/>
+      <c r="DX18" s="7"/>
+      <c r="DY18" s="7"/>
+      <c r="DZ18" s="7"/>
+      <c r="EA18" s="7"/>
+      <c r="EB18" s="7"/>
+      <c r="EC18" s="7"/>
+      <c r="ED18" s="7"/>
+      <c r="EE18" s="7"/>
+      <c r="EF18" s="7"/>
+      <c r="EG18" s="7"/>
+      <c r="EH18" s="7"/>
+      <c r="EI18" s="7"/>
+      <c r="EJ18" s="7"/>
+      <c r="EK18" s="7"/>
+      <c r="EL18" s="7"/>
+      <c r="EM18" s="7"/>
+      <c r="EN18" s="7"/>
+      <c r="EO18" s="7"/>
+      <c r="EP18" s="7"/>
+      <c r="EQ18" s="7"/>
+      <c r="ER18" s="7"/>
+      <c r="ES18" s="7"/>
+      <c r="ET18" s="7"/>
+      <c r="EU18" s="7"/>
+      <c r="EV18" s="7"/>
+      <c r="EW18" s="7"/>
+      <c r="EX18" s="7"/>
+      <c r="EY18" s="7"/>
+      <c r="EZ18" s="7"/>
+      <c r="FA18" s="7"/>
+      <c r="FB18" s="7"/>
+      <c r="FC18" s="7"/>
+      <c r="FD18" s="7"/>
+      <c r="FE18" s="7"/>
+      <c r="FF18" s="7"/>
+      <c r="FG18" s="7"/>
+      <c r="FH18" s="7"/>
+      <c r="FI18" s="7"/>
+      <c r="FJ18" s="7"/>
+      <c r="FK18" s="7"/>
+      <c r="FL18" s="7"/>
+      <c r="FM18" s="7"/>
+      <c r="FN18" s="7"/>
+      <c r="FO18" s="7"/>
+      <c r="FP18" s="7"/>
+      <c r="FQ18" s="7"/>
+      <c r="FR18" s="7"/>
+      <c r="FS18" s="7"/>
+      <c r="FT18" s="7"/>
+      <c r="FU18" s="7"/>
+      <c r="FV18" s="7"/>
+      <c r="FW18" s="7"/>
+      <c r="FX18" s="7"/>
+      <c r="FY18" s="7"/>
+      <c r="FZ18" s="7"/>
+      <c r="GA18" s="7"/>
+      <c r="GB18" s="7"/>
+      <c r="GC18" s="7"/>
+      <c r="GD18" s="7"/>
+      <c r="GE18" s="7"/>
+      <c r="GF18" s="7"/>
+      <c r="GG18" s="7"/>
+      <c r="GH18" s="7"/>
+      <c r="GI18" s="7"/>
+      <c r="GJ18" s="7"/>
+      <c r="GK18" s="7"/>
+      <c r="GL18" s="7"/>
+      <c r="GM18" s="7"/>
+      <c r="GN18" s="7"/>
+      <c r="GO18" s="7"/>
+      <c r="GP18" s="7"/>
+      <c r="GQ18" s="7"/>
+      <c r="GR18" s="7"/>
+      <c r="GS18" s="7"/>
+      <c r="GT18" s="7"/>
+      <c r="GU18" s="7"/>
+      <c r="GV18" s="7"/>
+      <c r="GW18" s="7"/>
+      <c r="GX18" s="7"/>
+      <c r="GY18" s="7"/>
+      <c r="GZ18" s="7"/>
+      <c r="HA18" s="7"/>
+      <c r="HB18" s="7"/>
+      <c r="HC18" s="7"/>
+      <c r="HD18" s="7"/>
+      <c r="HE18" s="7"/>
+      <c r="HF18" s="7"/>
+      <c r="HG18" s="7"/>
+      <c r="HH18" s="7"/>
+      <c r="HI18" s="7"/>
+      <c r="HJ18" s="7"/>
+      <c r="HK18" s="7"/>
+      <c r="HL18" s="7"/>
+      <c r="HM18" s="7"/>
+      <c r="HN18" s="7"/>
+      <c r="HO18" s="7"/>
+      <c r="HP18" s="7"/>
+      <c r="HQ18" s="7"/>
+      <c r="HR18" s="7"/>
+      <c r="HS18" s="7"/>
+      <c r="HT18" s="7"/>
+      <c r="HU18" s="7"/>
+      <c r="HV18" s="7"/>
+      <c r="HW18" s="7"/>
+      <c r="HX18" s="7"/>
+      <c r="HY18" s="7"/>
+      <c r="HZ18" s="7"/>
+      <c r="IA18" s="7"/>
+      <c r="IB18" s="7"/>
+      <c r="IC18" s="7"/>
+      <c r="ID18" s="7"/>
+      <c r="IE18" s="7"/>
+      <c r="IF18" s="7"/>
+      <c r="IG18" s="7"/>
+      <c r="IH18" s="7"/>
+      <c r="II18" s="7"/>
+      <c r="IJ18" s="7"/>
+      <c r="IK18" s="7"/>
+      <c r="IL18" s="7"/>
+      <c r="IM18" s="7"/>
+      <c r="IN18" s="7"/>
+      <c r="IO18" s="7"/>
+      <c r="IP18" s="7"/>
+      <c r="IQ18" s="7"/>
+      <c r="IR18" s="7"/>
+      <c r="IS18" s="7"/>
+      <c r="IT18" s="7"/>
+      <c r="IU18" s="7"/>
+      <c r="IV18" s="7"/>
+      <c r="IW18" s="7"/>
+      <c r="IX18" s="7"/>
+      <c r="IY18" s="7"/>
+      <c r="IZ18" s="7"/>
+      <c r="JA18" s="7"/>
+      <c r="JB18" s="7"/>
+      <c r="JC18" s="7"/>
+      <c r="JD18" s="7"/>
+      <c r="JE18" s="7"/>
+      <c r="JF18" s="7"/>
+      <c r="JG18" s="7"/>
+      <c r="JH18" s="7"/>
+      <c r="JI18" s="7"/>
+      <c r="JJ18" s="7"/>
+      <c r="JK18" s="7"/>
+      <c r="JL18" s="7"/>
+      <c r="JM18" s="7"/>
+      <c r="JN18" s="7"/>
+    </row>
+    <row r="19" s="4" customFormat="1" ht="42.75">
+      <c r="A19" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="H19" s="21"/>
+      <c r="I19" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="L19" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="M14" s="17"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="21"/>
-      <c r="W14" s="21"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="21"/>
-      <c r="Z14" s="21"/>
-      <c r="AA14" s="21"/>
-      <c r="AB14" s="21"/>
-      <c r="AC14" s="21"/>
-      <c r="AD14" s="21"/>
-      <c r="AE14" s="21"/>
-      <c r="AF14" s="21"/>
-      <c r="AG14" s="21"/>
-      <c r="AH14" s="21"/>
-      <c r="AI14" s="21"/>
-      <c r="AJ14" s="21"/>
-      <c r="AK14" s="21"/>
-      <c r="AL14" s="21"/>
-      <c r="AM14" s="21"/>
-      <c r="AN14" s="21"/>
-      <c r="AO14" s="21"/>
-      <c r="AP14" s="21"/>
-      <c r="AQ14" s="21"/>
-      <c r="AR14" s="21"/>
-      <c r="AS14" s="21"/>
-      <c r="AT14" s="21"/>
-      <c r="AU14" s="21"/>
-      <c r="AV14" s="21"/>
-      <c r="AW14" s="21"/>
-      <c r="AX14" s="21"/>
-      <c r="AY14" s="21"/>
-      <c r="AZ14" s="21"/>
-      <c r="BA14" s="21"/>
-      <c r="BB14" s="21"/>
-      <c r="BC14" s="21"/>
-      <c r="BD14" s="21"/>
-      <c r="BE14" s="21"/>
-      <c r="BF14" s="21"/>
-      <c r="BG14" s="21"/>
-      <c r="BH14" s="21"/>
-      <c r="BI14" s="21"/>
-      <c r="BJ14" s="21"/>
-      <c r="BK14" s="21"/>
-      <c r="BL14" s="21"/>
-      <c r="BM14" s="21"/>
-      <c r="BN14" s="21"/>
-      <c r="BO14" s="21"/>
-      <c r="BP14" s="21"/>
-      <c r="BQ14" s="21"/>
-      <c r="BR14" s="21"/>
-      <c r="BS14" s="21"/>
-      <c r="BT14" s="21"/>
-      <c r="BU14" s="21"/>
-      <c r="BV14" s="21"/>
-      <c r="BW14" s="21"/>
-      <c r="BX14" s="21"/>
-      <c r="BY14" s="21"/>
-      <c r="BZ14" s="21"/>
-      <c r="CA14" s="21"/>
-      <c r="CB14" s="21"/>
-      <c r="CC14" s="21"/>
-      <c r="CD14" s="21"/>
-      <c r="CE14" s="21"/>
-      <c r="CF14" s="21"/>
-      <c r="CG14" s="21"/>
-      <c r="CH14" s="21"/>
-      <c r="CI14" s="21"/>
-      <c r="CJ14" s="21"/>
-      <c r="CK14" s="21"/>
-      <c r="CL14" s="21"/>
-      <c r="CM14" s="21"/>
-      <c r="CN14" s="21"/>
-      <c r="CO14" s="21"/>
-      <c r="CP14" s="21"/>
-      <c r="CQ14" s="21"/>
-      <c r="CR14" s="21"/>
-      <c r="CS14" s="21"/>
-      <c r="CT14" s="21"/>
-      <c r="CU14" s="21"/>
-      <c r="CV14" s="21"/>
-      <c r="CW14" s="21"/>
-      <c r="CX14" s="21"/>
-      <c r="CY14" s="21"/>
-      <c r="CZ14" s="21"/>
-      <c r="DA14" s="21"/>
-      <c r="DB14" s="21"/>
-      <c r="DC14" s="21"/>
-      <c r="DD14" s="21"/>
-      <c r="DE14" s="21"/>
-      <c r="DF14" s="21"/>
-      <c r="DG14" s="21"/>
-      <c r="DH14" s="21"/>
-      <c r="DI14" s="21"/>
-      <c r="DJ14" s="21"/>
-      <c r="DK14" s="21"/>
-      <c r="DL14" s="21"/>
-      <c r="DM14" s="21"/>
-      <c r="DN14" s="21"/>
-      <c r="DO14" s="21"/>
-      <c r="DP14" s="21"/>
-      <c r="DQ14" s="21"/>
-      <c r="DR14" s="21"/>
-      <c r="DS14" s="21"/>
-      <c r="DT14" s="21"/>
-      <c r="DU14" s="21"/>
-      <c r="DV14" s="21"/>
-      <c r="DW14" s="21"/>
-      <c r="DX14" s="21"/>
-      <c r="DY14" s="21"/>
-      <c r="DZ14" s="21"/>
-      <c r="EA14" s="21"/>
-      <c r="EB14" s="21"/>
-      <c r="EC14" s="21"/>
-      <c r="ED14" s="21"/>
-      <c r="EE14" s="21"/>
-      <c r="EF14" s="21"/>
-      <c r="EG14" s="21"/>
-      <c r="EH14" s="21"/>
-      <c r="EI14" s="21"/>
-      <c r="EJ14" s="21"/>
-      <c r="EK14" s="21"/>
-      <c r="EL14" s="21"/>
-      <c r="EM14" s="21"/>
-      <c r="EN14" s="21"/>
-      <c r="EO14" s="21"/>
-      <c r="EP14" s="21"/>
-      <c r="EQ14" s="21"/>
-      <c r="ER14" s="21"/>
-      <c r="ES14" s="21"/>
-      <c r="ET14" s="21"/>
-      <c r="EU14" s="21"/>
-      <c r="EV14" s="21"/>
-      <c r="EW14" s="21"/>
-      <c r="EX14" s="21"/>
-      <c r="EY14" s="21"/>
-      <c r="EZ14" s="21"/>
-      <c r="FA14" s="21"/>
-      <c r="FB14" s="21"/>
-      <c r="FC14" s="21"/>
-      <c r="FD14" s="21"/>
-      <c r="FE14" s="21"/>
-      <c r="FF14" s="21"/>
-      <c r="FG14" s="21"/>
-      <c r="FH14" s="21"/>
-      <c r="FI14" s="21"/>
-      <c r="FJ14" s="21"/>
-      <c r="FK14" s="21"/>
-      <c r="FL14" s="21"/>
-      <c r="FM14" s="21"/>
-      <c r="FN14" s="21"/>
-      <c r="FO14" s="21"/>
-      <c r="FP14" s="21"/>
-      <c r="FQ14" s="21"/>
-      <c r="FR14" s="21"/>
-      <c r="FS14" s="21"/>
-      <c r="FT14" s="21"/>
-      <c r="FU14" s="21"/>
-      <c r="FV14" s="21"/>
-      <c r="FW14" s="21"/>
-      <c r="FX14" s="21"/>
-      <c r="FY14" s="21"/>
-      <c r="FZ14" s="21"/>
-      <c r="GA14" s="21"/>
-      <c r="GB14" s="21"/>
-      <c r="GC14" s="21"/>
-      <c r="GD14" s="21"/>
-      <c r="GE14" s="21"/>
-      <c r="GF14" s="21"/>
-      <c r="GG14" s="21"/>
-      <c r="GH14" s="21"/>
-      <c r="GI14" s="21"/>
-      <c r="GJ14" s="21"/>
-      <c r="GK14" s="21"/>
-      <c r="GL14" s="21"/>
-      <c r="GM14" s="21"/>
-      <c r="GN14" s="21"/>
-      <c r="GO14" s="21"/>
-      <c r="GP14" s="21"/>
-      <c r="GQ14" s="21"/>
-      <c r="GR14" s="21"/>
-      <c r="GS14" s="21"/>
-      <c r="GT14" s="21"/>
-      <c r="GU14" s="21"/>
-      <c r="GV14" s="21"/>
-      <c r="GW14" s="21"/>
-      <c r="GX14" s="21"/>
-      <c r="GY14" s="21"/>
-      <c r="GZ14" s="21"/>
-      <c r="HA14" s="21"/>
-      <c r="HB14" s="21"/>
-      <c r="HC14" s="21"/>
-      <c r="HD14" s="21"/>
-      <c r="HE14" s="21"/>
-      <c r="HF14" s="21"/>
-      <c r="HG14" s="21"/>
-      <c r="HH14" s="21"/>
-      <c r="HI14" s="21"/>
-      <c r="HJ14" s="21"/>
-      <c r="HK14" s="21"/>
-      <c r="HL14" s="21"/>
-      <c r="HM14" s="21"/>
-      <c r="HN14" s="21"/>
-      <c r="HO14" s="21"/>
-      <c r="HP14" s="21"/>
-      <c r="HQ14" s="21"/>
-      <c r="HR14" s="21"/>
-      <c r="HS14" s="21"/>
-      <c r="HT14" s="21"/>
-      <c r="HU14" s="21"/>
-      <c r="HV14" s="21"/>
-      <c r="HW14" s="21"/>
-      <c r="HX14" s="21"/>
-      <c r="HY14" s="21"/>
-      <c r="HZ14" s="21"/>
-      <c r="IA14" s="21"/>
-      <c r="IB14" s="21"/>
-      <c r="IC14" s="21"/>
-      <c r="ID14" s="21"/>
-      <c r="IE14" s="21"/>
-      <c r="IF14" s="21"/>
-      <c r="IG14" s="21"/>
-      <c r="IH14" s="21"/>
-      <c r="II14" s="21"/>
-      <c r="IJ14" s="21"/>
-      <c r="IK14" s="21"/>
-      <c r="IL14" s="21"/>
-      <c r="IM14" s="21"/>
-      <c r="IN14" s="21"/>
-      <c r="IO14" s="21"/>
-      <c r="IP14" s="21"/>
-      <c r="IQ14" s="21"/>
-      <c r="IR14" s="21"/>
-      <c r="IS14" s="21"/>
-      <c r="IT14" s="21"/>
-      <c r="IU14" s="21"/>
-      <c r="IV14" s="21"/>
-      <c r="IW14" s="21"/>
-      <c r="IX14" s="21"/>
-      <c r="IY14" s="21"/>
-      <c r="IZ14" s="21"/>
-      <c r="JA14" s="21"/>
-      <c r="JB14" s="21"/>
-      <c r="JC14" s="21"/>
-      <c r="JD14" s="21"/>
-      <c r="JE14" s="21"/>
-      <c r="JF14" s="21"/>
-      <c r="JG14" s="21"/>
-      <c r="JH14" s="21"/>
-      <c r="JI14" s="21"/>
-      <c r="JJ14" s="21"/>
-      <c r="JK14" s="21"/>
-      <c r="JL14" s="21"/>
-      <c r="JM14" s="21"/>
-      <c r="JN14" s="21"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="35"/>
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="35"/>
+      <c r="AC19" s="35"/>
+      <c r="AD19" s="35"/>
+      <c r="AE19" s="35"/>
+      <c r="AF19" s="35"/>
+      <c r="AG19" s="35"/>
+      <c r="AH19" s="35"/>
+      <c r="AI19" s="35"/>
+      <c r="AJ19" s="35"/>
+      <c r="AK19" s="35"/>
+      <c r="AL19" s="35"/>
+      <c r="AM19" s="35"/>
+      <c r="AN19" s="35"/>
+      <c r="AO19" s="35"/>
+      <c r="AP19" s="35"/>
+      <c r="AQ19" s="35"/>
+      <c r="AR19" s="35"/>
+      <c r="AS19" s="35"/>
+      <c r="AT19" s="35"/>
+      <c r="AU19" s="35"/>
+      <c r="AV19" s="35"/>
+      <c r="AW19" s="35"/>
+      <c r="AX19" s="35"/>
+      <c r="AY19" s="35"/>
+      <c r="AZ19" s="35"/>
+      <c r="BA19" s="35"/>
+      <c r="BB19" s="35"/>
+      <c r="BC19" s="35"/>
+      <c r="BD19" s="35"/>
+      <c r="BE19" s="35"/>
+      <c r="BF19" s="35"/>
+      <c r="BG19" s="35"/>
+      <c r="BH19" s="35"/>
+      <c r="BI19" s="35"/>
+      <c r="BJ19" s="35"/>
+      <c r="BK19" s="35"/>
+      <c r="BL19" s="35"/>
+      <c r="BM19" s="35"/>
+      <c r="BN19" s="35"/>
+      <c r="BO19" s="35"/>
+      <c r="BP19" s="35"/>
+      <c r="BQ19" s="35"/>
+      <c r="BR19" s="35"/>
+      <c r="BS19" s="35"/>
+      <c r="BT19" s="35"/>
+      <c r="BU19" s="35"/>
+      <c r="BV19" s="35"/>
+      <c r="BW19" s="35"/>
+      <c r="BX19" s="35"/>
+      <c r="BY19" s="35"/>
+      <c r="BZ19" s="35"/>
+      <c r="CA19" s="35"/>
+      <c r="CB19" s="35"/>
+      <c r="CC19" s="35"/>
+      <c r="CD19" s="35"/>
+      <c r="CE19" s="35"/>
+      <c r="CF19" s="35"/>
+      <c r="CG19" s="35"/>
+      <c r="CH19" s="35"/>
+      <c r="CI19" s="35"/>
+      <c r="CJ19" s="35"/>
+      <c r="CK19" s="35"/>
+      <c r="CL19" s="35"/>
+      <c r="CM19" s="35"/>
+      <c r="CN19" s="35"/>
+      <c r="CO19" s="35"/>
+      <c r="CP19" s="35"/>
+      <c r="CQ19" s="35"/>
+      <c r="CR19" s="35"/>
+      <c r="CS19" s="35"/>
+      <c r="CT19" s="35"/>
+      <c r="CU19" s="35"/>
+      <c r="CV19" s="35"/>
+      <c r="CW19" s="35"/>
+      <c r="CX19" s="35"/>
+      <c r="CY19" s="35"/>
+      <c r="CZ19" s="35"/>
+      <c r="DA19" s="35"/>
+      <c r="DB19" s="35"/>
+      <c r="DC19" s="35"/>
+      <c r="DD19" s="35"/>
+      <c r="DE19" s="35"/>
+      <c r="DF19" s="35"/>
+      <c r="DG19" s="35"/>
+      <c r="DH19" s="35"/>
+      <c r="DI19" s="35"/>
+      <c r="DJ19" s="35"/>
+      <c r="DK19" s="35"/>
+      <c r="DL19" s="35"/>
+      <c r="DM19" s="35"/>
+      <c r="DN19" s="35"/>
+      <c r="DO19" s="35"/>
+      <c r="DP19" s="35"/>
+      <c r="DQ19" s="35"/>
+      <c r="DR19" s="35"/>
+      <c r="DS19" s="35"/>
+      <c r="DT19" s="35"/>
+      <c r="DU19" s="35"/>
+      <c r="DV19" s="35"/>
+      <c r="DW19" s="35"/>
+      <c r="DX19" s="35"/>
+      <c r="DY19" s="35"/>
+      <c r="DZ19" s="35"/>
+      <c r="EA19" s="35"/>
+      <c r="EB19" s="35"/>
+      <c r="EC19" s="35"/>
+      <c r="ED19" s="35"/>
+      <c r="EE19" s="35"/>
+      <c r="EF19" s="35"/>
+      <c r="EG19" s="35"/>
+      <c r="EH19" s="35"/>
+      <c r="EI19" s="35"/>
+      <c r="EJ19" s="35"/>
+      <c r="EK19" s="35"/>
+      <c r="EL19" s="35"/>
+      <c r="EM19" s="35"/>
+      <c r="EN19" s="35"/>
+      <c r="EO19" s="35"/>
+      <c r="EP19" s="35"/>
+      <c r="EQ19" s="35"/>
+      <c r="ER19" s="35"/>
+      <c r="ES19" s="35"/>
+      <c r="ET19" s="35"/>
+      <c r="EU19" s="35"/>
+      <c r="EV19" s="35"/>
+      <c r="EW19" s="35"/>
+      <c r="EX19" s="35"/>
+      <c r="EY19" s="35"/>
+      <c r="EZ19" s="35"/>
+      <c r="FA19" s="35"/>
+      <c r="FB19" s="35"/>
+      <c r="FC19" s="35"/>
+      <c r="FD19" s="35"/>
+      <c r="FE19" s="35"/>
+      <c r="FF19" s="35"/>
+      <c r="FG19" s="35"/>
+      <c r="FH19" s="35"/>
+      <c r="FI19" s="35"/>
+      <c r="FJ19" s="35"/>
+      <c r="FK19" s="35"/>
+      <c r="FL19" s="35"/>
+      <c r="FM19" s="35"/>
+      <c r="FN19" s="35"/>
+      <c r="FO19" s="35"/>
+      <c r="FP19" s="35"/>
+      <c r="FQ19" s="35"/>
+      <c r="FR19" s="35"/>
+      <c r="FS19" s="35"/>
+      <c r="FT19" s="35"/>
+      <c r="FU19" s="35"/>
+      <c r="FV19" s="35"/>
+      <c r="FW19" s="35"/>
+      <c r="FX19" s="35"/>
+      <c r="FY19" s="35"/>
+      <c r="FZ19" s="35"/>
+      <c r="GA19" s="35"/>
+      <c r="GB19" s="35"/>
+      <c r="GC19" s="35"/>
+      <c r="GD19" s="35"/>
+      <c r="GE19" s="35"/>
+      <c r="GF19" s="35"/>
+      <c r="GG19" s="35"/>
+      <c r="GH19" s="35"/>
+      <c r="GI19" s="35"/>
+      <c r="GJ19" s="35"/>
+      <c r="GK19" s="35"/>
+      <c r="GL19" s="35"/>
+      <c r="GM19" s="35"/>
+      <c r="GN19" s="35"/>
+      <c r="GO19" s="35"/>
+      <c r="GP19" s="35"/>
+      <c r="GQ19" s="35"/>
+      <c r="GR19" s="35"/>
+      <c r="GS19" s="35"/>
+      <c r="GT19" s="35"/>
+      <c r="GU19" s="35"/>
+      <c r="GV19" s="35"/>
+      <c r="GW19" s="35"/>
+      <c r="GX19" s="35"/>
+      <c r="GY19" s="35"/>
+      <c r="GZ19" s="35"/>
+      <c r="HA19" s="35"/>
+      <c r="HB19" s="35"/>
+      <c r="HC19" s="35"/>
+      <c r="HD19" s="35"/>
+      <c r="HE19" s="35"/>
+      <c r="HF19" s="35"/>
+      <c r="HG19" s="35"/>
+      <c r="HH19" s="35"/>
+      <c r="HI19" s="35"/>
+      <c r="HJ19" s="35"/>
+      <c r="HK19" s="35"/>
+      <c r="HL19" s="35"/>
+      <c r="HM19" s="35"/>
+      <c r="HN19" s="35"/>
+      <c r="HO19" s="35"/>
+      <c r="HP19" s="35"/>
+      <c r="HQ19" s="35"/>
+      <c r="HR19" s="35"/>
+      <c r="HS19" s="35"/>
+      <c r="HT19" s="35"/>
+      <c r="HU19" s="35"/>
+      <c r="HV19" s="35"/>
+      <c r="HW19" s="35"/>
+      <c r="HX19" s="35"/>
+      <c r="HY19" s="35"/>
+      <c r="HZ19" s="35"/>
+      <c r="IA19" s="35"/>
+      <c r="IB19" s="35"/>
+      <c r="IC19" s="35"/>
+      <c r="ID19" s="35"/>
+      <c r="IE19" s="35"/>
+      <c r="IF19" s="35"/>
+      <c r="IG19" s="35"/>
+      <c r="IH19" s="35"/>
+      <c r="II19" s="35"/>
+      <c r="IJ19" s="35"/>
+      <c r="IK19" s="35"/>
+      <c r="IL19" s="35"/>
+      <c r="IM19" s="35"/>
+      <c r="IN19" s="35"/>
+      <c r="IO19" s="35"/>
+      <c r="IP19" s="35"/>
+      <c r="IQ19" s="35"/>
+      <c r="IR19" s="35"/>
+      <c r="IS19" s="35"/>
+      <c r="IT19" s="35"/>
+      <c r="IU19" s="35"/>
+      <c r="IV19" s="35"/>
+      <c r="IW19" s="35"/>
+      <c r="IX19" s="35"/>
+      <c r="IY19" s="35"/>
+      <c r="IZ19" s="35"/>
+      <c r="JA19" s="35"/>
+      <c r="JB19" s="35"/>
+      <c r="JC19" s="35"/>
+      <c r="JD19" s="35"/>
+      <c r="JE19" s="35"/>
+      <c r="JF19" s="35"/>
+      <c r="JG19" s="35"/>
+      <c r="JH19" s="35"/>
+      <c r="JI19" s="35"/>
+      <c r="JJ19" s="35"/>
+      <c r="JK19" s="35"/>
+      <c r="JL19" s="35"/>
+      <c r="JM19" s="35"/>
+      <c r="JN19" s="35"/>
     </row>
-    <row r="15" s="27" customFormat="1" ht="89.25">
-      <c r="A15" s="17" t="s">
+    <row r="20" s="36" customFormat="1" ht="28.5">
+      <c r="A20" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="J15" s="26"/>
-      <c r="K15" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L15" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="M15" s="17"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="28"/>
-      <c r="U15" s="28"/>
-      <c r="V15" s="28"/>
-      <c r="W15" s="28"/>
-      <c r="X15" s="28"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="28"/>
-      <c r="AA15" s="28"/>
-      <c r="AB15" s="28"/>
-      <c r="AC15" s="28"/>
-      <c r="AD15" s="28"/>
-      <c r="AE15" s="28"/>
-      <c r="AF15" s="28"/>
-      <c r="AG15" s="28"/>
-      <c r="AH15" s="28"/>
-      <c r="AI15" s="28"/>
-      <c r="AJ15" s="28"/>
-      <c r="AK15" s="28"/>
-      <c r="AL15" s="28"/>
-      <c r="AM15" s="28"/>
-      <c r="AN15" s="28"/>
-      <c r="AO15" s="28"/>
-      <c r="AP15" s="28"/>
-      <c r="AQ15" s="28"/>
-      <c r="AR15" s="28"/>
-      <c r="AS15" s="28"/>
-      <c r="AT15" s="28"/>
-      <c r="AU15" s="28"/>
-      <c r="AV15" s="28"/>
-      <c r="AW15" s="28"/>
-      <c r="AX15" s="28"/>
-      <c r="AY15" s="28"/>
-      <c r="AZ15" s="28"/>
-      <c r="BA15" s="28"/>
-      <c r="BB15" s="28"/>
-      <c r="BC15" s="28"/>
-      <c r="BD15" s="28"/>
-      <c r="BE15" s="28"/>
-      <c r="BF15" s="28"/>
-      <c r="BG15" s="28"/>
-      <c r="BH15" s="28"/>
-      <c r="BI15" s="28"/>
-      <c r="BJ15" s="28"/>
-      <c r="BK15" s="28"/>
-      <c r="BL15" s="28"/>
-      <c r="BM15" s="28"/>
-      <c r="BN15" s="28"/>
-      <c r="BO15" s="28"/>
-      <c r="BP15" s="28"/>
-      <c r="BQ15" s="28"/>
-      <c r="BR15" s="28"/>
-      <c r="BS15" s="28"/>
-      <c r="BT15" s="28"/>
-      <c r="BU15" s="28"/>
-      <c r="BV15" s="28"/>
-      <c r="BW15" s="28"/>
-      <c r="BX15" s="28"/>
-      <c r="BY15" s="28"/>
-      <c r="BZ15" s="28"/>
-      <c r="CA15" s="28"/>
-      <c r="CB15" s="28"/>
-      <c r="CC15" s="28"/>
-      <c r="CD15" s="28"/>
-      <c r="CE15" s="28"/>
-      <c r="CF15" s="28"/>
-      <c r="CG15" s="28"/>
-      <c r="CH15" s="28"/>
-      <c r="CI15" s="28"/>
-      <c r="CJ15" s="28"/>
-      <c r="CK15" s="28"/>
-      <c r="CL15" s="28"/>
-      <c r="CM15" s="28"/>
-      <c r="CN15" s="28"/>
-      <c r="CO15" s="28"/>
-      <c r="CP15" s="28"/>
-      <c r="CQ15" s="28"/>
-      <c r="CR15" s="28"/>
-      <c r="CS15" s="28"/>
-      <c r="CT15" s="28"/>
-      <c r="CU15" s="28"/>
-      <c r="CV15" s="28"/>
-      <c r="CW15" s="28"/>
-      <c r="CX15" s="28"/>
-      <c r="CY15" s="28"/>
-      <c r="CZ15" s="28"/>
-      <c r="DA15" s="28"/>
-      <c r="DB15" s="28"/>
-      <c r="DC15" s="28"/>
-      <c r="DD15" s="28"/>
-      <c r="DE15" s="28"/>
-      <c r="DF15" s="28"/>
-      <c r="DG15" s="28"/>
-      <c r="DH15" s="28"/>
-      <c r="DI15" s="28"/>
-      <c r="DJ15" s="28"/>
-      <c r="DK15" s="28"/>
-      <c r="DL15" s="28"/>
-      <c r="DM15" s="28"/>
-      <c r="DN15" s="28"/>
-      <c r="DO15" s="28"/>
-      <c r="DP15" s="28"/>
-      <c r="DQ15" s="28"/>
-      <c r="DR15" s="28"/>
-      <c r="DS15" s="28"/>
-      <c r="DT15" s="28"/>
-      <c r="DU15" s="28"/>
-      <c r="DV15" s="28"/>
-      <c r="DW15" s="28"/>
-      <c r="DX15" s="28"/>
-      <c r="DY15" s="28"/>
-      <c r="DZ15" s="28"/>
-      <c r="EA15" s="28"/>
-      <c r="EB15" s="28"/>
-      <c r="EC15" s="28"/>
-      <c r="ED15" s="28"/>
-      <c r="EE15" s="28"/>
-      <c r="EF15" s="28"/>
-      <c r="EG15" s="28"/>
-      <c r="EH15" s="28"/>
-      <c r="EI15" s="28"/>
-      <c r="EJ15" s="28"/>
-      <c r="EK15" s="28"/>
-      <c r="EL15" s="28"/>
-      <c r="EM15" s="28"/>
-      <c r="EN15" s="28"/>
-      <c r="EO15" s="28"/>
-      <c r="EP15" s="28"/>
-      <c r="EQ15" s="28"/>
-      <c r="ER15" s="28"/>
-      <c r="ES15" s="28"/>
-      <c r="ET15" s="28"/>
-      <c r="EU15" s="28"/>
-      <c r="EV15" s="28"/>
-      <c r="EW15" s="28"/>
-      <c r="EX15" s="28"/>
-      <c r="EY15" s="28"/>
-      <c r="EZ15" s="28"/>
-      <c r="FA15" s="28"/>
-      <c r="FB15" s="28"/>
-      <c r="FC15" s="28"/>
-      <c r="FD15" s="28"/>
-      <c r="FE15" s="28"/>
-      <c r="FF15" s="28"/>
-      <c r="FG15" s="28"/>
-      <c r="FH15" s="28"/>
-      <c r="FI15" s="28"/>
-      <c r="FJ15" s="28"/>
-      <c r="FK15" s="28"/>
-      <c r="FL15" s="28"/>
-      <c r="FM15" s="28"/>
-      <c r="FN15" s="28"/>
-      <c r="FO15" s="28"/>
-      <c r="FP15" s="28"/>
-      <c r="FQ15" s="28"/>
-      <c r="FR15" s="28"/>
-      <c r="FS15" s="28"/>
-      <c r="FT15" s="28"/>
-      <c r="FU15" s="28"/>
-      <c r="FV15" s="28"/>
-      <c r="FW15" s="28"/>
-      <c r="FX15" s="28"/>
-      <c r="FY15" s="28"/>
-      <c r="FZ15" s="28"/>
-      <c r="GA15" s="28"/>
-      <c r="GB15" s="28"/>
-      <c r="GC15" s="28"/>
-      <c r="GD15" s="28"/>
-      <c r="GE15" s="28"/>
-      <c r="GF15" s="28"/>
-      <c r="GG15" s="28"/>
-      <c r="GH15" s="28"/>
-      <c r="GI15" s="28"/>
-      <c r="GJ15" s="28"/>
-      <c r="GK15" s="28"/>
-      <c r="GL15" s="28"/>
-      <c r="GM15" s="28"/>
-      <c r="GN15" s="28"/>
-      <c r="GO15" s="28"/>
-      <c r="GP15" s="28"/>
-      <c r="GQ15" s="28"/>
-      <c r="GR15" s="28"/>
-      <c r="GS15" s="28"/>
-      <c r="GT15" s="28"/>
-      <c r="GU15" s="28"/>
-      <c r="GV15" s="28"/>
-      <c r="GW15" s="28"/>
-      <c r="GX15" s="28"/>
-      <c r="GY15" s="28"/>
-      <c r="GZ15" s="28"/>
-      <c r="HA15" s="28"/>
-      <c r="HB15" s="28"/>
-      <c r="HC15" s="28"/>
-      <c r="HD15" s="28"/>
-      <c r="HE15" s="28"/>
-      <c r="HF15" s="28"/>
-      <c r="HG15" s="28"/>
-      <c r="HH15" s="28"/>
-      <c r="HI15" s="28"/>
-      <c r="HJ15" s="28"/>
-      <c r="HK15" s="28"/>
-      <c r="HL15" s="28"/>
-      <c r="HM15" s="28"/>
-      <c r="HN15" s="28"/>
-      <c r="HO15" s="28"/>
-      <c r="HP15" s="28"/>
-      <c r="HQ15" s="28"/>
-      <c r="HR15" s="28"/>
-      <c r="HS15" s="28"/>
-      <c r="HT15" s="28"/>
-      <c r="HU15" s="28"/>
-      <c r="HV15" s="28"/>
-      <c r="HW15" s="28"/>
-      <c r="HX15" s="28"/>
-      <c r="HY15" s="28"/>
-      <c r="HZ15" s="28"/>
-      <c r="IA15" s="28"/>
-      <c r="IB15" s="28"/>
-      <c r="IC15" s="28"/>
-      <c r="ID15" s="28"/>
-      <c r="IE15" s="28"/>
-      <c r="IF15" s="28"/>
-      <c r="IG15" s="28"/>
-      <c r="IH15" s="28"/>
-      <c r="II15" s="28"/>
-      <c r="IJ15" s="28"/>
-      <c r="IK15" s="28"/>
-      <c r="IL15" s="28"/>
-      <c r="IM15" s="28"/>
-      <c r="IN15" s="28"/>
-      <c r="IO15" s="28"/>
-      <c r="IP15" s="28"/>
-      <c r="IQ15" s="28"/>
-      <c r="IR15" s="28"/>
-      <c r="IS15" s="28"/>
-      <c r="IT15" s="28"/>
-      <c r="IU15" s="28"/>
-      <c r="IV15" s="28"/>
-      <c r="IW15" s="28"/>
-      <c r="IX15" s="28"/>
-      <c r="IY15" s="28"/>
-      <c r="IZ15" s="28"/>
-      <c r="JA15" s="28"/>
-      <c r="JB15" s="28"/>
-      <c r="JC15" s="28"/>
-      <c r="JD15" s="28"/>
-      <c r="JE15" s="28"/>
-      <c r="JF15" s="28"/>
-      <c r="JG15" s="28"/>
-      <c r="JH15" s="28"/>
-      <c r="JI15" s="28"/>
-      <c r="JJ15" s="28"/>
-      <c r="JK15" s="28"/>
-      <c r="JL15" s="28"/>
-      <c r="JM15" s="28"/>
-      <c r="JN15" s="28"/>
-    </row>
-    <row r="16" s="27" customFormat="1" ht="42.75">
-      <c r="A16" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="H16" s="17" t="s">
+      <c r="C20" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="H20" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="I16" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="L16" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
-      <c r="U16" s="28"/>
-      <c r="V16" s="28"/>
-      <c r="W16" s="28"/>
-      <c r="X16" s="28"/>
-      <c r="Y16" s="28"/>
-      <c r="Z16" s="28"/>
-      <c r="AA16" s="28"/>
-      <c r="AB16" s="28"/>
-      <c r="AC16" s="28"/>
-      <c r="AD16" s="28"/>
-      <c r="AE16" s="28"/>
-      <c r="AF16" s="28"/>
-      <c r="AG16" s="28"/>
-      <c r="AH16" s="28"/>
-      <c r="AI16" s="28"/>
-      <c r="AJ16" s="28"/>
-      <c r="AK16" s="28"/>
-      <c r="AL16" s="28"/>
-      <c r="AM16" s="28"/>
-      <c r="AN16" s="28"/>
-      <c r="AO16" s="28"/>
-      <c r="AP16" s="28"/>
-      <c r="AQ16" s="28"/>
-      <c r="AR16" s="28"/>
-      <c r="AS16" s="28"/>
-      <c r="AT16" s="28"/>
-      <c r="AU16" s="28"/>
-      <c r="AV16" s="28"/>
-      <c r="AW16" s="28"/>
-      <c r="AX16" s="28"/>
-      <c r="AY16" s="28"/>
-      <c r="AZ16" s="28"/>
-      <c r="BA16" s="28"/>
-      <c r="BB16" s="28"/>
-      <c r="BC16" s="28"/>
-      <c r="BD16" s="28"/>
-      <c r="BE16" s="28"/>
-      <c r="BF16" s="28"/>
-      <c r="BG16" s="28"/>
-      <c r="BH16" s="28"/>
-      <c r="BI16" s="28"/>
-      <c r="BJ16" s="28"/>
-      <c r="BK16" s="28"/>
-      <c r="BL16" s="28"/>
-      <c r="BM16" s="28"/>
-      <c r="BN16" s="28"/>
-      <c r="BO16" s="28"/>
-      <c r="BP16" s="28"/>
-      <c r="BQ16" s="28"/>
-      <c r="BR16" s="28"/>
-      <c r="BS16" s="28"/>
-      <c r="BT16" s="28"/>
-      <c r="BU16" s="28"/>
-      <c r="BV16" s="28"/>
-      <c r="BW16" s="28"/>
-      <c r="BX16" s="28"/>
-      <c r="BY16" s="28"/>
-      <c r="BZ16" s="28"/>
-      <c r="CA16" s="28"/>
-      <c r="CB16" s="28"/>
-      <c r="CC16" s="28"/>
-      <c r="CD16" s="28"/>
-      <c r="CE16" s="28"/>
-      <c r="CF16" s="28"/>
-      <c r="CG16" s="28"/>
-      <c r="CH16" s="28"/>
-      <c r="CI16" s="28"/>
-      <c r="CJ16" s="28"/>
-      <c r="CK16" s="28"/>
-      <c r="CL16" s="28"/>
-      <c r="CM16" s="28"/>
-      <c r="CN16" s="28"/>
-      <c r="CO16" s="28"/>
-      <c r="CP16" s="28"/>
-      <c r="CQ16" s="28"/>
-      <c r="CR16" s="28"/>
-      <c r="CS16" s="28"/>
-      <c r="CT16" s="28"/>
-      <c r="CU16" s="28"/>
-      <c r="CV16" s="28"/>
-      <c r="CW16" s="28"/>
-      <c r="CX16" s="28"/>
-      <c r="CY16" s="28"/>
-      <c r="CZ16" s="28"/>
-      <c r="DA16" s="28"/>
-      <c r="DB16" s="28"/>
-      <c r="DC16" s="28"/>
-      <c r="DD16" s="28"/>
-      <c r="DE16" s="28"/>
-      <c r="DF16" s="28"/>
-      <c r="DG16" s="28"/>
-      <c r="DH16" s="28"/>
-      <c r="DI16" s="28"/>
-      <c r="DJ16" s="28"/>
-      <c r="DK16" s="28"/>
-      <c r="DL16" s="28"/>
-      <c r="DM16" s="28"/>
-      <c r="DN16" s="28"/>
-      <c r="DO16" s="28"/>
-      <c r="DP16" s="28"/>
-      <c r="DQ16" s="28"/>
-      <c r="DR16" s="28"/>
-      <c r="DS16" s="28"/>
-      <c r="DT16" s="28"/>
-      <c r="DU16" s="28"/>
-      <c r="DV16" s="28"/>
-      <c r="DW16" s="28"/>
-      <c r="DX16" s="28"/>
-      <c r="DY16" s="28"/>
-      <c r="DZ16" s="28"/>
-      <c r="EA16" s="28"/>
-      <c r="EB16" s="28"/>
-      <c r="EC16" s="28"/>
-      <c r="ED16" s="28"/>
-      <c r="EE16" s="28"/>
-      <c r="EF16" s="28"/>
-      <c r="EG16" s="28"/>
-      <c r="EH16" s="28"/>
-      <c r="EI16" s="28"/>
-      <c r="EJ16" s="28"/>
-      <c r="EK16" s="28"/>
-      <c r="EL16" s="28"/>
-      <c r="EM16" s="28"/>
-      <c r="EN16" s="28"/>
-      <c r="EO16" s="28"/>
-      <c r="EP16" s="28"/>
-      <c r="EQ16" s="28"/>
-      <c r="ER16" s="28"/>
-      <c r="ES16" s="28"/>
-      <c r="ET16" s="28"/>
-      <c r="EU16" s="28"/>
-      <c r="EV16" s="28"/>
-      <c r="EW16" s="28"/>
-      <c r="EX16" s="28"/>
-      <c r="EY16" s="28"/>
-      <c r="EZ16" s="28"/>
-      <c r="FA16" s="28"/>
-      <c r="FB16" s="28"/>
-      <c r="FC16" s="28"/>
-      <c r="FD16" s="28"/>
-      <c r="FE16" s="28"/>
-      <c r="FF16" s="28"/>
-      <c r="FG16" s="28"/>
-      <c r="FH16" s="28"/>
-      <c r="FI16" s="28"/>
-      <c r="FJ16" s="28"/>
-      <c r="FK16" s="28"/>
-      <c r="FL16" s="28"/>
-      <c r="FM16" s="28"/>
-      <c r="FN16" s="28"/>
-      <c r="FO16" s="28"/>
-      <c r="FP16" s="28"/>
-      <c r="FQ16" s="28"/>
-      <c r="FR16" s="28"/>
-      <c r="FS16" s="28"/>
-      <c r="FT16" s="28"/>
-      <c r="FU16" s="28"/>
-      <c r="FV16" s="28"/>
-      <c r="FW16" s="28"/>
-      <c r="FX16" s="28"/>
-      <c r="FY16" s="28"/>
-      <c r="FZ16" s="28"/>
-      <c r="GA16" s="28"/>
-      <c r="GB16" s="28"/>
-      <c r="GC16" s="28"/>
-      <c r="GD16" s="28"/>
-      <c r="GE16" s="28"/>
-      <c r="GF16" s="28"/>
-      <c r="GG16" s="28"/>
-      <c r="GH16" s="28"/>
-      <c r="GI16" s="28"/>
-      <c r="GJ16" s="28"/>
-      <c r="GK16" s="28"/>
-      <c r="GL16" s="28"/>
-      <c r="GM16" s="28"/>
-      <c r="GN16" s="28"/>
-      <c r="GO16" s="28"/>
-      <c r="GP16" s="28"/>
-      <c r="GQ16" s="28"/>
-      <c r="GR16" s="28"/>
-      <c r="GS16" s="28"/>
-      <c r="GT16" s="28"/>
-      <c r="GU16" s="28"/>
-      <c r="GV16" s="28"/>
-      <c r="GW16" s="28"/>
-      <c r="GX16" s="28"/>
-      <c r="GY16" s="28"/>
-      <c r="GZ16" s="28"/>
-      <c r="HA16" s="28"/>
-      <c r="HB16" s="28"/>
-      <c r="HC16" s="28"/>
-      <c r="HD16" s="28"/>
-      <c r="HE16" s="28"/>
-      <c r="HF16" s="28"/>
-      <c r="HG16" s="28"/>
-      <c r="HH16" s="28"/>
-      <c r="HI16" s="28"/>
-      <c r="HJ16" s="28"/>
-      <c r="HK16" s="28"/>
-      <c r="HL16" s="28"/>
-      <c r="HM16" s="28"/>
-      <c r="HN16" s="28"/>
-      <c r="HO16" s="28"/>
-      <c r="HP16" s="28"/>
-      <c r="HQ16" s="28"/>
-      <c r="HR16" s="28"/>
-      <c r="HS16" s="28"/>
-      <c r="HT16" s="28"/>
-      <c r="HU16" s="28"/>
-      <c r="HV16" s="28"/>
-      <c r="HW16" s="28"/>
-      <c r="HX16" s="28"/>
-      <c r="HY16" s="28"/>
-      <c r="HZ16" s="28"/>
-      <c r="IA16" s="28"/>
-      <c r="IB16" s="28"/>
-      <c r="IC16" s="28"/>
-      <c r="ID16" s="28"/>
-      <c r="IE16" s="28"/>
-      <c r="IF16" s="28"/>
-      <c r="IG16" s="28"/>
-      <c r="IH16" s="28"/>
-      <c r="II16" s="28"/>
-      <c r="IJ16" s="28"/>
-      <c r="IK16" s="28"/>
-      <c r="IL16" s="28"/>
-      <c r="IM16" s="28"/>
-      <c r="IN16" s="28"/>
-      <c r="IO16" s="28"/>
-      <c r="IP16" s="28"/>
-      <c r="IQ16" s="28"/>
-      <c r="IR16" s="28"/>
-      <c r="IS16" s="28"/>
-      <c r="IT16" s="28"/>
-      <c r="IU16" s="28"/>
-      <c r="IV16" s="28"/>
-      <c r="IW16" s="28"/>
-      <c r="IX16" s="28"/>
-      <c r="IY16" s="28"/>
-      <c r="IZ16" s="28"/>
-      <c r="JA16" s="28"/>
-      <c r="JB16" s="28"/>
-      <c r="JC16" s="28"/>
-      <c r="JD16" s="28"/>
-      <c r="JE16" s="28"/>
-      <c r="JF16" s="28"/>
-      <c r="JG16" s="28"/>
-      <c r="JH16" s="28"/>
-      <c r="JI16" s="28"/>
-      <c r="JJ16" s="28"/>
-      <c r="JK16" s="28"/>
-      <c r="JL16" s="28"/>
-      <c r="JM16" s="28"/>
-      <c r="JN16" s="28"/>
-    </row>
-    <row r="17" s="27" customFormat="1" ht="38.25">
-      <c r="A17" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="F17" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="J17" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="L17" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="O17" s="28"/>
-      <c r="P17" s="28"/>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="28"/>
-      <c r="S17" s="28"/>
-      <c r="T17" s="28"/>
-      <c r="U17" s="28"/>
-      <c r="V17" s="28"/>
-      <c r="W17" s="28"/>
-      <c r="X17" s="28"/>
-      <c r="Y17" s="28"/>
-      <c r="Z17" s="28"/>
-      <c r="AA17" s="28"/>
-      <c r="AB17" s="28"/>
-      <c r="AC17" s="28"/>
-      <c r="AD17" s="28"/>
-      <c r="AE17" s="28"/>
-      <c r="AF17" s="28"/>
-      <c r="AG17" s="28"/>
-      <c r="AH17" s="28"/>
-      <c r="AI17" s="28"/>
-      <c r="AJ17" s="28"/>
-      <c r="AK17" s="28"/>
-      <c r="AL17" s="28"/>
-      <c r="AM17" s="28"/>
-      <c r="AN17" s="28"/>
-      <c r="AO17" s="28"/>
-      <c r="AP17" s="28"/>
-      <c r="AQ17" s="28"/>
-      <c r="AR17" s="28"/>
-      <c r="AS17" s="28"/>
-      <c r="AT17" s="28"/>
-      <c r="AU17" s="28"/>
-      <c r="AV17" s="28"/>
-      <c r="AW17" s="28"/>
-      <c r="AX17" s="28"/>
-      <c r="AY17" s="28"/>
-      <c r="AZ17" s="28"/>
-      <c r="BA17" s="28"/>
-      <c r="BB17" s="28"/>
-      <c r="BC17" s="28"/>
-      <c r="BD17" s="28"/>
-      <c r="BE17" s="28"/>
-      <c r="BF17" s="28"/>
-      <c r="BG17" s="28"/>
-      <c r="BH17" s="28"/>
-      <c r="BI17" s="28"/>
-      <c r="BJ17" s="28"/>
-      <c r="BK17" s="28"/>
-      <c r="BL17" s="28"/>
-      <c r="BM17" s="28"/>
-      <c r="BN17" s="28"/>
-      <c r="BO17" s="28"/>
-      <c r="BP17" s="28"/>
-      <c r="BQ17" s="28"/>
-      <c r="BR17" s="28"/>
-      <c r="BS17" s="28"/>
-      <c r="BT17" s="28"/>
-      <c r="BU17" s="28"/>
-      <c r="BV17" s="28"/>
-      <c r="BW17" s="28"/>
-      <c r="BX17" s="28"/>
-      <c r="BY17" s="28"/>
-      <c r="BZ17" s="28"/>
-      <c r="CA17" s="28"/>
-      <c r="CB17" s="28"/>
-      <c r="CC17" s="28"/>
-      <c r="CD17" s="28"/>
-      <c r="CE17" s="28"/>
-      <c r="CF17" s="28"/>
-      <c r="CG17" s="28"/>
-      <c r="CH17" s="28"/>
-      <c r="CI17" s="28"/>
-      <c r="CJ17" s="28"/>
-      <c r="CK17" s="28"/>
-      <c r="CL17" s="28"/>
-      <c r="CM17" s="28"/>
-      <c r="CN17" s="28"/>
-      <c r="CO17" s="28"/>
-      <c r="CP17" s="28"/>
-      <c r="CQ17" s="28"/>
-      <c r="CR17" s="28"/>
-      <c r="CS17" s="28"/>
-      <c r="CT17" s="28"/>
-      <c r="CU17" s="28"/>
-      <c r="CV17" s="28"/>
-      <c r="CW17" s="28"/>
-      <c r="CX17" s="28"/>
-      <c r="CY17" s="28"/>
-      <c r="CZ17" s="28"/>
-      <c r="DA17" s="28"/>
-      <c r="DB17" s="28"/>
-      <c r="DC17" s="28"/>
-      <c r="DD17" s="28"/>
-      <c r="DE17" s="28"/>
-      <c r="DF17" s="28"/>
-      <c r="DG17" s="28"/>
-      <c r="DH17" s="28"/>
-      <c r="DI17" s="28"/>
-      <c r="DJ17" s="28"/>
-      <c r="DK17" s="28"/>
-      <c r="DL17" s="28"/>
-      <c r="DM17" s="28"/>
-      <c r="DN17" s="28"/>
-      <c r="DO17" s="28"/>
-      <c r="DP17" s="28"/>
-      <c r="DQ17" s="28"/>
-      <c r="DR17" s="28"/>
-      <c r="DS17" s="28"/>
-      <c r="DT17" s="28"/>
-      <c r="DU17" s="28"/>
-      <c r="DV17" s="28"/>
-      <c r="DW17" s="28"/>
-      <c r="DX17" s="28"/>
-      <c r="DY17" s="28"/>
-      <c r="DZ17" s="28"/>
-      <c r="EA17" s="28"/>
-      <c r="EB17" s="28"/>
-      <c r="EC17" s="28"/>
-      <c r="ED17" s="28"/>
-      <c r="EE17" s="28"/>
-      <c r="EF17" s="28"/>
-      <c r="EG17" s="28"/>
-      <c r="EH17" s="28"/>
-      <c r="EI17" s="28"/>
-      <c r="EJ17" s="28"/>
-      <c r="EK17" s="28"/>
-      <c r="EL17" s="28"/>
-      <c r="EM17" s="28"/>
-      <c r="EN17" s="28"/>
-      <c r="EO17" s="28"/>
-      <c r="EP17" s="28"/>
-      <c r="EQ17" s="28"/>
-      <c r="ER17" s="28"/>
-      <c r="ES17" s="28"/>
-      <c r="ET17" s="28"/>
-      <c r="EU17" s="28"/>
-      <c r="EV17" s="28"/>
-      <c r="EW17" s="28"/>
-      <c r="EX17" s="28"/>
-      <c r="EY17" s="28"/>
-      <c r="EZ17" s="28"/>
-      <c r="FA17" s="28"/>
-      <c r="FB17" s="28"/>
-      <c r="FC17" s="28"/>
-      <c r="FD17" s="28"/>
-      <c r="FE17" s="28"/>
-      <c r="FF17" s="28"/>
-      <c r="FG17" s="28"/>
-      <c r="FH17" s="28"/>
-      <c r="FI17" s="28"/>
-      <c r="FJ17" s="28"/>
-      <c r="FK17" s="28"/>
-      <c r="FL17" s="28"/>
-      <c r="FM17" s="28"/>
-      <c r="FN17" s="28"/>
-      <c r="FO17" s="28"/>
-      <c r="FP17" s="28"/>
-      <c r="FQ17" s="28"/>
-      <c r="FR17" s="28"/>
-      <c r="FS17" s="28"/>
-      <c r="FT17" s="28"/>
-      <c r="FU17" s="28"/>
-      <c r="FV17" s="28"/>
-      <c r="FW17" s="28"/>
-      <c r="FX17" s="28"/>
-      <c r="FY17" s="28"/>
-      <c r="FZ17" s="28"/>
-      <c r="GA17" s="28"/>
-      <c r="GB17" s="28"/>
-      <c r="GC17" s="28"/>
-      <c r="GD17" s="28"/>
-      <c r="GE17" s="28"/>
-      <c r="GF17" s="28"/>
-      <c r="GG17" s="28"/>
-      <c r="GH17" s="28"/>
-      <c r="GI17" s="28"/>
-      <c r="GJ17" s="28"/>
-      <c r="GK17" s="28"/>
-      <c r="GL17" s="28"/>
-      <c r="GM17" s="28"/>
-      <c r="GN17" s="28"/>
-      <c r="GO17" s="28"/>
-      <c r="GP17" s="28"/>
-      <c r="GQ17" s="28"/>
-      <c r="GR17" s="28"/>
-      <c r="GS17" s="28"/>
-      <c r="GT17" s="28"/>
-      <c r="GU17" s="28"/>
-      <c r="GV17" s="28"/>
-      <c r="GW17" s="28"/>
-      <c r="GX17" s="28"/>
-      <c r="GY17" s="28"/>
-      <c r="GZ17" s="28"/>
-      <c r="HA17" s="28"/>
-      <c r="HB17" s="28"/>
-      <c r="HC17" s="28"/>
-      <c r="HD17" s="28"/>
-      <c r="HE17" s="28"/>
-      <c r="HF17" s="28"/>
-      <c r="HG17" s="28"/>
-      <c r="HH17" s="28"/>
-      <c r="HI17" s="28"/>
-      <c r="HJ17" s="28"/>
-      <c r="HK17" s="28"/>
-      <c r="HL17" s="28"/>
-      <c r="HM17" s="28"/>
-      <c r="HN17" s="28"/>
-      <c r="HO17" s="28"/>
-      <c r="HP17" s="28"/>
-      <c r="HQ17" s="28"/>
-      <c r="HR17" s="28"/>
-      <c r="HS17" s="28"/>
-      <c r="HT17" s="28"/>
-      <c r="HU17" s="28"/>
-      <c r="HV17" s="28"/>
-      <c r="HW17" s="28"/>
-      <c r="HX17" s="28"/>
-      <c r="HY17" s="28"/>
-      <c r="HZ17" s="28"/>
-      <c r="IA17" s="28"/>
-      <c r="IB17" s="28"/>
-      <c r="IC17" s="28"/>
-      <c r="ID17" s="28"/>
-      <c r="IE17" s="28"/>
-      <c r="IF17" s="28"/>
-      <c r="IG17" s="28"/>
-      <c r="IH17" s="28"/>
-      <c r="II17" s="28"/>
-      <c r="IJ17" s="28"/>
-      <c r="IK17" s="28"/>
-      <c r="IL17" s="28"/>
-      <c r="IM17" s="28"/>
-      <c r="IN17" s="28"/>
-      <c r="IO17" s="28"/>
-      <c r="IP17" s="28"/>
-      <c r="IQ17" s="28"/>
-      <c r="IR17" s="28"/>
-      <c r="IS17" s="28"/>
-      <c r="IT17" s="28"/>
-      <c r="IU17" s="28"/>
-      <c r="IV17" s="28"/>
-      <c r="IW17" s="28"/>
-      <c r="IX17" s="28"/>
-      <c r="IY17" s="28"/>
-      <c r="IZ17" s="28"/>
-      <c r="JA17" s="28"/>
-      <c r="JB17" s="28"/>
-      <c r="JC17" s="28"/>
-      <c r="JD17" s="28"/>
-      <c r="JE17" s="28"/>
-      <c r="JF17" s="28"/>
-      <c r="JG17" s="28"/>
-      <c r="JH17" s="28"/>
-      <c r="JI17" s="28"/>
-      <c r="JJ17" s="28"/>
-      <c r="JK17" s="28"/>
-      <c r="JL17" s="28"/>
-      <c r="JM17" s="28"/>
-      <c r="JN17" s="28"/>
-    </row>
-    <row r="18" s="27" customFormat="1" ht="25.5">
-      <c r="A18" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="H18" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="I18" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="K18" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="L18" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="O18" s="28"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="28"/>
-      <c r="V18" s="28"/>
-      <c r="W18" s="28"/>
-      <c r="X18" s="28"/>
-      <c r="Y18" s="28"/>
-      <c r="Z18" s="28"/>
-      <c r="AA18" s="28"/>
-      <c r="AB18" s="28"/>
-      <c r="AC18" s="28"/>
-      <c r="AD18" s="28"/>
-      <c r="AE18" s="28"/>
-      <c r="AF18" s="28"/>
-      <c r="AG18" s="28"/>
-      <c r="AH18" s="28"/>
-      <c r="AI18" s="28"/>
-      <c r="AJ18" s="28"/>
-      <c r="AK18" s="28"/>
-      <c r="AL18" s="28"/>
-      <c r="AM18" s="28"/>
-      <c r="AN18" s="28"/>
-      <c r="AO18" s="28"/>
-      <c r="AP18" s="28"/>
-      <c r="AQ18" s="28"/>
-      <c r="AR18" s="28"/>
-      <c r="AS18" s="28"/>
-      <c r="AT18" s="28"/>
-      <c r="AU18" s="28"/>
-      <c r="AV18" s="28"/>
-      <c r="AW18" s="28"/>
-      <c r="AX18" s="28"/>
-      <c r="AY18" s="28"/>
-      <c r="AZ18" s="28"/>
-      <c r="BA18" s="28"/>
-      <c r="BB18" s="28"/>
-      <c r="BC18" s="28"/>
-      <c r="BD18" s="28"/>
-      <c r="BE18" s="28"/>
-      <c r="BF18" s="28"/>
-      <c r="BG18" s="28"/>
-      <c r="BH18" s="28"/>
-      <c r="BI18" s="28"/>
-      <c r="BJ18" s="28"/>
-      <c r="BK18" s="28"/>
-      <c r="BL18" s="28"/>
-      <c r="BM18" s="28"/>
-      <c r="BN18" s="28"/>
-      <c r="BO18" s="28"/>
-      <c r="BP18" s="28"/>
-      <c r="BQ18" s="28"/>
-      <c r="BR18" s="28"/>
-      <c r="BS18" s="28"/>
-      <c r="BT18" s="28"/>
-      <c r="BU18" s="28"/>
-      <c r="BV18" s="28"/>
-      <c r="BW18" s="28"/>
-      <c r="BX18" s="28"/>
-      <c r="BY18" s="28"/>
-      <c r="BZ18" s="28"/>
-      <c r="CA18" s="28"/>
-      <c r="CB18" s="28"/>
-      <c r="CC18" s="28"/>
-      <c r="CD18" s="28"/>
-      <c r="CE18" s="28"/>
-      <c r="CF18" s="28"/>
-      <c r="CG18" s="28"/>
-      <c r="CH18" s="28"/>
-      <c r="CI18" s="28"/>
-      <c r="CJ18" s="28"/>
-      <c r="CK18" s="28"/>
-      <c r="CL18" s="28"/>
-      <c r="CM18" s="28"/>
-      <c r="CN18" s="28"/>
-      <c r="CO18" s="28"/>
-      <c r="CP18" s="28"/>
-      <c r="CQ18" s="28"/>
-      <c r="CR18" s="28"/>
-      <c r="CS18" s="28"/>
-      <c r="CT18" s="28"/>
-      <c r="CU18" s="28"/>
-      <c r="CV18" s="28"/>
-      <c r="CW18" s="28"/>
-      <c r="CX18" s="28"/>
-      <c r="CY18" s="28"/>
-      <c r="CZ18" s="28"/>
-      <c r="DA18" s="28"/>
-      <c r="DB18" s="28"/>
-      <c r="DC18" s="28"/>
-      <c r="DD18" s="28"/>
-      <c r="DE18" s="28"/>
-      <c r="DF18" s="28"/>
-      <c r="DG18" s="28"/>
-      <c r="DH18" s="28"/>
-      <c r="DI18" s="28"/>
-      <c r="DJ18" s="28"/>
-      <c r="DK18" s="28"/>
-      <c r="DL18" s="28"/>
-      <c r="DM18" s="28"/>
-      <c r="DN18" s="28"/>
-      <c r="DO18" s="28"/>
-      <c r="DP18" s="28"/>
-      <c r="DQ18" s="28"/>
-      <c r="DR18" s="28"/>
-      <c r="DS18" s="28"/>
-      <c r="DT18" s="28"/>
-      <c r="DU18" s="28"/>
-      <c r="DV18" s="28"/>
-      <c r="DW18" s="28"/>
-      <c r="DX18" s="28"/>
-      <c r="DY18" s="28"/>
-      <c r="DZ18" s="28"/>
-      <c r="EA18" s="28"/>
-      <c r="EB18" s="28"/>
-      <c r="EC18" s="28"/>
-      <c r="ED18" s="28"/>
-      <c r="EE18" s="28"/>
-      <c r="EF18" s="28"/>
-      <c r="EG18" s="28"/>
-      <c r="EH18" s="28"/>
-      <c r="EI18" s="28"/>
-      <c r="EJ18" s="28"/>
-      <c r="EK18" s="28"/>
-      <c r="EL18" s="28"/>
-      <c r="EM18" s="28"/>
-      <c r="EN18" s="28"/>
-      <c r="EO18" s="28"/>
-      <c r="EP18" s="28"/>
-      <c r="EQ18" s="28"/>
-      <c r="ER18" s="28"/>
-      <c r="ES18" s="28"/>
-      <c r="ET18" s="28"/>
-      <c r="EU18" s="28"/>
-      <c r="EV18" s="28"/>
-      <c r="EW18" s="28"/>
-      <c r="EX18" s="28"/>
-      <c r="EY18" s="28"/>
-      <c r="EZ18" s="28"/>
-      <c r="FA18" s="28"/>
-      <c r="FB18" s="28"/>
-      <c r="FC18" s="28"/>
-      <c r="FD18" s="28"/>
-      <c r="FE18" s="28"/>
-      <c r="FF18" s="28"/>
-      <c r="FG18" s="28"/>
-      <c r="FH18" s="28"/>
-      <c r="FI18" s="28"/>
-      <c r="FJ18" s="28"/>
-      <c r="FK18" s="28"/>
-      <c r="FL18" s="28"/>
-      <c r="FM18" s="28"/>
-      <c r="FN18" s="28"/>
-      <c r="FO18" s="28"/>
-      <c r="FP18" s="28"/>
-      <c r="FQ18" s="28"/>
-      <c r="FR18" s="28"/>
-      <c r="FS18" s="28"/>
-      <c r="FT18" s="28"/>
-      <c r="FU18" s="28"/>
-      <c r="FV18" s="28"/>
-      <c r="FW18" s="28"/>
-      <c r="FX18" s="28"/>
-      <c r="FY18" s="28"/>
-      <c r="FZ18" s="28"/>
-      <c r="GA18" s="28"/>
-      <c r="GB18" s="28"/>
-      <c r="GC18" s="28"/>
-      <c r="GD18" s="28"/>
-      <c r="GE18" s="28"/>
-      <c r="GF18" s="28"/>
-      <c r="GG18" s="28"/>
-      <c r="GH18" s="28"/>
-      <c r="GI18" s="28"/>
-      <c r="GJ18" s="28"/>
-      <c r="GK18" s="28"/>
-      <c r="GL18" s="28"/>
-      <c r="GM18" s="28"/>
-      <c r="GN18" s="28"/>
-      <c r="GO18" s="28"/>
-      <c r="GP18" s="28"/>
-      <c r="GQ18" s="28"/>
-      <c r="GR18" s="28"/>
-      <c r="GS18" s="28"/>
-      <c r="GT18" s="28"/>
-      <c r="GU18" s="28"/>
-      <c r="GV18" s="28"/>
-      <c r="GW18" s="28"/>
-      <c r="GX18" s="28"/>
-      <c r="GY18" s="28"/>
-      <c r="GZ18" s="28"/>
-      <c r="HA18" s="28"/>
-      <c r="HB18" s="28"/>
-      <c r="HC18" s="28"/>
-      <c r="HD18" s="28"/>
-      <c r="HE18" s="28"/>
-      <c r="HF18" s="28"/>
-      <c r="HG18" s="28"/>
-      <c r="HH18" s="28"/>
-      <c r="HI18" s="28"/>
-      <c r="HJ18" s="28"/>
-      <c r="HK18" s="28"/>
-      <c r="HL18" s="28"/>
-      <c r="HM18" s="28"/>
-      <c r="HN18" s="28"/>
-      <c r="HO18" s="28"/>
-      <c r="HP18" s="28"/>
-      <c r="HQ18" s="28"/>
-      <c r="HR18" s="28"/>
-      <c r="HS18" s="28"/>
-      <c r="HT18" s="28"/>
-      <c r="HU18" s="28"/>
-      <c r="HV18" s="28"/>
-      <c r="HW18" s="28"/>
-      <c r="HX18" s="28"/>
-      <c r="HY18" s="28"/>
-      <c r="HZ18" s="28"/>
-      <c r="IA18" s="28"/>
-      <c r="IB18" s="28"/>
-      <c r="IC18" s="28"/>
-      <c r="ID18" s="28"/>
-      <c r="IE18" s="28"/>
-      <c r="IF18" s="28"/>
-      <c r="IG18" s="28"/>
-      <c r="IH18" s="28"/>
-      <c r="II18" s="28"/>
-      <c r="IJ18" s="28"/>
-      <c r="IK18" s="28"/>
-      <c r="IL18" s="28"/>
-      <c r="IM18" s="28"/>
-      <c r="IN18" s="28"/>
-      <c r="IO18" s="28"/>
-      <c r="IP18" s="28"/>
-      <c r="IQ18" s="28"/>
-      <c r="IR18" s="28"/>
-      <c r="IS18" s="28"/>
-      <c r="IT18" s="28"/>
-      <c r="IU18" s="28"/>
-      <c r="IV18" s="28"/>
-      <c r="IW18" s="28"/>
-      <c r="IX18" s="28"/>
-      <c r="IY18" s="28"/>
-      <c r="IZ18" s="28"/>
-      <c r="JA18" s="28"/>
-      <c r="JB18" s="28"/>
-      <c r="JC18" s="28"/>
-      <c r="JD18" s="28"/>
-      <c r="JE18" s="28"/>
-      <c r="JF18" s="28"/>
-      <c r="JG18" s="28"/>
-      <c r="JH18" s="28"/>
-      <c r="JI18" s="28"/>
-      <c r="JJ18" s="28"/>
-      <c r="JK18" s="28"/>
-      <c r="JL18" s="28"/>
-      <c r="JM18" s="28"/>
-      <c r="JN18" s="28"/>
-    </row>
-    <row r="19" s="4" customFormat="1" ht="63.75">
-      <c r="A19" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="I19" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="O19" s="32"/>
-      <c r="P19" s="32"/>
-      <c r="Q19" s="32"/>
-      <c r="R19" s="32"/>
-      <c r="S19" s="32"/>
-      <c r="T19" s="32"/>
-      <c r="U19" s="32"/>
-      <c r="V19" s="32"/>
-      <c r="W19" s="32"/>
-      <c r="X19" s="32"/>
-      <c r="Y19" s="32"/>
-      <c r="Z19" s="32"/>
-      <c r="AA19" s="32"/>
-      <c r="AB19" s="32"/>
-      <c r="AC19" s="32"/>
-      <c r="AD19" s="32"/>
-      <c r="AE19" s="32"/>
-      <c r="AF19" s="32"/>
-      <c r="AG19" s="32"/>
-      <c r="AH19" s="32"/>
-      <c r="AI19" s="32"/>
-      <c r="AJ19" s="32"/>
-      <c r="AK19" s="32"/>
-      <c r="AL19" s="32"/>
-      <c r="AM19" s="32"/>
-      <c r="AN19" s="32"/>
-      <c r="AO19" s="32"/>
-      <c r="AP19" s="32"/>
-      <c r="AQ19" s="32"/>
-      <c r="AR19" s="32"/>
-      <c r="AS19" s="32"/>
-      <c r="AT19" s="32"/>
-      <c r="AU19" s="32"/>
-      <c r="AV19" s="32"/>
-      <c r="AW19" s="32"/>
-      <c r="AX19" s="32"/>
-      <c r="AY19" s="32"/>
-      <c r="AZ19" s="32"/>
-      <c r="BA19" s="32"/>
-      <c r="BB19" s="32"/>
-      <c r="BC19" s="32"/>
-      <c r="BD19" s="32"/>
-      <c r="BE19" s="32"/>
-      <c r="BF19" s="32"/>
-      <c r="BG19" s="32"/>
-      <c r="BH19" s="32"/>
-      <c r="BI19" s="32"/>
-      <c r="BJ19" s="32"/>
-      <c r="BK19" s="32"/>
-      <c r="BL19" s="32"/>
-      <c r="BM19" s="32"/>
-      <c r="BN19" s="32"/>
-      <c r="BO19" s="32"/>
-      <c r="BP19" s="32"/>
-      <c r="BQ19" s="32"/>
-      <c r="BR19" s="32"/>
-      <c r="BS19" s="32"/>
-      <c r="BT19" s="32"/>
-      <c r="BU19" s="32"/>
-      <c r="BV19" s="32"/>
-      <c r="BW19" s="32"/>
-      <c r="BX19" s="32"/>
-      <c r="BY19" s="32"/>
-      <c r="BZ19" s="32"/>
-      <c r="CA19" s="32"/>
-      <c r="CB19" s="32"/>
-      <c r="CC19" s="32"/>
-      <c r="CD19" s="32"/>
-      <c r="CE19" s="32"/>
-      <c r="CF19" s="32"/>
-      <c r="CG19" s="32"/>
-      <c r="CH19" s="32"/>
-      <c r="CI19" s="32"/>
-      <c r="CJ19" s="32"/>
-      <c r="CK19" s="32"/>
-      <c r="CL19" s="32"/>
-      <c r="CM19" s="32"/>
-      <c r="CN19" s="32"/>
-      <c r="CO19" s="32"/>
-      <c r="CP19" s="32"/>
-      <c r="CQ19" s="32"/>
-      <c r="CR19" s="32"/>
-      <c r="CS19" s="32"/>
-      <c r="CT19" s="32"/>
-      <c r="CU19" s="32"/>
-      <c r="CV19" s="32"/>
-      <c r="CW19" s="32"/>
-      <c r="CX19" s="32"/>
-      <c r="CY19" s="32"/>
-      <c r="CZ19" s="32"/>
-      <c r="DA19" s="32"/>
-      <c r="DB19" s="32"/>
-      <c r="DC19" s="32"/>
-      <c r="DD19" s="32"/>
-      <c r="DE19" s="32"/>
-      <c r="DF19" s="32"/>
-      <c r="DG19" s="32"/>
-      <c r="DH19" s="32"/>
-      <c r="DI19" s="32"/>
-      <c r="DJ19" s="32"/>
-      <c r="DK19" s="32"/>
-      <c r="DL19" s="32"/>
-      <c r="DM19" s="32"/>
-      <c r="DN19" s="32"/>
-      <c r="DO19" s="32"/>
-      <c r="DP19" s="32"/>
-      <c r="DQ19" s="32"/>
-      <c r="DR19" s="32"/>
-      <c r="DS19" s="32"/>
-      <c r="DT19" s="32"/>
-      <c r="DU19" s="32"/>
-      <c r="DV19" s="32"/>
-      <c r="DW19" s="32"/>
-      <c r="DX19" s="32"/>
-      <c r="DY19" s="32"/>
-      <c r="DZ19" s="32"/>
-      <c r="EA19" s="32"/>
-      <c r="EB19" s="32"/>
-      <c r="EC19" s="32"/>
-      <c r="ED19" s="32"/>
-      <c r="EE19" s="32"/>
-      <c r="EF19" s="32"/>
-      <c r="EG19" s="32"/>
-      <c r="EH19" s="32"/>
-      <c r="EI19" s="32"/>
-      <c r="EJ19" s="32"/>
-      <c r="EK19" s="32"/>
-      <c r="EL19" s="32"/>
-      <c r="EM19" s="32"/>
-      <c r="EN19" s="32"/>
-      <c r="EO19" s="32"/>
-      <c r="EP19" s="32"/>
-      <c r="EQ19" s="32"/>
-      <c r="ER19" s="32"/>
-      <c r="ES19" s="32"/>
-      <c r="ET19" s="32"/>
-      <c r="EU19" s="32"/>
-      <c r="EV19" s="32"/>
-      <c r="EW19" s="32"/>
-      <c r="EX19" s="32"/>
-      <c r="EY19" s="32"/>
-      <c r="EZ19" s="32"/>
-      <c r="FA19" s="32"/>
-      <c r="FB19" s="32"/>
-      <c r="FC19" s="32"/>
-      <c r="FD19" s="32"/>
-      <c r="FE19" s="32"/>
-      <c r="FF19" s="32"/>
-      <c r="FG19" s="32"/>
-      <c r="FH19" s="32"/>
-      <c r="FI19" s="32"/>
-      <c r="FJ19" s="32"/>
-      <c r="FK19" s="32"/>
-      <c r="FL19" s="32"/>
-      <c r="FM19" s="32"/>
-      <c r="FN19" s="32"/>
-      <c r="FO19" s="32"/>
-      <c r="FP19" s="32"/>
-      <c r="FQ19" s="32"/>
-      <c r="FR19" s="32"/>
-      <c r="FS19" s="32"/>
-      <c r="FT19" s="32"/>
-      <c r="FU19" s="32"/>
-      <c r="FV19" s="32"/>
-      <c r="FW19" s="32"/>
-      <c r="FX19" s="32"/>
-      <c r="FY19" s="32"/>
-      <c r="FZ19" s="32"/>
-      <c r="GA19" s="32"/>
-      <c r="GB19" s="32"/>
-      <c r="GC19" s="32"/>
-      <c r="GD19" s="32"/>
-      <c r="GE19" s="32"/>
-      <c r="GF19" s="32"/>
-      <c r="GG19" s="32"/>
-      <c r="GH19" s="32"/>
-      <c r="GI19" s="32"/>
-      <c r="GJ19" s="32"/>
-      <c r="GK19" s="32"/>
-      <c r="GL19" s="32"/>
-      <c r="GM19" s="32"/>
-      <c r="GN19" s="32"/>
-      <c r="GO19" s="32"/>
-      <c r="GP19" s="32"/>
-      <c r="GQ19" s="32"/>
-      <c r="GR19" s="32"/>
-      <c r="GS19" s="32"/>
-      <c r="GT19" s="32"/>
-      <c r="GU19" s="32"/>
-      <c r="GV19" s="32"/>
-      <c r="GW19" s="32"/>
-      <c r="GX19" s="32"/>
-      <c r="GY19" s="32"/>
-      <c r="GZ19" s="32"/>
-      <c r="HA19" s="32"/>
-      <c r="HB19" s="32"/>
-      <c r="HC19" s="32"/>
-      <c r="HD19" s="32"/>
-      <c r="HE19" s="32"/>
-      <c r="HF19" s="32"/>
-      <c r="HG19" s="32"/>
-      <c r="HH19" s="32"/>
-      <c r="HI19" s="32"/>
-      <c r="HJ19" s="32"/>
-      <c r="HK19" s="32"/>
-      <c r="HL19" s="32"/>
-      <c r="HM19" s="32"/>
-      <c r="HN19" s="32"/>
-      <c r="HO19" s="32"/>
-      <c r="HP19" s="32"/>
-      <c r="HQ19" s="32"/>
-      <c r="HR19" s="32"/>
-      <c r="HS19" s="32"/>
-      <c r="HT19" s="32"/>
-      <c r="HU19" s="32"/>
-      <c r="HV19" s="32"/>
-      <c r="HW19" s="32"/>
-      <c r="HX19" s="32"/>
-      <c r="HY19" s="32"/>
-      <c r="HZ19" s="32"/>
-      <c r="IA19" s="32"/>
-      <c r="IB19" s="32"/>
-      <c r="IC19" s="32"/>
-      <c r="ID19" s="32"/>
-      <c r="IE19" s="32"/>
-      <c r="IF19" s="32"/>
-      <c r="IG19" s="32"/>
-      <c r="IH19" s="32"/>
-      <c r="II19" s="32"/>
-      <c r="IJ19" s="32"/>
-      <c r="IK19" s="32"/>
-      <c r="IL19" s="32"/>
-      <c r="IM19" s="32"/>
-      <c r="IN19" s="32"/>
-      <c r="IO19" s="32"/>
-      <c r="IP19" s="32"/>
-      <c r="IQ19" s="32"/>
-      <c r="IR19" s="32"/>
-      <c r="IS19" s="32"/>
-      <c r="IT19" s="32"/>
-      <c r="IU19" s="32"/>
-      <c r="IV19" s="32"/>
-      <c r="IW19" s="32"/>
-      <c r="IX19" s="32"/>
-      <c r="IY19" s="32"/>
-      <c r="IZ19" s="32"/>
-      <c r="JA19" s="32"/>
-      <c r="JB19" s="32"/>
-      <c r="JC19" s="32"/>
-      <c r="JD19" s="32"/>
-      <c r="JE19" s="32"/>
-      <c r="JF19" s="32"/>
-      <c r="JG19" s="32"/>
-      <c r="JH19" s="32"/>
-      <c r="JI19" s="32"/>
-      <c r="JJ19" s="32"/>
-      <c r="JK19" s="32"/>
-      <c r="JL19" s="32"/>
-      <c r="JM19" s="32"/>
-      <c r="JN19" s="32"/>
-    </row>
-    <row r="20" s="33" customFormat="1" ht="28.5">
-      <c r="A20" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="E20" s="34" t="s">
+      <c r="I20" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="F20" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="G20" s="34" t="s">
+      <c r="J20" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="H20" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="36" t="s">
+      <c r="K20" s="40">
+        <v>2010</v>
+      </c>
+      <c r="L20" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="J20" s="34" t="s">
+      <c r="M20" s="37"/>
+      <c r="N20" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="K20" s="37">
-        <v>2010</v>
-      </c>
-      <c r="L20" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="M20" s="34"/>
-      <c r="N20" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="O20" s="39"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="39"/>
-      <c r="R20" s="39"/>
-      <c r="S20" s="39"/>
-      <c r="T20" s="39"/>
-      <c r="U20" s="39"/>
-      <c r="V20" s="39"/>
-      <c r="W20" s="39"/>
-      <c r="X20" s="39"/>
-      <c r="Y20" s="39"/>
-      <c r="Z20" s="39"/>
-      <c r="AA20" s="39"/>
-      <c r="AB20" s="39"/>
-      <c r="AC20" s="39"/>
-      <c r="AD20" s="39"/>
-      <c r="AE20" s="39"/>
-      <c r="AF20" s="39"/>
-      <c r="AG20" s="39"/>
-      <c r="AH20" s="39"/>
-      <c r="AI20" s="39"/>
-      <c r="AJ20" s="39"/>
-      <c r="AK20" s="39"/>
-      <c r="AL20" s="39"/>
-      <c r="AM20" s="39"/>
-      <c r="AN20" s="39"/>
-      <c r="AO20" s="39"/>
-      <c r="AP20" s="39"/>
-      <c r="AQ20" s="39"/>
-      <c r="AR20" s="39"/>
-      <c r="AS20" s="39"/>
-      <c r="AT20" s="39"/>
-      <c r="AU20" s="39"/>
-      <c r="AV20" s="39"/>
-      <c r="AW20" s="39"/>
-      <c r="AX20" s="39"/>
-      <c r="AY20" s="39"/>
-      <c r="AZ20" s="39"/>
-      <c r="BA20" s="39"/>
-      <c r="BB20" s="39"/>
-      <c r="BC20" s="39"/>
-      <c r="BD20" s="39"/>
-      <c r="BE20" s="39"/>
-      <c r="BF20" s="39"/>
-      <c r="BG20" s="39"/>
-      <c r="BH20" s="39"/>
-      <c r="BI20" s="39"/>
-      <c r="BJ20" s="39"/>
-      <c r="BK20" s="39"/>
-      <c r="BL20" s="39"/>
-      <c r="BM20" s="39"/>
-      <c r="BN20" s="39"/>
-      <c r="BO20" s="39"/>
-      <c r="BP20" s="39"/>
-      <c r="BQ20" s="39"/>
-      <c r="BR20" s="39"/>
-      <c r="BS20" s="39"/>
-      <c r="BT20" s="39"/>
-      <c r="BU20" s="39"/>
-      <c r="BV20" s="39"/>
-      <c r="BW20" s="39"/>
-      <c r="BX20" s="39"/>
-      <c r="BY20" s="39"/>
-      <c r="BZ20" s="39"/>
-      <c r="CA20" s="39"/>
-      <c r="CB20" s="39"/>
-      <c r="CC20" s="39"/>
-      <c r="CD20" s="39"/>
-      <c r="CE20" s="39"/>
-      <c r="CF20" s="39"/>
-      <c r="CG20" s="39"/>
-      <c r="CH20" s="39"/>
-      <c r="CI20" s="39"/>
-      <c r="CJ20" s="39"/>
-      <c r="CK20" s="39"/>
-      <c r="CL20" s="39"/>
-      <c r="CM20" s="39"/>
-      <c r="CN20" s="39"/>
-      <c r="CO20" s="39"/>
-      <c r="CP20" s="39"/>
-      <c r="CQ20" s="39"/>
-      <c r="CR20" s="39"/>
-      <c r="CS20" s="39"/>
-      <c r="CT20" s="39"/>
-      <c r="CU20" s="39"/>
-      <c r="CV20" s="39"/>
-      <c r="CW20" s="39"/>
-      <c r="CX20" s="39"/>
-      <c r="CY20" s="39"/>
-      <c r="CZ20" s="39"/>
-      <c r="DA20" s="39"/>
-      <c r="DB20" s="39"/>
-      <c r="DC20" s="39"/>
-      <c r="DD20" s="39"/>
-      <c r="DE20" s="39"/>
-      <c r="DF20" s="39"/>
-      <c r="DG20" s="39"/>
-      <c r="DH20" s="39"/>
-      <c r="DI20" s="39"/>
-      <c r="DJ20" s="39"/>
-      <c r="DK20" s="39"/>
-      <c r="DL20" s="39"/>
-      <c r="DM20" s="39"/>
-      <c r="DN20" s="39"/>
-      <c r="DO20" s="39"/>
-      <c r="DP20" s="39"/>
-      <c r="DQ20" s="39"/>
-      <c r="DR20" s="39"/>
-      <c r="DS20" s="39"/>
-      <c r="DT20" s="39"/>
-      <c r="DU20" s="39"/>
-      <c r="DV20" s="39"/>
-      <c r="DW20" s="39"/>
-      <c r="DX20" s="39"/>
-      <c r="DY20" s="39"/>
-      <c r="DZ20" s="39"/>
-      <c r="EA20" s="39"/>
-      <c r="EB20" s="39"/>
-      <c r="EC20" s="39"/>
-      <c r="ED20" s="39"/>
-      <c r="EE20" s="39"/>
-      <c r="EF20" s="39"/>
-      <c r="EG20" s="39"/>
-      <c r="EH20" s="39"/>
-      <c r="EI20" s="39"/>
-      <c r="EJ20" s="39"/>
-      <c r="EK20" s="39"/>
-      <c r="EL20" s="39"/>
-      <c r="EM20" s="39"/>
-      <c r="EN20" s="39"/>
-      <c r="EO20" s="39"/>
-      <c r="EP20" s="39"/>
-      <c r="EQ20" s="39"/>
-      <c r="ER20" s="39"/>
-      <c r="ES20" s="39"/>
-      <c r="ET20" s="39"/>
-      <c r="EU20" s="39"/>
-      <c r="EV20" s="39"/>
-      <c r="EW20" s="39"/>
-      <c r="EX20" s="39"/>
-      <c r="EY20" s="39"/>
-      <c r="EZ20" s="39"/>
-      <c r="FA20" s="39"/>
-      <c r="FB20" s="39"/>
-      <c r="FC20" s="39"/>
-      <c r="FD20" s="39"/>
-      <c r="FE20" s="39"/>
-      <c r="FF20" s="39"/>
-      <c r="FG20" s="39"/>
-      <c r="FH20" s="39"/>
-      <c r="FI20" s="39"/>
-      <c r="FJ20" s="39"/>
-      <c r="FK20" s="39"/>
-      <c r="FL20" s="39"/>
-      <c r="FM20" s="39"/>
-      <c r="FN20" s="39"/>
-      <c r="FO20" s="39"/>
-      <c r="FP20" s="39"/>
-      <c r="FQ20" s="39"/>
-      <c r="FR20" s="39"/>
-      <c r="FS20" s="39"/>
-      <c r="FT20" s="39"/>
-      <c r="FU20" s="39"/>
-      <c r="FV20" s="39"/>
-      <c r="FW20" s="39"/>
-      <c r="FX20" s="39"/>
-      <c r="FY20" s="39"/>
-      <c r="FZ20" s="39"/>
-      <c r="GA20" s="39"/>
-      <c r="GB20" s="39"/>
-      <c r="GC20" s="39"/>
-      <c r="GD20" s="39"/>
-      <c r="GE20" s="39"/>
-      <c r="GF20" s="39"/>
-      <c r="GG20" s="39"/>
-      <c r="GH20" s="39"/>
-      <c r="GI20" s="39"/>
-      <c r="GJ20" s="39"/>
-      <c r="GK20" s="39"/>
-      <c r="GL20" s="39"/>
-      <c r="GM20" s="39"/>
-      <c r="GN20" s="39"/>
-      <c r="GO20" s="39"/>
-      <c r="GP20" s="39"/>
-      <c r="GQ20" s="39"/>
-      <c r="GR20" s="39"/>
-      <c r="GS20" s="39"/>
-      <c r="GT20" s="39"/>
-      <c r="GU20" s="39"/>
-      <c r="GV20" s="39"/>
-      <c r="GW20" s="39"/>
-      <c r="GX20" s="39"/>
-      <c r="GY20" s="39"/>
-      <c r="GZ20" s="39"/>
-      <c r="HA20" s="39"/>
-      <c r="HB20" s="39"/>
-      <c r="HC20" s="39"/>
-      <c r="HD20" s="39"/>
-      <c r="HE20" s="39"/>
-      <c r="HF20" s="39"/>
-      <c r="HG20" s="39"/>
-      <c r="HH20" s="39"/>
-      <c r="HI20" s="39"/>
-      <c r="HJ20" s="39"/>
-      <c r="HK20" s="39"/>
-      <c r="HL20" s="39"/>
-      <c r="HM20" s="39"/>
-      <c r="HN20" s="39"/>
-      <c r="HO20" s="39"/>
-      <c r="HP20" s="39"/>
-      <c r="HQ20" s="39"/>
-      <c r="HR20" s="39"/>
-      <c r="HS20" s="39"/>
-      <c r="HT20" s="39"/>
-      <c r="HU20" s="39"/>
-      <c r="HV20" s="39"/>
-      <c r="HW20" s="39"/>
-      <c r="HX20" s="39"/>
-      <c r="HY20" s="39"/>
-      <c r="HZ20" s="39"/>
-      <c r="IA20" s="39"/>
-      <c r="IB20" s="39"/>
-      <c r="IC20" s="39"/>
-      <c r="ID20" s="39"/>
-      <c r="IE20" s="39"/>
-      <c r="IF20" s="39"/>
-      <c r="IG20" s="39"/>
-      <c r="IH20" s="39"/>
-      <c r="II20" s="39"/>
-      <c r="IJ20" s="39"/>
-      <c r="IK20" s="39"/>
-      <c r="IL20" s="39"/>
-      <c r="IM20" s="39"/>
-      <c r="IN20" s="39"/>
-      <c r="IO20" s="39"/>
-      <c r="IP20" s="39"/>
-      <c r="IQ20" s="39"/>
-      <c r="IR20" s="39"/>
-      <c r="IS20" s="39"/>
-      <c r="IT20" s="39"/>
-      <c r="IU20" s="39"/>
-      <c r="IV20" s="39"/>
-      <c r="IW20" s="39"/>
-      <c r="IX20" s="39"/>
-      <c r="IY20" s="39"/>
-      <c r="IZ20" s="39"/>
-      <c r="JA20" s="39"/>
-      <c r="JB20" s="39"/>
-      <c r="JC20" s="39"/>
-      <c r="JD20" s="39"/>
-      <c r="JE20" s="39"/>
-      <c r="JF20" s="39"/>
-      <c r="JG20" s="39"/>
-      <c r="JH20" s="39"/>
-      <c r="JI20" s="39"/>
-      <c r="JJ20" s="39"/>
-      <c r="JK20" s="39"/>
-      <c r="JL20" s="39"/>
-      <c r="JM20" s="39"/>
-      <c r="JN20" s="39"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42"/>
+      <c r="T20" s="42"/>
+      <c r="U20" s="42"/>
+      <c r="V20" s="42"/>
+      <c r="W20" s="42"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="42"/>
+      <c r="Z20" s="42"/>
+      <c r="AA20" s="42"/>
+      <c r="AB20" s="42"/>
+      <c r="AC20" s="42"/>
+      <c r="AD20" s="42"/>
+      <c r="AE20" s="42"/>
+      <c r="AF20" s="42"/>
+      <c r="AG20" s="42"/>
+      <c r="AH20" s="42"/>
+      <c r="AI20" s="42"/>
+      <c r="AJ20" s="42"/>
+      <c r="AK20" s="42"/>
+      <c r="AL20" s="42"/>
+      <c r="AM20" s="42"/>
+      <c r="AN20" s="42"/>
+      <c r="AO20" s="42"/>
+      <c r="AP20" s="42"/>
+      <c r="AQ20" s="42"/>
+      <c r="AR20" s="42"/>
+      <c r="AS20" s="42"/>
+      <c r="AT20" s="42"/>
+      <c r="AU20" s="42"/>
+      <c r="AV20" s="42"/>
+      <c r="AW20" s="42"/>
+      <c r="AX20" s="42"/>
+      <c r="AY20" s="42"/>
+      <c r="AZ20" s="42"/>
+      <c r="BA20" s="42"/>
+      <c r="BB20" s="42"/>
+      <c r="BC20" s="42"/>
+      <c r="BD20" s="42"/>
+      <c r="BE20" s="42"/>
+      <c r="BF20" s="42"/>
+      <c r="BG20" s="42"/>
+      <c r="BH20" s="42"/>
+      <c r="BI20" s="42"/>
+      <c r="BJ20" s="42"/>
+      <c r="BK20" s="42"/>
+      <c r="BL20" s="42"/>
+      <c r="BM20" s="42"/>
+      <c r="BN20" s="42"/>
+      <c r="BO20" s="42"/>
+      <c r="BP20" s="42"/>
+      <c r="BQ20" s="42"/>
+      <c r="BR20" s="42"/>
+      <c r="BS20" s="42"/>
+      <c r="BT20" s="42"/>
+      <c r="BU20" s="42"/>
+      <c r="BV20" s="42"/>
+      <c r="BW20" s="42"/>
+      <c r="BX20" s="42"/>
+      <c r="BY20" s="42"/>
+      <c r="BZ20" s="42"/>
+      <c r="CA20" s="42"/>
+      <c r="CB20" s="42"/>
+      <c r="CC20" s="42"/>
+      <c r="CD20" s="42"/>
+      <c r="CE20" s="42"/>
+      <c r="CF20" s="42"/>
+      <c r="CG20" s="42"/>
+      <c r="CH20" s="42"/>
+      <c r="CI20" s="42"/>
+      <c r="CJ20" s="42"/>
+      <c r="CK20" s="42"/>
+      <c r="CL20" s="42"/>
+      <c r="CM20" s="42"/>
+      <c r="CN20" s="42"/>
+      <c r="CO20" s="42"/>
+      <c r="CP20" s="42"/>
+      <c r="CQ20" s="42"/>
+      <c r="CR20" s="42"/>
+      <c r="CS20" s="42"/>
+      <c r="CT20" s="42"/>
+      <c r="CU20" s="42"/>
+      <c r="CV20" s="42"/>
+      <c r="CW20" s="42"/>
+      <c r="CX20" s="42"/>
+      <c r="CY20" s="42"/>
+      <c r="CZ20" s="42"/>
+      <c r="DA20" s="42"/>
+      <c r="DB20" s="42"/>
+      <c r="DC20" s="42"/>
+      <c r="DD20" s="42"/>
+      <c r="DE20" s="42"/>
+      <c r="DF20" s="42"/>
+      <c r="DG20" s="42"/>
+      <c r="DH20" s="42"/>
+      <c r="DI20" s="42"/>
+      <c r="DJ20" s="42"/>
+      <c r="DK20" s="42"/>
+      <c r="DL20" s="42"/>
+      <c r="DM20" s="42"/>
+      <c r="DN20" s="42"/>
+      <c r="DO20" s="42"/>
+      <c r="DP20" s="42"/>
+      <c r="DQ20" s="42"/>
+      <c r="DR20" s="42"/>
+      <c r="DS20" s="42"/>
+      <c r="DT20" s="42"/>
+      <c r="DU20" s="42"/>
+      <c r="DV20" s="42"/>
+      <c r="DW20" s="42"/>
+      <c r="DX20" s="42"/>
+      <c r="DY20" s="42"/>
+      <c r="DZ20" s="42"/>
+      <c r="EA20" s="42"/>
+      <c r="EB20" s="42"/>
+      <c r="EC20" s="42"/>
+      <c r="ED20" s="42"/>
+      <c r="EE20" s="42"/>
+      <c r="EF20" s="42"/>
+      <c r="EG20" s="42"/>
+      <c r="EH20" s="42"/>
+      <c r="EI20" s="42"/>
+      <c r="EJ20" s="42"/>
+      <c r="EK20" s="42"/>
+      <c r="EL20" s="42"/>
+      <c r="EM20" s="42"/>
+      <c r="EN20" s="42"/>
+      <c r="EO20" s="42"/>
+      <c r="EP20" s="42"/>
+      <c r="EQ20" s="42"/>
+      <c r="ER20" s="42"/>
+      <c r="ES20" s="42"/>
+      <c r="ET20" s="42"/>
+      <c r="EU20" s="42"/>
+      <c r="EV20" s="42"/>
+      <c r="EW20" s="42"/>
+      <c r="EX20" s="42"/>
+      <c r="EY20" s="42"/>
+      <c r="EZ20" s="42"/>
+      <c r="FA20" s="42"/>
+      <c r="FB20" s="42"/>
+      <c r="FC20" s="42"/>
+      <c r="FD20" s="42"/>
+      <c r="FE20" s="42"/>
+      <c r="FF20" s="42"/>
+      <c r="FG20" s="42"/>
+      <c r="FH20" s="42"/>
+      <c r="FI20" s="42"/>
+      <c r="FJ20" s="42"/>
+      <c r="FK20" s="42"/>
+      <c r="FL20" s="42"/>
+      <c r="FM20" s="42"/>
+      <c r="FN20" s="42"/>
+      <c r="FO20" s="42"/>
+      <c r="FP20" s="42"/>
+      <c r="FQ20" s="42"/>
+      <c r="FR20" s="42"/>
+      <c r="FS20" s="42"/>
+      <c r="FT20" s="42"/>
+      <c r="FU20" s="42"/>
+      <c r="FV20" s="42"/>
+      <c r="FW20" s="42"/>
+      <c r="FX20" s="42"/>
+      <c r="FY20" s="42"/>
+      <c r="FZ20" s="42"/>
+      <c r="GA20" s="42"/>
+      <c r="GB20" s="42"/>
+      <c r="GC20" s="42"/>
+      <c r="GD20" s="42"/>
+      <c r="GE20" s="42"/>
+      <c r="GF20" s="42"/>
+      <c r="GG20" s="42"/>
+      <c r="GH20" s="42"/>
+      <c r="GI20" s="42"/>
+      <c r="GJ20" s="42"/>
+      <c r="GK20" s="42"/>
+      <c r="GL20" s="42"/>
+      <c r="GM20" s="42"/>
+      <c r="GN20" s="42"/>
+      <c r="GO20" s="42"/>
+      <c r="GP20" s="42"/>
+      <c r="GQ20" s="42"/>
+      <c r="GR20" s="42"/>
+      <c r="GS20" s="42"/>
+      <c r="GT20" s="42"/>
+      <c r="GU20" s="42"/>
+      <c r="GV20" s="42"/>
+      <c r="GW20" s="42"/>
+      <c r="GX20" s="42"/>
+      <c r="GY20" s="42"/>
+      <c r="GZ20" s="42"/>
+      <c r="HA20" s="42"/>
+      <c r="HB20" s="42"/>
+      <c r="HC20" s="42"/>
+      <c r="HD20" s="42"/>
+      <c r="HE20" s="42"/>
+      <c r="HF20" s="42"/>
+      <c r="HG20" s="42"/>
+      <c r="HH20" s="42"/>
+      <c r="HI20" s="42"/>
+      <c r="HJ20" s="42"/>
+      <c r="HK20" s="42"/>
+      <c r="HL20" s="42"/>
+      <c r="HM20" s="42"/>
+      <c r="HN20" s="42"/>
+      <c r="HO20" s="42"/>
+      <c r="HP20" s="42"/>
+      <c r="HQ20" s="42"/>
+      <c r="HR20" s="42"/>
+      <c r="HS20" s="42"/>
+      <c r="HT20" s="42"/>
+      <c r="HU20" s="42"/>
+      <c r="HV20" s="42"/>
+      <c r="HW20" s="42"/>
+      <c r="HX20" s="42"/>
+      <c r="HY20" s="42"/>
+      <c r="HZ20" s="42"/>
+      <c r="IA20" s="42"/>
+      <c r="IB20" s="42"/>
+      <c r="IC20" s="42"/>
+      <c r="ID20" s="42"/>
+      <c r="IE20" s="42"/>
+      <c r="IF20" s="42"/>
+      <c r="IG20" s="42"/>
+      <c r="IH20" s="42"/>
+      <c r="II20" s="42"/>
+      <c r="IJ20" s="42"/>
+      <c r="IK20" s="42"/>
+      <c r="IL20" s="42"/>
+      <c r="IM20" s="42"/>
+      <c r="IN20" s="42"/>
+      <c r="IO20" s="42"/>
+      <c r="IP20" s="42"/>
+      <c r="IQ20" s="42"/>
+      <c r="IR20" s="42"/>
+      <c r="IS20" s="42"/>
+      <c r="IT20" s="42"/>
+      <c r="IU20" s="42"/>
+      <c r="IV20" s="42"/>
+      <c r="IW20" s="42"/>
+      <c r="IX20" s="42"/>
+      <c r="IY20" s="42"/>
+      <c r="IZ20" s="42"/>
+      <c r="JA20" s="42"/>
+      <c r="JB20" s="42"/>
+      <c r="JC20" s="42"/>
+      <c r="JD20" s="42"/>
+      <c r="JE20" s="42"/>
+      <c r="JF20" s="42"/>
+      <c r="JG20" s="42"/>
+      <c r="JH20" s="42"/>
+      <c r="JI20" s="42"/>
+      <c r="JJ20" s="42"/>
+      <c r="JK20" s="42"/>
+      <c r="JL20" s="42"/>
+      <c r="JM20" s="42"/>
+      <c r="JN20" s="42"/>
     </row>
     <row r="21" ht="25.5">
-      <c r="A21" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="34" t="s">
+      <c r="A21" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="F21" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="E21" s="34" t="s">
+      <c r="J21" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="K21" s="40">
+        <v>2010</v>
+      </c>
+      <c r="L21" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="M21" s="37"/>
+      <c r="N21" s="44" t="s">
         <v>171</v>
-      </c>
-      <c r="F21" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="J21" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="K21" s="37">
-        <v>2010</v>
-      </c>
-      <c r="L21" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="M21" s="34"/>
-      <c r="N21" s="41" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="22" ht="25.5">
-      <c r="A22" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="D22" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F22" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34" t="s">
+      <c r="A22" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="J22" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="K22" s="37">
+      <c r="I22" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="K22" s="40">
         <v>2010</v>
       </c>
-      <c r="L22" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="M22" s="34"/>
-      <c r="N22" s="41"/>
+      <c r="L22" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="M22" s="37"/>
+      <c r="N22" s="44"/>
     </row>
     <row r="23" ht="25.5">
-      <c r="A23" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="B23" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="D23" s="34" t="s">
+      <c r="A23" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="46"/>
+      <c r="H23" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="E23" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="F23" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="G23" s="43"/>
-      <c r="H23" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="I23" s="36" t="s">
-        <v>179</v>
-      </c>
-      <c r="J23" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="K23" s="37">
+      <c r="J23" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="K23" s="40">
         <v>2010</v>
       </c>
-      <c r="L23" s="34" t="s">
+      <c r="L23" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="M23" s="34"/>
-      <c r="N23" s="41"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="44"/>
     </row>
     <row r="24" ht="25.5">
-      <c r="A24" s="44" t="s">
+      <c r="A24" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="B24" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="47" t="s">
+        <v>178</v>
+      </c>
+      <c r="D24" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="E24" s="47" t="s">
         <v>180</v>
       </c>
-      <c r="B24" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="44" t="s">
+      <c r="F24" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="E24" s="44" t="s">
+      <c r="J24" s="47"/>
+      <c r="K24" s="47">
+        <v>2016</v>
+      </c>
+      <c r="L24" s="47" t="s">
         <v>183</v>
       </c>
-      <c r="F24" s="45" t="s">
-        <v>184</v>
-      </c>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="46" t="s">
-        <v>185</v>
-      </c>
-      <c r="J24" s="44"/>
-      <c r="K24" s="44">
-        <v>2016</v>
-      </c>
-      <c r="L24" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="M24" s="44"/>
-      <c r="N24" s="21"/>
+      <c r="M24" s="47"/>
+      <c r="N24" s="26"/>
     </row>
     <row r="25" ht="25.5">
-      <c r="A25" s="44" t="s">
+      <c r="A25" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="B25" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>178</v>
+      </c>
+      <c r="D25" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" s="47" t="s">
         <v>180</v>
       </c>
-      <c r="B25" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="44" t="s">
-        <v>181</v>
-      </c>
-      <c r="D25" s="44" t="s">
-        <v>187</v>
-      </c>
-      <c r="E25" s="44" t="s">
-        <v>183</v>
-      </c>
-      <c r="F25" s="45"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="44"/>
-      <c r="L25" s="44"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="21"/>
+      <c r="F25" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="47"/>
+      <c r="N25" s="26"/>
     </row>
     <row r="26" ht="25.5">
-      <c r="A26" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="B26" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="44" t="s">
+      <c r="A26" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="D26" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" s="47" t="s">
         <v>188</v>
       </c>
-      <c r="D26" s="44" t="s">
+      <c r="F26" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="E26" s="44" t="s">
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="49" t="s">
         <v>190</v>
       </c>
-      <c r="F26" s="44" t="s">
-        <v>191</v>
-      </c>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="46" t="s">
-        <v>192</v>
-      </c>
-      <c r="J26" s="49"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="21"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="47"/>
+      <c r="N26" s="26"/>
     </row>
     <row r="27" ht="38.25">
-      <c r="A27" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="B27" s="44" t="s">
+      <c r="A27" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="B27" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C27" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="D27" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="F27" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="E27" s="44" t="s">
+      <c r="G27" s="47" t="s">
         <v>194</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="H27" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="54" t="s">
         <v>195</v>
       </c>
-      <c r="G27" s="44" t="s">
+      <c r="J27" s="47" t="s">
         <v>196</v>
       </c>
-      <c r="H27" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="51" t="s">
+      <c r="K27" s="47"/>
+      <c r="L27" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="M27" s="47"/>
+      <c r="N27" s="55" t="s">
         <v>197</v>
-      </c>
-      <c r="J27" s="44" t="s">
-        <v>198</v>
-      </c>
-      <c r="K27" s="44"/>
-      <c r="L27" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="M27" s="44"/>
-      <c r="N27" s="52" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="28" ht="89.25">
-      <c r="A28" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="B28" s="44" t="s">
+      <c r="A28" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="44" t="s">
+      <c r="C28" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="44" t="s">
+      <c r="D28" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="F28" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="G28" s="47" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="44" t="s">
+      <c r="H28" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="J28" s="47" t="s">
         <v>201</v>
       </c>
-      <c r="F28" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="G28" s="44" t="s">
-        <v>202</v>
-      </c>
-      <c r="H28" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="J28" s="44" t="s">
-        <v>88</v>
-      </c>
-      <c r="K28" s="44" t="s">
-        <v>140</v>
-      </c>
-      <c r="L28" s="44" t="s">
+      <c r="K28" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="L28" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="M28" s="44"/>
-      <c r="N28" s="52" t="s">
-        <v>199</v>
+      <c r="M28" s="47"/>
+      <c r="N28" s="55" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="53" t="s">
+      <c r="A29" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B29" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="B29" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="53" t="s">
+      <c r="E29" s="56" t="s">
         <v>204</v>
       </c>
-      <c r="E29" s="53" t="s">
+      <c r="F29" s="57"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="58" t="s">
         <v>205</v>
       </c>
-      <c r="F29" s="54"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="53"/>
-      <c r="I29" s="55" t="s">
+      <c r="J29" s="59"/>
+      <c r="K29" s="56"/>
+      <c r="L29" s="56" t="s">
         <v>206</v>
       </c>
-      <c r="J29" s="56"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="53" t="s">
-        <v>207</v>
-      </c>
-      <c r="M29" s="53"/>
-      <c r="N29" s="28"/>
+      <c r="M29" s="56"/>
+      <c r="N29" s="32"/>
     </row>
     <row r="30" ht="25.5">
-      <c r="A30" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="B30" s="53" t="s">
+      <c r="A30" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B30" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="53" t="s">
+      <c r="D30" s="56" t="s">
+        <v>207</v>
+      </c>
+      <c r="E30" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="F30" s="57"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="58" t="s">
         <v>208</v>
       </c>
-      <c r="E30" s="53" t="s">
-        <v>205</v>
-      </c>
-      <c r="F30" s="54"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="55" t="s">
-        <v>209</v>
-      </c>
-      <c r="J30" s="53"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="53"/>
-      <c r="M30" s="53"/>
-      <c r="N30" s="28"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="32"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="B31" s="53" t="s">
+      <c r="A31" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B31" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="53" t="s">
-        <v>210</v>
-      </c>
-      <c r="E31" s="53" t="s">
+      <c r="D31" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="E31" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="F31" s="57"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="58" t="s">
         <v>205</v>
       </c>
-      <c r="F31" s="54"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="55" t="s">
+      <c r="J31" s="59"/>
+      <c r="K31" s="56"/>
+      <c r="L31" s="56" t="s">
         <v>206</v>
       </c>
-      <c r="J31" s="56"/>
-      <c r="K31" s="53"/>
-      <c r="L31" s="53" t="s">
-        <v>207</v>
-      </c>
-      <c r="M31" s="53"/>
-      <c r="N31" s="28"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="32"/>
     </row>
     <row r="32" ht="25.5">
-      <c r="A32" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="B32" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="53" t="s">
-        <v>169</v>
-      </c>
-      <c r="D32" s="53" t="s">
+      <c r="A32" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B32" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="56" t="s">
+        <v>167</v>
+      </c>
+      <c r="D32" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="E32" s="56"/>
+      <c r="F32" s="57" t="s">
         <v>211</v>
       </c>
-      <c r="E32" s="53"/>
-      <c r="F32" s="54" t="s">
-        <v>212</v>
-      </c>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="53"/>
-      <c r="M32" s="53"/>
-      <c r="N32" s="28"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="32"/>
     </row>
     <row r="33" ht="25.5">
-      <c r="A33" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="B33" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="53" t="s">
-        <v>188</v>
-      </c>
-      <c r="D33" s="53" t="s">
-        <v>213</v>
-      </c>
-      <c r="E33" s="53" t="s">
-        <v>205</v>
-      </c>
-      <c r="F33" s="54"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="28"/>
+      <c r="A33" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="56" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" s="56" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="F33" s="57"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="56"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="32"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="B34" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="53" t="s">
-        <v>188</v>
-      </c>
-      <c r="D34" s="53" t="s">
+      <c r="A34" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B34" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="56" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="E34" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="F34" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="E34" s="53" t="s">
-        <v>205</v>
-      </c>
-      <c r="F34" s="54" t="s">
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="61" t="s">
         <v>215</v>
       </c>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="J34" s="53"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="28"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="56"/>
+      <c r="N34" s="32"/>
     </row>
     <row r="35" ht="38.25">
-      <c r="A35" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="B35" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" s="53" t="s">
+      <c r="A35" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B35" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="D35" s="56" t="s">
         <v>217</v>
       </c>
-      <c r="D35" s="53" t="s">
+      <c r="E35" s="56" t="s">
         <v>218</v>
       </c>
-      <c r="E35" s="53" t="s">
+      <c r="F35" s="57" t="s">
         <v>219</v>
       </c>
-      <c r="F35" s="54" t="s">
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="58" t="s">
         <v>220</v>
       </c>
-      <c r="G35" s="53"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="55" t="s">
-        <v>221</v>
-      </c>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53" t="s">
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="M35" s="53"/>
-      <c r="N35" s="28"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="32"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="B36" s="53" t="s">
+      <c r="A36" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B36" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="53" t="s">
+      <c r="C36" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="D36" s="56" t="s">
         <v>222</v>
       </c>
-      <c r="D36" s="53" t="s">
+      <c r="E36" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="56"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="56" t="s">
         <v>223</v>
-      </c>
-      <c r="E36" s="53" t="s">
-        <v>205</v>
-      </c>
-      <c r="F36" s="53"/>
-      <c r="G36" s="53"/>
-      <c r="H36" s="53"/>
-      <c r="I36" s="53"/>
-      <c r="J36" s="53"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="53"/>
-      <c r="N36" s="53" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="B37" s="53" t="s">
+      <c r="A37" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B37" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="53" t="s">
-        <v>222</v>
-      </c>
-      <c r="D37" s="53" t="s">
-        <v>225</v>
-      </c>
-      <c r="E37" s="53" t="s">
-        <v>205</v>
-      </c>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="53"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="53"/>
-      <c r="N37" s="53" t="s">
+      <c r="C37" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="D37" s="56" t="s">
         <v>224</v>
+      </c>
+      <c r="E37" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="56"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="56"/>
+      <c r="N37" s="56" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="38" ht="51">
-      <c r="A38" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="B38" s="53" t="s">
+      <c r="A38" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B38" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="53" t="s">
+      <c r="C38" s="56" t="s">
+        <v>225</v>
+      </c>
+      <c r="D38" s="56" t="s">
         <v>226</v>
       </c>
-      <c r="D38" s="53" t="s">
+      <c r="E38" s="56" t="s">
         <v>227</v>
       </c>
-      <c r="E38" s="53" t="s">
+      <c r="F38" s="62" t="s">
         <v>228</v>
       </c>
-      <c r="F38" s="59" t="s">
-        <v>229</v>
-      </c>
-      <c r="G38" s="53"/>
-      <c r="H38" s="53"/>
-      <c r="I38" s="53"/>
-      <c r="J38" s="53"/>
-      <c r="K38" s="53"/>
-      <c r="L38" s="53"/>
-      <c r="M38" s="53"/>
-      <c r="N38" s="53" t="s">
-        <v>224</v>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="56"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="56" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="39" ht="25.5">
-      <c r="A39" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="B39" s="53" t="s">
+      <c r="A39" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B39" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="53" t="s">
+      <c r="C39" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="D39" s="53" t="s">
-        <v>230</v>
-      </c>
-      <c r="E39" s="53" t="s">
-        <v>205</v>
-      </c>
-      <c r="F39" s="53"/>
-      <c r="G39" s="53"/>
-      <c r="H39" s="53"/>
-      <c r="I39" s="53"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="53"/>
-      <c r="L39" s="53"/>
-      <c r="M39" s="53"/>
-      <c r="N39" s="53" t="s">
-        <v>224</v>
+      <c r="D39" s="56" t="s">
+        <v>229</v>
+      </c>
+      <c r="E39" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="56"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="56"/>
+      <c r="N39" s="56" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="40" ht="38.25">
-      <c r="A40" s="60" t="s">
+      <c r="A40" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B40" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" s="63" t="s">
         <v>231</v>
       </c>
-      <c r="B40" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" s="60" t="s">
+      <c r="E40" s="63" t="s">
         <v>232</v>
       </c>
-      <c r="E40" s="60" t="s">
+      <c r="F40" s="63"/>
+      <c r="G40" s="63" t="s">
         <v>233</v>
       </c>
-      <c r="F40" s="60"/>
-      <c r="G40" s="60" t="s">
-        <v>234</v>
-      </c>
-      <c r="H40" s="60" t="s">
+      <c r="H40" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="I40" s="60"/>
-      <c r="J40" s="60"/>
-      <c r="K40" s="60"/>
-      <c r="L40" s="60"/>
-      <c r="M40" s="60"/>
-      <c r="N40" s="60"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="63"/>
+      <c r="K40" s="63"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="63"/>
     </row>
     <row r="41" ht="38.25">
-      <c r="A41" s="60" t="s">
-        <v>231</v>
-      </c>
-      <c r="B41" s="60" t="s">
+      <c r="A41" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B41" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="60" t="s">
-        <v>135</v>
-      </c>
-      <c r="D41" s="60" t="s">
+      <c r="C41" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" s="63" t="s">
+        <v>234</v>
+      </c>
+      <c r="E41" s="63" t="s">
         <v>235</v>
       </c>
-      <c r="E41" s="60" t="s">
+      <c r="F41" s="63"/>
+      <c r="G41" s="63" t="s">
         <v>236</v>
       </c>
-      <c r="F41" s="60"/>
-      <c r="G41" s="60" t="s">
-        <v>237</v>
-      </c>
-      <c r="H41" s="60" t="s">
+      <c r="H41" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="I41" s="60"/>
-      <c r="J41" s="60"/>
-      <c r="K41" s="60"/>
-      <c r="L41" s="60"/>
-      <c r="M41" s="60"/>
-      <c r="N41" s="60"/>
+      <c r="I41" s="63"/>
+      <c r="J41" s="63"/>
+      <c r="K41" s="63"/>
+      <c r="L41" s="63"/>
+      <c r="M41" s="63"/>
+      <c r="N41" s="63"/>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="60" t="s">
-        <v>231</v>
-      </c>
-      <c r="B42" s="60" t="s">
+      <c r="A42" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B42" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="60" t="s">
-        <v>135</v>
-      </c>
-      <c r="D42" s="60" t="s">
+      <c r="C42" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" s="63" t="s">
+        <v>237</v>
+      </c>
+      <c r="E42" s="63" t="s">
         <v>238</v>
       </c>
-      <c r="E42" s="60" t="s">
+      <c r="F42" s="63"/>
+      <c r="G42" s="63" t="s">
         <v>239</v>
       </c>
-      <c r="F42" s="60"/>
-      <c r="G42" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="H42" s="60" t="s">
+      <c r="H42" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="I42" s="61"/>
-      <c r="J42" s="60"/>
-      <c r="K42" s="60"/>
-      <c r="L42" s="60"/>
-      <c r="M42" s="60"/>
-      <c r="N42" s="60"/>
+      <c r="I42" s="64"/>
+      <c r="J42" s="63"/>
+      <c r="K42" s="63"/>
+      <c r="L42" s="63"/>
+      <c r="M42" s="63"/>
+      <c r="N42" s="63"/>
     </row>
     <row r="43" ht="14.25">
       <c r="A43" s="1"/>
-      <c r="M43" s="62"/>
-      <c r="N43" s="62"/>
+      <c r="M43" s="65"/>
+      <c r="N43" s="65"/>
     </row>
     <row r="44" ht="14.25">
-      <c r="M44" s="62"/>
-      <c r="N44" s="62"/>
+      <c r="M44" s="65"/>
+      <c r="N44" s="65"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="M45" s="62"/>
-      <c r="N45" s="62"/>
+      <c r="M45" s="65"/>
+      <c r="N45" s="65"/>
     </row>
     <row r="46" ht="14.25">
-      <c r="M46" s="62"/>
-      <c r="N46" s="62"/>
+      <c r="M46" s="65"/>
+      <c r="N46" s="65"/>
     </row>
     <row r="47" ht="14.25">
-      <c r="M47" s="62"/>
-      <c r="N47" s="62"/>
+      <c r="M47" s="65"/>
+      <c r="N47" s="65"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="M48" s="62"/>
-      <c r="N48" s="62"/>
+      <c r="M48" s="65"/>
+      <c r="N48" s="65"/>
     </row>
     <row r="49" ht="14.25">
-      <c r="M49" s="62"/>
-      <c r="N49" s="62"/>
+      <c r="M49" s="65"/>
+      <c r="N49" s="65"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="M50" s="62"/>
-      <c r="N50" s="62"/>
+      <c r="M50" s="65"/>
+      <c r="N50" s="65"/>
     </row>
     <row r="51" ht="14.25">
-      <c r="M51" s="62"/>
-      <c r="N51" s="62"/>
+      <c r="M51" s="65"/>
+      <c r="N51" s="65"/>
     </row>
     <row r="52" ht="14.25">
-      <c r="M52" s="62"/>
-      <c r="N52" s="62"/>
+      <c r="M52" s="65"/>
+      <c r="N52" s="65"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="M53" s="62"/>
-      <c r="N53" s="62"/>
+      <c r="M53" s="65"/>
+      <c r="N53" s="65"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="M54" s="62"/>
-      <c r="N54" s="62"/>
+      <c r="M54" s="65"/>
+      <c r="N54" s="65"/>
     </row>
     <row r="55" ht="14.25">
-      <c r="M55" s="62"/>
-      <c r="N55" s="62"/>
+      <c r="M55" s="65"/>
+      <c r="N55" s="65"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="M56" s="62"/>
-      <c r="N56" s="62"/>
+      <c r="M56" s="65"/>
+      <c r="N56" s="65"/>
     </row>
     <row r="57" ht="14.25">
-      <c r="M57" s="62"/>
-      <c r="N57" s="62"/>
+      <c r="M57" s="65"/>
+      <c r="N57" s="65"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N20">
@@ -8611,31 +8581,30 @@
     <hyperlink r:id="rId5" ref="I6"/>
     <hyperlink r:id="rId6" ref="I7"/>
     <hyperlink r:id="rId7" ref="I8"/>
-    <hyperlink r:id="rId8" ref="M8"/>
-    <hyperlink r:id="rId9" location="c=indicator&amp;i=stru_2020_1.nbexpl20&amp;t=A02&amp;view=map11" ref="I9"/>
-    <hyperlink r:id="rId10" ref="I10"/>
-    <hyperlink r:id="rId11" ref="I11"/>
-    <hyperlink r:id="rId12" ref="I12"/>
-    <hyperlink r:id="rId9" location="c=indicator&amp;i=stru_2020_1.pbs20&amp;t=A02&amp;view=map11" ref="I13"/>
-    <hyperlink r:id="rId13" ref="I14"/>
-    <hyperlink r:id="rId14" ref="I15"/>
-    <hyperlink r:id="rId7" ref="I16"/>
-    <hyperlink r:id="rId15" ref="I17"/>
-    <hyperlink r:id="rId7" ref="I18"/>
-    <hyperlink r:id="rId7" ref="I19"/>
-    <hyperlink r:id="rId16" ref="I20"/>
-    <hyperlink r:id="rId9" location="c=indicator&amp;i=stru2.partssucnb10&amp;t=A01&amp;view=map2" ref="I21"/>
-    <hyperlink r:id="rId17" ref="I22"/>
-    <hyperlink r:id="rId18" ref="I23"/>
-    <hyperlink r:id="rId19" ref="I24"/>
-    <hyperlink r:id="rId20" ref="I26"/>
-    <hyperlink r:id="rId21" ref="I27"/>
+    <hyperlink r:id="rId7" ref="I9"/>
+    <hyperlink r:id="rId7" ref="I10"/>
+    <hyperlink r:id="rId7" ref="I11"/>
+    <hyperlink r:id="rId8" location="c=indicator&amp;i=stru_2020_1.nbexpl20&amp;t=A02&amp;view=map11" ref="I12"/>
+    <hyperlink r:id="rId9" ref="I13"/>
+    <hyperlink r:id="rId10" ref="I14"/>
+    <hyperlink r:id="rId11" ref="I15"/>
+    <hyperlink r:id="rId8" location="c=indicator&amp;i=stru_2020_1.pbs20&amp;t=A02&amp;view=map11" ref="I16"/>
+    <hyperlink r:id="rId12" ref="I17"/>
+    <hyperlink r:id="rId13" ref="I18"/>
+    <hyperlink r:id="rId14" ref="I19"/>
+    <hyperlink r:id="rId15" ref="I20"/>
+    <hyperlink r:id="rId8" location="c=indicator&amp;i=stru2.partssucnb10&amp;t=A01&amp;view=map2" ref="I21"/>
+    <hyperlink r:id="rId16" ref="I22"/>
+    <hyperlink r:id="rId17" ref="I23"/>
+    <hyperlink r:id="rId18" ref="I24"/>
+    <hyperlink r:id="rId19" ref="I26"/>
+    <hyperlink r:id="rId20" ref="I27"/>
     <hyperlink r:id="rId7" ref="I28"/>
-    <hyperlink r:id="rId22" ref="I29"/>
-    <hyperlink r:id="rId23" ref="I30"/>
-    <hyperlink r:id="rId22" ref="I31"/>
-    <hyperlink r:id="rId24" ref="I34"/>
-    <hyperlink r:id="rId25" ref="I35"/>
+    <hyperlink r:id="rId21" ref="I29"/>
+    <hyperlink r:id="rId22" ref="I30"/>
+    <hyperlink r:id="rId21" ref="I31"/>
+    <hyperlink r:id="rId23" ref="I34"/>
+    <hyperlink r:id="rId24" ref="I35"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -8653,60 +8622,60 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="66" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="66" t="s">
         <v>241</v>
-      </c>
-      <c r="B1" s="63" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="2" s="0" customFormat="1" ht="14.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="65" t="s">
-        <v>243</v>
+      <c r="B2" s="68" t="s">
+        <v>242</v>
       </c>
       <c r="C2"/>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="17" t="s">
-        <v>80</v>
+      <c r="A3" s="21" t="s">
+        <v>106</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="34" t="s">
-        <v>161</v>
+      <c r="A4" s="37" t="s">
+        <v>159</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="44" t="s">
-        <v>180</v>
+      <c r="A5" s="47" t="s">
+        <v>177</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="53" t="s">
-        <v>203</v>
+      <c r="A6" s="56" t="s">
+        <v>202</v>
       </c>
       <c r="B6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="60" t="s">
-        <v>231</v>
+      <c r="A7" s="63" t="s">
+        <v>230</v>
       </c>
       <c r="B7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -8729,20 +8698,20 @@
     <col customWidth="1" min="6" max="6" width="12.8515625"/>
     <col bestFit="1" customWidth="1" min="7" max="7" width="25.78125"/>
     <col bestFit="1" customWidth="1" min="8" max="8" width="21.3515625"/>
-    <col customWidth="1" min="9" max="9" style="66" width="32.7109375"/>
+    <col customWidth="1" min="9" max="9" style="69" width="32.7109375"/>
     <col customWidth="1" min="10" max="10" width="23.57421875"/>
     <col customWidth="1" min="11" max="11" width="44.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" s="63" customFormat="1" ht="25.5">
-      <c r="A1" s="63" t="s">
+    <row r="1" s="66" customFormat="1" ht="25.5">
+      <c r="A1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="66" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1" s="66" t="s">
         <v>249</v>
-      </c>
-      <c r="C1" s="63" t="s">
-        <v>250</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>9</v>
@@ -8759,49 +8728,49 @@
       <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="67" t="s">
+      <c r="I1" s="70" t="s">
+        <v>250</v>
+      </c>
+      <c r="J1" s="66" t="s">
         <v>251</v>
       </c>
-      <c r="J1" s="63" t="s">
+      <c r="K1" s="66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="71" customFormat="1" ht="28.5">
+      <c r="A2" s="72" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="73" t="s">
         <v>252</v>
       </c>
-      <c r="K1" s="63" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" s="68" customFormat="1" ht="28.5">
-      <c r="A2" s="69" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="70" t="s">
+      <c r="C2" s="72" t="s">
         <v>253</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="D2" s="73" t="s">
         <v>254</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="E2" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="F2" s="73" t="s">
         <v>256</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="G2" s="71" t="s">
         <v>257</v>
       </c>
-      <c r="G2" s="71" t="s">
+      <c r="H2" s="72" t="s">
         <v>258</v>
       </c>
-      <c r="H2" s="69" t="s">
+      <c r="I2" s="74" t="s">
         <v>259</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="J2" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="J2" s="68" t="s">
+      <c r="K2" s="75" t="s">
         <v>261</v>
-      </c>
-      <c r="K2" s="73" t="s">
-        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/progress/megatrends_RF.xlsx
+++ b/progress/megatrends_RF.xlsx
@@ -565,7 +565,22 @@
     <t xml:space="preserve">Road density</t>
   </si>
   <si>
-    <t xml:space="preserve">length of road network per area</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">length of road network per area
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="2"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">which kind of road?</t>
+    </r>
   </si>
   <si>
     <t>BD_TOPO</t>
@@ -6030,7 +6045,7 @@
       <c r="JM14" s="25"/>
       <c r="JN14" s="25"/>
     </row>
-    <row r="15" s="14" customFormat="1" ht="51">
+    <row r="15" s="14" customFormat="1" ht="25.5">
       <c r="A15" s="26" t="s">
         <v>14</v>
       </c>

--- a/progress/megatrends_RF.xlsx
+++ b/progress/megatrends_RF.xlsx
@@ -550,10 +550,12 @@
     <t xml:space="preserve">INSEE - ADMIN_EXPRESS</t>
   </si>
   <si>
-    <t>Pop_dens</t>
-  </si>
-  <si>
-    <t>https://www.insee.fr/fr/statistiques/3698339</t>
+    <t xml:space="preserve">Pop_dens - commune
+JRC - 100m raster?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.insee.fr/fr/statistiques/3698339
+https://www.insee.fr/fr/statistiques/8272002</t>
   </si>
   <si>
     <t xml:space="preserve">1876 - 2022</t>
@@ -1071,7 +1073,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1181,6 +1183,9 @@
     </xf>
     <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="6" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1801,7 +1806,7 @@
     <col customWidth="1" min="5" max="5" width="58.8515625"/>
     <col customWidth="1" min="6" max="6" width="32.140625"/>
     <col customWidth="1" min="7" max="7" width="31.140625"/>
-    <col customWidth="1" min="9" max="9" style="2" width="32.00390625"/>
+    <col customWidth="1" min="9" max="9" style="2" width="36.140625"/>
     <col customWidth="1" min="10" max="10" width="32.28125"/>
     <col customWidth="1" min="11" max="11" width="24.00390625"/>
     <col customWidth="1" min="12" max="12" width="12.140625"/>
@@ -7287,7 +7292,7 @@
       <c r="JM19" s="10"/>
       <c r="JN19" s="10"/>
     </row>
-    <row r="20" s="39" customFormat="1" ht="42.75">
+    <row r="20" s="39" customFormat="1" ht="51">
       <c r="A20" s="27" t="s">
         <v>132</v>
       </c>
@@ -7310,10 +7315,10 @@
         <v>162</v>
       </c>
       <c r="H20" s="27"/>
-      <c r="I20" s="32" t="s">
+      <c r="I20" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="J20" s="40"/>
+      <c r="J20" s="41"/>
       <c r="K20" s="27" t="s">
         <v>164</v>
       </c>
@@ -7324,268 +7329,268 @@
       <c r="N20" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="O20" s="41"/>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="41"/>
-      <c r="S20" s="41"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="41"/>
-      <c r="V20" s="41"/>
-      <c r="W20" s="41"/>
-      <c r="X20" s="41"/>
-      <c r="Y20" s="41"/>
-      <c r="Z20" s="41"/>
-      <c r="AA20" s="41"/>
-      <c r="AB20" s="41"/>
-      <c r="AC20" s="41"/>
-      <c r="AD20" s="41"/>
-      <c r="AE20" s="41"/>
-      <c r="AF20" s="41"/>
-      <c r="AG20" s="41"/>
-      <c r="AH20" s="41"/>
-      <c r="AI20" s="41"/>
-      <c r="AJ20" s="41"/>
-      <c r="AK20" s="41"/>
-      <c r="AL20" s="41"/>
-      <c r="AM20" s="41"/>
-      <c r="AN20" s="41"/>
-      <c r="AO20" s="41"/>
-      <c r="AP20" s="41"/>
-      <c r="AQ20" s="41"/>
-      <c r="AR20" s="41"/>
-      <c r="AS20" s="41"/>
-      <c r="AT20" s="41"/>
-      <c r="AU20" s="41"/>
-      <c r="AV20" s="41"/>
-      <c r="AW20" s="41"/>
-      <c r="AX20" s="41"/>
-      <c r="AY20" s="41"/>
-      <c r="AZ20" s="41"/>
-      <c r="BA20" s="41"/>
-      <c r="BB20" s="41"/>
-      <c r="BC20" s="41"/>
-      <c r="BD20" s="41"/>
-      <c r="BE20" s="41"/>
-      <c r="BF20" s="41"/>
-      <c r="BG20" s="41"/>
-      <c r="BH20" s="41"/>
-      <c r="BI20" s="41"/>
-      <c r="BJ20" s="41"/>
-      <c r="BK20" s="41"/>
-      <c r="BL20" s="41"/>
-      <c r="BM20" s="41"/>
-      <c r="BN20" s="41"/>
-      <c r="BO20" s="41"/>
-      <c r="BP20" s="41"/>
-      <c r="BQ20" s="41"/>
-      <c r="BR20" s="41"/>
-      <c r="BS20" s="41"/>
-      <c r="BT20" s="41"/>
-      <c r="BU20" s="41"/>
-      <c r="BV20" s="41"/>
-      <c r="BW20" s="41"/>
-      <c r="BX20" s="41"/>
-      <c r="BY20" s="41"/>
-      <c r="BZ20" s="41"/>
-      <c r="CA20" s="41"/>
-      <c r="CB20" s="41"/>
-      <c r="CC20" s="41"/>
-      <c r="CD20" s="41"/>
-      <c r="CE20" s="41"/>
-      <c r="CF20" s="41"/>
-      <c r="CG20" s="41"/>
-      <c r="CH20" s="41"/>
-      <c r="CI20" s="41"/>
-      <c r="CJ20" s="41"/>
-      <c r="CK20" s="41"/>
-      <c r="CL20" s="41"/>
-      <c r="CM20" s="41"/>
-      <c r="CN20" s="41"/>
-      <c r="CO20" s="41"/>
-      <c r="CP20" s="41"/>
-      <c r="CQ20" s="41"/>
-      <c r="CR20" s="41"/>
-      <c r="CS20" s="41"/>
-      <c r="CT20" s="41"/>
-      <c r="CU20" s="41"/>
-      <c r="CV20" s="41"/>
-      <c r="CW20" s="41"/>
-      <c r="CX20" s="41"/>
-      <c r="CY20" s="41"/>
-      <c r="CZ20" s="41"/>
-      <c r="DA20" s="41"/>
-      <c r="DB20" s="41"/>
-      <c r="DC20" s="41"/>
-      <c r="DD20" s="41"/>
-      <c r="DE20" s="41"/>
-      <c r="DF20" s="41"/>
-      <c r="DG20" s="41"/>
-      <c r="DH20" s="41"/>
-      <c r="DI20" s="41"/>
-      <c r="DJ20" s="41"/>
-      <c r="DK20" s="41"/>
-      <c r="DL20" s="41"/>
-      <c r="DM20" s="41"/>
-      <c r="DN20" s="41"/>
-      <c r="DO20" s="41"/>
-      <c r="DP20" s="41"/>
-      <c r="DQ20" s="41"/>
-      <c r="DR20" s="41"/>
-      <c r="DS20" s="41"/>
-      <c r="DT20" s="41"/>
-      <c r="DU20" s="41"/>
-      <c r="DV20" s="41"/>
-      <c r="DW20" s="41"/>
-      <c r="DX20" s="41"/>
-      <c r="DY20" s="41"/>
-      <c r="DZ20" s="41"/>
-      <c r="EA20" s="41"/>
-      <c r="EB20" s="41"/>
-      <c r="EC20" s="41"/>
-      <c r="ED20" s="41"/>
-      <c r="EE20" s="41"/>
-      <c r="EF20" s="41"/>
-      <c r="EG20" s="41"/>
-      <c r="EH20" s="41"/>
-      <c r="EI20" s="41"/>
-      <c r="EJ20" s="41"/>
-      <c r="EK20" s="41"/>
-      <c r="EL20" s="41"/>
-      <c r="EM20" s="41"/>
-      <c r="EN20" s="41"/>
-      <c r="EO20" s="41"/>
-      <c r="EP20" s="41"/>
-      <c r="EQ20" s="41"/>
-      <c r="ER20" s="41"/>
-      <c r="ES20" s="41"/>
-      <c r="ET20" s="41"/>
-      <c r="EU20" s="41"/>
-      <c r="EV20" s="41"/>
-      <c r="EW20" s="41"/>
-      <c r="EX20" s="41"/>
-      <c r="EY20" s="41"/>
-      <c r="EZ20" s="41"/>
-      <c r="FA20" s="41"/>
-      <c r="FB20" s="41"/>
-      <c r="FC20" s="41"/>
-      <c r="FD20" s="41"/>
-      <c r="FE20" s="41"/>
-      <c r="FF20" s="41"/>
-      <c r="FG20" s="41"/>
-      <c r="FH20" s="41"/>
-      <c r="FI20" s="41"/>
-      <c r="FJ20" s="41"/>
-      <c r="FK20" s="41"/>
-      <c r="FL20" s="41"/>
-      <c r="FM20" s="41"/>
-      <c r="FN20" s="41"/>
-      <c r="FO20" s="41"/>
-      <c r="FP20" s="41"/>
-      <c r="FQ20" s="41"/>
-      <c r="FR20" s="41"/>
-      <c r="FS20" s="41"/>
-      <c r="FT20" s="41"/>
-      <c r="FU20" s="41"/>
-      <c r="FV20" s="41"/>
-      <c r="FW20" s="41"/>
-      <c r="FX20" s="41"/>
-      <c r="FY20" s="41"/>
-      <c r="FZ20" s="41"/>
-      <c r="GA20" s="41"/>
-      <c r="GB20" s="41"/>
-      <c r="GC20" s="41"/>
-      <c r="GD20" s="41"/>
-      <c r="GE20" s="41"/>
-      <c r="GF20" s="41"/>
-      <c r="GG20" s="41"/>
-      <c r="GH20" s="41"/>
-      <c r="GI20" s="41"/>
-      <c r="GJ20" s="41"/>
-      <c r="GK20" s="41"/>
-      <c r="GL20" s="41"/>
-      <c r="GM20" s="41"/>
-      <c r="GN20" s="41"/>
-      <c r="GO20" s="41"/>
-      <c r="GP20" s="41"/>
-      <c r="GQ20" s="41"/>
-      <c r="GR20" s="41"/>
-      <c r="GS20" s="41"/>
-      <c r="GT20" s="41"/>
-      <c r="GU20" s="41"/>
-      <c r="GV20" s="41"/>
-      <c r="GW20" s="41"/>
-      <c r="GX20" s="41"/>
-      <c r="GY20" s="41"/>
-      <c r="GZ20" s="41"/>
-      <c r="HA20" s="41"/>
-      <c r="HB20" s="41"/>
-      <c r="HC20" s="41"/>
-      <c r="HD20" s="41"/>
-      <c r="HE20" s="41"/>
-      <c r="HF20" s="41"/>
-      <c r="HG20" s="41"/>
-      <c r="HH20" s="41"/>
-      <c r="HI20" s="41"/>
-      <c r="HJ20" s="41"/>
-      <c r="HK20" s="41"/>
-      <c r="HL20" s="41"/>
-      <c r="HM20" s="41"/>
-      <c r="HN20" s="41"/>
-      <c r="HO20" s="41"/>
-      <c r="HP20" s="41"/>
-      <c r="HQ20" s="41"/>
-      <c r="HR20" s="41"/>
-      <c r="HS20" s="41"/>
-      <c r="HT20" s="41"/>
-      <c r="HU20" s="41"/>
-      <c r="HV20" s="41"/>
-      <c r="HW20" s="41"/>
-      <c r="HX20" s="41"/>
-      <c r="HY20" s="41"/>
-      <c r="HZ20" s="41"/>
-      <c r="IA20" s="41"/>
-      <c r="IB20" s="41"/>
-      <c r="IC20" s="41"/>
-      <c r="ID20" s="41"/>
-      <c r="IE20" s="41"/>
-      <c r="IF20" s="41"/>
-      <c r="IG20" s="41"/>
-      <c r="IH20" s="41"/>
-      <c r="II20" s="41"/>
-      <c r="IJ20" s="41"/>
-      <c r="IK20" s="41"/>
-      <c r="IL20" s="41"/>
-      <c r="IM20" s="41"/>
-      <c r="IN20" s="41"/>
-      <c r="IO20" s="41"/>
-      <c r="IP20" s="41"/>
-      <c r="IQ20" s="41"/>
-      <c r="IR20" s="41"/>
-      <c r="IS20" s="41"/>
-      <c r="IT20" s="41"/>
-      <c r="IU20" s="41"/>
-      <c r="IV20" s="41"/>
-      <c r="IW20" s="41"/>
-      <c r="IX20" s="41"/>
-      <c r="IY20" s="41"/>
-      <c r="IZ20" s="41"/>
-      <c r="JA20" s="41"/>
-      <c r="JB20" s="41"/>
-      <c r="JC20" s="41"/>
-      <c r="JD20" s="41"/>
-      <c r="JE20" s="41"/>
-      <c r="JF20" s="41"/>
-      <c r="JG20" s="41"/>
-      <c r="JH20" s="41"/>
-      <c r="JI20" s="41"/>
-      <c r="JJ20" s="41"/>
-      <c r="JK20" s="41"/>
-      <c r="JL20" s="41"/>
-      <c r="JM20" s="41"/>
-      <c r="JN20" s="41"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42"/>
+      <c r="T20" s="42"/>
+      <c r="U20" s="42"/>
+      <c r="V20" s="42"/>
+      <c r="W20" s="42"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="42"/>
+      <c r="Z20" s="42"/>
+      <c r="AA20" s="42"/>
+      <c r="AB20" s="42"/>
+      <c r="AC20" s="42"/>
+      <c r="AD20" s="42"/>
+      <c r="AE20" s="42"/>
+      <c r="AF20" s="42"/>
+      <c r="AG20" s="42"/>
+      <c r="AH20" s="42"/>
+      <c r="AI20" s="42"/>
+      <c r="AJ20" s="42"/>
+      <c r="AK20" s="42"/>
+      <c r="AL20" s="42"/>
+      <c r="AM20" s="42"/>
+      <c r="AN20" s="42"/>
+      <c r="AO20" s="42"/>
+      <c r="AP20" s="42"/>
+      <c r="AQ20" s="42"/>
+      <c r="AR20" s="42"/>
+      <c r="AS20" s="42"/>
+      <c r="AT20" s="42"/>
+      <c r="AU20" s="42"/>
+      <c r="AV20" s="42"/>
+      <c r="AW20" s="42"/>
+      <c r="AX20" s="42"/>
+      <c r="AY20" s="42"/>
+      <c r="AZ20" s="42"/>
+      <c r="BA20" s="42"/>
+      <c r="BB20" s="42"/>
+      <c r="BC20" s="42"/>
+      <c r="BD20" s="42"/>
+      <c r="BE20" s="42"/>
+      <c r="BF20" s="42"/>
+      <c r="BG20" s="42"/>
+      <c r="BH20" s="42"/>
+      <c r="BI20" s="42"/>
+      <c r="BJ20" s="42"/>
+      <c r="BK20" s="42"/>
+      <c r="BL20" s="42"/>
+      <c r="BM20" s="42"/>
+      <c r="BN20" s="42"/>
+      <c r="BO20" s="42"/>
+      <c r="BP20" s="42"/>
+      <c r="BQ20" s="42"/>
+      <c r="BR20" s="42"/>
+      <c r="BS20" s="42"/>
+      <c r="BT20" s="42"/>
+      <c r="BU20" s="42"/>
+      <c r="BV20" s="42"/>
+      <c r="BW20" s="42"/>
+      <c r="BX20" s="42"/>
+      <c r="BY20" s="42"/>
+      <c r="BZ20" s="42"/>
+      <c r="CA20" s="42"/>
+      <c r="CB20" s="42"/>
+      <c r="CC20" s="42"/>
+      <c r="CD20" s="42"/>
+      <c r="CE20" s="42"/>
+      <c r="CF20" s="42"/>
+      <c r="CG20" s="42"/>
+      <c r="CH20" s="42"/>
+      <c r="CI20" s="42"/>
+      <c r="CJ20" s="42"/>
+      <c r="CK20" s="42"/>
+      <c r="CL20" s="42"/>
+      <c r="CM20" s="42"/>
+      <c r="CN20" s="42"/>
+      <c r="CO20" s="42"/>
+      <c r="CP20" s="42"/>
+      <c r="CQ20" s="42"/>
+      <c r="CR20" s="42"/>
+      <c r="CS20" s="42"/>
+      <c r="CT20" s="42"/>
+      <c r="CU20" s="42"/>
+      <c r="CV20" s="42"/>
+      <c r="CW20" s="42"/>
+      <c r="CX20" s="42"/>
+      <c r="CY20" s="42"/>
+      <c r="CZ20" s="42"/>
+      <c r="DA20" s="42"/>
+      <c r="DB20" s="42"/>
+      <c r="DC20" s="42"/>
+      <c r="DD20" s="42"/>
+      <c r="DE20" s="42"/>
+      <c r="DF20" s="42"/>
+      <c r="DG20" s="42"/>
+      <c r="DH20" s="42"/>
+      <c r="DI20" s="42"/>
+      <c r="DJ20" s="42"/>
+      <c r="DK20" s="42"/>
+      <c r="DL20" s="42"/>
+      <c r="DM20" s="42"/>
+      <c r="DN20" s="42"/>
+      <c r="DO20" s="42"/>
+      <c r="DP20" s="42"/>
+      <c r="DQ20" s="42"/>
+      <c r="DR20" s="42"/>
+      <c r="DS20" s="42"/>
+      <c r="DT20" s="42"/>
+      <c r="DU20" s="42"/>
+      <c r="DV20" s="42"/>
+      <c r="DW20" s="42"/>
+      <c r="DX20" s="42"/>
+      <c r="DY20" s="42"/>
+      <c r="DZ20" s="42"/>
+      <c r="EA20" s="42"/>
+      <c r="EB20" s="42"/>
+      <c r="EC20" s="42"/>
+      <c r="ED20" s="42"/>
+      <c r="EE20" s="42"/>
+      <c r="EF20" s="42"/>
+      <c r="EG20" s="42"/>
+      <c r="EH20" s="42"/>
+      <c r="EI20" s="42"/>
+      <c r="EJ20" s="42"/>
+      <c r="EK20" s="42"/>
+      <c r="EL20" s="42"/>
+      <c r="EM20" s="42"/>
+      <c r="EN20" s="42"/>
+      <c r="EO20" s="42"/>
+      <c r="EP20" s="42"/>
+      <c r="EQ20" s="42"/>
+      <c r="ER20" s="42"/>
+      <c r="ES20" s="42"/>
+      <c r="ET20" s="42"/>
+      <c r="EU20" s="42"/>
+      <c r="EV20" s="42"/>
+      <c r="EW20" s="42"/>
+      <c r="EX20" s="42"/>
+      <c r="EY20" s="42"/>
+      <c r="EZ20" s="42"/>
+      <c r="FA20" s="42"/>
+      <c r="FB20" s="42"/>
+      <c r="FC20" s="42"/>
+      <c r="FD20" s="42"/>
+      <c r="FE20" s="42"/>
+      <c r="FF20" s="42"/>
+      <c r="FG20" s="42"/>
+      <c r="FH20" s="42"/>
+      <c r="FI20" s="42"/>
+      <c r="FJ20" s="42"/>
+      <c r="FK20" s="42"/>
+      <c r="FL20" s="42"/>
+      <c r="FM20" s="42"/>
+      <c r="FN20" s="42"/>
+      <c r="FO20" s="42"/>
+      <c r="FP20" s="42"/>
+      <c r="FQ20" s="42"/>
+      <c r="FR20" s="42"/>
+      <c r="FS20" s="42"/>
+      <c r="FT20" s="42"/>
+      <c r="FU20" s="42"/>
+      <c r="FV20" s="42"/>
+      <c r="FW20" s="42"/>
+      <c r="FX20" s="42"/>
+      <c r="FY20" s="42"/>
+      <c r="FZ20" s="42"/>
+      <c r="GA20" s="42"/>
+      <c r="GB20" s="42"/>
+      <c r="GC20" s="42"/>
+      <c r="GD20" s="42"/>
+      <c r="GE20" s="42"/>
+      <c r="GF20" s="42"/>
+      <c r="GG20" s="42"/>
+      <c r="GH20" s="42"/>
+      <c r="GI20" s="42"/>
+      <c r="GJ20" s="42"/>
+      <c r="GK20" s="42"/>
+      <c r="GL20" s="42"/>
+      <c r="GM20" s="42"/>
+      <c r="GN20" s="42"/>
+      <c r="GO20" s="42"/>
+      <c r="GP20" s="42"/>
+      <c r="GQ20" s="42"/>
+      <c r="GR20" s="42"/>
+      <c r="GS20" s="42"/>
+      <c r="GT20" s="42"/>
+      <c r="GU20" s="42"/>
+      <c r="GV20" s="42"/>
+      <c r="GW20" s="42"/>
+      <c r="GX20" s="42"/>
+      <c r="GY20" s="42"/>
+      <c r="GZ20" s="42"/>
+      <c r="HA20" s="42"/>
+      <c r="HB20" s="42"/>
+      <c r="HC20" s="42"/>
+      <c r="HD20" s="42"/>
+      <c r="HE20" s="42"/>
+      <c r="HF20" s="42"/>
+      <c r="HG20" s="42"/>
+      <c r="HH20" s="42"/>
+      <c r="HI20" s="42"/>
+      <c r="HJ20" s="42"/>
+      <c r="HK20" s="42"/>
+      <c r="HL20" s="42"/>
+      <c r="HM20" s="42"/>
+      <c r="HN20" s="42"/>
+      <c r="HO20" s="42"/>
+      <c r="HP20" s="42"/>
+      <c r="HQ20" s="42"/>
+      <c r="HR20" s="42"/>
+      <c r="HS20" s="42"/>
+      <c r="HT20" s="42"/>
+      <c r="HU20" s="42"/>
+      <c r="HV20" s="42"/>
+      <c r="HW20" s="42"/>
+      <c r="HX20" s="42"/>
+      <c r="HY20" s="42"/>
+      <c r="HZ20" s="42"/>
+      <c r="IA20" s="42"/>
+      <c r="IB20" s="42"/>
+      <c r="IC20" s="42"/>
+      <c r="ID20" s="42"/>
+      <c r="IE20" s="42"/>
+      <c r="IF20" s="42"/>
+      <c r="IG20" s="42"/>
+      <c r="IH20" s="42"/>
+      <c r="II20" s="42"/>
+      <c r="IJ20" s="42"/>
+      <c r="IK20" s="42"/>
+      <c r="IL20" s="42"/>
+      <c r="IM20" s="42"/>
+      <c r="IN20" s="42"/>
+      <c r="IO20" s="42"/>
+      <c r="IP20" s="42"/>
+      <c r="IQ20" s="42"/>
+      <c r="IR20" s="42"/>
+      <c r="IS20" s="42"/>
+      <c r="IT20" s="42"/>
+      <c r="IU20" s="42"/>
+      <c r="IV20" s="42"/>
+      <c r="IW20" s="42"/>
+      <c r="IX20" s="42"/>
+      <c r="IY20" s="42"/>
+      <c r="IZ20" s="42"/>
+      <c r="JA20" s="42"/>
+      <c r="JB20" s="42"/>
+      <c r="JC20" s="42"/>
+      <c r="JD20" s="42"/>
+      <c r="JE20" s="42"/>
+      <c r="JF20" s="42"/>
+      <c r="JG20" s="42"/>
+      <c r="JH20" s="42"/>
+      <c r="JI20" s="42"/>
+      <c r="JJ20" s="42"/>
+      <c r="JK20" s="42"/>
+      <c r="JL20" s="42"/>
+      <c r="JM20" s="42"/>
+      <c r="JN20" s="42"/>
     </row>
-    <row r="21" s="42" customFormat="1" ht="25.5">
+    <row r="21" s="43" customFormat="1" ht="25.5">
       <c r="A21" s="27" t="s">
         <v>132</v>
       </c>
@@ -7611,7 +7616,7 @@
       <c r="I21" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="J21" s="40"/>
+      <c r="J21" s="41"/>
       <c r="K21" s="27">
         <v>2025</v>
       </c>
@@ -7620,971 +7625,971 @@
       </c>
       <c r="M21" s="27"/>
       <c r="N21" s="16"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="42"/>
-      <c r="R21" s="42"/>
-      <c r="S21" s="42"/>
-      <c r="T21" s="42"/>
-      <c r="U21" s="42"/>
-      <c r="V21" s="42"/>
-      <c r="W21" s="42"/>
-      <c r="X21" s="42"/>
-      <c r="Y21" s="42"/>
-      <c r="Z21" s="42"/>
-      <c r="AA21" s="42"/>
-      <c r="AB21" s="42"/>
-      <c r="AC21" s="42"/>
-      <c r="AD21" s="42"/>
-      <c r="AE21" s="42"/>
-      <c r="AF21" s="42"/>
-      <c r="AG21" s="42"/>
-      <c r="AH21" s="42"/>
-      <c r="AI21" s="42"/>
-      <c r="AJ21" s="42"/>
-      <c r="AK21" s="42"/>
-      <c r="AL21" s="42"/>
-      <c r="AM21" s="42"/>
-      <c r="AN21" s="42"/>
-      <c r="AO21" s="42"/>
-      <c r="AP21" s="42"/>
-      <c r="AQ21" s="42"/>
-      <c r="AR21" s="42"/>
-      <c r="AS21" s="42"/>
-      <c r="AT21" s="42"/>
-      <c r="AU21" s="42"/>
-      <c r="AV21" s="42"/>
-      <c r="AW21" s="42"/>
-      <c r="AX21" s="42"/>
-      <c r="AY21" s="42"/>
-      <c r="AZ21" s="42"/>
-      <c r="BA21" s="42"/>
-      <c r="BB21" s="42"/>
-      <c r="BC21" s="42"/>
-      <c r="BD21" s="42"/>
-      <c r="BE21" s="42"/>
-      <c r="BF21" s="42"/>
-      <c r="BG21" s="42"/>
-      <c r="BH21" s="42"/>
-      <c r="BI21" s="42"/>
-      <c r="BJ21" s="42"/>
-      <c r="BK21" s="42"/>
-      <c r="BL21" s="42"/>
-      <c r="BM21" s="42"/>
-      <c r="BN21" s="42"/>
-      <c r="BO21" s="42"/>
-      <c r="BP21" s="42"/>
-      <c r="BQ21" s="42"/>
-      <c r="BR21" s="42"/>
-      <c r="BS21" s="42"/>
-      <c r="BT21" s="42"/>
-      <c r="BU21" s="42"/>
-      <c r="BV21" s="42"/>
-      <c r="BW21" s="42"/>
-      <c r="BX21" s="42"/>
-      <c r="BY21" s="42"/>
-      <c r="BZ21" s="42"/>
-      <c r="CA21" s="42"/>
-      <c r="CB21" s="42"/>
-      <c r="CC21" s="42"/>
-      <c r="CD21" s="42"/>
-      <c r="CE21" s="42"/>
-      <c r="CF21" s="42"/>
-      <c r="CG21" s="42"/>
-      <c r="CH21" s="42"/>
-      <c r="CI21" s="42"/>
-      <c r="CJ21" s="42"/>
-      <c r="CK21" s="42"/>
-      <c r="CL21" s="42"/>
-      <c r="CM21" s="42"/>
-      <c r="CN21" s="42"/>
-      <c r="CO21" s="42"/>
-      <c r="CP21" s="42"/>
-      <c r="CQ21" s="42"/>
-      <c r="CR21" s="42"/>
-      <c r="CS21" s="42"/>
-      <c r="CT21" s="42"/>
-      <c r="CU21" s="42"/>
-      <c r="CV21" s="42"/>
-      <c r="CW21" s="42"/>
-      <c r="CX21" s="42"/>
-      <c r="CY21" s="42"/>
-      <c r="CZ21" s="42"/>
-      <c r="DA21" s="42"/>
-      <c r="DB21" s="42"/>
-      <c r="DC21" s="42"/>
-      <c r="DD21" s="42"/>
-      <c r="DE21" s="42"/>
-      <c r="DF21" s="42"/>
-      <c r="DG21" s="42"/>
-      <c r="DH21" s="42"/>
-      <c r="DI21" s="42"/>
-      <c r="DJ21" s="42"/>
-      <c r="DK21" s="42"/>
-      <c r="DL21" s="42"/>
-      <c r="DM21" s="42"/>
-      <c r="DN21" s="42"/>
-      <c r="DO21" s="42"/>
-      <c r="DP21" s="42"/>
-      <c r="DQ21" s="42"/>
-      <c r="DR21" s="42"/>
-      <c r="DS21" s="42"/>
-      <c r="DT21" s="42"/>
-      <c r="DU21" s="42"/>
-      <c r="DV21" s="42"/>
-      <c r="DW21" s="42"/>
-      <c r="DX21" s="42"/>
-      <c r="DY21" s="42"/>
-      <c r="DZ21" s="42"/>
-      <c r="EA21" s="42"/>
-      <c r="EB21" s="42"/>
-      <c r="EC21" s="42"/>
-      <c r="ED21" s="42"/>
-      <c r="EE21" s="42"/>
-      <c r="EF21" s="42"/>
-      <c r="EG21" s="42"/>
-      <c r="EH21" s="42"/>
-      <c r="EI21" s="42"/>
-      <c r="EJ21" s="42"/>
-      <c r="EK21" s="42"/>
-      <c r="EL21" s="42"/>
-      <c r="EM21" s="42"/>
-      <c r="EN21" s="42"/>
-      <c r="EO21" s="42"/>
-      <c r="EP21" s="42"/>
-      <c r="EQ21" s="42"/>
-      <c r="ER21" s="42"/>
-      <c r="ES21" s="42"/>
-      <c r="ET21" s="42"/>
-      <c r="EU21" s="42"/>
-      <c r="EV21" s="42"/>
-      <c r="EW21" s="42"/>
-      <c r="EX21" s="42"/>
-      <c r="EY21" s="42"/>
-      <c r="EZ21" s="42"/>
-      <c r="FA21" s="42"/>
-      <c r="FB21" s="42"/>
-      <c r="FC21" s="42"/>
-      <c r="FD21" s="42"/>
-      <c r="FE21" s="42"/>
-      <c r="FF21" s="42"/>
-      <c r="FG21" s="42"/>
-      <c r="FH21" s="42"/>
-      <c r="FI21" s="42"/>
-      <c r="FJ21" s="42"/>
-      <c r="FK21" s="42"/>
-      <c r="FL21" s="42"/>
-      <c r="FM21" s="42"/>
-      <c r="FN21" s="42"/>
-      <c r="FO21" s="42"/>
-      <c r="FP21" s="42"/>
-      <c r="FQ21" s="42"/>
-      <c r="FR21" s="42"/>
-      <c r="FS21" s="42"/>
-      <c r="FT21" s="42"/>
-      <c r="FU21" s="42"/>
-      <c r="FV21" s="42"/>
-      <c r="FW21" s="42"/>
-      <c r="FX21" s="42"/>
-      <c r="FY21" s="42"/>
-      <c r="FZ21" s="42"/>
-      <c r="GA21" s="42"/>
-      <c r="GB21" s="42"/>
-      <c r="GC21" s="42"/>
-      <c r="GD21" s="42"/>
-      <c r="GE21" s="42"/>
-      <c r="GF21" s="42"/>
-      <c r="GG21" s="42"/>
-      <c r="GH21" s="42"/>
-      <c r="GI21" s="42"/>
-      <c r="GJ21" s="42"/>
-      <c r="GK21" s="42"/>
-      <c r="GL21" s="42"/>
-      <c r="GM21" s="42"/>
-      <c r="GN21" s="42"/>
-      <c r="GO21" s="42"/>
-      <c r="GP21" s="42"/>
-      <c r="GQ21" s="42"/>
-      <c r="GR21" s="42"/>
-      <c r="GS21" s="42"/>
-      <c r="GT21" s="42"/>
-      <c r="GU21" s="42"/>
-      <c r="GV21" s="42"/>
-      <c r="GW21" s="42"/>
-      <c r="GX21" s="42"/>
-      <c r="GY21" s="42"/>
-      <c r="GZ21" s="42"/>
-      <c r="HA21" s="42"/>
-      <c r="HB21" s="42"/>
-      <c r="HC21" s="42"/>
-      <c r="HD21" s="42"/>
-      <c r="HE21" s="42"/>
-      <c r="HF21" s="42"/>
-      <c r="HG21" s="42"/>
-      <c r="HH21" s="42"/>
-      <c r="HI21" s="42"/>
-      <c r="HJ21" s="42"/>
-      <c r="HK21" s="42"/>
-      <c r="HL21" s="42"/>
-      <c r="HM21" s="42"/>
-      <c r="HN21" s="42"/>
-      <c r="HO21" s="42"/>
-      <c r="HP21" s="42"/>
-      <c r="HQ21" s="42"/>
-      <c r="HR21" s="42"/>
-      <c r="HS21" s="42"/>
-      <c r="HT21" s="42"/>
-      <c r="HU21" s="42"/>
-      <c r="HV21" s="42"/>
-      <c r="HW21" s="42"/>
-      <c r="HX21" s="42"/>
-      <c r="HY21" s="42"/>
-      <c r="HZ21" s="42"/>
-      <c r="IA21" s="42"/>
-      <c r="IB21" s="42"/>
-      <c r="IC21" s="42"/>
-      <c r="ID21" s="42"/>
-      <c r="IE21" s="42"/>
-      <c r="IF21" s="42"/>
-      <c r="IG21" s="42"/>
-      <c r="IH21" s="42"/>
-      <c r="II21" s="42"/>
-      <c r="IJ21" s="42"/>
-      <c r="IK21" s="42"/>
-      <c r="IL21" s="42"/>
-      <c r="IM21" s="42"/>
-      <c r="IN21" s="42"/>
-      <c r="IO21" s="42"/>
-      <c r="IP21" s="42"/>
-      <c r="IQ21" s="42"/>
-      <c r="IR21" s="42"/>
-      <c r="IS21" s="42"/>
-      <c r="IT21" s="42"/>
-      <c r="IU21" s="42"/>
-      <c r="IV21" s="42"/>
-      <c r="IW21" s="42"/>
-      <c r="IX21" s="42"/>
-      <c r="IY21" s="42"/>
-      <c r="IZ21" s="42"/>
-      <c r="JA21" s="42"/>
-      <c r="JB21" s="42"/>
-      <c r="JC21" s="42"/>
-      <c r="JD21" s="42"/>
-      <c r="JE21" s="42"/>
-      <c r="JF21" s="42"/>
-      <c r="JG21" s="42"/>
-      <c r="JH21" s="42"/>
-      <c r="JI21" s="42"/>
-      <c r="JJ21" s="42"/>
-      <c r="JK21" s="42"/>
-      <c r="JL21" s="42"/>
-      <c r="JM21" s="42"/>
-      <c r="JN21" s="42"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="43"/>
+      <c r="U21" s="43"/>
+      <c r="V21" s="43"/>
+      <c r="W21" s="43"/>
+      <c r="X21" s="43"/>
+      <c r="Y21" s="43"/>
+      <c r="Z21" s="43"/>
+      <c r="AA21" s="43"/>
+      <c r="AB21" s="43"/>
+      <c r="AC21" s="43"/>
+      <c r="AD21" s="43"/>
+      <c r="AE21" s="43"/>
+      <c r="AF21" s="43"/>
+      <c r="AG21" s="43"/>
+      <c r="AH21" s="43"/>
+      <c r="AI21" s="43"/>
+      <c r="AJ21" s="43"/>
+      <c r="AK21" s="43"/>
+      <c r="AL21" s="43"/>
+      <c r="AM21" s="43"/>
+      <c r="AN21" s="43"/>
+      <c r="AO21" s="43"/>
+      <c r="AP21" s="43"/>
+      <c r="AQ21" s="43"/>
+      <c r="AR21" s="43"/>
+      <c r="AS21" s="43"/>
+      <c r="AT21" s="43"/>
+      <c r="AU21" s="43"/>
+      <c r="AV21" s="43"/>
+      <c r="AW21" s="43"/>
+      <c r="AX21" s="43"/>
+      <c r="AY21" s="43"/>
+      <c r="AZ21" s="43"/>
+      <c r="BA21" s="43"/>
+      <c r="BB21" s="43"/>
+      <c r="BC21" s="43"/>
+      <c r="BD21" s="43"/>
+      <c r="BE21" s="43"/>
+      <c r="BF21" s="43"/>
+      <c r="BG21" s="43"/>
+      <c r="BH21" s="43"/>
+      <c r="BI21" s="43"/>
+      <c r="BJ21" s="43"/>
+      <c r="BK21" s="43"/>
+      <c r="BL21" s="43"/>
+      <c r="BM21" s="43"/>
+      <c r="BN21" s="43"/>
+      <c r="BO21" s="43"/>
+      <c r="BP21" s="43"/>
+      <c r="BQ21" s="43"/>
+      <c r="BR21" s="43"/>
+      <c r="BS21" s="43"/>
+      <c r="BT21" s="43"/>
+      <c r="BU21" s="43"/>
+      <c r="BV21" s="43"/>
+      <c r="BW21" s="43"/>
+      <c r="BX21" s="43"/>
+      <c r="BY21" s="43"/>
+      <c r="BZ21" s="43"/>
+      <c r="CA21" s="43"/>
+      <c r="CB21" s="43"/>
+      <c r="CC21" s="43"/>
+      <c r="CD21" s="43"/>
+      <c r="CE21" s="43"/>
+      <c r="CF21" s="43"/>
+      <c r="CG21" s="43"/>
+      <c r="CH21" s="43"/>
+      <c r="CI21" s="43"/>
+      <c r="CJ21" s="43"/>
+      <c r="CK21" s="43"/>
+      <c r="CL21" s="43"/>
+      <c r="CM21" s="43"/>
+      <c r="CN21" s="43"/>
+      <c r="CO21" s="43"/>
+      <c r="CP21" s="43"/>
+      <c r="CQ21" s="43"/>
+      <c r="CR21" s="43"/>
+      <c r="CS21" s="43"/>
+      <c r="CT21" s="43"/>
+      <c r="CU21" s="43"/>
+      <c r="CV21" s="43"/>
+      <c r="CW21" s="43"/>
+      <c r="CX21" s="43"/>
+      <c r="CY21" s="43"/>
+      <c r="CZ21" s="43"/>
+      <c r="DA21" s="43"/>
+      <c r="DB21" s="43"/>
+      <c r="DC21" s="43"/>
+      <c r="DD21" s="43"/>
+      <c r="DE21" s="43"/>
+      <c r="DF21" s="43"/>
+      <c r="DG21" s="43"/>
+      <c r="DH21" s="43"/>
+      <c r="DI21" s="43"/>
+      <c r="DJ21" s="43"/>
+      <c r="DK21" s="43"/>
+      <c r="DL21" s="43"/>
+      <c r="DM21" s="43"/>
+      <c r="DN21" s="43"/>
+      <c r="DO21" s="43"/>
+      <c r="DP21" s="43"/>
+      <c r="DQ21" s="43"/>
+      <c r="DR21" s="43"/>
+      <c r="DS21" s="43"/>
+      <c r="DT21" s="43"/>
+      <c r="DU21" s="43"/>
+      <c r="DV21" s="43"/>
+      <c r="DW21" s="43"/>
+      <c r="DX21" s="43"/>
+      <c r="DY21" s="43"/>
+      <c r="DZ21" s="43"/>
+      <c r="EA21" s="43"/>
+      <c r="EB21" s="43"/>
+      <c r="EC21" s="43"/>
+      <c r="ED21" s="43"/>
+      <c r="EE21" s="43"/>
+      <c r="EF21" s="43"/>
+      <c r="EG21" s="43"/>
+      <c r="EH21" s="43"/>
+      <c r="EI21" s="43"/>
+      <c r="EJ21" s="43"/>
+      <c r="EK21" s="43"/>
+      <c r="EL21" s="43"/>
+      <c r="EM21" s="43"/>
+      <c r="EN21" s="43"/>
+      <c r="EO21" s="43"/>
+      <c r="EP21" s="43"/>
+      <c r="EQ21" s="43"/>
+      <c r="ER21" s="43"/>
+      <c r="ES21" s="43"/>
+      <c r="ET21" s="43"/>
+      <c r="EU21" s="43"/>
+      <c r="EV21" s="43"/>
+      <c r="EW21" s="43"/>
+      <c r="EX21" s="43"/>
+      <c r="EY21" s="43"/>
+      <c r="EZ21" s="43"/>
+      <c r="FA21" s="43"/>
+      <c r="FB21" s="43"/>
+      <c r="FC21" s="43"/>
+      <c r="FD21" s="43"/>
+      <c r="FE21" s="43"/>
+      <c r="FF21" s="43"/>
+      <c r="FG21" s="43"/>
+      <c r="FH21" s="43"/>
+      <c r="FI21" s="43"/>
+      <c r="FJ21" s="43"/>
+      <c r="FK21" s="43"/>
+      <c r="FL21" s="43"/>
+      <c r="FM21" s="43"/>
+      <c r="FN21" s="43"/>
+      <c r="FO21" s="43"/>
+      <c r="FP21" s="43"/>
+      <c r="FQ21" s="43"/>
+      <c r="FR21" s="43"/>
+      <c r="FS21" s="43"/>
+      <c r="FT21" s="43"/>
+      <c r="FU21" s="43"/>
+      <c r="FV21" s="43"/>
+      <c r="FW21" s="43"/>
+      <c r="FX21" s="43"/>
+      <c r="FY21" s="43"/>
+      <c r="FZ21" s="43"/>
+      <c r="GA21" s="43"/>
+      <c r="GB21" s="43"/>
+      <c r="GC21" s="43"/>
+      <c r="GD21" s="43"/>
+      <c r="GE21" s="43"/>
+      <c r="GF21" s="43"/>
+      <c r="GG21" s="43"/>
+      <c r="GH21" s="43"/>
+      <c r="GI21" s="43"/>
+      <c r="GJ21" s="43"/>
+      <c r="GK21" s="43"/>
+      <c r="GL21" s="43"/>
+      <c r="GM21" s="43"/>
+      <c r="GN21" s="43"/>
+      <c r="GO21" s="43"/>
+      <c r="GP21" s="43"/>
+      <c r="GQ21" s="43"/>
+      <c r="GR21" s="43"/>
+      <c r="GS21" s="43"/>
+      <c r="GT21" s="43"/>
+      <c r="GU21" s="43"/>
+      <c r="GV21" s="43"/>
+      <c r="GW21" s="43"/>
+      <c r="GX21" s="43"/>
+      <c r="GY21" s="43"/>
+      <c r="GZ21" s="43"/>
+      <c r="HA21" s="43"/>
+      <c r="HB21" s="43"/>
+      <c r="HC21" s="43"/>
+      <c r="HD21" s="43"/>
+      <c r="HE21" s="43"/>
+      <c r="HF21" s="43"/>
+      <c r="HG21" s="43"/>
+      <c r="HH21" s="43"/>
+      <c r="HI21" s="43"/>
+      <c r="HJ21" s="43"/>
+      <c r="HK21" s="43"/>
+      <c r="HL21" s="43"/>
+      <c r="HM21" s="43"/>
+      <c r="HN21" s="43"/>
+      <c r="HO21" s="43"/>
+      <c r="HP21" s="43"/>
+      <c r="HQ21" s="43"/>
+      <c r="HR21" s="43"/>
+      <c r="HS21" s="43"/>
+      <c r="HT21" s="43"/>
+      <c r="HU21" s="43"/>
+      <c r="HV21" s="43"/>
+      <c r="HW21" s="43"/>
+      <c r="HX21" s="43"/>
+      <c r="HY21" s="43"/>
+      <c r="HZ21" s="43"/>
+      <c r="IA21" s="43"/>
+      <c r="IB21" s="43"/>
+      <c r="IC21" s="43"/>
+      <c r="ID21" s="43"/>
+      <c r="IE21" s="43"/>
+      <c r="IF21" s="43"/>
+      <c r="IG21" s="43"/>
+      <c r="IH21" s="43"/>
+      <c r="II21" s="43"/>
+      <c r="IJ21" s="43"/>
+      <c r="IK21" s="43"/>
+      <c r="IL21" s="43"/>
+      <c r="IM21" s="43"/>
+      <c r="IN21" s="43"/>
+      <c r="IO21" s="43"/>
+      <c r="IP21" s="43"/>
+      <c r="IQ21" s="43"/>
+      <c r="IR21" s="43"/>
+      <c r="IS21" s="43"/>
+      <c r="IT21" s="43"/>
+      <c r="IU21" s="43"/>
+      <c r="IV21" s="43"/>
+      <c r="IW21" s="43"/>
+      <c r="IX21" s="43"/>
+      <c r="IY21" s="43"/>
+      <c r="IZ21" s="43"/>
+      <c r="JA21" s="43"/>
+      <c r="JB21" s="43"/>
+      <c r="JC21" s="43"/>
+      <c r="JD21" s="43"/>
+      <c r="JE21" s="43"/>
+      <c r="JF21" s="43"/>
+      <c r="JG21" s="43"/>
+      <c r="JH21" s="43"/>
+      <c r="JI21" s="43"/>
+      <c r="JJ21" s="43"/>
+      <c r="JK21" s="43"/>
+      <c r="JL21" s="43"/>
+      <c r="JM21" s="43"/>
+      <c r="JN21" s="43"/>
     </row>
     <row r="22" ht="42.75">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="43" t="s">
+      <c r="D22" s="44" t="s">
         <v>173</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E22" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="44" t="s">
+      <c r="F22" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="G22" s="43" t="s">
+      <c r="G22" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="H22" s="43" t="s">
+      <c r="H22" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="45" t="s">
+      <c r="I22" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="J22" s="43" t="s">
+      <c r="J22" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="K22" s="46">
+      <c r="K22" s="47">
         <v>2010</v>
       </c>
-      <c r="L22" s="46" t="s">
+      <c r="L22" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="M22" s="43"/>
-      <c r="N22" s="47" t="s">
+      <c r="M22" s="44"/>
+      <c r="N22" s="48" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="23" s="16" customFormat="1" ht="25.5">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="43" t="s">
+      <c r="D23" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="E23" s="46" t="s">
+      <c r="E23" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="F23" s="44" t="s">
+      <c r="F23" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43" t="s">
+      <c r="G23" s="44"/>
+      <c r="H23" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="I23" s="48" t="s">
+      <c r="I23" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="J23" s="43" t="s">
+      <c r="J23" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="K23" s="46">
+      <c r="K23" s="47">
         <v>2010</v>
       </c>
-      <c r="L23" s="46" t="s">
+      <c r="L23" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="M23" s="43"/>
-      <c r="N23" s="49" t="s">
+      <c r="M23" s="44"/>
+      <c r="N23" s="50" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="24" ht="28.5">
-      <c r="A24" s="43" t="s">
+      <c r="A24" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="43" t="s">
+      <c r="C24" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="D24" s="43" t="s">
+      <c r="D24" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="E24" s="43" t="s">
+      <c r="E24" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="F24" s="44" t="s">
+      <c r="F24" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43" t="s">
+      <c r="G24" s="44"/>
+      <c r="H24" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="I24" s="50" t="s">
+      <c r="I24" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="J24" s="43" t="s">
+      <c r="J24" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="K24" s="46">
+      <c r="K24" s="47">
         <v>2010</v>
       </c>
-      <c r="L24" s="46" t="s">
+      <c r="L24" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="M24" s="43"/>
-      <c r="N24" s="47" t="s">
+      <c r="M24" s="44"/>
+      <c r="N24" s="48" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="25" ht="25.5">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="B25" s="51" t="s">
+      <c r="B25" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="52" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="51" t="s">
+      <c r="D25" s="52" t="s">
         <v>188</v>
       </c>
-      <c r="E25" s="51" t="s">
+      <c r="E25" s="52" t="s">
         <v>189</v>
       </c>
-      <c r="F25" s="52" t="s">
+      <c r="F25" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="53" t="s">
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="54" t="s">
         <v>191</v>
       </c>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51">
+      <c r="J25" s="52"/>
+      <c r="K25" s="52">
         <v>2016</v>
       </c>
-      <c r="L25" s="51" t="s">
+      <c r="L25" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="M25" s="51"/>
+      <c r="M25" s="52"/>
       <c r="N25" s="25"/>
     </row>
     <row r="26" ht="25.5">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="52" t="s">
         <v>187</v>
       </c>
-      <c r="D26" s="51" t="s">
+      <c r="D26" s="52" t="s">
         <v>193</v>
       </c>
-      <c r="E26" s="51" t="s">
+      <c r="E26" s="52" t="s">
         <v>189</v>
       </c>
-      <c r="F26" s="52" t="s">
+      <c r="F26" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="55"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="51"/>
-      <c r="M26" s="51"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="52"/>
       <c r="N26" s="25"/>
     </row>
     <row r="27" ht="25.5">
-      <c r="A27" s="51" t="s">
+      <c r="A27" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="52" t="s">
         <v>195</v>
       </c>
-      <c r="D27" s="51" t="s">
+      <c r="D27" s="52" t="s">
         <v>196</v>
       </c>
-      <c r="E27" s="51" t="s">
+      <c r="E27" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="F27" s="51" t="s">
+      <c r="F27" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="53" t="s">
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="J27" s="56"/>
-      <c r="K27" s="51"/>
-      <c r="L27" s="51"/>
-      <c r="M27" s="51"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
       <c r="N27" s="25"/>
     </row>
     <row r="28" ht="38.25">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="51" t="s">
+      <c r="B28" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="51" t="s">
+      <c r="D28" s="52" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="51" t="s">
+      <c r="E28" s="52" t="s">
         <v>201</v>
       </c>
-      <c r="F28" s="57" t="s">
+      <c r="F28" s="58" t="s">
         <v>202</v>
       </c>
-      <c r="G28" s="51" t="s">
+      <c r="G28" s="52" t="s">
         <v>203</v>
       </c>
-      <c r="H28" s="51" t="s">
+      <c r="H28" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="I28" s="58" t="s">
+      <c r="I28" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="J28" s="51" t="s">
+      <c r="J28" s="52" t="s">
         <v>205</v>
       </c>
-      <c r="K28" s="51"/>
-      <c r="L28" s="51" t="s">
+      <c r="K28" s="52"/>
+      <c r="L28" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="M28" s="51"/>
-      <c r="N28" s="59" t="s">
+      <c r="M28" s="52"/>
+      <c r="N28" s="60" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="29" ht="89.25">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="51" t="s">
+      <c r="D29" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="E29" s="51" t="s">
+      <c r="E29" s="52" t="s">
         <v>208</v>
       </c>
-      <c r="F29" s="51" t="s">
+      <c r="F29" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="51" t="s">
+      <c r="G29" s="52" t="s">
         <v>209</v>
       </c>
-      <c r="H29" s="51" t="s">
+      <c r="H29" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="58" t="s">
+      <c r="I29" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="J29" s="51" t="s">
+      <c r="J29" s="52" t="s">
         <v>210</v>
       </c>
-      <c r="K29" s="51" t="s">
+      <c r="K29" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="L29" s="51" t="s">
+      <c r="L29" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="51"/>
-      <c r="N29" s="59" t="s">
+      <c r="M29" s="52"/>
+      <c r="N29" s="60" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="30" ht="25.5">
-      <c r="A30" s="60" t="s">
+      <c r="A30" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="B30" s="60" t="s">
+      <c r="B30" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="60" t="s">
+      <c r="C30" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="60" t="s">
+      <c r="D30" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="E30" s="60" t="s">
+      <c r="E30" s="61" t="s">
         <v>213</v>
       </c>
-      <c r="F30" s="61"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="62" t="s">
+      <c r="F30" s="62"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="63" t="s">
         <v>214</v>
       </c>
-      <c r="J30" s="63"/>
-      <c r="K30" s="60"/>
-      <c r="L30" s="60" t="s">
+      <c r="J30" s="64"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="61" t="s">
         <v>215</v>
       </c>
-      <c r="M30" s="60"/>
+      <c r="M30" s="61"/>
       <c r="N30" s="36"/>
     </row>
     <row r="31" ht="25.5">
-      <c r="A31" s="60" t="s">
+      <c r="A31" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="60" t="s">
+      <c r="C31" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="60" t="s">
+      <c r="D31" s="61" t="s">
         <v>216</v>
       </c>
-      <c r="E31" s="60" t="s">
+      <c r="E31" s="61" t="s">
         <v>213</v>
       </c>
-      <c r="F31" s="61"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="62" t="s">
+      <c r="F31" s="62"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="63" t="s">
         <v>217</v>
       </c>
-      <c r="J31" s="60"/>
-      <c r="K31" s="60"/>
-      <c r="L31" s="60"/>
-      <c r="M31" s="60"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="61"/>
       <c r="N31" s="36"/>
     </row>
     <row r="32" ht="25.5">
-      <c r="A32" s="60" t="s">
+      <c r="A32" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="60" t="s">
+      <c r="C32" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="D32" s="60" t="s">
+      <c r="D32" s="61" t="s">
         <v>218</v>
       </c>
-      <c r="E32" s="60" t="s">
+      <c r="E32" s="61" t="s">
         <v>213</v>
       </c>
-      <c r="F32" s="61"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="62" t="s">
+      <c r="F32" s="62"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="63" t="s">
         <v>214</v>
       </c>
-      <c r="J32" s="63"/>
-      <c r="K32" s="60"/>
-      <c r="L32" s="60" t="s">
+      <c r="J32" s="64"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61" t="s">
         <v>215</v>
       </c>
-      <c r="M32" s="60"/>
+      <c r="M32" s="61"/>
       <c r="N32" s="36"/>
     </row>
     <row r="33" ht="25.5">
-      <c r="A33" s="60" t="s">
+      <c r="A33" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="B33" s="60" t="s">
+      <c r="B33" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="60" t="s">
+      <c r="C33" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="D33" s="60" t="s">
+      <c r="D33" s="61" t="s">
         <v>219</v>
       </c>
-      <c r="E33" s="60"/>
-      <c r="F33" s="61" t="s">
+      <c r="E33" s="61"/>
+      <c r="F33" s="62" t="s">
         <v>220</v>
       </c>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="60"/>
-      <c r="K33" s="60"/>
-      <c r="L33" s="60"/>
-      <c r="M33" s="60"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="65"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
+      <c r="L33" s="61"/>
+      <c r="M33" s="61"/>
       <c r="N33" s="36"/>
     </row>
     <row r="34" ht="25.5">
-      <c r="A34" s="60" t="s">
+      <c r="A34" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="B34" s="60" t="s">
+      <c r="B34" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="C34" s="60" t="s">
+      <c r="C34" s="61" t="s">
         <v>195</v>
       </c>
-      <c r="D34" s="60" t="s">
+      <c r="D34" s="61" t="s">
         <v>221</v>
       </c>
-      <c r="E34" s="60" t="s">
+      <c r="E34" s="61" t="s">
         <v>213</v>
       </c>
-      <c r="F34" s="61"/>
-      <c r="G34" s="60"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="65"/>
-      <c r="J34" s="60"/>
-      <c r="K34" s="60"/>
-      <c r="L34" s="60"/>
-      <c r="M34" s="60"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="66"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="61"/>
       <c r="N34" s="36"/>
     </row>
     <row r="35" ht="38.25">
-      <c r="A35" s="60" t="s">
+      <c r="A35" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="B35" s="60" t="s">
+      <c r="B35" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="60" t="s">
+      <c r="C35" s="61" t="s">
         <v>195</v>
       </c>
-      <c r="D35" s="60" t="s">
+      <c r="D35" s="61" t="s">
         <v>222</v>
       </c>
-      <c r="E35" s="60" t="s">
+      <c r="E35" s="61" t="s">
         <v>213</v>
       </c>
-      <c r="F35" s="61" t="s">
+      <c r="F35" s="62" t="s">
         <v>223</v>
       </c>
-      <c r="G35" s="60"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="62" t="s">
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="63" t="s">
         <v>224</v>
       </c>
-      <c r="J35" s="60"/>
-      <c r="K35" s="60"/>
-      <c r="L35" s="60"/>
-      <c r="M35" s="60"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="61"/>
+      <c r="M35" s="61"/>
       <c r="N35" s="36"/>
     </row>
     <row r="36" ht="38.25">
-      <c r="A36" s="60" t="s">
+      <c r="A36" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="B36" s="60" t="s">
+      <c r="B36" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="60" t="s">
+      <c r="C36" s="61" t="s">
         <v>225</v>
       </c>
-      <c r="D36" s="60" t="s">
+      <c r="D36" s="61" t="s">
         <v>226</v>
       </c>
-      <c r="E36" s="60" t="s">
+      <c r="E36" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="F36" s="61" t="s">
+      <c r="F36" s="62" t="s">
         <v>228</v>
       </c>
-      <c r="G36" s="60"/>
-      <c r="H36" s="60"/>
-      <c r="I36" s="62" t="s">
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="63" t="s">
         <v>229</v>
       </c>
-      <c r="J36" s="60"/>
-      <c r="K36" s="60"/>
-      <c r="L36" s="60" t="s">
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="M36" s="60"/>
+      <c r="M36" s="61"/>
       <c r="N36" s="36"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="60" t="s">
+      <c r="A37" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="B37" s="60" t="s">
+      <c r="B37" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="60" t="s">
+      <c r="C37" s="61" t="s">
         <v>230</v>
       </c>
-      <c r="D37" s="60" t="s">
+      <c r="D37" s="61" t="s">
         <v>231</v>
       </c>
-      <c r="E37" s="60" t="s">
+      <c r="E37" s="61" t="s">
         <v>213</v>
       </c>
-      <c r="F37" s="60"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="66"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="60"/>
-      <c r="L37" s="60"/>
-      <c r="M37" s="60"/>
-      <c r="N37" s="60" t="s">
+      <c r="F37" s="61"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="67"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="61"/>
+      <c r="N37" s="61" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="38" ht="51">
-      <c r="A38" s="60" t="s">
+      <c r="A38" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="B38" s="60" t="s">
+      <c r="B38" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="60" t="s">
+      <c r="C38" s="61" t="s">
         <v>230</v>
       </c>
-      <c r="D38" s="60" t="s">
+      <c r="D38" s="61" t="s">
         <v>233</v>
       </c>
-      <c r="E38" s="60" t="s">
+      <c r="E38" s="61" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="60"/>
-      <c r="G38" s="60"/>
-      <c r="H38" s="60"/>
-      <c r="I38" s="66"/>
-      <c r="J38" s="60"/>
-      <c r="K38" s="60"/>
-      <c r="L38" s="60"/>
-      <c r="M38" s="60"/>
-      <c r="N38" s="60" t="s">
+      <c r="F38" s="61"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="61"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="61"/>
+      <c r="M38" s="61"/>
+      <c r="N38" s="61" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="39" ht="51">
-      <c r="A39" s="60" t="s">
+      <c r="A39" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="B39" s="60" t="s">
+      <c r="B39" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="60" t="s">
+      <c r="C39" s="61" t="s">
         <v>234</v>
       </c>
-      <c r="D39" s="60" t="s">
+      <c r="D39" s="61" t="s">
         <v>235</v>
       </c>
-      <c r="E39" s="60" t="s">
+      <c r="E39" s="61" t="s">
         <v>236</v>
       </c>
-      <c r="F39" s="67" t="s">
+      <c r="F39" s="68" t="s">
         <v>237</v>
       </c>
-      <c r="G39" s="60"/>
-      <c r="H39" s="60"/>
-      <c r="I39" s="66"/>
-      <c r="J39" s="60"/>
-      <c r="K39" s="60"/>
-      <c r="L39" s="60"/>
-      <c r="M39" s="60"/>
-      <c r="N39" s="60" t="s">
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="61"/>
+      <c r="M39" s="61"/>
+      <c r="N39" s="61" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="40" s="10" customFormat="1" ht="25.5">
-      <c r="A40" s="60" t="s">
+      <c r="A40" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="B40" s="60" t="s">
+      <c r="B40" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="60" t="s">
+      <c r="C40" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="60" t="s">
+      <c r="D40" s="61" t="s">
         <v>238</v>
       </c>
-      <c r="E40" s="60" t="s">
+      <c r="E40" s="61" t="s">
         <v>213</v>
       </c>
-      <c r="F40" s="60"/>
-      <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="60"/>
-      <c r="K40" s="60"/>
-      <c r="L40" s="60"/>
-      <c r="M40" s="60"/>
-      <c r="N40" s="60" t="s">
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="61"/>
+      <c r="M40" s="61"/>
+      <c r="N40" s="61" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="68" t="s">
+      <c r="A41" s="69" t="s">
         <v>239</v>
       </c>
-      <c r="B41" s="68" t="s">
+      <c r="B41" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="68" t="s">
+      <c r="C41" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="68" t="s">
+      <c r="D41" s="69" t="s">
         <v>240</v>
       </c>
-      <c r="E41" s="68" t="s">
+      <c r="E41" s="69" t="s">
         <v>241</v>
       </c>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68" t="s">
+      <c r="F41" s="69"/>
+      <c r="G41" s="69" t="s">
         <v>242</v>
       </c>
-      <c r="H41" s="68" t="s">
+      <c r="H41" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="I41" s="69"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="68"/>
-      <c r="M41" s="68" t="s">
+      <c r="I41" s="70"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
+      <c r="L41" s="69"/>
+      <c r="M41" s="69" t="s">
         <v>140</v>
       </c>
-      <c r="N41" s="68"/>
+      <c r="N41" s="69"/>
     </row>
     <row r="42" ht="14.25">
       <c r="A42" s="1"/>
-      <c r="M42" s="70"/>
-      <c r="N42" s="70"/>
+      <c r="M42" s="71"/>
+      <c r="N42" s="71"/>
     </row>
     <row r="43" ht="14.25">
-      <c r="M43" s="70"/>
-      <c r="N43" s="70"/>
+      <c r="M43" s="71"/>
+      <c r="N43" s="71"/>
     </row>
     <row r="44" ht="14.25">
-      <c r="M44" s="70"/>
-      <c r="N44" s="70"/>
+      <c r="M44" s="71"/>
+      <c r="N44" s="71"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="M45" s="70"/>
-      <c r="N45" s="70"/>
+      <c r="M45" s="71"/>
+      <c r="N45" s="71"/>
     </row>
     <row r="46" ht="14.25">
-      <c r="M46" s="70"/>
-      <c r="N46" s="70"/>
+      <c r="M46" s="71"/>
+      <c r="N46" s="71"/>
     </row>
     <row r="47" ht="14.25">
-      <c r="M47" s="70"/>
-      <c r="N47" s="70"/>
+      <c r="M47" s="71"/>
+      <c r="N47" s="71"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="M48" s="70"/>
-      <c r="N48" s="70"/>
+      <c r="M48" s="71"/>
+      <c r="N48" s="71"/>
     </row>
     <row r="49" ht="14.25">
-      <c r="M49" s="70"/>
-      <c r="N49" s="70"/>
+      <c r="M49" s="71"/>
+      <c r="N49" s="71"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="M50" s="70"/>
-      <c r="N50" s="70"/>
+      <c r="M50" s="71"/>
+      <c r="N50" s="71"/>
     </row>
     <row r="51" ht="14.25">
-      <c r="M51" s="70"/>
-      <c r="N51" s="70"/>
+      <c r="M51" s="71"/>
+      <c r="N51" s="71"/>
     </row>
     <row r="52" ht="14.25">
-      <c r="M52" s="70"/>
-      <c r="N52" s="70"/>
+      <c r="M52" s="71"/>
+      <c r="N52" s="71"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="M53" s="70"/>
-      <c r="N53" s="70"/>
+      <c r="M53" s="71"/>
+      <c r="N53" s="71"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="M54" s="70"/>
-      <c r="N54" s="70"/>
+      <c r="M54" s="71"/>
+      <c r="N54" s="71"/>
     </row>
     <row r="55" ht="14.25">
-      <c r="M55" s="70"/>
-      <c r="N55" s="70"/>
+      <c r="M55" s="71"/>
+      <c r="N55" s="71"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="M56" s="70"/>
-      <c r="N56" s="70"/>
+      <c r="M56" s="71"/>
+      <c r="N56" s="71"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N41">
@@ -8644,18 +8649,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="72" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="2" s="0" customFormat="1" ht="14.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="74" t="s">
         <v>245</v>
       </c>
       <c r="C2"/>
@@ -8669,7 +8674,7 @@
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="44" t="s">
         <v>172</v>
       </c>
       <c r="B4" t="s">
@@ -8677,7 +8682,7 @@
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="52" t="s">
         <v>186</v>
       </c>
       <c r="B5" t="s">
@@ -8685,7 +8690,7 @@
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="61" t="s">
         <v>211</v>
       </c>
       <c r="B6" t="s">
@@ -8693,7 +8698,7 @@
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="69" t="s">
         <v>239</v>
       </c>
       <c r="B7" t="s">
@@ -8720,19 +8725,19 @@
     <col customWidth="1" min="6" max="6" width="12.8515625"/>
     <col bestFit="1" customWidth="1" min="7" max="7" width="25.78125"/>
     <col bestFit="1" customWidth="1" min="8" max="8" width="21.3515625"/>
-    <col customWidth="1" min="9" max="9" style="74" width="32.7109375"/>
+    <col customWidth="1" min="9" max="9" style="75" width="32.7109375"/>
     <col customWidth="1" min="10" max="10" width="23.57421875"/>
     <col customWidth="1" min="11" max="11" width="44.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" s="71" customFormat="1" ht="25.5">
-      <c r="A1" s="71" t="s">
+    <row r="1" s="72" customFormat="1" ht="25.5">
+      <c r="A1" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="72" t="s">
         <v>251</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="72" t="s">
         <v>252</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -8750,48 +8755,48 @@
       <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="75" t="s">
+      <c r="I1" s="76" t="s">
         <v>253</v>
       </c>
-      <c r="J1" s="71" t="s">
+      <c r="J1" s="72" t="s">
         <v>254</v>
       </c>
-      <c r="K1" s="71" t="s">
+      <c r="K1" s="72" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="76" customFormat="1" ht="28.5">
-      <c r="A2" s="77" t="s">
+    <row r="2" s="77" customFormat="1" ht="28.5">
+      <c r="A2" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="79" t="s">
         <v>255</v>
       </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="78" t="s">
         <v>256</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="D2" s="79" t="s">
         <v>257</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="79" t="s">
         <v>258</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="79" t="s">
         <v>259</v>
       </c>
-      <c r="G2" s="76" t="s">
+      <c r="G2" s="77" t="s">
         <v>260</v>
       </c>
-      <c r="H2" s="77" t="s">
+      <c r="H2" s="78" t="s">
         <v>261</v>
       </c>
-      <c r="I2" s="79" t="s">
+      <c r="I2" s="80" t="s">
         <v>262</v>
       </c>
-      <c r="J2" s="76" t="s">
+      <c r="J2" s="77" t="s">
         <v>263</v>
       </c>
-      <c r="K2" s="80" t="s">
+      <c r="K2" s="81" t="s">
         <v>264</v>
       </c>
     </row>

--- a/progress/megatrends_RF.xlsx
+++ b/progress/megatrends_RF.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="270">
   <si>
     <t>Calcul</t>
   </si>
@@ -393,7 +393,7 @@
     <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=stru_2020_1.nbexpl20&amp;t=A02&amp;view=map11</t>
   </si>
   <si>
-    <t>data_Agreste_Commune.csv</t>
+    <t>data_Agreste_Commune2020.csv</t>
   </si>
   <si>
     <t>02h_get_agreste.R</t>
@@ -429,6 +429,52 @@
     <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=stru_2020_1.pbs20&amp;t=A02&amp;view=map11</t>
   </si>
   <si>
+    <t xml:space="preserve">Education level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pct_Superieur → Percent of farm holders with higher education.</t>
+  </si>
+  <si>
+    <t>AGRESTE_EDUSUP_PCT_2010</t>
+  </si>
+  <si>
+    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=empl1.partformsup10&amp;t=A02&amp;view=map1</t>
+  </si>
+  <si>
+    <t>data_Agreste_Commune2010.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changes in the farmer populations </t>
+  </si>
+  <si>
+    <t xml:space="preserve">farm size</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Average farm size per commune
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="2"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OPPOSITE OF Density of farmer</t>
+    </r>
+  </si>
+  <si>
+    <t>AGRESTE_FARMSIZE_HA_2010</t>
+  </si>
+  <si>
+    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=raanc2.saumoyaa&amp;s=2010&amp;t=A02&amp;view=map1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Crop rotation</t>
   </si>
   <si>
@@ -454,6 +500,40 @@
   </si>
   <si>
     <t xml:space="preserve">could be calculated per field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance to a training center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euclidean distance (in km) from the centroid of each municipality to the centroid of the nearest municipality containing one or more agricultural training centers.</t>
+  </si>
+  <si>
+    <t>MASA</t>
+  </si>
+  <si>
+    <t>REFEA_DIST_KM_2025</t>
+  </si>
+  <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>https://www.data.gouv.fr/fr/datasets/refea-liste-des-etablissements-proposant-des-formations-agricoles/</t>
+  </si>
+  <si>
+    <t>refea_2025-2026.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2006, 2026</t>
+  </si>
+  <si>
+    <t>coordinates</t>
+  </si>
+  <si>
+    <t>02j_get_refea.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://enseignement-agricole.opendatasoft.com/explore/dataset/uai_vu1_1_1/export/
+https://enseignement-agricole.opendatasoft.com/explore/dataset/refea-liste-des-etablissements-proposant-des-formations-agricoles-2025-2026/export/</t>
   </si>
   <si>
     <t xml:space="preserve">1. almost</t>
@@ -486,56 +566,6 @@
   <si>
     <t xml:space="preserve">not same commune (3000 mismatch)
 can it be calculated at maille level?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distance to a training center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euclidean distance (in km) from the centroid of each municipality to the centroid of the nearest municipality containing one or more agricultural training centers.</t>
-  </si>
-  <si>
-    <t>MASA</t>
-  </si>
-  <si>
-    <t>DIST_TRAIN</t>
-  </si>
-  <si>
-    <t>km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.data.gouv.fr/fr/datasets/refea-liste-des-etablissements-proposant-des-formations-agricoles/
-https://enseignement-agricole.opendatasoft.com/explore/dataset/uai_vu1_1_1/export/
-https://enseignement-agricole.opendatasoft.com/explore/dataset/refea-liste-des-etablissements-proposant-des-formations-agricoles-2025-2026/export/</t>
-  </si>
-  <si>
-    <t>refea_2025-2026.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2006, 2026</t>
-  </si>
-  <si>
-    <t>coordinates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Education level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pct_Superieur → Percent of farm holders with higher education.</t>
-  </si>
-  <si>
-    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=empl1.partformsup10&amp;t=A02&amp;view=map1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changes in the farmer populations </t>
-  </si>
-  <si>
-    <t xml:space="preserve">farm size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average farm size per commune</t>
-  </si>
-  <si>
-    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=raanc2.saumoyaa&amp;s=2010&amp;t=A02&amp;view=map1</t>
   </si>
   <si>
     <t>Urbanization</t>
@@ -978,14 +1008,13 @@
     </font>
     <font>
       <sz val="10.000000"/>
-      <color indexed="2"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="10.000000"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
+      <color indexed="2"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -1008,7 +1037,8 @@
     <font>
       <sz val="10.000000"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1044,12 +1074,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="-0.249977111117893"/>
-        <bgColor theme="7" tint="-0.249977111117893"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.099978637043366805"/>
         <bgColor theme="2" tint="-0.099978637043366805"/>
       </patternFill>
@@ -1058,6 +1082,12 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor theme="7" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor theme="7" tint="-0.249977111117893"/>
       </patternFill>
     </fill>
   </fills>
@@ -1073,7 +1103,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="78">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1147,13 +1177,19 @@
     <xf fontId="10" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="11" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf fontId="2" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="12" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="12" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1161,28 +1197,6 @@
     </xf>
     <xf fontId="2" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="5" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="6" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="12" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1194,26 +1208,29 @@
       <alignment vertical="center"/>
     </xf>
     <xf fontId="10" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="5" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="3" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="4" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="13" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="13" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="14" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="14" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="9" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="3" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="9" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="3" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="2" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1234,7 +1251,7 @@
     <xf fontId="6" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="11" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="12" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1243,37 +1260,38 @@
     <xf fontId="1" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="2" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="5" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="11" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="12" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="2" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf fontId="5" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="6" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="17" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="5" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="17" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6055,10 +6073,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>123</v>
@@ -6066,31 +6084,31 @@
       <c r="E15" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="18" t="s">
+      <c r="J15" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>129</v>
+      <c r="K15" s="9">
+        <v>2010</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M15" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>131</v>
-      </c>
+      <c r="M15" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="N15" s="27"/>
       <c r="O15" s="16"/>
       <c r="P15" s="16"/>
       <c r="Q15" s="16"/>
@@ -6353,48 +6371,46 @@
       <c r="JN15" s="16"/>
     </row>
     <row r="16" s="6" customFormat="1" ht="51">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="B16" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="H16" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="J16" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="K16" s="27">
-        <v>2023</v>
-      </c>
-      <c r="L16" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="N16" s="28" t="s">
-        <v>141</v>
-      </c>
+      <c r="J16" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="K16" s="9">
+        <v>2010</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M16" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="N16" s="10"/>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
@@ -6656,381 +6672,395 @@
       <c r="JM16" s="10"/>
       <c r="JN16" s="10"/>
     </row>
-    <row r="17" s="30" customFormat="1" ht="38.25">
-      <c r="A17" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="F17" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="H17" s="27" t="s">
-        <v>146</v>
-      </c>
-      <c r="I17" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="J17" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="L17" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="M17" s="27"/>
-      <c r="N17" s="16"/>
+    <row r="17" s="6" customFormat="1" ht="38.25">
+      <c r="A17" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="18" s="6" customFormat="1" ht="25.5">
-      <c r="A18" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="B18" s="27" t="s">
+      <c r="A18" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="M18" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="N18" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="F18" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27" t="s">
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
+      <c r="AA18" s="10"/>
+      <c r="AB18" s="10"/>
+      <c r="AC18" s="10"/>
+      <c r="AD18" s="10"/>
+      <c r="AE18" s="10"/>
+      <c r="AF18" s="10"/>
+      <c r="AG18" s="10"/>
+      <c r="AH18" s="10"/>
+      <c r="AI18" s="10"/>
+      <c r="AJ18" s="10"/>
+      <c r="AK18" s="10"/>
+      <c r="AL18" s="10"/>
+      <c r="AM18" s="10"/>
+      <c r="AN18" s="10"/>
+      <c r="AO18" s="10"/>
+      <c r="AP18" s="10"/>
+      <c r="AQ18" s="10"/>
+      <c r="AR18" s="10"/>
+      <c r="AS18" s="10"/>
+      <c r="AT18" s="10"/>
+      <c r="AU18" s="10"/>
+      <c r="AV18" s="10"/>
+      <c r="AW18" s="10"/>
+      <c r="AX18" s="10"/>
+      <c r="AY18" s="10"/>
+      <c r="AZ18" s="10"/>
+      <c r="BA18" s="10"/>
+      <c r="BB18" s="10"/>
+      <c r="BC18" s="10"/>
+      <c r="BD18" s="10"/>
+      <c r="BE18" s="10"/>
+      <c r="BF18" s="10"/>
+      <c r="BG18" s="10"/>
+      <c r="BH18" s="10"/>
+      <c r="BI18" s="10"/>
+      <c r="BJ18" s="10"/>
+      <c r="BK18" s="10"/>
+      <c r="BL18" s="10"/>
+      <c r="BM18" s="10"/>
+      <c r="BN18" s="10"/>
+      <c r="BO18" s="10"/>
+      <c r="BP18" s="10"/>
+      <c r="BQ18" s="10"/>
+      <c r="BR18" s="10"/>
+      <c r="BS18" s="10"/>
+      <c r="BT18" s="10"/>
+      <c r="BU18" s="10"/>
+      <c r="BV18" s="10"/>
+      <c r="BW18" s="10"/>
+      <c r="BX18" s="10"/>
+      <c r="BY18" s="10"/>
+      <c r="BZ18" s="10"/>
+      <c r="CA18" s="10"/>
+      <c r="CB18" s="10"/>
+      <c r="CC18" s="10"/>
+      <c r="CD18" s="10"/>
+      <c r="CE18" s="10"/>
+      <c r="CF18" s="10"/>
+      <c r="CG18" s="10"/>
+      <c r="CH18" s="10"/>
+      <c r="CI18" s="10"/>
+      <c r="CJ18" s="10"/>
+      <c r="CK18" s="10"/>
+      <c r="CL18" s="10"/>
+      <c r="CM18" s="10"/>
+      <c r="CN18" s="10"/>
+      <c r="CO18" s="10"/>
+      <c r="CP18" s="10"/>
+      <c r="CQ18" s="10"/>
+      <c r="CR18" s="10"/>
+      <c r="CS18" s="10"/>
+      <c r="CT18" s="10"/>
+      <c r="CU18" s="10"/>
+      <c r="CV18" s="10"/>
+      <c r="CW18" s="10"/>
+      <c r="CX18" s="10"/>
+      <c r="CY18" s="10"/>
+      <c r="CZ18" s="10"/>
+      <c r="DA18" s="10"/>
+      <c r="DB18" s="10"/>
+      <c r="DC18" s="10"/>
+      <c r="DD18" s="10"/>
+      <c r="DE18" s="10"/>
+      <c r="DF18" s="10"/>
+      <c r="DG18" s="10"/>
+      <c r="DH18" s="10"/>
+      <c r="DI18" s="10"/>
+      <c r="DJ18" s="10"/>
+      <c r="DK18" s="10"/>
+      <c r="DL18" s="10"/>
+      <c r="DM18" s="10"/>
+      <c r="DN18" s="10"/>
+      <c r="DO18" s="10"/>
+      <c r="DP18" s="10"/>
+      <c r="DQ18" s="10"/>
+      <c r="DR18" s="10"/>
+      <c r="DS18" s="10"/>
+      <c r="DT18" s="10"/>
+      <c r="DU18" s="10"/>
+      <c r="DV18" s="10"/>
+      <c r="DW18" s="10"/>
+      <c r="DX18" s="10"/>
+      <c r="DY18" s="10"/>
+      <c r="DZ18" s="10"/>
+      <c r="EA18" s="10"/>
+      <c r="EB18" s="10"/>
+      <c r="EC18" s="10"/>
+      <c r="ED18" s="10"/>
+      <c r="EE18" s="10"/>
+      <c r="EF18" s="10"/>
+      <c r="EG18" s="10"/>
+      <c r="EH18" s="10"/>
+      <c r="EI18" s="10"/>
+      <c r="EJ18" s="10"/>
+      <c r="EK18" s="10"/>
+      <c r="EL18" s="10"/>
+      <c r="EM18" s="10"/>
+      <c r="EN18" s="10"/>
+      <c r="EO18" s="10"/>
+      <c r="EP18" s="10"/>
+      <c r="EQ18" s="10"/>
+      <c r="ER18" s="10"/>
+      <c r="ES18" s="10"/>
+      <c r="ET18" s="10"/>
+      <c r="EU18" s="10"/>
+      <c r="EV18" s="10"/>
+      <c r="EW18" s="10"/>
+      <c r="EX18" s="10"/>
+      <c r="EY18" s="10"/>
+      <c r="EZ18" s="10"/>
+      <c r="FA18" s="10"/>
+      <c r="FB18" s="10"/>
+      <c r="FC18" s="10"/>
+      <c r="FD18" s="10"/>
+      <c r="FE18" s="10"/>
+      <c r="FF18" s="10"/>
+      <c r="FG18" s="10"/>
+      <c r="FH18" s="10"/>
+      <c r="FI18" s="10"/>
+      <c r="FJ18" s="10"/>
+      <c r="FK18" s="10"/>
+      <c r="FL18" s="10"/>
+      <c r="FM18" s="10"/>
+      <c r="FN18" s="10"/>
+      <c r="FO18" s="10"/>
+      <c r="FP18" s="10"/>
+      <c r="FQ18" s="10"/>
+      <c r="FR18" s="10"/>
+      <c r="FS18" s="10"/>
+      <c r="FT18" s="10"/>
+      <c r="FU18" s="10"/>
+      <c r="FV18" s="10"/>
+      <c r="FW18" s="10"/>
+      <c r="FX18" s="10"/>
+      <c r="FY18" s="10"/>
+      <c r="FZ18" s="10"/>
+      <c r="GA18" s="10"/>
+      <c r="GB18" s="10"/>
+      <c r="GC18" s="10"/>
+      <c r="GD18" s="10"/>
+      <c r="GE18" s="10"/>
+      <c r="GF18" s="10"/>
+      <c r="GG18" s="10"/>
+      <c r="GH18" s="10"/>
+      <c r="GI18" s="10"/>
+      <c r="GJ18" s="10"/>
+      <c r="GK18" s="10"/>
+      <c r="GL18" s="10"/>
+      <c r="GM18" s="10"/>
+      <c r="GN18" s="10"/>
+      <c r="GO18" s="10"/>
+      <c r="GP18" s="10"/>
+      <c r="GQ18" s="10"/>
+      <c r="GR18" s="10"/>
+      <c r="GS18" s="10"/>
+      <c r="GT18" s="10"/>
+      <c r="GU18" s="10"/>
+      <c r="GV18" s="10"/>
+      <c r="GW18" s="10"/>
+      <c r="GX18" s="10"/>
+      <c r="GY18" s="10"/>
+      <c r="GZ18" s="10"/>
+      <c r="HA18" s="10"/>
+      <c r="HB18" s="10"/>
+      <c r="HC18" s="10"/>
+      <c r="HD18" s="10"/>
+      <c r="HE18" s="10"/>
+      <c r="HF18" s="10"/>
+      <c r="HG18" s="10"/>
+      <c r="HH18" s="10"/>
+      <c r="HI18" s="10"/>
+      <c r="HJ18" s="10"/>
+      <c r="HK18" s="10"/>
+      <c r="HL18" s="10"/>
+      <c r="HM18" s="10"/>
+      <c r="HN18" s="10"/>
+      <c r="HO18" s="10"/>
+      <c r="HP18" s="10"/>
+      <c r="HQ18" s="10"/>
+      <c r="HR18" s="10"/>
+      <c r="HS18" s="10"/>
+      <c r="HT18" s="10"/>
+      <c r="HU18" s="10"/>
+      <c r="HV18" s="10"/>
+      <c r="HW18" s="10"/>
+      <c r="HX18" s="10"/>
+      <c r="HY18" s="10"/>
+      <c r="HZ18" s="10"/>
+      <c r="IA18" s="10"/>
+      <c r="IB18" s="10"/>
+      <c r="IC18" s="10"/>
+      <c r="ID18" s="10"/>
+      <c r="IE18" s="10"/>
+      <c r="IF18" s="10"/>
+      <c r="IG18" s="10"/>
+      <c r="IH18" s="10"/>
+      <c r="II18" s="10"/>
+      <c r="IJ18" s="10"/>
+      <c r="IK18" s="10"/>
+      <c r="IL18" s="10"/>
+      <c r="IM18" s="10"/>
+      <c r="IN18" s="10"/>
+      <c r="IO18" s="10"/>
+      <c r="IP18" s="10"/>
+      <c r="IQ18" s="10"/>
+      <c r="IR18" s="10"/>
+      <c r="IS18" s="10"/>
+      <c r="IT18" s="10"/>
+      <c r="IU18" s="10"/>
+      <c r="IV18" s="10"/>
+      <c r="IW18" s="10"/>
+      <c r="IX18" s="10"/>
+      <c r="IY18" s="10"/>
+      <c r="IZ18" s="10"/>
+      <c r="JA18" s="10"/>
+      <c r="JB18" s="10"/>
+      <c r="JC18" s="10"/>
+      <c r="JD18" s="10"/>
+      <c r="JE18" s="10"/>
+      <c r="JF18" s="10"/>
+      <c r="JG18" s="10"/>
+      <c r="JH18" s="10"/>
+      <c r="JI18" s="10"/>
+      <c r="JJ18" s="10"/>
+      <c r="JK18" s="10"/>
+      <c r="JL18" s="10"/>
+      <c r="JM18" s="10"/>
+      <c r="JN18" s="10"/>
+    </row>
+    <row r="19" s="6" customFormat="1" ht="28.5">
+      <c r="A19" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H19" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="I18" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="J18" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="K18" s="35">
-        <v>2010</v>
-      </c>
-      <c r="L18" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="M18" s="27"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
-      <c r="S18" s="36"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="36"/>
-      <c r="V18" s="36"/>
-      <c r="W18" s="36"/>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="36"/>
-      <c r="Z18" s="36"/>
-      <c r="AA18" s="36"/>
-      <c r="AB18" s="36"/>
-      <c r="AC18" s="36"/>
-      <c r="AD18" s="36"/>
-      <c r="AE18" s="36"/>
-      <c r="AF18" s="36"/>
-      <c r="AG18" s="36"/>
-      <c r="AH18" s="36"/>
-      <c r="AI18" s="36"/>
-      <c r="AJ18" s="36"/>
-      <c r="AK18" s="36"/>
-      <c r="AL18" s="36"/>
-      <c r="AM18" s="36"/>
-      <c r="AN18" s="36"/>
-      <c r="AO18" s="36"/>
-      <c r="AP18" s="36"/>
-      <c r="AQ18" s="36"/>
-      <c r="AR18" s="36"/>
-      <c r="AS18" s="36"/>
-      <c r="AT18" s="36"/>
-      <c r="AU18" s="36"/>
-      <c r="AV18" s="36"/>
-      <c r="AW18" s="36"/>
-      <c r="AX18" s="36"/>
-      <c r="AY18" s="36"/>
-      <c r="AZ18" s="36"/>
-      <c r="BA18" s="36"/>
-      <c r="BB18" s="36"/>
-      <c r="BC18" s="36"/>
-      <c r="BD18" s="36"/>
-      <c r="BE18" s="36"/>
-      <c r="BF18" s="36"/>
-      <c r="BG18" s="36"/>
-      <c r="BH18" s="36"/>
-      <c r="BI18" s="36"/>
-      <c r="BJ18" s="36"/>
-      <c r="BK18" s="36"/>
-      <c r="BL18" s="36"/>
-      <c r="BM18" s="36"/>
-      <c r="BN18" s="36"/>
-      <c r="BO18" s="36"/>
-      <c r="BP18" s="36"/>
-      <c r="BQ18" s="36"/>
-      <c r="BR18" s="36"/>
-      <c r="BS18" s="36"/>
-      <c r="BT18" s="36"/>
-      <c r="BU18" s="36"/>
-      <c r="BV18" s="36"/>
-      <c r="BW18" s="36"/>
-      <c r="BX18" s="36"/>
-      <c r="BY18" s="36"/>
-      <c r="BZ18" s="36"/>
-      <c r="CA18" s="36"/>
-      <c r="CB18" s="36"/>
-      <c r="CC18" s="36"/>
-      <c r="CD18" s="36"/>
-      <c r="CE18" s="36"/>
-      <c r="CF18" s="36"/>
-      <c r="CG18" s="36"/>
-      <c r="CH18" s="36"/>
-      <c r="CI18" s="36"/>
-      <c r="CJ18" s="36"/>
-      <c r="CK18" s="36"/>
-      <c r="CL18" s="36"/>
-      <c r="CM18" s="36"/>
-      <c r="CN18" s="36"/>
-      <c r="CO18" s="36"/>
-      <c r="CP18" s="36"/>
-      <c r="CQ18" s="36"/>
-      <c r="CR18" s="36"/>
-      <c r="CS18" s="36"/>
-      <c r="CT18" s="36"/>
-      <c r="CU18" s="36"/>
-      <c r="CV18" s="36"/>
-      <c r="CW18" s="36"/>
-      <c r="CX18" s="36"/>
-      <c r="CY18" s="36"/>
-      <c r="CZ18" s="36"/>
-      <c r="DA18" s="36"/>
-      <c r="DB18" s="36"/>
-      <c r="DC18" s="36"/>
-      <c r="DD18" s="36"/>
-      <c r="DE18" s="36"/>
-      <c r="DF18" s="36"/>
-      <c r="DG18" s="36"/>
-      <c r="DH18" s="36"/>
-      <c r="DI18" s="36"/>
-      <c r="DJ18" s="36"/>
-      <c r="DK18" s="36"/>
-      <c r="DL18" s="36"/>
-      <c r="DM18" s="36"/>
-      <c r="DN18" s="36"/>
-      <c r="DO18" s="36"/>
-      <c r="DP18" s="36"/>
-      <c r="DQ18" s="36"/>
-      <c r="DR18" s="36"/>
-      <c r="DS18" s="36"/>
-      <c r="DT18" s="36"/>
-      <c r="DU18" s="36"/>
-      <c r="DV18" s="36"/>
-      <c r="DW18" s="36"/>
-      <c r="DX18" s="36"/>
-      <c r="DY18" s="36"/>
-      <c r="DZ18" s="36"/>
-      <c r="EA18" s="36"/>
-      <c r="EB18" s="36"/>
-      <c r="EC18" s="36"/>
-      <c r="ED18" s="36"/>
-      <c r="EE18" s="36"/>
-      <c r="EF18" s="36"/>
-      <c r="EG18" s="36"/>
-      <c r="EH18" s="36"/>
-      <c r="EI18" s="36"/>
-      <c r="EJ18" s="36"/>
-      <c r="EK18" s="36"/>
-      <c r="EL18" s="36"/>
-      <c r="EM18" s="36"/>
-      <c r="EN18" s="36"/>
-      <c r="EO18" s="36"/>
-      <c r="EP18" s="36"/>
-      <c r="EQ18" s="36"/>
-      <c r="ER18" s="36"/>
-      <c r="ES18" s="36"/>
-      <c r="ET18" s="36"/>
-      <c r="EU18" s="36"/>
-      <c r="EV18" s="36"/>
-      <c r="EW18" s="36"/>
-      <c r="EX18" s="36"/>
-      <c r="EY18" s="36"/>
-      <c r="EZ18" s="36"/>
-      <c r="FA18" s="36"/>
-      <c r="FB18" s="36"/>
-      <c r="FC18" s="36"/>
-      <c r="FD18" s="36"/>
-      <c r="FE18" s="36"/>
-      <c r="FF18" s="36"/>
-      <c r="FG18" s="36"/>
-      <c r="FH18" s="36"/>
-      <c r="FI18" s="36"/>
-      <c r="FJ18" s="36"/>
-      <c r="FK18" s="36"/>
-      <c r="FL18" s="36"/>
-      <c r="FM18" s="36"/>
-      <c r="FN18" s="36"/>
-      <c r="FO18" s="36"/>
-      <c r="FP18" s="36"/>
-      <c r="FQ18" s="36"/>
-      <c r="FR18" s="36"/>
-      <c r="FS18" s="36"/>
-      <c r="FT18" s="36"/>
-      <c r="FU18" s="36"/>
-      <c r="FV18" s="36"/>
-      <c r="FW18" s="36"/>
-      <c r="FX18" s="36"/>
-      <c r="FY18" s="36"/>
-      <c r="FZ18" s="36"/>
-      <c r="GA18" s="36"/>
-      <c r="GB18" s="36"/>
-      <c r="GC18" s="36"/>
-      <c r="GD18" s="36"/>
-      <c r="GE18" s="36"/>
-      <c r="GF18" s="36"/>
-      <c r="GG18" s="36"/>
-      <c r="GH18" s="36"/>
-      <c r="GI18" s="36"/>
-      <c r="GJ18" s="36"/>
-      <c r="GK18" s="36"/>
-      <c r="GL18" s="36"/>
-      <c r="GM18" s="36"/>
-      <c r="GN18" s="36"/>
-      <c r="GO18" s="36"/>
-      <c r="GP18" s="36"/>
-      <c r="GQ18" s="36"/>
-      <c r="GR18" s="36"/>
-      <c r="GS18" s="36"/>
-      <c r="GT18" s="36"/>
-      <c r="GU18" s="36"/>
-      <c r="GV18" s="36"/>
-      <c r="GW18" s="36"/>
-      <c r="GX18" s="36"/>
-      <c r="GY18" s="36"/>
-      <c r="GZ18" s="36"/>
-      <c r="HA18" s="36"/>
-      <c r="HB18" s="36"/>
-      <c r="HC18" s="36"/>
-      <c r="HD18" s="36"/>
-      <c r="HE18" s="36"/>
-      <c r="HF18" s="36"/>
-      <c r="HG18" s="36"/>
-      <c r="HH18" s="36"/>
-      <c r="HI18" s="36"/>
-      <c r="HJ18" s="36"/>
-      <c r="HK18" s="36"/>
-      <c r="HL18" s="36"/>
-      <c r="HM18" s="36"/>
-      <c r="HN18" s="36"/>
-      <c r="HO18" s="36"/>
-      <c r="HP18" s="36"/>
-      <c r="HQ18" s="36"/>
-      <c r="HR18" s="36"/>
-      <c r="HS18" s="36"/>
-      <c r="HT18" s="36"/>
-      <c r="HU18" s="36"/>
-      <c r="HV18" s="36"/>
-      <c r="HW18" s="36"/>
-      <c r="HX18" s="36"/>
-      <c r="HY18" s="36"/>
-      <c r="HZ18" s="36"/>
-      <c r="IA18" s="36"/>
-      <c r="IB18" s="36"/>
-      <c r="IC18" s="36"/>
-      <c r="ID18" s="36"/>
-      <c r="IE18" s="36"/>
-      <c r="IF18" s="36"/>
-      <c r="IG18" s="36"/>
-      <c r="IH18" s="36"/>
-      <c r="II18" s="36"/>
-      <c r="IJ18" s="36"/>
-      <c r="IK18" s="36"/>
-      <c r="IL18" s="36"/>
-      <c r="IM18" s="36"/>
-      <c r="IN18" s="36"/>
-      <c r="IO18" s="36"/>
-      <c r="IP18" s="36"/>
-      <c r="IQ18" s="36"/>
-      <c r="IR18" s="36"/>
-      <c r="IS18" s="36"/>
-      <c r="IT18" s="36"/>
-      <c r="IU18" s="36"/>
-      <c r="IV18" s="36"/>
-      <c r="IW18" s="36"/>
-      <c r="IX18" s="36"/>
-      <c r="IY18" s="36"/>
-      <c r="IZ18" s="36"/>
-      <c r="JA18" s="36"/>
-      <c r="JB18" s="36"/>
-      <c r="JC18" s="36"/>
-      <c r="JD18" s="36"/>
-      <c r="JE18" s="36"/>
-      <c r="JF18" s="36"/>
-      <c r="JG18" s="36"/>
-      <c r="JH18" s="36"/>
-      <c r="JI18" s="36"/>
-      <c r="JJ18" s="36"/>
-      <c r="JK18" s="36"/>
-      <c r="JL18" s="36"/>
-      <c r="JM18" s="36"/>
-      <c r="JN18" s="36"/>
-    </row>
-    <row r="19" s="6" customFormat="1" ht="25.5">
-      <c r="A19" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I19" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="J19" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="K19" s="35">
-        <v>2010</v>
-      </c>
-      <c r="L19" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="M19" s="27"/>
-      <c r="N19" s="16"/>
+      <c r="I19" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="J19" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="K19" s="29">
+        <v>2023</v>
+      </c>
+      <c r="L19" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="M19" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="N19" s="30" t="s">
+        <v>162</v>
+      </c>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
       <c r="Q19" s="10"/>
@@ -7292,1304 +7322,1304 @@
       <c r="JM19" s="10"/>
       <c r="JN19" s="10"/>
     </row>
-    <row r="20" s="39" customFormat="1" ht="51">
-      <c r="A20" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="27" t="s">
+    <row r="20" s="32" customFormat="1" ht="51">
+      <c r="A20" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="G20" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="H20" s="27"/>
-      <c r="I20" s="40" t="s">
+      <c r="C20" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="J20" s="41"/>
-      <c r="K20" s="27" t="s">
+      <c r="D20" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="L20" s="27" t="s">
+      <c r="E20" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="H20" s="29"/>
+      <c r="I20" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="J20" s="35"/>
+      <c r="K20" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="L20" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="M20" s="27"/>
+      <c r="M20" s="29"/>
       <c r="N20" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="O20" s="42"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="42"/>
-      <c r="U20" s="42"/>
-      <c r="V20" s="42"/>
-      <c r="W20" s="42"/>
-      <c r="X20" s="42"/>
-      <c r="Y20" s="42"/>
-      <c r="Z20" s="42"/>
-      <c r="AA20" s="42"/>
-      <c r="AB20" s="42"/>
-      <c r="AC20" s="42"/>
-      <c r="AD20" s="42"/>
-      <c r="AE20" s="42"/>
-      <c r="AF20" s="42"/>
-      <c r="AG20" s="42"/>
-      <c r="AH20" s="42"/>
-      <c r="AI20" s="42"/>
-      <c r="AJ20" s="42"/>
-      <c r="AK20" s="42"/>
-      <c r="AL20" s="42"/>
-      <c r="AM20" s="42"/>
-      <c r="AN20" s="42"/>
-      <c r="AO20" s="42"/>
-      <c r="AP20" s="42"/>
-      <c r="AQ20" s="42"/>
-      <c r="AR20" s="42"/>
-      <c r="AS20" s="42"/>
-      <c r="AT20" s="42"/>
-      <c r="AU20" s="42"/>
-      <c r="AV20" s="42"/>
-      <c r="AW20" s="42"/>
-      <c r="AX20" s="42"/>
-      <c r="AY20" s="42"/>
-      <c r="AZ20" s="42"/>
-      <c r="BA20" s="42"/>
-      <c r="BB20" s="42"/>
-      <c r="BC20" s="42"/>
-      <c r="BD20" s="42"/>
-      <c r="BE20" s="42"/>
-      <c r="BF20" s="42"/>
-      <c r="BG20" s="42"/>
-      <c r="BH20" s="42"/>
-      <c r="BI20" s="42"/>
-      <c r="BJ20" s="42"/>
-      <c r="BK20" s="42"/>
-      <c r="BL20" s="42"/>
-      <c r="BM20" s="42"/>
-      <c r="BN20" s="42"/>
-      <c r="BO20" s="42"/>
-      <c r="BP20" s="42"/>
-      <c r="BQ20" s="42"/>
-      <c r="BR20" s="42"/>
-      <c r="BS20" s="42"/>
-      <c r="BT20" s="42"/>
-      <c r="BU20" s="42"/>
-      <c r="BV20" s="42"/>
-      <c r="BW20" s="42"/>
-      <c r="BX20" s="42"/>
-      <c r="BY20" s="42"/>
-      <c r="BZ20" s="42"/>
-      <c r="CA20" s="42"/>
-      <c r="CB20" s="42"/>
-      <c r="CC20" s="42"/>
-      <c r="CD20" s="42"/>
-      <c r="CE20" s="42"/>
-      <c r="CF20" s="42"/>
-      <c r="CG20" s="42"/>
-      <c r="CH20" s="42"/>
-      <c r="CI20" s="42"/>
-      <c r="CJ20" s="42"/>
-      <c r="CK20" s="42"/>
-      <c r="CL20" s="42"/>
-      <c r="CM20" s="42"/>
-      <c r="CN20" s="42"/>
-      <c r="CO20" s="42"/>
-      <c r="CP20" s="42"/>
-      <c r="CQ20" s="42"/>
-      <c r="CR20" s="42"/>
-      <c r="CS20" s="42"/>
-      <c r="CT20" s="42"/>
-      <c r="CU20" s="42"/>
-      <c r="CV20" s="42"/>
-      <c r="CW20" s="42"/>
-      <c r="CX20" s="42"/>
-      <c r="CY20" s="42"/>
-      <c r="CZ20" s="42"/>
-      <c r="DA20" s="42"/>
-      <c r="DB20" s="42"/>
-      <c r="DC20" s="42"/>
-      <c r="DD20" s="42"/>
-      <c r="DE20" s="42"/>
-      <c r="DF20" s="42"/>
-      <c r="DG20" s="42"/>
-      <c r="DH20" s="42"/>
-      <c r="DI20" s="42"/>
-      <c r="DJ20" s="42"/>
-      <c r="DK20" s="42"/>
-      <c r="DL20" s="42"/>
-      <c r="DM20" s="42"/>
-      <c r="DN20" s="42"/>
-      <c r="DO20" s="42"/>
-      <c r="DP20" s="42"/>
-      <c r="DQ20" s="42"/>
-      <c r="DR20" s="42"/>
-      <c r="DS20" s="42"/>
-      <c r="DT20" s="42"/>
-      <c r="DU20" s="42"/>
-      <c r="DV20" s="42"/>
-      <c r="DW20" s="42"/>
-      <c r="DX20" s="42"/>
-      <c r="DY20" s="42"/>
-      <c r="DZ20" s="42"/>
-      <c r="EA20" s="42"/>
-      <c r="EB20" s="42"/>
-      <c r="EC20" s="42"/>
-      <c r="ED20" s="42"/>
-      <c r="EE20" s="42"/>
-      <c r="EF20" s="42"/>
-      <c r="EG20" s="42"/>
-      <c r="EH20" s="42"/>
-      <c r="EI20" s="42"/>
-      <c r="EJ20" s="42"/>
-      <c r="EK20" s="42"/>
-      <c r="EL20" s="42"/>
-      <c r="EM20" s="42"/>
-      <c r="EN20" s="42"/>
-      <c r="EO20" s="42"/>
-      <c r="EP20" s="42"/>
-      <c r="EQ20" s="42"/>
-      <c r="ER20" s="42"/>
-      <c r="ES20" s="42"/>
-      <c r="ET20" s="42"/>
-      <c r="EU20" s="42"/>
-      <c r="EV20" s="42"/>
-      <c r="EW20" s="42"/>
-      <c r="EX20" s="42"/>
-      <c r="EY20" s="42"/>
-      <c r="EZ20" s="42"/>
-      <c r="FA20" s="42"/>
-      <c r="FB20" s="42"/>
-      <c r="FC20" s="42"/>
-      <c r="FD20" s="42"/>
-      <c r="FE20" s="42"/>
-      <c r="FF20" s="42"/>
-      <c r="FG20" s="42"/>
-      <c r="FH20" s="42"/>
-      <c r="FI20" s="42"/>
-      <c r="FJ20" s="42"/>
-      <c r="FK20" s="42"/>
-      <c r="FL20" s="42"/>
-      <c r="FM20" s="42"/>
-      <c r="FN20" s="42"/>
-      <c r="FO20" s="42"/>
-      <c r="FP20" s="42"/>
-      <c r="FQ20" s="42"/>
-      <c r="FR20" s="42"/>
-      <c r="FS20" s="42"/>
-      <c r="FT20" s="42"/>
-      <c r="FU20" s="42"/>
-      <c r="FV20" s="42"/>
-      <c r="FW20" s="42"/>
-      <c r="FX20" s="42"/>
-      <c r="FY20" s="42"/>
-      <c r="FZ20" s="42"/>
-      <c r="GA20" s="42"/>
-      <c r="GB20" s="42"/>
-      <c r="GC20" s="42"/>
-      <c r="GD20" s="42"/>
-      <c r="GE20" s="42"/>
-      <c r="GF20" s="42"/>
-      <c r="GG20" s="42"/>
-      <c r="GH20" s="42"/>
-      <c r="GI20" s="42"/>
-      <c r="GJ20" s="42"/>
-      <c r="GK20" s="42"/>
-      <c r="GL20" s="42"/>
-      <c r="GM20" s="42"/>
-      <c r="GN20" s="42"/>
-      <c r="GO20" s="42"/>
-      <c r="GP20" s="42"/>
-      <c r="GQ20" s="42"/>
-      <c r="GR20" s="42"/>
-      <c r="GS20" s="42"/>
-      <c r="GT20" s="42"/>
-      <c r="GU20" s="42"/>
-      <c r="GV20" s="42"/>
-      <c r="GW20" s="42"/>
-      <c r="GX20" s="42"/>
-      <c r="GY20" s="42"/>
-      <c r="GZ20" s="42"/>
-      <c r="HA20" s="42"/>
-      <c r="HB20" s="42"/>
-      <c r="HC20" s="42"/>
-      <c r="HD20" s="42"/>
-      <c r="HE20" s="42"/>
-      <c r="HF20" s="42"/>
-      <c r="HG20" s="42"/>
-      <c r="HH20" s="42"/>
-      <c r="HI20" s="42"/>
-      <c r="HJ20" s="42"/>
-      <c r="HK20" s="42"/>
-      <c r="HL20" s="42"/>
-      <c r="HM20" s="42"/>
-      <c r="HN20" s="42"/>
-      <c r="HO20" s="42"/>
-      <c r="HP20" s="42"/>
-      <c r="HQ20" s="42"/>
-      <c r="HR20" s="42"/>
-      <c r="HS20" s="42"/>
-      <c r="HT20" s="42"/>
-      <c r="HU20" s="42"/>
-      <c r="HV20" s="42"/>
-      <c r="HW20" s="42"/>
-      <c r="HX20" s="42"/>
-      <c r="HY20" s="42"/>
-      <c r="HZ20" s="42"/>
-      <c r="IA20" s="42"/>
-      <c r="IB20" s="42"/>
-      <c r="IC20" s="42"/>
-      <c r="ID20" s="42"/>
-      <c r="IE20" s="42"/>
-      <c r="IF20" s="42"/>
-      <c r="IG20" s="42"/>
-      <c r="IH20" s="42"/>
-      <c r="II20" s="42"/>
-      <c r="IJ20" s="42"/>
-      <c r="IK20" s="42"/>
-      <c r="IL20" s="42"/>
-      <c r="IM20" s="42"/>
-      <c r="IN20" s="42"/>
-      <c r="IO20" s="42"/>
-      <c r="IP20" s="42"/>
-      <c r="IQ20" s="42"/>
-      <c r="IR20" s="42"/>
-      <c r="IS20" s="42"/>
-      <c r="IT20" s="42"/>
-      <c r="IU20" s="42"/>
-      <c r="IV20" s="42"/>
-      <c r="IW20" s="42"/>
-      <c r="IX20" s="42"/>
-      <c r="IY20" s="42"/>
-      <c r="IZ20" s="42"/>
-      <c r="JA20" s="42"/>
-      <c r="JB20" s="42"/>
-      <c r="JC20" s="42"/>
-      <c r="JD20" s="42"/>
-      <c r="JE20" s="42"/>
-      <c r="JF20" s="42"/>
-      <c r="JG20" s="42"/>
-      <c r="JH20" s="42"/>
-      <c r="JI20" s="42"/>
-      <c r="JJ20" s="42"/>
-      <c r="JK20" s="42"/>
-      <c r="JL20" s="42"/>
-      <c r="JM20" s="42"/>
-      <c r="JN20" s="42"/>
+        <v>170</v>
+      </c>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
+      <c r="S20" s="36"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="36"/>
+      <c r="W20" s="36"/>
+      <c r="X20" s="36"/>
+      <c r="Y20" s="36"/>
+      <c r="Z20" s="36"/>
+      <c r="AA20" s="36"/>
+      <c r="AB20" s="36"/>
+      <c r="AC20" s="36"/>
+      <c r="AD20" s="36"/>
+      <c r="AE20" s="36"/>
+      <c r="AF20" s="36"/>
+      <c r="AG20" s="36"/>
+      <c r="AH20" s="36"/>
+      <c r="AI20" s="36"/>
+      <c r="AJ20" s="36"/>
+      <c r="AK20" s="36"/>
+      <c r="AL20" s="36"/>
+      <c r="AM20" s="36"/>
+      <c r="AN20" s="36"/>
+      <c r="AO20" s="36"/>
+      <c r="AP20" s="36"/>
+      <c r="AQ20" s="36"/>
+      <c r="AR20" s="36"/>
+      <c r="AS20" s="36"/>
+      <c r="AT20" s="36"/>
+      <c r="AU20" s="36"/>
+      <c r="AV20" s="36"/>
+      <c r="AW20" s="36"/>
+      <c r="AX20" s="36"/>
+      <c r="AY20" s="36"/>
+      <c r="AZ20" s="36"/>
+      <c r="BA20" s="36"/>
+      <c r="BB20" s="36"/>
+      <c r="BC20" s="36"/>
+      <c r="BD20" s="36"/>
+      <c r="BE20" s="36"/>
+      <c r="BF20" s="36"/>
+      <c r="BG20" s="36"/>
+      <c r="BH20" s="36"/>
+      <c r="BI20" s="36"/>
+      <c r="BJ20" s="36"/>
+      <c r="BK20" s="36"/>
+      <c r="BL20" s="36"/>
+      <c r="BM20" s="36"/>
+      <c r="BN20" s="36"/>
+      <c r="BO20" s="36"/>
+      <c r="BP20" s="36"/>
+      <c r="BQ20" s="36"/>
+      <c r="BR20" s="36"/>
+      <c r="BS20" s="36"/>
+      <c r="BT20" s="36"/>
+      <c r="BU20" s="36"/>
+      <c r="BV20" s="36"/>
+      <c r="BW20" s="36"/>
+      <c r="BX20" s="36"/>
+      <c r="BY20" s="36"/>
+      <c r="BZ20" s="36"/>
+      <c r="CA20" s="36"/>
+      <c r="CB20" s="36"/>
+      <c r="CC20" s="36"/>
+      <c r="CD20" s="36"/>
+      <c r="CE20" s="36"/>
+      <c r="CF20" s="36"/>
+      <c r="CG20" s="36"/>
+      <c r="CH20" s="36"/>
+      <c r="CI20" s="36"/>
+      <c r="CJ20" s="36"/>
+      <c r="CK20" s="36"/>
+      <c r="CL20" s="36"/>
+      <c r="CM20" s="36"/>
+      <c r="CN20" s="36"/>
+      <c r="CO20" s="36"/>
+      <c r="CP20" s="36"/>
+      <c r="CQ20" s="36"/>
+      <c r="CR20" s="36"/>
+      <c r="CS20" s="36"/>
+      <c r="CT20" s="36"/>
+      <c r="CU20" s="36"/>
+      <c r="CV20" s="36"/>
+      <c r="CW20" s="36"/>
+      <c r="CX20" s="36"/>
+      <c r="CY20" s="36"/>
+      <c r="CZ20" s="36"/>
+      <c r="DA20" s="36"/>
+      <c r="DB20" s="36"/>
+      <c r="DC20" s="36"/>
+      <c r="DD20" s="36"/>
+      <c r="DE20" s="36"/>
+      <c r="DF20" s="36"/>
+      <c r="DG20" s="36"/>
+      <c r="DH20" s="36"/>
+      <c r="DI20" s="36"/>
+      <c r="DJ20" s="36"/>
+      <c r="DK20" s="36"/>
+      <c r="DL20" s="36"/>
+      <c r="DM20" s="36"/>
+      <c r="DN20" s="36"/>
+      <c r="DO20" s="36"/>
+      <c r="DP20" s="36"/>
+      <c r="DQ20" s="36"/>
+      <c r="DR20" s="36"/>
+      <c r="DS20" s="36"/>
+      <c r="DT20" s="36"/>
+      <c r="DU20" s="36"/>
+      <c r="DV20" s="36"/>
+      <c r="DW20" s="36"/>
+      <c r="DX20" s="36"/>
+      <c r="DY20" s="36"/>
+      <c r="DZ20" s="36"/>
+      <c r="EA20" s="36"/>
+      <c r="EB20" s="36"/>
+      <c r="EC20" s="36"/>
+      <c r="ED20" s="36"/>
+      <c r="EE20" s="36"/>
+      <c r="EF20" s="36"/>
+      <c r="EG20" s="36"/>
+      <c r="EH20" s="36"/>
+      <c r="EI20" s="36"/>
+      <c r="EJ20" s="36"/>
+      <c r="EK20" s="36"/>
+      <c r="EL20" s="36"/>
+      <c r="EM20" s="36"/>
+      <c r="EN20" s="36"/>
+      <c r="EO20" s="36"/>
+      <c r="EP20" s="36"/>
+      <c r="EQ20" s="36"/>
+      <c r="ER20" s="36"/>
+      <c r="ES20" s="36"/>
+      <c r="ET20" s="36"/>
+      <c r="EU20" s="36"/>
+      <c r="EV20" s="36"/>
+      <c r="EW20" s="36"/>
+      <c r="EX20" s="36"/>
+      <c r="EY20" s="36"/>
+      <c r="EZ20" s="36"/>
+      <c r="FA20" s="36"/>
+      <c r="FB20" s="36"/>
+      <c r="FC20" s="36"/>
+      <c r="FD20" s="36"/>
+      <c r="FE20" s="36"/>
+      <c r="FF20" s="36"/>
+      <c r="FG20" s="36"/>
+      <c r="FH20" s="36"/>
+      <c r="FI20" s="36"/>
+      <c r="FJ20" s="36"/>
+      <c r="FK20" s="36"/>
+      <c r="FL20" s="36"/>
+      <c r="FM20" s="36"/>
+      <c r="FN20" s="36"/>
+      <c r="FO20" s="36"/>
+      <c r="FP20" s="36"/>
+      <c r="FQ20" s="36"/>
+      <c r="FR20" s="36"/>
+      <c r="FS20" s="36"/>
+      <c r="FT20" s="36"/>
+      <c r="FU20" s="36"/>
+      <c r="FV20" s="36"/>
+      <c r="FW20" s="36"/>
+      <c r="FX20" s="36"/>
+      <c r="FY20" s="36"/>
+      <c r="FZ20" s="36"/>
+      <c r="GA20" s="36"/>
+      <c r="GB20" s="36"/>
+      <c r="GC20" s="36"/>
+      <c r="GD20" s="36"/>
+      <c r="GE20" s="36"/>
+      <c r="GF20" s="36"/>
+      <c r="GG20" s="36"/>
+      <c r="GH20" s="36"/>
+      <c r="GI20" s="36"/>
+      <c r="GJ20" s="36"/>
+      <c r="GK20" s="36"/>
+      <c r="GL20" s="36"/>
+      <c r="GM20" s="36"/>
+      <c r="GN20" s="36"/>
+      <c r="GO20" s="36"/>
+      <c r="GP20" s="36"/>
+      <c r="GQ20" s="36"/>
+      <c r="GR20" s="36"/>
+      <c r="GS20" s="36"/>
+      <c r="GT20" s="36"/>
+      <c r="GU20" s="36"/>
+      <c r="GV20" s="36"/>
+      <c r="GW20" s="36"/>
+      <c r="GX20" s="36"/>
+      <c r="GY20" s="36"/>
+      <c r="GZ20" s="36"/>
+      <c r="HA20" s="36"/>
+      <c r="HB20" s="36"/>
+      <c r="HC20" s="36"/>
+      <c r="HD20" s="36"/>
+      <c r="HE20" s="36"/>
+      <c r="HF20" s="36"/>
+      <c r="HG20" s="36"/>
+      <c r="HH20" s="36"/>
+      <c r="HI20" s="36"/>
+      <c r="HJ20" s="36"/>
+      <c r="HK20" s="36"/>
+      <c r="HL20" s="36"/>
+      <c r="HM20" s="36"/>
+      <c r="HN20" s="36"/>
+      <c r="HO20" s="36"/>
+      <c r="HP20" s="36"/>
+      <c r="HQ20" s="36"/>
+      <c r="HR20" s="36"/>
+      <c r="HS20" s="36"/>
+      <c r="HT20" s="36"/>
+      <c r="HU20" s="36"/>
+      <c r="HV20" s="36"/>
+      <c r="HW20" s="36"/>
+      <c r="HX20" s="36"/>
+      <c r="HY20" s="36"/>
+      <c r="HZ20" s="36"/>
+      <c r="IA20" s="36"/>
+      <c r="IB20" s="36"/>
+      <c r="IC20" s="36"/>
+      <c r="ID20" s="36"/>
+      <c r="IE20" s="36"/>
+      <c r="IF20" s="36"/>
+      <c r="IG20" s="36"/>
+      <c r="IH20" s="36"/>
+      <c r="II20" s="36"/>
+      <c r="IJ20" s="36"/>
+      <c r="IK20" s="36"/>
+      <c r="IL20" s="36"/>
+      <c r="IM20" s="36"/>
+      <c r="IN20" s="36"/>
+      <c r="IO20" s="36"/>
+      <c r="IP20" s="36"/>
+      <c r="IQ20" s="36"/>
+      <c r="IR20" s="36"/>
+      <c r="IS20" s="36"/>
+      <c r="IT20" s="36"/>
+      <c r="IU20" s="36"/>
+      <c r="IV20" s="36"/>
+      <c r="IW20" s="36"/>
+      <c r="IX20" s="36"/>
+      <c r="IY20" s="36"/>
+      <c r="IZ20" s="36"/>
+      <c r="JA20" s="36"/>
+      <c r="JB20" s="36"/>
+      <c r="JC20" s="36"/>
+      <c r="JD20" s="36"/>
+      <c r="JE20" s="36"/>
+      <c r="JF20" s="36"/>
+      <c r="JG20" s="36"/>
+      <c r="JH20" s="36"/>
+      <c r="JI20" s="36"/>
+      <c r="JJ20" s="36"/>
+      <c r="JK20" s="36"/>
+      <c r="JL20" s="36"/>
+      <c r="JM20" s="36"/>
+      <c r="JN20" s="36"/>
     </row>
-    <row r="21" s="43" customFormat="1" ht="25.5">
-      <c r="A21" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="B21" s="27" t="s">
+    <row r="21" s="37" customFormat="1" ht="25.5">
+      <c r="A21" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="D21" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="E21" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="J21" s="41"/>
-      <c r="K21" s="27">
+      <c r="C21" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="I21" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="J21" s="35"/>
+      <c r="K21" s="29">
         <v>2025</v>
       </c>
-      <c r="L21" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="M21" s="27"/>
+      <c r="L21" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="M21" s="29"/>
       <c r="N21" s="16"/>
-      <c r="O21" s="43"/>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="43"/>
-      <c r="R21" s="43"/>
-      <c r="S21" s="43"/>
-      <c r="T21" s="43"/>
-      <c r="U21" s="43"/>
-      <c r="V21" s="43"/>
-      <c r="W21" s="43"/>
-      <c r="X21" s="43"/>
-      <c r="Y21" s="43"/>
-      <c r="Z21" s="43"/>
-      <c r="AA21" s="43"/>
-      <c r="AB21" s="43"/>
-      <c r="AC21" s="43"/>
-      <c r="AD21" s="43"/>
-      <c r="AE21" s="43"/>
-      <c r="AF21" s="43"/>
-      <c r="AG21" s="43"/>
-      <c r="AH21" s="43"/>
-      <c r="AI21" s="43"/>
-      <c r="AJ21" s="43"/>
-      <c r="AK21" s="43"/>
-      <c r="AL21" s="43"/>
-      <c r="AM21" s="43"/>
-      <c r="AN21" s="43"/>
-      <c r="AO21" s="43"/>
-      <c r="AP21" s="43"/>
-      <c r="AQ21" s="43"/>
-      <c r="AR21" s="43"/>
-      <c r="AS21" s="43"/>
-      <c r="AT21" s="43"/>
-      <c r="AU21" s="43"/>
-      <c r="AV21" s="43"/>
-      <c r="AW21" s="43"/>
-      <c r="AX21" s="43"/>
-      <c r="AY21" s="43"/>
-      <c r="AZ21" s="43"/>
-      <c r="BA21" s="43"/>
-      <c r="BB21" s="43"/>
-      <c r="BC21" s="43"/>
-      <c r="BD21" s="43"/>
-      <c r="BE21" s="43"/>
-      <c r="BF21" s="43"/>
-      <c r="BG21" s="43"/>
-      <c r="BH21" s="43"/>
-      <c r="BI21" s="43"/>
-      <c r="BJ21" s="43"/>
-      <c r="BK21" s="43"/>
-      <c r="BL21" s="43"/>
-      <c r="BM21" s="43"/>
-      <c r="BN21" s="43"/>
-      <c r="BO21" s="43"/>
-      <c r="BP21" s="43"/>
-      <c r="BQ21" s="43"/>
-      <c r="BR21" s="43"/>
-      <c r="BS21" s="43"/>
-      <c r="BT21" s="43"/>
-      <c r="BU21" s="43"/>
-      <c r="BV21" s="43"/>
-      <c r="BW21" s="43"/>
-      <c r="BX21" s="43"/>
-      <c r="BY21" s="43"/>
-      <c r="BZ21" s="43"/>
-      <c r="CA21" s="43"/>
-      <c r="CB21" s="43"/>
-      <c r="CC21" s="43"/>
-      <c r="CD21" s="43"/>
-      <c r="CE21" s="43"/>
-      <c r="CF21" s="43"/>
-      <c r="CG21" s="43"/>
-      <c r="CH21" s="43"/>
-      <c r="CI21" s="43"/>
-      <c r="CJ21" s="43"/>
-      <c r="CK21" s="43"/>
-      <c r="CL21" s="43"/>
-      <c r="CM21" s="43"/>
-      <c r="CN21" s="43"/>
-      <c r="CO21" s="43"/>
-      <c r="CP21" s="43"/>
-      <c r="CQ21" s="43"/>
-      <c r="CR21" s="43"/>
-      <c r="CS21" s="43"/>
-      <c r="CT21" s="43"/>
-      <c r="CU21" s="43"/>
-      <c r="CV21" s="43"/>
-      <c r="CW21" s="43"/>
-      <c r="CX21" s="43"/>
-      <c r="CY21" s="43"/>
-      <c r="CZ21" s="43"/>
-      <c r="DA21" s="43"/>
-      <c r="DB21" s="43"/>
-      <c r="DC21" s="43"/>
-      <c r="DD21" s="43"/>
-      <c r="DE21" s="43"/>
-      <c r="DF21" s="43"/>
-      <c r="DG21" s="43"/>
-      <c r="DH21" s="43"/>
-      <c r="DI21" s="43"/>
-      <c r="DJ21" s="43"/>
-      <c r="DK21" s="43"/>
-      <c r="DL21" s="43"/>
-      <c r="DM21" s="43"/>
-      <c r="DN21" s="43"/>
-      <c r="DO21" s="43"/>
-      <c r="DP21" s="43"/>
-      <c r="DQ21" s="43"/>
-      <c r="DR21" s="43"/>
-      <c r="DS21" s="43"/>
-      <c r="DT21" s="43"/>
-      <c r="DU21" s="43"/>
-      <c r="DV21" s="43"/>
-      <c r="DW21" s="43"/>
-      <c r="DX21" s="43"/>
-      <c r="DY21" s="43"/>
-      <c r="DZ21" s="43"/>
-      <c r="EA21" s="43"/>
-      <c r="EB21" s="43"/>
-      <c r="EC21" s="43"/>
-      <c r="ED21" s="43"/>
-      <c r="EE21" s="43"/>
-      <c r="EF21" s="43"/>
-      <c r="EG21" s="43"/>
-      <c r="EH21" s="43"/>
-      <c r="EI21" s="43"/>
-      <c r="EJ21" s="43"/>
-      <c r="EK21" s="43"/>
-      <c r="EL21" s="43"/>
-      <c r="EM21" s="43"/>
-      <c r="EN21" s="43"/>
-      <c r="EO21" s="43"/>
-      <c r="EP21" s="43"/>
-      <c r="EQ21" s="43"/>
-      <c r="ER21" s="43"/>
-      <c r="ES21" s="43"/>
-      <c r="ET21" s="43"/>
-      <c r="EU21" s="43"/>
-      <c r="EV21" s="43"/>
-      <c r="EW21" s="43"/>
-      <c r="EX21" s="43"/>
-      <c r="EY21" s="43"/>
-      <c r="EZ21" s="43"/>
-      <c r="FA21" s="43"/>
-      <c r="FB21" s="43"/>
-      <c r="FC21" s="43"/>
-      <c r="FD21" s="43"/>
-      <c r="FE21" s="43"/>
-      <c r="FF21" s="43"/>
-      <c r="FG21" s="43"/>
-      <c r="FH21" s="43"/>
-      <c r="FI21" s="43"/>
-      <c r="FJ21" s="43"/>
-      <c r="FK21" s="43"/>
-      <c r="FL21" s="43"/>
-      <c r="FM21" s="43"/>
-      <c r="FN21" s="43"/>
-      <c r="FO21" s="43"/>
-      <c r="FP21" s="43"/>
-      <c r="FQ21" s="43"/>
-      <c r="FR21" s="43"/>
-      <c r="FS21" s="43"/>
-      <c r="FT21" s="43"/>
-      <c r="FU21" s="43"/>
-      <c r="FV21" s="43"/>
-      <c r="FW21" s="43"/>
-      <c r="FX21" s="43"/>
-      <c r="FY21" s="43"/>
-      <c r="FZ21" s="43"/>
-      <c r="GA21" s="43"/>
-      <c r="GB21" s="43"/>
-      <c r="GC21" s="43"/>
-      <c r="GD21" s="43"/>
-      <c r="GE21" s="43"/>
-      <c r="GF21" s="43"/>
-      <c r="GG21" s="43"/>
-      <c r="GH21" s="43"/>
-      <c r="GI21" s="43"/>
-      <c r="GJ21" s="43"/>
-      <c r="GK21" s="43"/>
-      <c r="GL21" s="43"/>
-      <c r="GM21" s="43"/>
-      <c r="GN21" s="43"/>
-      <c r="GO21" s="43"/>
-      <c r="GP21" s="43"/>
-      <c r="GQ21" s="43"/>
-      <c r="GR21" s="43"/>
-      <c r="GS21" s="43"/>
-      <c r="GT21" s="43"/>
-      <c r="GU21" s="43"/>
-      <c r="GV21" s="43"/>
-      <c r="GW21" s="43"/>
-      <c r="GX21" s="43"/>
-      <c r="GY21" s="43"/>
-      <c r="GZ21" s="43"/>
-      <c r="HA21" s="43"/>
-      <c r="HB21" s="43"/>
-      <c r="HC21" s="43"/>
-      <c r="HD21" s="43"/>
-      <c r="HE21" s="43"/>
-      <c r="HF21" s="43"/>
-      <c r="HG21" s="43"/>
-      <c r="HH21" s="43"/>
-      <c r="HI21" s="43"/>
-      <c r="HJ21" s="43"/>
-      <c r="HK21" s="43"/>
-      <c r="HL21" s="43"/>
-      <c r="HM21" s="43"/>
-      <c r="HN21" s="43"/>
-      <c r="HO21" s="43"/>
-      <c r="HP21" s="43"/>
-      <c r="HQ21" s="43"/>
-      <c r="HR21" s="43"/>
-      <c r="HS21" s="43"/>
-      <c r="HT21" s="43"/>
-      <c r="HU21" s="43"/>
-      <c r="HV21" s="43"/>
-      <c r="HW21" s="43"/>
-      <c r="HX21" s="43"/>
-      <c r="HY21" s="43"/>
-      <c r="HZ21" s="43"/>
-      <c r="IA21" s="43"/>
-      <c r="IB21" s="43"/>
-      <c r="IC21" s="43"/>
-      <c r="ID21" s="43"/>
-      <c r="IE21" s="43"/>
-      <c r="IF21" s="43"/>
-      <c r="IG21" s="43"/>
-      <c r="IH21" s="43"/>
-      <c r="II21" s="43"/>
-      <c r="IJ21" s="43"/>
-      <c r="IK21" s="43"/>
-      <c r="IL21" s="43"/>
-      <c r="IM21" s="43"/>
-      <c r="IN21" s="43"/>
-      <c r="IO21" s="43"/>
-      <c r="IP21" s="43"/>
-      <c r="IQ21" s="43"/>
-      <c r="IR21" s="43"/>
-      <c r="IS21" s="43"/>
-      <c r="IT21" s="43"/>
-      <c r="IU21" s="43"/>
-      <c r="IV21" s="43"/>
-      <c r="IW21" s="43"/>
-      <c r="IX21" s="43"/>
-      <c r="IY21" s="43"/>
-      <c r="IZ21" s="43"/>
-      <c r="JA21" s="43"/>
-      <c r="JB21" s="43"/>
-      <c r="JC21" s="43"/>
-      <c r="JD21" s="43"/>
-      <c r="JE21" s="43"/>
-      <c r="JF21" s="43"/>
-      <c r="JG21" s="43"/>
-      <c r="JH21" s="43"/>
-      <c r="JI21" s="43"/>
-      <c r="JJ21" s="43"/>
-      <c r="JK21" s="43"/>
-      <c r="JL21" s="43"/>
-      <c r="JM21" s="43"/>
-      <c r="JN21" s="43"/>
+      <c r="O21" s="37"/>
+      <c r="P21" s="37"/>
+      <c r="Q21" s="37"/>
+      <c r="R21" s="37"/>
+      <c r="S21" s="37"/>
+      <c r="T21" s="37"/>
+      <c r="U21" s="37"/>
+      <c r="V21" s="37"/>
+      <c r="W21" s="37"/>
+      <c r="X21" s="37"/>
+      <c r="Y21" s="37"/>
+      <c r="Z21" s="37"/>
+      <c r="AA21" s="37"/>
+      <c r="AB21" s="37"/>
+      <c r="AC21" s="37"/>
+      <c r="AD21" s="37"/>
+      <c r="AE21" s="37"/>
+      <c r="AF21" s="37"/>
+      <c r="AG21" s="37"/>
+      <c r="AH21" s="37"/>
+      <c r="AI21" s="37"/>
+      <c r="AJ21" s="37"/>
+      <c r="AK21" s="37"/>
+      <c r="AL21" s="37"/>
+      <c r="AM21" s="37"/>
+      <c r="AN21" s="37"/>
+      <c r="AO21" s="37"/>
+      <c r="AP21" s="37"/>
+      <c r="AQ21" s="37"/>
+      <c r="AR21" s="37"/>
+      <c r="AS21" s="37"/>
+      <c r="AT21" s="37"/>
+      <c r="AU21" s="37"/>
+      <c r="AV21" s="37"/>
+      <c r="AW21" s="37"/>
+      <c r="AX21" s="37"/>
+      <c r="AY21" s="37"/>
+      <c r="AZ21" s="37"/>
+      <c r="BA21" s="37"/>
+      <c r="BB21" s="37"/>
+      <c r="BC21" s="37"/>
+      <c r="BD21" s="37"/>
+      <c r="BE21" s="37"/>
+      <c r="BF21" s="37"/>
+      <c r="BG21" s="37"/>
+      <c r="BH21" s="37"/>
+      <c r="BI21" s="37"/>
+      <c r="BJ21" s="37"/>
+      <c r="BK21" s="37"/>
+      <c r="BL21" s="37"/>
+      <c r="BM21" s="37"/>
+      <c r="BN21" s="37"/>
+      <c r="BO21" s="37"/>
+      <c r="BP21" s="37"/>
+      <c r="BQ21" s="37"/>
+      <c r="BR21" s="37"/>
+      <c r="BS21" s="37"/>
+      <c r="BT21" s="37"/>
+      <c r="BU21" s="37"/>
+      <c r="BV21" s="37"/>
+      <c r="BW21" s="37"/>
+      <c r="BX21" s="37"/>
+      <c r="BY21" s="37"/>
+      <c r="BZ21" s="37"/>
+      <c r="CA21" s="37"/>
+      <c r="CB21" s="37"/>
+      <c r="CC21" s="37"/>
+      <c r="CD21" s="37"/>
+      <c r="CE21" s="37"/>
+      <c r="CF21" s="37"/>
+      <c r="CG21" s="37"/>
+      <c r="CH21" s="37"/>
+      <c r="CI21" s="37"/>
+      <c r="CJ21" s="37"/>
+      <c r="CK21" s="37"/>
+      <c r="CL21" s="37"/>
+      <c r="CM21" s="37"/>
+      <c r="CN21" s="37"/>
+      <c r="CO21" s="37"/>
+      <c r="CP21" s="37"/>
+      <c r="CQ21" s="37"/>
+      <c r="CR21" s="37"/>
+      <c r="CS21" s="37"/>
+      <c r="CT21" s="37"/>
+      <c r="CU21" s="37"/>
+      <c r="CV21" s="37"/>
+      <c r="CW21" s="37"/>
+      <c r="CX21" s="37"/>
+      <c r="CY21" s="37"/>
+      <c r="CZ21" s="37"/>
+      <c r="DA21" s="37"/>
+      <c r="DB21" s="37"/>
+      <c r="DC21" s="37"/>
+      <c r="DD21" s="37"/>
+      <c r="DE21" s="37"/>
+      <c r="DF21" s="37"/>
+      <c r="DG21" s="37"/>
+      <c r="DH21" s="37"/>
+      <c r="DI21" s="37"/>
+      <c r="DJ21" s="37"/>
+      <c r="DK21" s="37"/>
+      <c r="DL21" s="37"/>
+      <c r="DM21" s="37"/>
+      <c r="DN21" s="37"/>
+      <c r="DO21" s="37"/>
+      <c r="DP21" s="37"/>
+      <c r="DQ21" s="37"/>
+      <c r="DR21" s="37"/>
+      <c r="DS21" s="37"/>
+      <c r="DT21" s="37"/>
+      <c r="DU21" s="37"/>
+      <c r="DV21" s="37"/>
+      <c r="DW21" s="37"/>
+      <c r="DX21" s="37"/>
+      <c r="DY21" s="37"/>
+      <c r="DZ21" s="37"/>
+      <c r="EA21" s="37"/>
+      <c r="EB21" s="37"/>
+      <c r="EC21" s="37"/>
+      <c r="ED21" s="37"/>
+      <c r="EE21" s="37"/>
+      <c r="EF21" s="37"/>
+      <c r="EG21" s="37"/>
+      <c r="EH21" s="37"/>
+      <c r="EI21" s="37"/>
+      <c r="EJ21" s="37"/>
+      <c r="EK21" s="37"/>
+      <c r="EL21" s="37"/>
+      <c r="EM21" s="37"/>
+      <c r="EN21" s="37"/>
+      <c r="EO21" s="37"/>
+      <c r="EP21" s="37"/>
+      <c r="EQ21" s="37"/>
+      <c r="ER21" s="37"/>
+      <c r="ES21" s="37"/>
+      <c r="ET21" s="37"/>
+      <c r="EU21" s="37"/>
+      <c r="EV21" s="37"/>
+      <c r="EW21" s="37"/>
+      <c r="EX21" s="37"/>
+      <c r="EY21" s="37"/>
+      <c r="EZ21" s="37"/>
+      <c r="FA21" s="37"/>
+      <c r="FB21" s="37"/>
+      <c r="FC21" s="37"/>
+      <c r="FD21" s="37"/>
+      <c r="FE21" s="37"/>
+      <c r="FF21" s="37"/>
+      <c r="FG21" s="37"/>
+      <c r="FH21" s="37"/>
+      <c r="FI21" s="37"/>
+      <c r="FJ21" s="37"/>
+      <c r="FK21" s="37"/>
+      <c r="FL21" s="37"/>
+      <c r="FM21" s="37"/>
+      <c r="FN21" s="37"/>
+      <c r="FO21" s="37"/>
+      <c r="FP21" s="37"/>
+      <c r="FQ21" s="37"/>
+      <c r="FR21" s="37"/>
+      <c r="FS21" s="37"/>
+      <c r="FT21" s="37"/>
+      <c r="FU21" s="37"/>
+      <c r="FV21" s="37"/>
+      <c r="FW21" s="37"/>
+      <c r="FX21" s="37"/>
+      <c r="FY21" s="37"/>
+      <c r="FZ21" s="37"/>
+      <c r="GA21" s="37"/>
+      <c r="GB21" s="37"/>
+      <c r="GC21" s="37"/>
+      <c r="GD21" s="37"/>
+      <c r="GE21" s="37"/>
+      <c r="GF21" s="37"/>
+      <c r="GG21" s="37"/>
+      <c r="GH21" s="37"/>
+      <c r="GI21" s="37"/>
+      <c r="GJ21" s="37"/>
+      <c r="GK21" s="37"/>
+      <c r="GL21" s="37"/>
+      <c r="GM21" s="37"/>
+      <c r="GN21" s="37"/>
+      <c r="GO21" s="37"/>
+      <c r="GP21" s="37"/>
+      <c r="GQ21" s="37"/>
+      <c r="GR21" s="37"/>
+      <c r="GS21" s="37"/>
+      <c r="GT21" s="37"/>
+      <c r="GU21" s="37"/>
+      <c r="GV21" s="37"/>
+      <c r="GW21" s="37"/>
+      <c r="GX21" s="37"/>
+      <c r="GY21" s="37"/>
+      <c r="GZ21" s="37"/>
+      <c r="HA21" s="37"/>
+      <c r="HB21" s="37"/>
+      <c r="HC21" s="37"/>
+      <c r="HD21" s="37"/>
+      <c r="HE21" s="37"/>
+      <c r="HF21" s="37"/>
+      <c r="HG21" s="37"/>
+      <c r="HH21" s="37"/>
+      <c r="HI21" s="37"/>
+      <c r="HJ21" s="37"/>
+      <c r="HK21" s="37"/>
+      <c r="HL21" s="37"/>
+      <c r="HM21" s="37"/>
+      <c r="HN21" s="37"/>
+      <c r="HO21" s="37"/>
+      <c r="HP21" s="37"/>
+      <c r="HQ21" s="37"/>
+      <c r="HR21" s="37"/>
+      <c r="HS21" s="37"/>
+      <c r="HT21" s="37"/>
+      <c r="HU21" s="37"/>
+      <c r="HV21" s="37"/>
+      <c r="HW21" s="37"/>
+      <c r="HX21" s="37"/>
+      <c r="HY21" s="37"/>
+      <c r="HZ21" s="37"/>
+      <c r="IA21" s="37"/>
+      <c r="IB21" s="37"/>
+      <c r="IC21" s="37"/>
+      <c r="ID21" s="37"/>
+      <c r="IE21" s="37"/>
+      <c r="IF21" s="37"/>
+      <c r="IG21" s="37"/>
+      <c r="IH21" s="37"/>
+      <c r="II21" s="37"/>
+      <c r="IJ21" s="37"/>
+      <c r="IK21" s="37"/>
+      <c r="IL21" s="37"/>
+      <c r="IM21" s="37"/>
+      <c r="IN21" s="37"/>
+      <c r="IO21" s="37"/>
+      <c r="IP21" s="37"/>
+      <c r="IQ21" s="37"/>
+      <c r="IR21" s="37"/>
+      <c r="IS21" s="37"/>
+      <c r="IT21" s="37"/>
+      <c r="IU21" s="37"/>
+      <c r="IV21" s="37"/>
+      <c r="IW21" s="37"/>
+      <c r="IX21" s="37"/>
+      <c r="IY21" s="37"/>
+      <c r="IZ21" s="37"/>
+      <c r="JA21" s="37"/>
+      <c r="JB21" s="37"/>
+      <c r="JC21" s="37"/>
+      <c r="JD21" s="37"/>
+      <c r="JE21" s="37"/>
+      <c r="JF21" s="37"/>
+      <c r="JG21" s="37"/>
+      <c r="JH21" s="37"/>
+      <c r="JI21" s="37"/>
+      <c r="JJ21" s="37"/>
+      <c r="JK21" s="37"/>
+      <c r="JL21" s="37"/>
+      <c r="JM21" s="37"/>
+      <c r="JN21" s="37"/>
     </row>
     <row r="22" ht="42.75">
-      <c r="A22" s="44" t="s">
-        <v>172</v>
-      </c>
-      <c r="B22" s="44" t="s">
+      <c r="A22" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="B22" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="44" t="s">
+      <c r="C22" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="E22" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="F22" s="45" t="s">
+      <c r="D22" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="F22" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="G22" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="H22" s="44" t="s">
+      <c r="G22" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="H22" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="J22" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="K22" s="47">
+      <c r="I22" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="J22" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="K22" s="42">
         <v>2010</v>
       </c>
-      <c r="L22" s="47" t="s">
-        <v>178</v>
-      </c>
-      <c r="M22" s="44"/>
-      <c r="N22" s="48" t="s">
-        <v>179</v>
+      <c r="L22" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="M22" s="39"/>
+      <c r="N22" s="43" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="23" s="16" customFormat="1" ht="25.5">
-      <c r="A23" s="44" t="s">
-        <v>172</v>
-      </c>
-      <c r="B23" s="44" t="s">
+      <c r="A23" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="B23" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="D23" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="E23" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="F23" s="45" t="s">
+      <c r="C23" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="F23" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44" t="s">
+      <c r="G23" s="39"/>
+      <c r="H23" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="I23" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="J23" s="44" t="s">
-        <v>139</v>
-      </c>
-      <c r="K23" s="47">
+      <c r="I23" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="K23" s="42">
         <v>2010</v>
       </c>
-      <c r="L23" s="47" t="s">
-        <v>178</v>
-      </c>
-      <c r="M23" s="44"/>
-      <c r="N23" s="50" t="s">
+      <c r="L23" s="42" t="s">
         <v>183</v>
+      </c>
+      <c r="M23" s="39"/>
+      <c r="N23" s="45" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="24" ht="28.5">
-      <c r="A24" s="44" t="s">
-        <v>172</v>
-      </c>
-      <c r="B24" s="44" t="s">
+      <c r="A24" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="B24" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="D24" s="44" t="s">
+      <c r="C24" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="F24" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="J24" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="K24" s="42">
+        <v>2010</v>
+      </c>
+      <c r="L24" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="M24" s="39"/>
+      <c r="N24" s="43" t="s">
         <v>184</v>
-      </c>
-      <c r="E24" s="44" t="s">
-        <v>184</v>
-      </c>
-      <c r="F24" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="J24" s="44" t="s">
-        <v>139</v>
-      </c>
-      <c r="K24" s="47">
-        <v>2010</v>
-      </c>
-      <c r="L24" s="47" t="s">
-        <v>178</v>
-      </c>
-      <c r="M24" s="44"/>
-      <c r="N24" s="48" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="25" ht="25.5">
-      <c r="A25" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="B25" s="52" t="s">
+      <c r="A25" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="B25" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="D25" s="52" t="s">
-        <v>188</v>
-      </c>
-      <c r="E25" s="52" t="s">
-        <v>189</v>
-      </c>
-      <c r="F25" s="53" t="s">
-        <v>190</v>
-      </c>
-      <c r="G25" s="52"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="54" t="s">
-        <v>191</v>
-      </c>
-      <c r="J25" s="52"/>
-      <c r="K25" s="52">
+      <c r="C25" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="D25" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="F25" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="J25" s="47"/>
+      <c r="K25" s="47">
         <v>2016</v>
       </c>
-      <c r="L25" s="52" t="s">
-        <v>192</v>
-      </c>
-      <c r="M25" s="52"/>
+      <c r="L25" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="M25" s="47"/>
       <c r="N25" s="25"/>
     </row>
     <row r="26" ht="25.5">
-      <c r="A26" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="B26" s="52" t="s">
+      <c r="A26" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="B26" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="C26" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="D26" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="E26" s="52" t="s">
-        <v>189</v>
-      </c>
-      <c r="F26" s="53" t="s">
+      <c r="C26" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="D26" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="E26" s="47" t="s">
         <v>194</v>
       </c>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="56"/>
-      <c r="K26" s="52"/>
-      <c r="L26" s="52"/>
-      <c r="M26" s="52"/>
+      <c r="F26" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="47"/>
       <c r="N26" s="25"/>
     </row>
     <row r="27" ht="25.5">
-      <c r="A27" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="B27" s="52" t="s">
+      <c r="A27" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="B27" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="52" t="s">
-        <v>195</v>
-      </c>
-      <c r="D27" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="E27" s="52" t="s">
-        <v>197</v>
-      </c>
-      <c r="F27" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="54" t="s">
-        <v>199</v>
-      </c>
-      <c r="J27" s="57"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="52"/>
+      <c r="C27" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="47" t="s">
+        <v>201</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="J27" s="52"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
       <c r="N27" s="25"/>
     </row>
     <row r="28" ht="38.25">
-      <c r="A28" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="B28" s="52" t="s">
+      <c r="A28" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="B28" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="E28" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="F28" s="58" t="s">
-        <v>202</v>
-      </c>
-      <c r="G28" s="52" t="s">
-        <v>203</v>
-      </c>
-      <c r="H28" s="52" t="s">
+      <c r="D28" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="G28" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="H28" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="I28" s="59" t="s">
-        <v>204</v>
-      </c>
-      <c r="J28" s="52" t="s">
-        <v>205</v>
-      </c>
-      <c r="K28" s="52"/>
-      <c r="L28" s="52" t="s">
+      <c r="I28" s="54" t="s">
+        <v>209</v>
+      </c>
+      <c r="J28" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="K28" s="47"/>
+      <c r="L28" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="M28" s="52"/>
-      <c r="N28" s="60" t="s">
-        <v>206</v>
+      <c r="M28" s="47"/>
+      <c r="N28" s="55" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="29" ht="89.25">
-      <c r="A29" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="B29" s="52" t="s">
+      <c r="A29" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="B29" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="52" t="s">
-        <v>207</v>
-      </c>
-      <c r="E29" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="F29" s="52" t="s">
+      <c r="D29" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" s="47" t="s">
+        <v>213</v>
+      </c>
+      <c r="F29" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="52" t="s">
-        <v>209</v>
-      </c>
-      <c r="H29" s="52" t="s">
+      <c r="G29" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="H29" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="59" t="s">
+      <c r="I29" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="J29" s="52" t="s">
-        <v>210</v>
-      </c>
-      <c r="K29" s="52" t="s">
+      <c r="J29" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="K29" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="L29" s="52" t="s">
+      <c r="L29" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="52"/>
-      <c r="N29" s="60" t="s">
-        <v>206</v>
+      <c r="M29" s="47"/>
+      <c r="N29" s="55" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="30" ht="25.5">
-      <c r="A30" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="B30" s="61" t="s">
+      <c r="A30" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B30" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="61" t="s">
+      <c r="C30" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="61" t="s">
-        <v>212</v>
-      </c>
-      <c r="E30" s="61" t="s">
-        <v>213</v>
-      </c>
-      <c r="F30" s="62"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="63" t="s">
-        <v>214</v>
-      </c>
-      <c r="J30" s="64"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="61" t="s">
-        <v>215</v>
-      </c>
-      <c r="M30" s="61"/>
-      <c r="N30" s="36"/>
+      <c r="D30" s="56" t="s">
+        <v>217</v>
+      </c>
+      <c r="E30" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="F30" s="57"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="J30" s="59"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="56" t="s">
+        <v>220</v>
+      </c>
+      <c r="M30" s="56"/>
+      <c r="N30" s="60"/>
     </row>
     <row r="31" ht="25.5">
-      <c r="A31" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="B31" s="61" t="s">
+      <c r="A31" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B31" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="61" t="s">
+      <c r="C31" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="61" t="s">
-        <v>216</v>
-      </c>
-      <c r="E31" s="61" t="s">
-        <v>213</v>
-      </c>
-      <c r="F31" s="62"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="63" t="s">
-        <v>217</v>
-      </c>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="36"/>
+      <c r="D31" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="E31" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="F31" s="57"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="58" t="s">
+        <v>222</v>
+      </c>
+      <c r="J31" s="56"/>
+      <c r="K31" s="56"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="60"/>
     </row>
     <row r="32" ht="25.5">
-      <c r="A32" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="B32" s="61" t="s">
+      <c r="A32" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B32" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="61" t="s">
+      <c r="C32" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="D32" s="61" t="s">
+      <c r="D32" s="56" t="s">
+        <v>223</v>
+      </c>
+      <c r="E32" s="56" t="s">
         <v>218</v>
       </c>
-      <c r="E32" s="61" t="s">
-        <v>213</v>
-      </c>
-      <c r="F32" s="62"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="63" t="s">
-        <v>214</v>
-      </c>
-      <c r="J32" s="64"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="61" t="s">
-        <v>215</v>
-      </c>
-      <c r="M32" s="61"/>
-      <c r="N32" s="36"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="J32" s="59"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56" t="s">
+        <v>220</v>
+      </c>
+      <c r="M32" s="56"/>
+      <c r="N32" s="60"/>
     </row>
     <row r="33" ht="25.5">
-      <c r="A33" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="B33" s="61" t="s">
+      <c r="A33" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B33" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="61" t="s">
-        <v>154</v>
-      </c>
-      <c r="D33" s="61" t="s">
-        <v>219</v>
-      </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="62" t="s">
-        <v>220</v>
-      </c>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="65"/>
-      <c r="J33" s="61"/>
-      <c r="K33" s="61"/>
-      <c r="L33" s="61"/>
-      <c r="M33" s="61"/>
-      <c r="N33" s="36"/>
+      <c r="C33" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="56" t="s">
+        <v>224</v>
+      </c>
+      <c r="E33" s="56"/>
+      <c r="F33" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="56"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="60"/>
     </row>
     <row r="34" ht="25.5">
-      <c r="A34" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="B34" s="61" t="s">
+      <c r="A34" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="C34" s="61" t="s">
-        <v>195</v>
-      </c>
-      <c r="D34" s="61" t="s">
-        <v>221</v>
-      </c>
-      <c r="E34" s="61" t="s">
-        <v>213</v>
-      </c>
-      <c r="F34" s="62"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="66"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="61"/>
-      <c r="M34" s="61"/>
-      <c r="N34" s="36"/>
+      <c r="C34" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="D34" s="56" t="s">
+        <v>226</v>
+      </c>
+      <c r="E34" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="F34" s="57"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="56"/>
+      <c r="N34" s="60"/>
     </row>
     <row r="35" ht="38.25">
-      <c r="A35" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="B35" s="61" t="s">
+      <c r="A35" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B35" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="61" t="s">
-        <v>195</v>
-      </c>
-      <c r="D35" s="61" t="s">
-        <v>222</v>
-      </c>
-      <c r="E35" s="61" t="s">
-        <v>213</v>
-      </c>
-      <c r="F35" s="62" t="s">
-        <v>223</v>
-      </c>
-      <c r="G35" s="61"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="63" t="s">
-        <v>224</v>
-      </c>
-      <c r="J35" s="61"/>
-      <c r="K35" s="61"/>
-      <c r="L35" s="61"/>
-      <c r="M35" s="61"/>
-      <c r="N35" s="36"/>
+      <c r="C35" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="D35" s="56" t="s">
+        <v>227</v>
+      </c>
+      <c r="E35" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="F35" s="57" t="s">
+        <v>228</v>
+      </c>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="58" t="s">
+        <v>229</v>
+      </c>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="60"/>
     </row>
     <row r="36" ht="38.25">
-      <c r="A36" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="B36" s="61" t="s">
+      <c r="A36" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B36" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="61" t="s">
-        <v>225</v>
-      </c>
-      <c r="D36" s="61" t="s">
-        <v>226</v>
-      </c>
-      <c r="E36" s="61" t="s">
-        <v>227</v>
-      </c>
-      <c r="F36" s="62" t="s">
-        <v>228</v>
-      </c>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="63" t="s">
-        <v>229</v>
-      </c>
-      <c r="J36" s="61"/>
-      <c r="K36" s="61"/>
-      <c r="L36" s="61" t="s">
+      <c r="C36" s="56" t="s">
+        <v>230</v>
+      </c>
+      <c r="D36" s="56" t="s">
+        <v>231</v>
+      </c>
+      <c r="E36" s="56" t="s">
+        <v>232</v>
+      </c>
+      <c r="F36" s="57" t="s">
+        <v>233</v>
+      </c>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="58" t="s">
+        <v>234</v>
+      </c>
+      <c r="J36" s="56"/>
+      <c r="K36" s="56"/>
+      <c r="L36" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="M36" s="61"/>
-      <c r="N36" s="36"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="60"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="B37" s="61" t="s">
+      <c r="A37" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B37" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="61" t="s">
-        <v>230</v>
-      </c>
-      <c r="D37" s="61" t="s">
-        <v>231</v>
-      </c>
-      <c r="E37" s="61" t="s">
-        <v>213</v>
-      </c>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="67"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="61"/>
-      <c r="M37" s="61"/>
-      <c r="N37" s="61" t="s">
-        <v>232</v>
+      <c r="C37" s="56" t="s">
+        <v>235</v>
+      </c>
+      <c r="D37" s="56" t="s">
+        <v>236</v>
+      </c>
+      <c r="E37" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="56"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="56"/>
+      <c r="N37" s="56" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="38" ht="51">
-      <c r="A38" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="B38" s="61" t="s">
+      <c r="A38" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B38" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="61" t="s">
-        <v>230</v>
-      </c>
-      <c r="D38" s="61" t="s">
-        <v>233</v>
-      </c>
-      <c r="E38" s="61" t="s">
-        <v>213</v>
-      </c>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="61"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="61"/>
-      <c r="M38" s="61"/>
-      <c r="N38" s="61" t="s">
-        <v>232</v>
+      <c r="C38" s="56" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" s="56" t="s">
+        <v>238</v>
+      </c>
+      <c r="E38" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="63"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="56"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="56" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="39" ht="51">
-      <c r="A39" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="B39" s="61" t="s">
+      <c r="A39" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B39" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="61" t="s">
-        <v>234</v>
-      </c>
-      <c r="D39" s="61" t="s">
-        <v>235</v>
-      </c>
-      <c r="E39" s="61" t="s">
-        <v>236</v>
-      </c>
-      <c r="F39" s="68" t="s">
+      <c r="C39" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="D39" s="56" t="s">
+        <v>240</v>
+      </c>
+      <c r="E39" s="56" t="s">
+        <v>241</v>
+      </c>
+      <c r="F39" s="64" t="s">
+        <v>242</v>
+      </c>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="63"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="56"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="56"/>
+      <c r="N39" s="56" t="s">
         <v>237</v>
-      </c>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="61"/>
-      <c r="K39" s="61"/>
-      <c r="L39" s="61"/>
-      <c r="M39" s="61"/>
-      <c r="N39" s="61" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="40" s="10" customFormat="1" ht="25.5">
-      <c r="A40" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="B40" s="61" t="s">
+      <c r="A40" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B40" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="61" t="s">
+      <c r="C40" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="61" t="s">
-        <v>238</v>
-      </c>
-      <c r="E40" s="61" t="s">
-        <v>213</v>
-      </c>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="61"/>
-      <c r="M40" s="61"/>
-      <c r="N40" s="61" t="s">
-        <v>232</v>
+      <c r="D40" s="56" t="s">
+        <v>243</v>
+      </c>
+      <c r="E40" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="56" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="69" t="s">
-        <v>239</v>
-      </c>
-      <c r="B41" s="69" t="s">
+      <c r="A41" s="65" t="s">
+        <v>244</v>
+      </c>
+      <c r="B41" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="69" t="s">
+      <c r="C41" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="69" t="s">
-        <v>240</v>
-      </c>
-      <c r="E41" s="69" t="s">
-        <v>241</v>
-      </c>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69" t="s">
-        <v>242</v>
-      </c>
-      <c r="H41" s="69" t="s">
+      <c r="D41" s="65" t="s">
+        <v>245</v>
+      </c>
+      <c r="E41" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="F41" s="65"/>
+      <c r="G41" s="65" t="s">
+        <v>247</v>
+      </c>
+      <c r="H41" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="I41" s="70"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69" t="s">
-        <v>140</v>
-      </c>
-      <c r="N41" s="69"/>
+      <c r="I41" s="66"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="65"/>
+      <c r="L41" s="65"/>
+      <c r="M41" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="N41" s="65"/>
     </row>
     <row r="42" ht="14.25">
       <c r="A42" s="1"/>
-      <c r="M42" s="71"/>
-      <c r="N42" s="71"/>
+      <c r="M42" s="67"/>
+      <c r="N42" s="67"/>
     </row>
     <row r="43" ht="14.25">
-      <c r="M43" s="71"/>
-      <c r="N43" s="71"/>
+      <c r="M43" s="67"/>
+      <c r="N43" s="67"/>
     </row>
     <row r="44" ht="14.25">
-      <c r="M44" s="71"/>
-      <c r="N44" s="71"/>
+      <c r="M44" s="67"/>
+      <c r="N44" s="67"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="M45" s="71"/>
-      <c r="N45" s="71"/>
+      <c r="M45" s="67"/>
+      <c r="N45" s="67"/>
     </row>
     <row r="46" ht="14.25">
-      <c r="M46" s="71"/>
-      <c r="N46" s="71"/>
+      <c r="M46" s="67"/>
+      <c r="N46" s="67"/>
     </row>
     <row r="47" ht="14.25">
-      <c r="M47" s="71"/>
-      <c r="N47" s="71"/>
+      <c r="M47" s="67"/>
+      <c r="N47" s="67"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="M48" s="71"/>
-      <c r="N48" s="71"/>
+      <c r="M48" s="67"/>
+      <c r="N48" s="67"/>
     </row>
     <row r="49" ht="14.25">
-      <c r="M49" s="71"/>
-      <c r="N49" s="71"/>
+      <c r="M49" s="67"/>
+      <c r="N49" s="67"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="M50" s="71"/>
-      <c r="N50" s="71"/>
+      <c r="M50" s="67"/>
+      <c r="N50" s="67"/>
     </row>
     <row r="51" ht="14.25">
-      <c r="M51" s="71"/>
-      <c r="N51" s="71"/>
+      <c r="M51" s="67"/>
+      <c r="N51" s="67"/>
     </row>
     <row r="52" ht="14.25">
-      <c r="M52" s="71"/>
-      <c r="N52" s="71"/>
+      <c r="M52" s="67"/>
+      <c r="N52" s="67"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="M53" s="71"/>
-      <c r="N53" s="71"/>
+      <c r="M53" s="67"/>
+      <c r="N53" s="67"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="M54" s="71"/>
-      <c r="N54" s="71"/>
+      <c r="M54" s="67"/>
+      <c r="N54" s="67"/>
     </row>
     <row r="55" ht="14.25">
-      <c r="M55" s="71"/>
-      <c r="N55" s="71"/>
+      <c r="M55" s="67"/>
+      <c r="N55" s="67"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="M56" s="71"/>
-      <c r="N56" s="71"/>
+      <c r="M56" s="67"/>
+      <c r="N56" s="67"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N41">
@@ -8615,9 +8645,9 @@
     <hyperlink r:id="rId9" ref="I13"/>
     <hyperlink r:id="rId10" location="c=indicator&amp;i=stru_2020_1.pbs20&amp;t=A02&amp;view=map11" ref="I14"/>
     <hyperlink r:id="rId11" ref="I15"/>
-    <hyperlink r:id="rId12" ref="I17"/>
-    <hyperlink r:id="rId13" ref="I18"/>
-    <hyperlink r:id="rId14" ref="I19"/>
+    <hyperlink r:id="rId12" ref="I16"/>
+    <hyperlink r:id="rId13" ref="I17"/>
+    <hyperlink r:id="rId14" ref="I18"/>
     <hyperlink r:id="rId15" ref="I20"/>
     <hyperlink r:id="rId16" ref="I21"/>
     <hyperlink r:id="rId17" ref="I22"/>
@@ -8649,60 +8679,60 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="72" t="s">
-        <v>243</v>
-      </c>
-      <c r="B1" s="72" t="s">
-        <v>244</v>
+      <c r="A1" s="68" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="2" s="0" customFormat="1" ht="14.25">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="74" t="s">
-        <v>245</v>
+      <c r="B2" s="70" t="s">
+        <v>250</v>
       </c>
       <c r="C2"/>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="27" t="s">
-        <v>132</v>
+      <c r="A3" s="29" t="s">
+        <v>153</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="44" t="s">
-        <v>172</v>
+      <c r="A4" s="39" t="s">
+        <v>177</v>
       </c>
       <c r="B4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="52" t="s">
-        <v>186</v>
+      <c r="A5" s="47" t="s">
+        <v>191</v>
       </c>
       <c r="B5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="61" t="s">
-        <v>211</v>
+      <c r="A6" s="56" t="s">
+        <v>216</v>
       </c>
       <c r="B6" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="69" t="s">
-        <v>239</v>
+      <c r="A7" s="65" t="s">
+        <v>244</v>
       </c>
       <c r="B7" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -8725,20 +8755,20 @@
     <col customWidth="1" min="6" max="6" width="12.8515625"/>
     <col bestFit="1" customWidth="1" min="7" max="7" width="25.78125"/>
     <col bestFit="1" customWidth="1" min="8" max="8" width="21.3515625"/>
-    <col customWidth="1" min="9" max="9" style="75" width="32.7109375"/>
+    <col customWidth="1" min="9" max="9" style="71" width="32.7109375"/>
     <col customWidth="1" min="10" max="10" width="23.57421875"/>
     <col customWidth="1" min="11" max="11" width="44.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" s="72" customFormat="1" ht="25.5">
-      <c r="A1" s="72" t="s">
+    <row r="1" s="68" customFormat="1" ht="25.5">
+      <c r="A1" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="72" t="s">
-        <v>251</v>
-      </c>
-      <c r="C1" s="72" t="s">
-        <v>252</v>
+      <c r="B1" s="68" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>257</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>9</v>
@@ -8755,49 +8785,49 @@
       <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="76" t="s">
-        <v>253</v>
-      </c>
-      <c r="J1" s="72" t="s">
-        <v>254</v>
-      </c>
-      <c r="K1" s="72" t="s">
+      <c r="I1" s="72" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1" s="68" t="s">
+        <v>259</v>
+      </c>
+      <c r="K1" s="68" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="77" customFormat="1" ht="28.5">
-      <c r="A2" s="78" t="s">
+    <row r="2" s="73" customFormat="1" ht="28.5">
+      <c r="A2" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="79" t="s">
-        <v>255</v>
-      </c>
-      <c r="C2" s="78" t="s">
-        <v>256</v>
-      </c>
-      <c r="D2" s="79" t="s">
-        <v>257</v>
-      </c>
-      <c r="E2" s="79" t="s">
-        <v>258</v>
-      </c>
-      <c r="F2" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="G2" s="77" t="s">
+      <c r="B2" s="75" t="s">
         <v>260</v>
       </c>
-      <c r="H2" s="78" t="s">
+      <c r="C2" s="74" t="s">
         <v>261</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="D2" s="75" t="s">
         <v>262</v>
       </c>
-      <c r="J2" s="77" t="s">
+      <c r="E2" s="75" t="s">
         <v>263</v>
       </c>
-      <c r="K2" s="81" t="s">
+      <c r="F2" s="75" t="s">
         <v>264</v>
+      </c>
+      <c r="G2" s="73" t="s">
+        <v>265</v>
+      </c>
+      <c r="H2" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="I2" s="76" t="s">
+        <v>267</v>
+      </c>
+      <c r="J2" s="73" t="s">
+        <v>268</v>
+      </c>
+      <c r="K2" s="77" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/progress/megatrends_RF.xlsx
+++ b/progress/megatrends_RF.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Abandonned" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Megatrends!$A$1:$N$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Megatrends!$A$1:$N$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Megatrends!$A$1:$N$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Megatrends!$A$1:$N$72</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="400">
   <si>
     <t>Calcul</t>
   </si>
@@ -69,37 +69,42 @@
     <t xml:space="preserve">0. ready</t>
   </si>
   <si>
+    <t xml:space="preserve">Political stringency
+Productivism shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHG emissions reduction + Pesticide use reduction
+Land-cover change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% organic farming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of organic crop relative to the cultivated area </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agence Bio (Cartobio)</t>
+  </si>
+  <si>
+    <t>BIO_AREA_PCT</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>https://www.data.gouv.fr/datasets/parcelles-certifiees-en-agriculture-biologique-sur-cartobio</t>
+  </si>
+  <si>
+    <t>cartobio_parcelles_2024_francemet_2154.gpkg</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>02a_get_bio.R</t>
+  </si>
+  <si>
     <t xml:space="preserve">Political stringency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHG emissions reduction + Pesticide use reduction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% organic farming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% of organic crop relative to the cultivated area </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agence Bio (Cartobio)</t>
-  </si>
-  <si>
-    <t>BIO_AREA_PCT</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>https://www.data.gouv.fr/datasets/parcelles-certifiees-en-agriculture-biologique-sur-cartobio</t>
-  </si>
-  <si>
-    <t>cartobio_parcelles_2024_francemet_2154.gpkg</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>02a_get_bio.R</t>
   </si>
   <si>
     <t xml:space="preserve">Protected area</t>
@@ -199,8 +204,14 @@
     <t>02d_get_telepac.R</t>
   </si>
   <si>
+    <t xml:space="preserve">Political stringency
+Demographic change
+Productivism shift</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pesticide use reduction
-Changes in farming practices</t>
+Changes in farming practices
+Land-use intensity</t>
   </si>
   <si>
     <t xml:space="preserve">Pesticide residues on land and water</t>
@@ -234,7 +245,8 @@
   </si>
   <si>
     <t xml:space="preserve">Fertilizer use reduction
-Changes in farming practices</t>
+Changes in farming practices
+Land-use intensity</t>
   </si>
   <si>
     <t xml:space="preserve">Nitrate levels</t>
@@ -292,10 +304,12 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Demographic change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changes in farming practices</t>
+    <t xml:space="preserve">Demographic change
+Productivism shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changes in farming practices
+Farm system + Land-use intensity</t>
   </si>
   <si>
     <t xml:space="preserve">Field size</t>
@@ -326,7 +340,45 @@
     <t>02g_get_rpg.R</t>
   </si>
   <si>
-    <t xml:space="preserve">GHG emissions reduction</t>
+    <t xml:space="preserve">Political stringency
+Climate change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pesticide + Fertilizer use reduction
+Precipitation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crop type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominant crop by municipality in term of surface area</t>
+  </si>
+  <si>
+    <t>CROP_DOMINANT</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP subsidies 
+Changes in farming practices
+Land-use intensity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crop diversity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shannon index calculated with all RPG classes</t>
+  </si>
+  <si>
+    <t>CROP_DIV_SHANNON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHG emissions reduction
+Land-use intensity + Land-cover change</t>
   </si>
   <si>
     <t xml:space="preserve">% fallow land</t>
@@ -338,38 +390,22 @@
     <t>FALLOW_AREA_PCT</t>
   </si>
   <si>
-    <t xml:space="preserve">2007 to 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pesticide + Fertilizer use reduction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crop type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominant crop by municipality in term of surface area</t>
-  </si>
-  <si>
-    <t>CROP_DOMINANT</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>Farm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP subsidies 
-Changes in farming practices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crop diversity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shannon index calculated with all RPG classes</t>
-  </si>
-  <si>
-    <t>CROP_DIV_SHANNON</t>
+    <t xml:space="preserve">Productivism shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land-cover change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% crop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent of cropland per municipality</t>
+  </si>
+  <si>
+    <t>CULTIVATED_AREA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demographic change</t>
   </si>
   <si>
     <t xml:space="preserve">Changes in farmer population structure</t>
@@ -414,6 +450,28 @@
     <t xml:space="preserve">MANY NA</t>
   </si>
   <si>
+    <t xml:space="preserve">Changes in farming practices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pct_Superieur → Percent of farm holders with higher education.</t>
+  </si>
+  <si>
+    <t>AGRESTE_EDUSUP_PCT_2010</t>
+  </si>
+  <si>
+    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=empl1.partformsup10&amp;t=A02&amp;view=map1</t>
+  </si>
+  <si>
+    <t>data_Agreste_Commune2010.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changes in farming practices
+Productivity of farm</t>
+  </si>
+  <si>
     <t>Productivity</t>
   </si>
   <si>
@@ -429,25 +487,11 @@
     <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=stru_2020_1.pbs20&amp;t=A02&amp;view=map11</t>
   </si>
   <si>
-    <t xml:space="preserve">Education level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pct_Superieur → Percent of farm holders with higher education.</t>
-  </si>
-  <si>
-    <t>AGRESTE_EDUSUP_PCT_2010</t>
-  </si>
-  <si>
-    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=empl1.partformsup10&amp;t=A02&amp;view=map1</t>
-  </si>
-  <si>
-    <t>data_Agreste_Commune2010.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changes in the farmer populations </t>
-  </si>
-  <si>
-    <t xml:space="preserve">farm size</t>
+    <t xml:space="preserve">Changes in the farmer populations 
+Farm system + Productivity of farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farm size</t>
   </si>
   <si>
     <r>
@@ -461,6 +505,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <color indexed="2"/>
         <rFont val="Calibri"/>
         <scheme val="minor"/>
@@ -475,6 +520,25 @@
     <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=raanc2.saumoyaa&amp;s=2010&amp;t=A02&amp;view=map1</t>
   </si>
   <si>
+    <t xml:space="preserve">Land-use intensity</t>
+  </si>
+  <si>
+    <t>Irrigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part_irrig_2020 → Average UAA (Utilized Agricultural Area) irrigated per municipality in 2020.</t>
+  </si>
+  <si>
+    <t>AGRESTE_IRRIGATED</t>
+  </si>
+  <si>
+    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=cult_2020_2.partirrig20_&amp;t=A02&amp;view=map11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pesticide + Fertilizer use reduction
+Land-use intensity</t>
+  </si>
+  <si>
     <t xml:space="preserve">Crop rotation</t>
   </si>
   <si>
@@ -536,73 +600,372 @@
 https://enseignement-agricole.opendatasoft.com/explore/dataset/refea-liste-des-etablissements-proposant-des-formations-agricoles-2025-2026/export/</t>
   </si>
   <si>
-    <t xml:space="preserve">1. almost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP subsidies
-GHG emissions reduction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% area dedicated to different measures (AES, organic farming, Mesures agroenvironnementales et climatiques (MAEC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AES, bio, MAEC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPG niveau 2</t>
-  </si>
-  <si>
-    <t>PS_GREEN_AREA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">restricted information</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Meurice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not same commune (3000 mismatch)
-can it be calculated at maille level?</t>
-  </si>
-  <si>
-    <t>Urbanization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Population density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nb inhabitants/municipality area (km²)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSEE - ADMIN_EXPRESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pop_dens - commune
-JRC - 100m raster?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.insee.fr/fr/statistiques/3698339
-https://www.insee.fr/fr/statistiques/8272002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1876 - 2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">can we spatialize the density?</t>
+    <t xml:space="preserve">Sensitivity to nature protection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Density of hiking path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiking linear line density</t>
+  </si>
+  <si>
+    <t>OSM</t>
+  </si>
+  <si>
+    <t>OSM_HIKING</t>
+  </si>
+  <si>
+    <t>km/ha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.data.gouv.fr/fr/datasets/itineraires-de-randonnee-dans-openstreetmap/
+https://download.geofabrik.de/</t>
+  </si>
+  <si>
+    <t>geofabrik_france-latest.gpkg</t>
+  </si>
+  <si>
+    <t>linear</t>
+  </si>
+  <si>
+    <t>02k_get_osm.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urbanization
+Land-use intensity</t>
   </si>
   <si>
     <t xml:space="preserve">Road density</t>
   </si>
   <si>
+    <t xml:space="preserve">length of road network per area</t>
+  </si>
+  <si>
+    <t>OSM_ROADS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://geoservices.ign.fr/bdtopo
+https://download.geofabrik.de/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Climate change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme events</t>
+  </si>
+  <si>
+    <t>Drought</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average spring–summer 2025 SPEI calculated for each municipality.</t>
+  </si>
+  <si>
+    <t>JRC</t>
+  </si>
+  <si>
+    <t>https://drought.emergency.copernicus.eu/tumbo/edo/download/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme events
+Precipitation </t>
+  </si>
+  <si>
+    <t>Frost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average number of frost days in 2023 for each municipality</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>WORDCLIM</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">length of road network per area
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>CHELSA</t>
+    </r>
+  </si>
+  <si>
+    <t>frost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precipitation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual precipitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual mean precipitation computed from the monthly mean values per municipality.</t>
+  </si>
+  <si>
+    <t>PREC_mn_24</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.worldclim.org/data/worldclim21.html https://donneespubliques.meteofrance.fr/?fond=produit&amp;id_produit=113&amp;id_rubrique=37
+</t>
+  </si>
+  <si>
+    <t>1km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer precipitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer mean precipitation computed from the monthly mean values per municipality.</t>
+  </si>
+  <si>
+    <t>PREC_mn_24_sum</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>https://www.worldclim.org/data/worldclim21.html</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>https://donneespubliques.meteofrance.fr/?fond=produit&amp;id_produit=113&amp;id_rubrique=37</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature increase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual mean minimum and maximum temperature computed from the monthly mean values per municipality.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMIN_mn_24, TMAX_mn_24</t>
+  </si>
+  <si>
+    <t>°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer mean minimum and maximum precipitation computed from the monthly mean values per municipality.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMIN_mn_24_sum, TMAX_mn_24_sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sex ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of female farm holders</t>
+  </si>
+  <si>
+    <t>SEX_RATIO_F</t>
+  </si>
+  <si>
+    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=empl1.partfcexcoex10&amp;t=A01&amp;view=map2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not yet</t>
+  </si>
+  <si>
+    <t>Canton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">only available for 2010 at canton levels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changes in the farmer populations </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evolution of the number of farms</t>
+  </si>
+  <si>
+    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=empl1.cexcoexev&amp;t=A01&amp;view=map2</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changes in the farmer populations
+Land-cover change + Land-use intensity</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> % farmland abandonment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of farm with unknown successor</t>
+  </si>
+  <si>
+    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=stru2.partssucnb10&amp;t=A01&amp;view=map2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same as Evolution of farms?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urbanization
+Land-use intensity + Land-cover change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Population density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nb inhabitants/municipality area (km²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSEE - ADMIN_EXPRESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pop_dens - commune
+JRC - 100m raster?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.insee.fr/fr/statistiques/3698339
+https://www.insee.fr/fr/statistiques/8272002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1876 - 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">can we spatialize the density?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Productivism shift
+Climate change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land-cover change + Land-use intensity
+Temperature increase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alley cropping density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEDGEROW_dens → Hedgerow linear density (m/ha)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGN BD HAIES
+GRAIN_BOCAGER? Liu 2023?</t>
+  </si>
+  <si>
+    <t>HEDGEROW_dens</t>
+  </si>
+  <si>
+    <t>m/ha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://geoservices.ign.fr/bdhaie
+https://cartes.gouv.fr/rechercher-une-donnee/dataset/INRAE_GRAIN-BOCAGER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BD HAIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alley cropping not informed by BD Haies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land-use intensity
+Precipitation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean topographic slope</t>
+  </si>
+  <si>
+    <t>geomorph90m</t>
+  </si>
+  <si>
+    <t>GEOMORPH_SLOPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://geoservices.ign.fr/bdalti
+https://geoservices.ign.fr/rgealti
+https://portal.opentopography.org/dataspace/dataset?opentopoID=OTDS.012020.4326.1</t>
+  </si>
+  <si>
+    <t>Geomorph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. on hold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature increase
+Extreme events
+Precipitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vegetation cover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not clear? linked to Ecolandscape?</t>
+  </si>
+  <si>
+    <t>OSO?</t>
+  </si>
+  <si>
+    <t>https://geoservices.ign.fr/documentation/donnees/vecteur/bdtopo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BD TOPO</t>
+  </si>
+  <si>
+    <t>https://geoservices.ign.fr/sites/default/files/2024-08/DC_BDTOPO_3-4.pdf</t>
+  </si>
+  <si>
+    <t>Floods</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Percent of floods area per municipality
 </t>
     </r>
     <r>
@@ -611,65 +974,58 @@
         <color indexed="2"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">which kind of road?</t>
+      <t xml:space="preserve">based on history? groundwater?</t>
     </r>
-  </si>
-  <si>
-    <t>BD_TOPO</t>
-  </si>
-  <si>
-    <t>km/ha</t>
-  </si>
-  <si>
-    <t>https://geoservices.ign.fr/bdtopo</t>
-  </si>
-  <si>
-    <t>linear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sex ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage of female farm holders</t>
-  </si>
-  <si>
-    <t>SEX_RATIO_F</t>
-  </si>
-  <si>
-    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=empl1.partfcexcoex10&amp;t=A01&amp;view=map2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not yet</t>
-  </si>
-  <si>
-    <t>Canton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">only available for 2010 at canton levels</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> % farmland abandonment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage of farm with unknown successor</t>
-  </si>
-  <si>
-    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=stru2.partssucnb10&amp;t=A01&amp;view=map2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same as Evolution of farms?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evolution of the number of farms</t>
-  </si>
-  <si>
-    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=empl1.cexcoexev&amp;t=A01&amp;view=map2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. on hold</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Georisques</t>
+  </si>
+  <si>
+    <t>FLOODS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">httpswww.georisques.gouv.frdonneesbases-de-donneeszonages-inondation-rapportage-2020
+https://www.georisques.gouv.fr/donnees/bases-de-donnees/inondations-par-remontee-de-nappes</t>
+  </si>
+  <si>
+    <t>Re_nappes_fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precipitation 
+Extreme events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runoff and infiltration</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://entrepot.recherche.data.gouv.fr/dataset.xhtml?persistentId=doi:10.15454/BPN57S
+https://www.drias-eau.fr/commande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vegetation structure (vertical)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">height_mean → Average vegetation height
+height_sd → Variability of vegetation height
+strat → Vertical stratification (Shannon index)
+wooded_pixel→ Number of wooded pixels per municipality</t>
+  </si>
+  <si>
+    <t>GRAIN_BOCAGER</t>
+  </si>
+  <si>
+    <t>https://cartes.gouv.fr/rechercher-une-donnee/dataset/INRAE_GRAIN-BOCAGER</t>
   </si>
   <si>
     <t xml:space="preserve">Sensitivity to agroecology</t>
@@ -694,47 +1050,6 @@
   </si>
   <si>
     <t>?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitivity to nature protection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Density of hiking path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIKING_dens → Hiking linear line density (m/ha)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BD_TOPO?
-OSM?</t>
-  </si>
-  <si>
-    <t>https://www.data.gouv.fr/fr/datasets/itineraires-de-randonnee-dans-openstreetmap/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P_FOR→ % of forest relative to the total area of the municipality (standardized by municipality size)
-Too correlated with land cover?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IGN BD FORET
-BD TOPO? 
-OSO?</t>
-  </si>
-  <si>
-    <t>PS_FOREST_AREA</t>
-  </si>
-  <si>
-    <t>https://geoservices.ign.fr/bdforet</t>
-  </si>
-  <si>
-    <t>BD_FORET_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">too corralated 
-to land cover</t>
   </si>
   <si>
     <t xml:space="preserve">% grassland</t>
@@ -774,9 +1089,162 @@
     <t>IGNF_RPG_2-1</t>
   </si>
   <si>
+    <t xml:space="preserve">2007 to 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">too corralated 
+to land cover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHG emissions reduction + Pesticide use reduction
+Land-cover change + Extreme events + Precipitation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">% forest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_FOR→ % of forest relative to the total area of the municipality (standardized by municipality size)
+Too correlated with land cover?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGN BD FORET
+BD TOPO? 
+OSO?</t>
+  </si>
+  <si>
+    <t>PS_FOREST_AREA</t>
+  </si>
+  <si>
+    <t>https://geoservices.ign.fr/bdforet</t>
+  </si>
+  <si>
+    <t>BD_FORET_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farm system
+Land-use intensity</t>
+  </si>
+  <si>
+    <t>Specialization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPEC → Techno-economic orientation of farms by municipality in 2025. For municipalities that merged in 2020 and 2025, the orientation of the largest municipality was retained.</t>
+  </si>
+  <si>
+    <t>OTEX</t>
+  </si>
+  <si>
+    <t>https://stats.agriculture.gouv.fr/cartostat/#c=indicator&amp;i=otex_2020_1.otefdd20&amp;t=A02&amp;view=map11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010 - 2020</t>
+  </si>
+  <si>
+    <t>Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 or 17 categories?
+how to group them per cell?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land artificialization</t>
+  </si>
+  <si>
+    <t>https://geoservices.ign.fr/bdtopo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree density in and around crops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">similar to Alley cropping density ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAIN_BOCAGER?
+BD HAIES? Liu 2023?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://geoservices.ign.fr/bdforet
+https://cosia.ign.fr/info#export
+Liu et al. 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio between the number of livestock units (LU) and crop production.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which metrics and how to combine crop and liverstock?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">https://agreste.agriculture.gouv.fr/agreste-web/disaron/G_2141/detail/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>https://geoservices.ign.fr/rpg</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipality (Agreste)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Productivity of farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suitability of soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réserve utile : bdgsf_classe_ru : Cette carte donne la classe de réserve utile en eau dominante par Unité Cartographique de Sol de la Base de Données Géographique des Sols de France à 1/1 000 000. Les valeurs des classes sont : 1 : &lt; 50 mm 2 : 50-100 mm 3 : 100-150 mm 4 : 150 - 200 mm 5 : &gt;= 200 mm 9 : non sols (villes, lacs, etc.) French (2011-07-27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://esdac.jrc.ec.europa.eu/resource-type/european-soil-database-soil-properties
+https://geodata.inrae.fr/datahub/search?q=info%26sols
+https://geodata.inrae.fr/datahub/dataset/393d8106-4400-51cd-9767-e8bbef2f73a6
+https://entrepot.recherche.data.gouv.fr/dataset.xhtml?persistentId=doi%3A10.15454%2FJPB9RB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1km * 1km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil suitability seems different than productivity of farm
+How to get a numeric or categorical variable per spatial unit?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land fragmentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which landscape metrics?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGN RPG
+OSO?</t>
+  </si>
+  <si>
     <t xml:space="preserve">4. no idea</t>
   </si>
   <si>
+    <t xml:space="preserve">RUNOFF (Modele RUSLE) : https://cosia.ign.fr/info#export
+https://entrepot.recherche.data.gouv.fr/dataverse/bdgsf
+https://www.worldclim.org/data/worldclim21.html
+https://geoservices.ign.fr/rgealti</t>
+  </si>
+  <si>
+    <t>Pixel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runoff = RUSLE
+Infiltration = P - Q </t>
+  </si>
+  <si>
     <t xml:space="preserve">Adhesion to a cooperative</t>
   </si>
   <si>
@@ -784,9 +1252,6 @@
   </si>
   <si>
     <t>https://link.mycuma.fr/carte?zoom=10&amp;lat=42.638889&amp;lng=2.694444666666667</t>
-  </si>
-  <si>
-    <t>Municipality</t>
   </si>
   <si>
     <t xml:space="preserve">Average distance of field from farm headquarter</t>
@@ -861,9 +1326,80 @@
     <t xml:space="preserve">Fertilizer sales</t>
   </si>
   <si>
+    <t xml:space="preserve">% type of farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forest management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grassland management</t>
+  </si>
+  <si>
+    <t>Incomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trade practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local/global trade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type of resellers</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">https://link.mycuma.fr/carte?zoom=10&amp;lat=42.638889&amp;lng=2.694444666666667
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>https://www.cuma.fr/contacter-une-federation/</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">5. Paul</t>
   </si>
   <si>
+    <t xml:space="preserve">CAP subsidies
+GHG emissions reduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% area dedicated to different measures (AES, organic farming, Mesures agroenvironnementales et climatiques (MAEC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AES, bio, MAEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPG niveau 2</t>
+  </si>
+  <si>
+    <t>PS_GREEN_AREA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">restricted information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Meurice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not same commune (3000 mismatch)
+can it be calculated at maille level?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHG emissions reduction
+Land-use intensity</t>
+  </si>
+  <si>
     <t>Agroforestry</t>
   </si>
   <si>
@@ -880,6 +1416,9 @@
   </si>
   <si>
     <t xml:space="preserve">script is ready and running, some details might be improved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. almost</t>
   </si>
   <si>
     <t xml:space="preserve">data is available, calculations are clear and feasible =&gt; indicator calculated or under reach</t>
@@ -946,7 +1485,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -1012,11 +1551,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.000000"/>
-      <color indexed="2"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -1028,15 +1562,26 @@
       <color indexed="4"/>
     </font>
     <font>
-      <u/>
+      <sz val="10.000000"/>
+      <color indexed="2"/>
+      <name val="Arial"/>
     </font>
     <font>
+      <sz val="10.000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="10.000000"/>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -1103,7 +1648,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="100">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1167,11 +1712,15 @@
     <xf fontId="8" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="9" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="10" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1183,35 +1732,27 @@
     <xf fontId="11" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="12" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="12" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="5" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1">
+      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="10" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="5" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="10" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="6" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="4" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1220,39 +1761,66 @@
     <xf fontId="3" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf fontId="12" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="13" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="14" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf fontId="9" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="3" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf fontId="14" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="6" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="9" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="15" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="11" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="16" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf fontId="14" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="15" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="5" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="17" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="16" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="18" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="12" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1260,9 +1828,43 @@
     <xf fontId="1" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="3" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="11" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="6" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="6" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="8" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="2" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="5" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="2" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1272,7 +1874,6 @@
     <xf fontId="6" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="11" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1282,25 +1883,36 @@
     <xf fontId="2" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="12" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="14" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="15" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="2" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="14" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="14" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="5" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="17" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="2" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1819,7 +2431,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" style="1" width="15.421875"/>
     <col customWidth="1" min="2" max="2" width="19.8515625"/>
-    <col customWidth="1" min="3" max="3" width="27.57421875"/>
+    <col customWidth="1" min="3" max="3" width="32.421875"/>
     <col customWidth="1" min="4" max="4" width="31.57421875"/>
     <col customWidth="1" min="5" max="5" width="58.8515625"/>
     <col customWidth="1" min="6" max="6" width="32.140625"/>
@@ -1830,6 +2442,7 @@
     <col customWidth="1" min="12" max="12" width="12.140625"/>
     <col customWidth="1" min="13" max="13" width="21.28125"/>
     <col customWidth="1" min="14" max="14" width="21.140625"/>
+    <col min="15" max="75" style="0" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="1" ht="25.5">
@@ -2177,67 +2790,67 @@
         <v>25</v>
       </c>
       <c r="N2" s="9"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AG2" s="10"/>
-      <c r="AH2" s="10"/>
-      <c r="AI2" s="10"/>
-      <c r="AJ2" s="10"/>
-      <c r="AK2" s="10"/>
-      <c r="AL2" s="10"/>
-      <c r="AM2" s="10"/>
-      <c r="AN2" s="10"/>
-      <c r="AO2" s="10"/>
-      <c r="AP2" s="10"/>
-      <c r="AQ2" s="10"/>
-      <c r="AR2" s="10"/>
-      <c r="AS2" s="10"/>
-      <c r="AT2" s="10"/>
-      <c r="AU2" s="10"/>
-      <c r="AV2" s="10"/>
-      <c r="AW2" s="10"/>
-      <c r="AX2" s="10"/>
-      <c r="AY2" s="10"/>
-      <c r="AZ2" s="10"/>
-      <c r="BA2" s="10"/>
-      <c r="BB2" s="10"/>
-      <c r="BC2" s="10"/>
-      <c r="BD2" s="10"/>
-      <c r="BE2" s="10"/>
-      <c r="BF2" s="10"/>
-      <c r="BG2" s="10"/>
-      <c r="BH2" s="10"/>
-      <c r="BI2" s="10"/>
-      <c r="BJ2" s="10"/>
-      <c r="BK2" s="10"/>
-      <c r="BL2" s="10"/>
-      <c r="BM2" s="10"/>
-      <c r="BN2" s="10"/>
-      <c r="BO2" s="10"/>
-      <c r="BP2" s="10"/>
-      <c r="BQ2" s="10"/>
-      <c r="BR2" s="10"/>
-      <c r="BS2" s="10"/>
-      <c r="BT2" s="10"/>
-      <c r="BU2" s="10"/>
-      <c r="BV2" s="10"/>
-      <c r="BW2" s="10"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
       <c r="BX2" s="10"/>
       <c r="BY2" s="10"/>
       <c r="BZ2" s="10"/>
@@ -2443,105 +3056,105 @@
         <v>14</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" s="7">
         <v>2026</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-      <c r="AB3" s="10"/>
-      <c r="AC3" s="10"/>
-      <c r="AD3" s="10"/>
-      <c r="AE3" s="10"/>
-      <c r="AF3" s="10"/>
-      <c r="AG3" s="10"/>
-      <c r="AH3" s="10"/>
-      <c r="AI3" s="10"/>
-      <c r="AJ3" s="10"/>
-      <c r="AK3" s="10"/>
-      <c r="AL3" s="10"/>
-      <c r="AM3" s="10"/>
-      <c r="AN3" s="10"/>
-      <c r="AO3" s="10"/>
-      <c r="AP3" s="10"/>
-      <c r="AQ3" s="10"/>
-      <c r="AR3" s="10"/>
-      <c r="AS3" s="10"/>
-      <c r="AT3" s="10"/>
-      <c r="AU3" s="10"/>
-      <c r="AV3" s="10"/>
-      <c r="AW3" s="10"/>
-      <c r="AX3" s="10"/>
-      <c r="AY3" s="10"/>
-      <c r="AZ3" s="10"/>
-      <c r="BA3" s="10"/>
-      <c r="BB3" s="10"/>
-      <c r="BC3" s="10"/>
-      <c r="BD3" s="10"/>
-      <c r="BE3" s="10"/>
-      <c r="BF3" s="10"/>
-      <c r="BG3" s="10"/>
-      <c r="BH3" s="10"/>
-      <c r="BI3" s="10"/>
-      <c r="BJ3" s="10"/>
-      <c r="BK3" s="10"/>
-      <c r="BL3" s="10"/>
-      <c r="BM3" s="10"/>
-      <c r="BN3" s="10"/>
-      <c r="BO3" s="10"/>
-      <c r="BP3" s="10"/>
-      <c r="BQ3" s="10"/>
-      <c r="BR3" s="10"/>
-      <c r="BS3" s="10"/>
-      <c r="BT3" s="10"/>
-      <c r="BU3" s="10"/>
-      <c r="BV3" s="10"/>
-      <c r="BW3" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+      <c r="AB3"/>
+      <c r="AC3"/>
+      <c r="AD3"/>
+      <c r="AE3"/>
+      <c r="AF3"/>
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3"/>
+      <c r="AJ3"/>
+      <c r="AK3"/>
+      <c r="AL3"/>
+      <c r="AM3"/>
+      <c r="AN3"/>
+      <c r="AO3"/>
+      <c r="AP3"/>
+      <c r="AQ3"/>
+      <c r="AR3"/>
+      <c r="AS3"/>
+      <c r="AT3"/>
+      <c r="AU3"/>
+      <c r="AV3"/>
+      <c r="AW3"/>
+      <c r="AX3"/>
+      <c r="AY3"/>
+      <c r="AZ3"/>
+      <c r="BA3"/>
+      <c r="BB3"/>
+      <c r="BC3"/>
+      <c r="BD3"/>
+      <c r="BE3"/>
+      <c r="BF3"/>
+      <c r="BG3"/>
+      <c r="BH3"/>
+      <c r="BI3"/>
+      <c r="BJ3"/>
+      <c r="BK3"/>
+      <c r="BL3"/>
+      <c r="BM3"/>
+      <c r="BN3"/>
+      <c r="BO3"/>
+      <c r="BP3"/>
+      <c r="BQ3"/>
+      <c r="BR3"/>
+      <c r="BS3"/>
+      <c r="BT3"/>
+      <c r="BU3"/>
+      <c r="BV3"/>
+      <c r="BW3"/>
       <c r="BX3" s="10"/>
       <c r="BY3" s="10"/>
       <c r="BZ3" s="10"/>
@@ -2747,103 +3360,103 @@
         <v>14</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N4" s="7"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="10"/>
-      <c r="AF4" s="10"/>
-      <c r="AG4" s="10"/>
-      <c r="AH4" s="10"/>
-      <c r="AI4" s="10"/>
-      <c r="AJ4" s="10"/>
-      <c r="AK4" s="10"/>
-      <c r="AL4" s="10"/>
-      <c r="AM4" s="10"/>
-      <c r="AN4" s="10"/>
-      <c r="AO4" s="10"/>
-      <c r="AP4" s="10"/>
-      <c r="AQ4" s="10"/>
-      <c r="AR4" s="10"/>
-      <c r="AS4" s="10"/>
-      <c r="AT4" s="10"/>
-      <c r="AU4" s="10"/>
-      <c r="AV4" s="10"/>
-      <c r="AW4" s="10"/>
-      <c r="AX4" s="10"/>
-      <c r="AY4" s="10"/>
-      <c r="AZ4" s="10"/>
-      <c r="BA4" s="10"/>
-      <c r="BB4" s="10"/>
-      <c r="BC4" s="10"/>
-      <c r="BD4" s="10"/>
-      <c r="BE4" s="10"/>
-      <c r="BF4" s="10"/>
-      <c r="BG4" s="10"/>
-      <c r="BH4" s="10"/>
-      <c r="BI4" s="10"/>
-      <c r="BJ4" s="10"/>
-      <c r="BK4" s="10"/>
-      <c r="BL4" s="10"/>
-      <c r="BM4" s="10"/>
-      <c r="BN4" s="10"/>
-      <c r="BO4" s="10"/>
-      <c r="BP4" s="10"/>
-      <c r="BQ4" s="10"/>
-      <c r="BR4" s="10"/>
-      <c r="BS4" s="10"/>
-      <c r="BT4" s="10"/>
-      <c r="BU4" s="10"/>
-      <c r="BV4" s="10"/>
-      <c r="BW4" s="10"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4"/>
+      <c r="AB4"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
+      <c r="AE4"/>
+      <c r="AF4"/>
+      <c r="AG4"/>
+      <c r="AH4"/>
+      <c r="AI4"/>
+      <c r="AJ4"/>
+      <c r="AK4"/>
+      <c r="AL4"/>
+      <c r="AM4"/>
+      <c r="AN4"/>
+      <c r="AO4"/>
+      <c r="AP4"/>
+      <c r="AQ4"/>
+      <c r="AR4"/>
+      <c r="AS4"/>
+      <c r="AT4"/>
+      <c r="AU4"/>
+      <c r="AV4"/>
+      <c r="AW4"/>
+      <c r="AX4"/>
+      <c r="AY4"/>
+      <c r="AZ4"/>
+      <c r="BA4"/>
+      <c r="BB4"/>
+      <c r="BC4"/>
+      <c r="BD4"/>
+      <c r="BE4"/>
+      <c r="BF4"/>
+      <c r="BG4"/>
+      <c r="BH4"/>
+      <c r="BI4"/>
+      <c r="BJ4"/>
+      <c r="BK4"/>
+      <c r="BL4"/>
+      <c r="BM4"/>
+      <c r="BN4"/>
+      <c r="BO4"/>
+      <c r="BP4"/>
+      <c r="BQ4"/>
+      <c r="BR4"/>
+      <c r="BS4"/>
+      <c r="BT4"/>
+      <c r="BU4"/>
+      <c r="BV4"/>
+      <c r="BW4"/>
       <c r="BX4" s="10"/>
       <c r="BY4" s="10"/>
       <c r="BZ4" s="10"/>
@@ -3049,103 +3662,103 @@
         <v>14</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N5" s="7"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10"/>
-      <c r="AB5" s="10"/>
-      <c r="AC5" s="10"/>
-      <c r="AD5" s="10"/>
-      <c r="AE5" s="10"/>
-      <c r="AF5" s="10"/>
-      <c r="AG5" s="10"/>
-      <c r="AH5" s="10"/>
-      <c r="AI5" s="10"/>
-      <c r="AJ5" s="10"/>
-      <c r="AK5" s="10"/>
-      <c r="AL5" s="10"/>
-      <c r="AM5" s="10"/>
-      <c r="AN5" s="10"/>
-      <c r="AO5" s="10"/>
-      <c r="AP5" s="10"/>
-      <c r="AQ5" s="10"/>
-      <c r="AR5" s="10"/>
-      <c r="AS5" s="10"/>
-      <c r="AT5" s="10"/>
-      <c r="AU5" s="10"/>
-      <c r="AV5" s="10"/>
-      <c r="AW5" s="10"/>
-      <c r="AX5" s="10"/>
-      <c r="AY5" s="10"/>
-      <c r="AZ5" s="10"/>
-      <c r="BA5" s="10"/>
-      <c r="BB5" s="10"/>
-      <c r="BC5" s="10"/>
-      <c r="BD5" s="10"/>
-      <c r="BE5" s="10"/>
-      <c r="BF5" s="10"/>
-      <c r="BG5" s="10"/>
-      <c r="BH5" s="10"/>
-      <c r="BI5" s="10"/>
-      <c r="BJ5" s="10"/>
-      <c r="BK5" s="10"/>
-      <c r="BL5" s="10"/>
-      <c r="BM5" s="10"/>
-      <c r="BN5" s="10"/>
-      <c r="BO5" s="10"/>
-      <c r="BP5" s="10"/>
-      <c r="BQ5" s="10"/>
-      <c r="BR5" s="10"/>
-      <c r="BS5" s="10"/>
-      <c r="BT5" s="10"/>
-      <c r="BU5" s="10"/>
-      <c r="BV5" s="10"/>
-      <c r="BW5" s="10"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5"/>
+      <c r="AF5"/>
+      <c r="AG5"/>
+      <c r="AH5"/>
+      <c r="AI5"/>
+      <c r="AJ5"/>
+      <c r="AK5"/>
+      <c r="AL5"/>
+      <c r="AM5"/>
+      <c r="AN5"/>
+      <c r="AO5"/>
+      <c r="AP5"/>
+      <c r="AQ5"/>
+      <c r="AR5"/>
+      <c r="AS5"/>
+      <c r="AT5"/>
+      <c r="AU5"/>
+      <c r="AV5"/>
+      <c r="AW5"/>
+      <c r="AX5"/>
+      <c r="AY5"/>
+      <c r="AZ5"/>
+      <c r="BA5"/>
+      <c r="BB5"/>
+      <c r="BC5"/>
+      <c r="BD5"/>
+      <c r="BE5"/>
+      <c r="BF5"/>
+      <c r="BG5"/>
+      <c r="BH5"/>
+      <c r="BI5"/>
+      <c r="BJ5"/>
+      <c r="BK5"/>
+      <c r="BL5"/>
+      <c r="BM5"/>
+      <c r="BN5"/>
+      <c r="BO5"/>
+      <c r="BP5"/>
+      <c r="BQ5"/>
+      <c r="BR5"/>
+      <c r="BS5"/>
+      <c r="BT5"/>
+      <c r="BU5"/>
+      <c r="BV5"/>
+      <c r="BW5"/>
       <c r="BX5" s="10"/>
       <c r="BY5" s="10"/>
       <c r="BZ5" s="10"/>
@@ -3351,103 +3964,103 @@
         <v>14</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="16"/>
-      <c r="AA6" s="16"/>
-      <c r="AB6" s="16"/>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="16"/>
-      <c r="AE6" s="16"/>
-      <c r="AF6" s="16"/>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="16"/>
-      <c r="AI6" s="16"/>
-      <c r="AJ6" s="16"/>
-      <c r="AK6" s="16"/>
-      <c r="AL6" s="16"/>
-      <c r="AM6" s="16"/>
-      <c r="AN6" s="16"/>
-      <c r="AO6" s="16"/>
-      <c r="AP6" s="16"/>
-      <c r="AQ6" s="16"/>
-      <c r="AR6" s="16"/>
-      <c r="AS6" s="16"/>
-      <c r="AT6" s="16"/>
-      <c r="AU6" s="16"/>
-      <c r="AV6" s="16"/>
-      <c r="AW6" s="16"/>
-      <c r="AX6" s="16"/>
-      <c r="AY6" s="16"/>
-      <c r="AZ6" s="16"/>
-      <c r="BA6" s="16"/>
-      <c r="BB6" s="16"/>
-      <c r="BC6" s="16"/>
-      <c r="BD6" s="16"/>
-      <c r="BE6" s="16"/>
-      <c r="BF6" s="16"/>
-      <c r="BG6" s="16"/>
-      <c r="BH6" s="16"/>
-      <c r="BI6" s="16"/>
-      <c r="BJ6" s="16"/>
-      <c r="BK6" s="16"/>
-      <c r="BL6" s="16"/>
-      <c r="BM6" s="16"/>
-      <c r="BN6" s="16"/>
-      <c r="BO6" s="16"/>
-      <c r="BP6" s="16"/>
-      <c r="BQ6" s="16"/>
-      <c r="BR6" s="16"/>
-      <c r="BS6" s="16"/>
-      <c r="BT6" s="16"/>
-      <c r="BU6" s="16"/>
-      <c r="BV6" s="16"/>
-      <c r="BW6" s="16"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6"/>
+      <c r="AF6"/>
+      <c r="AG6"/>
+      <c r="AH6"/>
+      <c r="AI6"/>
+      <c r="AJ6"/>
+      <c r="AK6"/>
+      <c r="AL6"/>
+      <c r="AM6"/>
+      <c r="AN6"/>
+      <c r="AO6"/>
+      <c r="AP6"/>
+      <c r="AQ6"/>
+      <c r="AR6"/>
+      <c r="AS6"/>
+      <c r="AT6"/>
+      <c r="AU6"/>
+      <c r="AV6"/>
+      <c r="AW6"/>
+      <c r="AX6"/>
+      <c r="AY6"/>
+      <c r="AZ6"/>
+      <c r="BA6"/>
+      <c r="BB6"/>
+      <c r="BC6"/>
+      <c r="BD6"/>
+      <c r="BE6"/>
+      <c r="BF6"/>
+      <c r="BG6"/>
+      <c r="BH6"/>
+      <c r="BI6"/>
+      <c r="BJ6"/>
+      <c r="BK6"/>
+      <c r="BL6"/>
+      <c r="BM6"/>
+      <c r="BN6"/>
+      <c r="BO6"/>
+      <c r="BP6"/>
+      <c r="BQ6"/>
+      <c r="BR6"/>
+      <c r="BS6"/>
+      <c r="BT6"/>
+      <c r="BU6"/>
+      <c r="BV6"/>
+      <c r="BW6"/>
       <c r="BX6" s="16"/>
       <c r="BY6" s="16"/>
       <c r="BZ6" s="16"/>
@@ -3653,105 +4266,105 @@
         <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K7" s="7">
         <v>2025</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="16"/>
-      <c r="AB7" s="16"/>
-      <c r="AC7" s="16"/>
-      <c r="AD7" s="16"/>
-      <c r="AE7" s="16"/>
-      <c r="AF7" s="16"/>
-      <c r="AG7" s="16"/>
-      <c r="AH7" s="16"/>
-      <c r="AI7" s="16"/>
-      <c r="AJ7" s="16"/>
-      <c r="AK7" s="16"/>
-      <c r="AL7" s="16"/>
-      <c r="AM7" s="16"/>
-      <c r="AN7" s="16"/>
-      <c r="AO7" s="16"/>
-      <c r="AP7" s="16"/>
-      <c r="AQ7" s="16"/>
-      <c r="AR7" s="16"/>
-      <c r="AS7" s="16"/>
-      <c r="AT7" s="16"/>
-      <c r="AU7" s="16"/>
-      <c r="AV7" s="16"/>
-      <c r="AW7" s="16"/>
-      <c r="AX7" s="16"/>
-      <c r="AY7" s="16"/>
-      <c r="AZ7" s="16"/>
-      <c r="BA7" s="16"/>
-      <c r="BB7" s="16"/>
-      <c r="BC7" s="16"/>
-      <c r="BD7" s="16"/>
-      <c r="BE7" s="16"/>
-      <c r="BF7" s="16"/>
-      <c r="BG7" s="16"/>
-      <c r="BH7" s="16"/>
-      <c r="BI7" s="16"/>
-      <c r="BJ7" s="16"/>
-      <c r="BK7" s="16"/>
-      <c r="BL7" s="16"/>
-      <c r="BM7" s="16"/>
-      <c r="BN7" s="16"/>
-      <c r="BO7" s="16"/>
-      <c r="BP7" s="16"/>
-      <c r="BQ7" s="16"/>
-      <c r="BR7" s="16"/>
-      <c r="BS7" s="16"/>
-      <c r="BT7" s="16"/>
-      <c r="BU7" s="16"/>
-      <c r="BV7" s="16"/>
-      <c r="BW7" s="16"/>
+        <v>79</v>
+      </c>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7"/>
+      <c r="AB7"/>
+      <c r="AC7"/>
+      <c r="AD7"/>
+      <c r="AE7"/>
+      <c r="AF7"/>
+      <c r="AG7"/>
+      <c r="AH7"/>
+      <c r="AI7"/>
+      <c r="AJ7"/>
+      <c r="AK7"/>
+      <c r="AL7"/>
+      <c r="AM7"/>
+      <c r="AN7"/>
+      <c r="AO7"/>
+      <c r="AP7"/>
+      <c r="AQ7"/>
+      <c r="AR7"/>
+      <c r="AS7"/>
+      <c r="AT7"/>
+      <c r="AU7"/>
+      <c r="AV7"/>
+      <c r="AW7"/>
+      <c r="AX7"/>
+      <c r="AY7"/>
+      <c r="AZ7"/>
+      <c r="BA7"/>
+      <c r="BB7"/>
+      <c r="BC7"/>
+      <c r="BD7"/>
+      <c r="BE7"/>
+      <c r="BF7"/>
+      <c r="BG7"/>
+      <c r="BH7"/>
+      <c r="BI7"/>
+      <c r="BJ7"/>
+      <c r="BK7"/>
+      <c r="BL7"/>
+      <c r="BM7"/>
+      <c r="BN7"/>
+      <c r="BO7"/>
+      <c r="BP7"/>
+      <c r="BQ7"/>
+      <c r="BR7"/>
+      <c r="BS7"/>
+      <c r="BT7"/>
+      <c r="BU7"/>
+      <c r="BV7"/>
+      <c r="BW7"/>
       <c r="BX7" s="16"/>
       <c r="BY7" s="16"/>
       <c r="BZ7" s="16"/>
@@ -3952,108 +4565,108 @@
       <c r="JM7" s="16"/>
       <c r="JN7" s="16"/>
     </row>
-    <row r="8" s="6" customFormat="1" ht="25.5">
+    <row r="8" s="6" customFormat="1" ht="28.5" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>24</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="10"/>
-      <c r="AA8" s="10"/>
-      <c r="AB8" s="10"/>
-      <c r="AC8" s="10"/>
-      <c r="AD8" s="10"/>
-      <c r="AE8" s="10"/>
-      <c r="AF8" s="10"/>
-      <c r="AG8" s="10"/>
-      <c r="AH8" s="10"/>
-      <c r="AI8" s="10"/>
-      <c r="AJ8" s="10"/>
-      <c r="AK8" s="10"/>
-      <c r="AL8" s="10"/>
-      <c r="AM8" s="10"/>
-      <c r="AN8" s="10"/>
-      <c r="AO8" s="10"/>
-      <c r="AP8" s="10"/>
-      <c r="AQ8" s="10"/>
-      <c r="AR8" s="10"/>
-      <c r="AS8" s="10"/>
-      <c r="AT8" s="10"/>
-      <c r="AU8" s="10"/>
-      <c r="AV8" s="10"/>
-      <c r="AW8" s="10"/>
-      <c r="AX8" s="10"/>
-      <c r="AY8" s="10"/>
-      <c r="AZ8" s="10"/>
-      <c r="BA8" s="10"/>
-      <c r="BB8" s="10"/>
-      <c r="BC8" s="10"/>
-      <c r="BD8" s="10"/>
-      <c r="BE8" s="10"/>
-      <c r="BF8" s="10"/>
-      <c r="BG8" s="10"/>
-      <c r="BH8" s="10"/>
-      <c r="BI8" s="10"/>
-      <c r="BJ8" s="10"/>
-      <c r="BK8" s="10"/>
-      <c r="BL8" s="10"/>
-      <c r="BM8" s="10"/>
-      <c r="BN8" s="10"/>
-      <c r="BO8" s="10"/>
-      <c r="BP8" s="10"/>
-      <c r="BQ8" s="10"/>
-      <c r="BR8" s="10"/>
-      <c r="BS8" s="10"/>
-      <c r="BT8" s="10"/>
-      <c r="BU8" s="10"/>
-      <c r="BV8" s="10"/>
-      <c r="BW8" s="10"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
+      <c r="Z8"/>
+      <c r="AA8"/>
+      <c r="AB8"/>
+      <c r="AC8"/>
+      <c r="AD8"/>
+      <c r="AE8"/>
+      <c r="AF8"/>
+      <c r="AG8"/>
+      <c r="AH8"/>
+      <c r="AI8"/>
+      <c r="AJ8"/>
+      <c r="AK8"/>
+      <c r="AL8"/>
+      <c r="AM8"/>
+      <c r="AN8"/>
+      <c r="AO8"/>
+      <c r="AP8"/>
+      <c r="AQ8"/>
+      <c r="AR8"/>
+      <c r="AS8"/>
+      <c r="AT8"/>
+      <c r="AU8"/>
+      <c r="AV8"/>
+      <c r="AW8"/>
+      <c r="AX8"/>
+      <c r="AY8"/>
+      <c r="AZ8"/>
+      <c r="BA8"/>
+      <c r="BB8"/>
+      <c r="BC8"/>
+      <c r="BD8"/>
+      <c r="BE8"/>
+      <c r="BF8"/>
+      <c r="BG8"/>
+      <c r="BH8"/>
+      <c r="BI8"/>
+      <c r="BJ8"/>
+      <c r="BK8"/>
+      <c r="BL8"/>
+      <c r="BM8"/>
+      <c r="BN8"/>
+      <c r="BO8"/>
+      <c r="BP8"/>
+      <c r="BQ8"/>
+      <c r="BR8"/>
+      <c r="BS8"/>
+      <c r="BT8"/>
+      <c r="BU8"/>
+      <c r="BV8"/>
+      <c r="BW8"/>
       <c r="BX8" s="10"/>
       <c r="BY8" s="10"/>
       <c r="BZ8" s="10"/>
@@ -4259,103 +4872,103 @@
         <v>14</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="L9" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="M9" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="J9" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="22" t="s">
-        <v>88</v>
-      </c>
       <c r="N9" s="7"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="16"/>
-      <c r="AE9" s="16"/>
-      <c r="AF9" s="16"/>
-      <c r="AG9" s="16"/>
-      <c r="AH9" s="16"/>
-      <c r="AI9" s="16"/>
-      <c r="AJ9" s="16"/>
-      <c r="AK9" s="16"/>
-      <c r="AL9" s="16"/>
-      <c r="AM9" s="16"/>
-      <c r="AN9" s="16"/>
-      <c r="AO9" s="16"/>
-      <c r="AP9" s="16"/>
-      <c r="AQ9" s="16"/>
-      <c r="AR9" s="16"/>
-      <c r="AS9" s="16"/>
-      <c r="AT9" s="16"/>
-      <c r="AU9" s="16"/>
-      <c r="AV9" s="16"/>
-      <c r="AW9" s="16"/>
-      <c r="AX9" s="16"/>
-      <c r="AY9" s="16"/>
-      <c r="AZ9" s="16"/>
-      <c r="BA9" s="16"/>
-      <c r="BB9" s="16"/>
-      <c r="BC9" s="16"/>
-      <c r="BD9" s="16"/>
-      <c r="BE9" s="16"/>
-      <c r="BF9" s="16"/>
-      <c r="BG9" s="16"/>
-      <c r="BH9" s="16"/>
-      <c r="BI9" s="16"/>
-      <c r="BJ9" s="16"/>
-      <c r="BK9" s="16"/>
-      <c r="BL9" s="16"/>
-      <c r="BM9" s="16"/>
-      <c r="BN9" s="16"/>
-      <c r="BO9" s="16"/>
-      <c r="BP9" s="16"/>
-      <c r="BQ9" s="16"/>
-      <c r="BR9" s="16"/>
-      <c r="BS9" s="16"/>
-      <c r="BT9" s="16"/>
-      <c r="BU9" s="16"/>
-      <c r="BV9" s="16"/>
-      <c r="BW9" s="16"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9"/>
+      <c r="Z9"/>
+      <c r="AA9"/>
+      <c r="AB9"/>
+      <c r="AC9"/>
+      <c r="AD9"/>
+      <c r="AE9"/>
+      <c r="AF9"/>
+      <c r="AG9"/>
+      <c r="AH9"/>
+      <c r="AI9"/>
+      <c r="AJ9"/>
+      <c r="AK9"/>
+      <c r="AL9"/>
+      <c r="AM9"/>
+      <c r="AN9"/>
+      <c r="AO9"/>
+      <c r="AP9"/>
+      <c r="AQ9"/>
+      <c r="AR9"/>
+      <c r="AS9"/>
+      <c r="AT9"/>
+      <c r="AU9"/>
+      <c r="AV9"/>
+      <c r="AW9"/>
+      <c r="AX9"/>
+      <c r="AY9"/>
+      <c r="AZ9"/>
+      <c r="BA9"/>
+      <c r="BB9"/>
+      <c r="BC9"/>
+      <c r="BD9"/>
+      <c r="BE9"/>
+      <c r="BF9"/>
+      <c r="BG9"/>
+      <c r="BH9"/>
+      <c r="BI9"/>
+      <c r="BJ9"/>
+      <c r="BK9"/>
+      <c r="BL9"/>
+      <c r="BM9"/>
+      <c r="BN9"/>
+      <c r="BO9"/>
+      <c r="BP9"/>
+      <c r="BQ9"/>
+      <c r="BR9"/>
+      <c r="BS9"/>
+      <c r="BT9"/>
+      <c r="BU9"/>
+      <c r="BV9"/>
+      <c r="BW9"/>
       <c r="BX9" s="16"/>
       <c r="BY9" s="16"/>
       <c r="BZ9" s="16"/>
@@ -4556,108 +5169,108 @@
       <c r="JM9" s="16"/>
       <c r="JN9" s="16"/>
     </row>
-    <row r="10" s="14" customFormat="1" ht="25.5">
+    <row r="10" s="14" customFormat="1" ht="38.25">
       <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="I10" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="H10" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>99</v>
-      </c>
       <c r="M10" s="22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N10" s="7"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="16"/>
-      <c r="AB10" s="16"/>
-      <c r="AC10" s="16"/>
-      <c r="AD10" s="16"/>
-      <c r="AE10" s="16"/>
-      <c r="AF10" s="16"/>
-      <c r="AG10" s="16"/>
-      <c r="AH10" s="16"/>
-      <c r="AI10" s="16"/>
-      <c r="AJ10" s="16"/>
-      <c r="AK10" s="16"/>
-      <c r="AL10" s="16"/>
-      <c r="AM10" s="16"/>
-      <c r="AN10" s="16"/>
-      <c r="AO10" s="16"/>
-      <c r="AP10" s="16"/>
-      <c r="AQ10" s="16"/>
-      <c r="AR10" s="16"/>
-      <c r="AS10" s="16"/>
-      <c r="AT10" s="16"/>
-      <c r="AU10" s="16"/>
-      <c r="AV10" s="16"/>
-      <c r="AW10" s="16"/>
-      <c r="AX10" s="16"/>
-      <c r="AY10" s="16"/>
-      <c r="AZ10" s="16"/>
-      <c r="BA10" s="16"/>
-      <c r="BB10" s="16"/>
-      <c r="BC10" s="16"/>
-      <c r="BD10" s="16"/>
-      <c r="BE10" s="16"/>
-      <c r="BF10" s="16"/>
-      <c r="BG10" s="16"/>
-      <c r="BH10" s="16"/>
-      <c r="BI10" s="16"/>
-      <c r="BJ10" s="16"/>
-      <c r="BK10" s="16"/>
-      <c r="BL10" s="16"/>
-      <c r="BM10" s="16"/>
-      <c r="BN10" s="16"/>
-      <c r="BO10" s="16"/>
-      <c r="BP10" s="16"/>
-      <c r="BQ10" s="16"/>
-      <c r="BR10" s="16"/>
-      <c r="BS10" s="16"/>
-      <c r="BT10" s="16"/>
-      <c r="BU10" s="16"/>
-      <c r="BV10" s="16"/>
-      <c r="BW10" s="16"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10"/>
+      <c r="Z10"/>
+      <c r="AA10"/>
+      <c r="AB10"/>
+      <c r="AC10"/>
+      <c r="AD10"/>
+      <c r="AE10"/>
+      <c r="AF10"/>
+      <c r="AG10"/>
+      <c r="AH10"/>
+      <c r="AI10"/>
+      <c r="AJ10"/>
+      <c r="AK10"/>
+      <c r="AL10"/>
+      <c r="AM10"/>
+      <c r="AN10"/>
+      <c r="AO10"/>
+      <c r="AP10"/>
+      <c r="AQ10"/>
+      <c r="AR10"/>
+      <c r="AS10"/>
+      <c r="AT10"/>
+      <c r="AU10"/>
+      <c r="AV10"/>
+      <c r="AW10"/>
+      <c r="AX10"/>
+      <c r="AY10"/>
+      <c r="AZ10"/>
+      <c r="BA10"/>
+      <c r="BB10"/>
+      <c r="BC10"/>
+      <c r="BD10"/>
+      <c r="BE10"/>
+      <c r="BF10"/>
+      <c r="BG10"/>
+      <c r="BH10"/>
+      <c r="BI10"/>
+      <c r="BJ10"/>
+      <c r="BK10"/>
+      <c r="BL10"/>
+      <c r="BM10"/>
+      <c r="BN10"/>
+      <c r="BO10"/>
+      <c r="BP10"/>
+      <c r="BQ10"/>
+      <c r="BR10"/>
+      <c r="BS10"/>
+      <c r="BT10"/>
+      <c r="BU10"/>
+      <c r="BV10"/>
+      <c r="BW10"/>
       <c r="BX10" s="16"/>
       <c r="BY10" s="16"/>
       <c r="BZ10" s="16"/>
@@ -4858,108 +5471,108 @@
       <c r="JM10" s="16"/>
       <c r="JN10" s="16"/>
     </row>
-    <row r="11" s="14" customFormat="1" ht="25.5">
+    <row r="11" s="14" customFormat="1" ht="38.25">
       <c r="A11" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="M11" s="22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N11" s="7"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10"/>
-      <c r="AA11" s="10"/>
-      <c r="AB11" s="10"/>
-      <c r="AC11" s="10"/>
-      <c r="AD11" s="10"/>
-      <c r="AE11" s="10"/>
-      <c r="AF11" s="10"/>
-      <c r="AG11" s="10"/>
-      <c r="AH11" s="10"/>
-      <c r="AI11" s="10"/>
-      <c r="AJ11" s="10"/>
-      <c r="AK11" s="10"/>
-      <c r="AL11" s="10"/>
-      <c r="AM11" s="10"/>
-      <c r="AN11" s="10"/>
-      <c r="AO11" s="10"/>
-      <c r="AP11" s="10"/>
-      <c r="AQ11" s="10"/>
-      <c r="AR11" s="10"/>
-      <c r="AS11" s="10"/>
-      <c r="AT11" s="10"/>
-      <c r="AU11" s="10"/>
-      <c r="AV11" s="10"/>
-      <c r="AW11" s="10"/>
-      <c r="AX11" s="10"/>
-      <c r="AY11" s="10"/>
-      <c r="AZ11" s="10"/>
-      <c r="BA11" s="10"/>
-      <c r="BB11" s="10"/>
-      <c r="BC11" s="10"/>
-      <c r="BD11" s="10"/>
-      <c r="BE11" s="10"/>
-      <c r="BF11" s="10"/>
-      <c r="BG11" s="10"/>
-      <c r="BH11" s="10"/>
-      <c r="BI11" s="10"/>
-      <c r="BJ11" s="10"/>
-      <c r="BK11" s="10"/>
-      <c r="BL11" s="10"/>
-      <c r="BM11" s="10"/>
-      <c r="BN11" s="10"/>
-      <c r="BO11" s="10"/>
-      <c r="BP11" s="10"/>
-      <c r="BQ11" s="10"/>
-      <c r="BR11" s="10"/>
-      <c r="BS11" s="10"/>
-      <c r="BT11" s="10"/>
-      <c r="BU11" s="10"/>
-      <c r="BV11" s="10"/>
-      <c r="BW11" s="10"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11"/>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11"/>
+      <c r="Z11"/>
+      <c r="AA11"/>
+      <c r="AB11"/>
+      <c r="AC11"/>
+      <c r="AD11"/>
+      <c r="AE11"/>
+      <c r="AF11"/>
+      <c r="AG11"/>
+      <c r="AH11"/>
+      <c r="AI11"/>
+      <c r="AJ11"/>
+      <c r="AK11"/>
+      <c r="AL11"/>
+      <c r="AM11"/>
+      <c r="AN11"/>
+      <c r="AO11"/>
+      <c r="AP11"/>
+      <c r="AQ11"/>
+      <c r="AR11"/>
+      <c r="AS11"/>
+      <c r="AT11"/>
+      <c r="AU11"/>
+      <c r="AV11"/>
+      <c r="AW11"/>
+      <c r="AX11"/>
+      <c r="AY11"/>
+      <c r="AZ11"/>
+      <c r="BA11"/>
+      <c r="BB11"/>
+      <c r="BC11"/>
+      <c r="BD11"/>
+      <c r="BE11"/>
+      <c r="BF11"/>
+      <c r="BG11"/>
+      <c r="BH11"/>
+      <c r="BI11"/>
+      <c r="BJ11"/>
+      <c r="BK11"/>
+      <c r="BL11"/>
+      <c r="BM11"/>
+      <c r="BN11"/>
+      <c r="BO11"/>
+      <c r="BP11"/>
+      <c r="BQ11"/>
+      <c r="BR11"/>
+      <c r="BS11"/>
+      <c r="BT11"/>
+      <c r="BU11"/>
+      <c r="BV11"/>
+      <c r="BW11"/>
       <c r="BX11" s="10"/>
       <c r="BY11" s="10"/>
       <c r="BZ11" s="10"/>
@@ -5160,108 +5773,108 @@
       <c r="JM11" s="10"/>
       <c r="JN11" s="10"/>
     </row>
-    <row r="12" s="6" customFormat="1" ht="25.5">
+    <row r="12" s="6" customFormat="1" ht="42.75">
       <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>110</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="K12" s="7">
-        <v>2020</v>
+        <v>21</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="M12" s="22" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10"/>
-      <c r="AB12" s="10"/>
-      <c r="AC12" s="10"/>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="10"/>
-      <c r="AF12" s="10"/>
-      <c r="AG12" s="10"/>
-      <c r="AH12" s="10"/>
-      <c r="AI12" s="10"/>
-      <c r="AJ12" s="10"/>
-      <c r="AK12" s="10"/>
-      <c r="AL12" s="10"/>
-      <c r="AM12" s="10"/>
-      <c r="AN12" s="10"/>
-      <c r="AO12" s="10"/>
-      <c r="AP12" s="10"/>
-      <c r="AQ12" s="10"/>
-      <c r="AR12" s="10"/>
-      <c r="AS12" s="10"/>
-      <c r="AT12" s="10"/>
-      <c r="AU12" s="10"/>
-      <c r="AV12" s="10"/>
-      <c r="AW12" s="10"/>
-      <c r="AX12" s="10"/>
-      <c r="AY12" s="10"/>
-      <c r="AZ12" s="10"/>
-      <c r="BA12" s="10"/>
-      <c r="BB12" s="10"/>
-      <c r="BC12" s="10"/>
-      <c r="BD12" s="10"/>
-      <c r="BE12" s="10"/>
-      <c r="BF12" s="10"/>
-      <c r="BG12" s="10"/>
-      <c r="BH12" s="10"/>
-      <c r="BI12" s="10"/>
-      <c r="BJ12" s="10"/>
-      <c r="BK12" s="10"/>
-      <c r="BL12" s="10"/>
-      <c r="BM12" s="10"/>
-      <c r="BN12" s="10"/>
-      <c r="BO12" s="10"/>
-      <c r="BP12" s="10"/>
-      <c r="BQ12" s="10"/>
-      <c r="BR12" s="10"/>
-      <c r="BS12" s="10"/>
-      <c r="BT12" s="10"/>
-      <c r="BU12" s="10"/>
-      <c r="BV12" s="10"/>
-      <c r="BW12" s="10"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12"/>
+      <c r="Z12"/>
+      <c r="AA12"/>
+      <c r="AB12"/>
+      <c r="AC12"/>
+      <c r="AD12"/>
+      <c r="AE12"/>
+      <c r="AF12"/>
+      <c r="AG12"/>
+      <c r="AH12"/>
+      <c r="AI12"/>
+      <c r="AJ12"/>
+      <c r="AK12"/>
+      <c r="AL12"/>
+      <c r="AM12"/>
+      <c r="AN12"/>
+      <c r="AO12"/>
+      <c r="AP12"/>
+      <c r="AQ12"/>
+      <c r="AR12"/>
+      <c r="AS12"/>
+      <c r="AT12"/>
+      <c r="AU12"/>
+      <c r="AV12"/>
+      <c r="AW12"/>
+      <c r="AX12"/>
+      <c r="AY12"/>
+      <c r="AZ12"/>
+      <c r="BA12"/>
+      <c r="BB12"/>
+      <c r="BC12"/>
+      <c r="BD12"/>
+      <c r="BE12"/>
+      <c r="BF12"/>
+      <c r="BG12"/>
+      <c r="BH12"/>
+      <c r="BI12"/>
+      <c r="BJ12"/>
+      <c r="BK12"/>
+      <c r="BL12"/>
+      <c r="BM12"/>
+      <c r="BN12"/>
+      <c r="BO12"/>
+      <c r="BP12"/>
+      <c r="BQ12"/>
+      <c r="BR12"/>
+      <c r="BS12"/>
+      <c r="BT12"/>
+      <c r="BU12"/>
+      <c r="BV12"/>
+      <c r="BW12"/>
       <c r="BX12" s="10"/>
       <c r="BY12" s="10"/>
       <c r="BZ12" s="10"/>
@@ -5467,10 +6080,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>113</v>
@@ -5479,93 +6092,91 @@
         <v>114</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="K13" s="7">
         <v>2020</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M13" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="N13" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-      <c r="AA13" s="10"/>
-      <c r="AB13" s="10"/>
-      <c r="AC13" s="10"/>
-      <c r="AD13" s="10"/>
-      <c r="AE13" s="10"/>
-      <c r="AF13" s="10"/>
-      <c r="AG13" s="10"/>
-      <c r="AH13" s="10"/>
-      <c r="AI13" s="10"/>
-      <c r="AJ13" s="10"/>
-      <c r="AK13" s="10"/>
-      <c r="AL13" s="10"/>
-      <c r="AM13" s="10"/>
-      <c r="AN13" s="10"/>
-      <c r="AO13" s="10"/>
-      <c r="AP13" s="10"/>
-      <c r="AQ13" s="10"/>
-      <c r="AR13" s="10"/>
-      <c r="AS13" s="10"/>
-      <c r="AT13" s="10"/>
-      <c r="AU13" s="10"/>
-      <c r="AV13" s="10"/>
-      <c r="AW13" s="10"/>
-      <c r="AX13" s="10"/>
-      <c r="AY13" s="10"/>
-      <c r="AZ13" s="10"/>
-      <c r="BA13" s="10"/>
-      <c r="BB13" s="10"/>
-      <c r="BC13" s="10"/>
-      <c r="BD13" s="10"/>
-      <c r="BE13" s="10"/>
-      <c r="BF13" s="10"/>
-      <c r="BG13" s="10"/>
-      <c r="BH13" s="10"/>
-      <c r="BI13" s="10"/>
-      <c r="BJ13" s="10"/>
-      <c r="BK13" s="10"/>
-      <c r="BL13" s="10"/>
-      <c r="BM13" s="10"/>
-      <c r="BN13" s="10"/>
-      <c r="BO13" s="10"/>
-      <c r="BP13" s="10"/>
-      <c r="BQ13" s="10"/>
-      <c r="BR13" s="10"/>
-      <c r="BS13" s="10"/>
-      <c r="BT13" s="10"/>
-      <c r="BU13" s="10"/>
-      <c r="BV13" s="10"/>
-      <c r="BW13" s="10"/>
+        <v>120</v>
+      </c>
+      <c r="N13" s="10"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+      <c r="Y13"/>
+      <c r="Z13"/>
+      <c r="AA13"/>
+      <c r="AB13"/>
+      <c r="AC13"/>
+      <c r="AD13"/>
+      <c r="AE13"/>
+      <c r="AF13"/>
+      <c r="AG13"/>
+      <c r="AH13"/>
+      <c r="AI13"/>
+      <c r="AJ13"/>
+      <c r="AK13"/>
+      <c r="AL13"/>
+      <c r="AM13"/>
+      <c r="AN13"/>
+      <c r="AO13"/>
+      <c r="AP13"/>
+      <c r="AQ13"/>
+      <c r="AR13"/>
+      <c r="AS13"/>
+      <c r="AT13"/>
+      <c r="AU13"/>
+      <c r="AV13"/>
+      <c r="AW13"/>
+      <c r="AX13"/>
+      <c r="AY13"/>
+      <c r="AZ13"/>
+      <c r="BA13"/>
+      <c r="BB13"/>
+      <c r="BC13"/>
+      <c r="BD13"/>
+      <c r="BE13"/>
+      <c r="BF13"/>
+      <c r="BG13"/>
+      <c r="BH13"/>
+      <c r="BI13"/>
+      <c r="BJ13"/>
+      <c r="BK13"/>
+      <c r="BL13"/>
+      <c r="BM13"/>
+      <c r="BN13"/>
+      <c r="BO13"/>
+      <c r="BP13"/>
+      <c r="BQ13"/>
+      <c r="BR13"/>
+      <c r="BS13"/>
+      <c r="BT13"/>
+      <c r="BU13"/>
+      <c r="BV13"/>
+      <c r="BW13"/>
       <c r="BX13" s="10"/>
       <c r="BY13" s="10"/>
       <c r="BZ13" s="10"/>
@@ -5766,410 +6377,412 @@
       <c r="JM13" s="10"/>
       <c r="JN13" s="10"/>
     </row>
-    <row r="14" s="24" customFormat="1" ht="38.25">
+    <row r="14" s="24" customFormat="1" ht="25.5">
       <c r="A14" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E14" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="K14" s="7">
         <v>2020</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M14" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="N14" s="10"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
-      <c r="S14" s="25"/>
-      <c r="T14" s="25"/>
-      <c r="U14" s="25"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="25"/>
-      <c r="X14" s="25"/>
-      <c r="Y14" s="25"/>
-      <c r="Z14" s="25"/>
-      <c r="AA14" s="25"/>
-      <c r="AB14" s="25"/>
-      <c r="AC14" s="25"/>
-      <c r="AD14" s="25"/>
-      <c r="AE14" s="25"/>
-      <c r="AF14" s="25"/>
-      <c r="AG14" s="25"/>
-      <c r="AH14" s="25"/>
-      <c r="AI14" s="25"/>
-      <c r="AJ14" s="25"/>
-      <c r="AK14" s="25"/>
-      <c r="AL14" s="25"/>
-      <c r="AM14" s="25"/>
-      <c r="AN14" s="25"/>
-      <c r="AO14" s="25"/>
-      <c r="AP14" s="25"/>
-      <c r="AQ14" s="25"/>
-      <c r="AR14" s="25"/>
-      <c r="AS14" s="25"/>
-      <c r="AT14" s="25"/>
-      <c r="AU14" s="25"/>
-      <c r="AV14" s="25"/>
-      <c r="AW14" s="25"/>
-      <c r="AX14" s="25"/>
-      <c r="AY14" s="25"/>
-      <c r="AZ14" s="25"/>
-      <c r="BA14" s="25"/>
-      <c r="BB14" s="25"/>
-      <c r="BC14" s="25"/>
-      <c r="BD14" s="25"/>
-      <c r="BE14" s="25"/>
-      <c r="BF14" s="25"/>
-      <c r="BG14" s="25"/>
-      <c r="BH14" s="25"/>
-      <c r="BI14" s="25"/>
-      <c r="BJ14" s="25"/>
-      <c r="BK14" s="25"/>
-      <c r="BL14" s="25"/>
-      <c r="BM14" s="25"/>
-      <c r="BN14" s="25"/>
-      <c r="BO14" s="25"/>
-      <c r="BP14" s="25"/>
-      <c r="BQ14" s="25"/>
-      <c r="BR14" s="25"/>
-      <c r="BS14" s="25"/>
-      <c r="BT14" s="25"/>
-      <c r="BU14" s="25"/>
-      <c r="BV14" s="25"/>
-      <c r="BW14" s="25"/>
-      <c r="BX14" s="25"/>
-      <c r="BY14" s="25"/>
-      <c r="BZ14" s="25"/>
-      <c r="CA14" s="25"/>
-      <c r="CB14" s="25"/>
-      <c r="CC14" s="25"/>
-      <c r="CD14" s="25"/>
-      <c r="CE14" s="25"/>
-      <c r="CF14" s="25"/>
-      <c r="CG14" s="25"/>
-      <c r="CH14" s="25"/>
-      <c r="CI14" s="25"/>
-      <c r="CJ14" s="25"/>
-      <c r="CK14" s="25"/>
-      <c r="CL14" s="25"/>
-      <c r="CM14" s="25"/>
-      <c r="CN14" s="25"/>
-      <c r="CO14" s="25"/>
-      <c r="CP14" s="25"/>
-      <c r="CQ14" s="25"/>
-      <c r="CR14" s="25"/>
-      <c r="CS14" s="25"/>
-      <c r="CT14" s="25"/>
-      <c r="CU14" s="25"/>
-      <c r="CV14" s="25"/>
-      <c r="CW14" s="25"/>
-      <c r="CX14" s="25"/>
-      <c r="CY14" s="25"/>
-      <c r="CZ14" s="25"/>
-      <c r="DA14" s="25"/>
-      <c r="DB14" s="25"/>
-      <c r="DC14" s="25"/>
-      <c r="DD14" s="25"/>
-      <c r="DE14" s="25"/>
-      <c r="DF14" s="25"/>
-      <c r="DG14" s="25"/>
-      <c r="DH14" s="25"/>
-      <c r="DI14" s="25"/>
-      <c r="DJ14" s="25"/>
-      <c r="DK14" s="25"/>
-      <c r="DL14" s="25"/>
-      <c r="DM14" s="25"/>
-      <c r="DN14" s="25"/>
-      <c r="DO14" s="25"/>
-      <c r="DP14" s="25"/>
-      <c r="DQ14" s="25"/>
-      <c r="DR14" s="25"/>
-      <c r="DS14" s="25"/>
-      <c r="DT14" s="25"/>
-      <c r="DU14" s="25"/>
-      <c r="DV14" s="25"/>
-      <c r="DW14" s="25"/>
-      <c r="DX14" s="25"/>
-      <c r="DY14" s="25"/>
-      <c r="DZ14" s="25"/>
-      <c r="EA14" s="25"/>
-      <c r="EB14" s="25"/>
-      <c r="EC14" s="25"/>
-      <c r="ED14" s="25"/>
-      <c r="EE14" s="25"/>
-      <c r="EF14" s="25"/>
-      <c r="EG14" s="25"/>
-      <c r="EH14" s="25"/>
-      <c r="EI14" s="25"/>
-      <c r="EJ14" s="25"/>
-      <c r="EK14" s="25"/>
-      <c r="EL14" s="25"/>
-      <c r="EM14" s="25"/>
-      <c r="EN14" s="25"/>
-      <c r="EO14" s="25"/>
-      <c r="EP14" s="25"/>
-      <c r="EQ14" s="25"/>
-      <c r="ER14" s="25"/>
-      <c r="ES14" s="25"/>
-      <c r="ET14" s="25"/>
-      <c r="EU14" s="25"/>
-      <c r="EV14" s="25"/>
-      <c r="EW14" s="25"/>
-      <c r="EX14" s="25"/>
-      <c r="EY14" s="25"/>
-      <c r="EZ14" s="25"/>
-      <c r="FA14" s="25"/>
-      <c r="FB14" s="25"/>
-      <c r="FC14" s="25"/>
-      <c r="FD14" s="25"/>
-      <c r="FE14" s="25"/>
-      <c r="FF14" s="25"/>
-      <c r="FG14" s="25"/>
-      <c r="FH14" s="25"/>
-      <c r="FI14" s="25"/>
-      <c r="FJ14" s="25"/>
-      <c r="FK14" s="25"/>
-      <c r="FL14" s="25"/>
-      <c r="FM14" s="25"/>
-      <c r="FN14" s="25"/>
-      <c r="FO14" s="25"/>
-      <c r="FP14" s="25"/>
-      <c r="FQ14" s="25"/>
-      <c r="FR14" s="25"/>
-      <c r="FS14" s="25"/>
-      <c r="FT14" s="25"/>
-      <c r="FU14" s="25"/>
-      <c r="FV14" s="25"/>
-      <c r="FW14" s="25"/>
-      <c r="FX14" s="25"/>
-      <c r="FY14" s="25"/>
-      <c r="FZ14" s="25"/>
-      <c r="GA14" s="25"/>
-      <c r="GB14" s="25"/>
-      <c r="GC14" s="25"/>
-      <c r="GD14" s="25"/>
-      <c r="GE14" s="25"/>
-      <c r="GF14" s="25"/>
-      <c r="GG14" s="25"/>
-      <c r="GH14" s="25"/>
-      <c r="GI14" s="25"/>
-      <c r="GJ14" s="25"/>
-      <c r="GK14" s="25"/>
-      <c r="GL14" s="25"/>
-      <c r="GM14" s="25"/>
-      <c r="GN14" s="25"/>
-      <c r="GO14" s="25"/>
-      <c r="GP14" s="25"/>
-      <c r="GQ14" s="25"/>
-      <c r="GR14" s="25"/>
-      <c r="GS14" s="25"/>
-      <c r="GT14" s="25"/>
-      <c r="GU14" s="25"/>
-      <c r="GV14" s="25"/>
-      <c r="GW14" s="25"/>
-      <c r="GX14" s="25"/>
-      <c r="GY14" s="25"/>
-      <c r="GZ14" s="25"/>
-      <c r="HA14" s="25"/>
-      <c r="HB14" s="25"/>
-      <c r="HC14" s="25"/>
-      <c r="HD14" s="25"/>
-      <c r="HE14" s="25"/>
-      <c r="HF14" s="25"/>
-      <c r="HG14" s="25"/>
-      <c r="HH14" s="25"/>
-      <c r="HI14" s="25"/>
-      <c r="HJ14" s="25"/>
-      <c r="HK14" s="25"/>
-      <c r="HL14" s="25"/>
-      <c r="HM14" s="25"/>
-      <c r="HN14" s="25"/>
-      <c r="HO14" s="25"/>
-      <c r="HP14" s="25"/>
-      <c r="HQ14" s="25"/>
-      <c r="HR14" s="25"/>
-      <c r="HS14" s="25"/>
-      <c r="HT14" s="25"/>
-      <c r="HU14" s="25"/>
-      <c r="HV14" s="25"/>
-      <c r="HW14" s="25"/>
-      <c r="HX14" s="25"/>
-      <c r="HY14" s="25"/>
-      <c r="HZ14" s="25"/>
-      <c r="IA14" s="25"/>
-      <c r="IB14" s="25"/>
-      <c r="IC14" s="25"/>
-      <c r="ID14" s="25"/>
-      <c r="IE14" s="25"/>
-      <c r="IF14" s="25"/>
-      <c r="IG14" s="25"/>
-      <c r="IH14" s="25"/>
-      <c r="II14" s="25"/>
-      <c r="IJ14" s="25"/>
-      <c r="IK14" s="25"/>
-      <c r="IL14" s="25"/>
-      <c r="IM14" s="25"/>
-      <c r="IN14" s="25"/>
-      <c r="IO14" s="25"/>
-      <c r="IP14" s="25"/>
-      <c r="IQ14" s="25"/>
-      <c r="IR14" s="25"/>
-      <c r="IS14" s="25"/>
-      <c r="IT14" s="25"/>
-      <c r="IU14" s="25"/>
-      <c r="IV14" s="25"/>
-      <c r="IW14" s="25"/>
-      <c r="IX14" s="25"/>
-      <c r="IY14" s="25"/>
-      <c r="IZ14" s="25"/>
-      <c r="JA14" s="25"/>
-      <c r="JB14" s="25"/>
-      <c r="JC14" s="25"/>
-      <c r="JD14" s="25"/>
-      <c r="JE14" s="25"/>
-      <c r="JF14" s="25"/>
-      <c r="JG14" s="25"/>
-      <c r="JH14" s="25"/>
-      <c r="JI14" s="25"/>
-      <c r="JJ14" s="25"/>
-      <c r="JK14" s="25"/>
-      <c r="JL14" s="25"/>
-      <c r="JM14" s="25"/>
-      <c r="JN14" s="25"/>
+        <v>120</v>
+      </c>
+      <c r="N14" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+      <c r="Y14"/>
+      <c r="Z14"/>
+      <c r="AA14"/>
+      <c r="AB14"/>
+      <c r="AC14"/>
+      <c r="AD14"/>
+      <c r="AE14"/>
+      <c r="AF14"/>
+      <c r="AG14"/>
+      <c r="AH14"/>
+      <c r="AI14"/>
+      <c r="AJ14"/>
+      <c r="AK14"/>
+      <c r="AL14"/>
+      <c r="AM14"/>
+      <c r="AN14"/>
+      <c r="AO14"/>
+      <c r="AP14"/>
+      <c r="AQ14"/>
+      <c r="AR14"/>
+      <c r="AS14"/>
+      <c r="AT14"/>
+      <c r="AU14"/>
+      <c r="AV14"/>
+      <c r="AW14"/>
+      <c r="AX14"/>
+      <c r="AY14"/>
+      <c r="AZ14"/>
+      <c r="BA14"/>
+      <c r="BB14"/>
+      <c r="BC14"/>
+      <c r="BD14"/>
+      <c r="BE14"/>
+      <c r="BF14"/>
+      <c r="BG14"/>
+      <c r="BH14"/>
+      <c r="BI14"/>
+      <c r="BJ14"/>
+      <c r="BK14"/>
+      <c r="BL14"/>
+      <c r="BM14"/>
+      <c r="BN14"/>
+      <c r="BO14"/>
+      <c r="BP14"/>
+      <c r="BQ14"/>
+      <c r="BR14"/>
+      <c r="BS14"/>
+      <c r="BT14"/>
+      <c r="BU14"/>
+      <c r="BV14"/>
+      <c r="BW14"/>
+      <c r="BX14" s="26"/>
+      <c r="BY14" s="26"/>
+      <c r="BZ14" s="26"/>
+      <c r="CA14" s="26"/>
+      <c r="CB14" s="26"/>
+      <c r="CC14" s="26"/>
+      <c r="CD14" s="26"/>
+      <c r="CE14" s="26"/>
+      <c r="CF14" s="26"/>
+      <c r="CG14" s="26"/>
+      <c r="CH14" s="26"/>
+      <c r="CI14" s="26"/>
+      <c r="CJ14" s="26"/>
+      <c r="CK14" s="26"/>
+      <c r="CL14" s="26"/>
+      <c r="CM14" s="26"/>
+      <c r="CN14" s="26"/>
+      <c r="CO14" s="26"/>
+      <c r="CP14" s="26"/>
+      <c r="CQ14" s="26"/>
+      <c r="CR14" s="26"/>
+      <c r="CS14" s="26"/>
+      <c r="CT14" s="26"/>
+      <c r="CU14" s="26"/>
+      <c r="CV14" s="26"/>
+      <c r="CW14" s="26"/>
+      <c r="CX14" s="26"/>
+      <c r="CY14" s="26"/>
+      <c r="CZ14" s="26"/>
+      <c r="DA14" s="26"/>
+      <c r="DB14" s="26"/>
+      <c r="DC14" s="26"/>
+      <c r="DD14" s="26"/>
+      <c r="DE14" s="26"/>
+      <c r="DF14" s="26"/>
+      <c r="DG14" s="26"/>
+      <c r="DH14" s="26"/>
+      <c r="DI14" s="26"/>
+      <c r="DJ14" s="26"/>
+      <c r="DK14" s="26"/>
+      <c r="DL14" s="26"/>
+      <c r="DM14" s="26"/>
+      <c r="DN14" s="26"/>
+      <c r="DO14" s="26"/>
+      <c r="DP14" s="26"/>
+      <c r="DQ14" s="26"/>
+      <c r="DR14" s="26"/>
+      <c r="DS14" s="26"/>
+      <c r="DT14" s="26"/>
+      <c r="DU14" s="26"/>
+      <c r="DV14" s="26"/>
+      <c r="DW14" s="26"/>
+      <c r="DX14" s="26"/>
+      <c r="DY14" s="26"/>
+      <c r="DZ14" s="26"/>
+      <c r="EA14" s="26"/>
+      <c r="EB14" s="26"/>
+      <c r="EC14" s="26"/>
+      <c r="ED14" s="26"/>
+      <c r="EE14" s="26"/>
+      <c r="EF14" s="26"/>
+      <c r="EG14" s="26"/>
+      <c r="EH14" s="26"/>
+      <c r="EI14" s="26"/>
+      <c r="EJ14" s="26"/>
+      <c r="EK14" s="26"/>
+      <c r="EL14" s="26"/>
+      <c r="EM14" s="26"/>
+      <c r="EN14" s="26"/>
+      <c r="EO14" s="26"/>
+      <c r="EP14" s="26"/>
+      <c r="EQ14" s="26"/>
+      <c r="ER14" s="26"/>
+      <c r="ES14" s="26"/>
+      <c r="ET14" s="26"/>
+      <c r="EU14" s="26"/>
+      <c r="EV14" s="26"/>
+      <c r="EW14" s="26"/>
+      <c r="EX14" s="26"/>
+      <c r="EY14" s="26"/>
+      <c r="EZ14" s="26"/>
+      <c r="FA14" s="26"/>
+      <c r="FB14" s="26"/>
+      <c r="FC14" s="26"/>
+      <c r="FD14" s="26"/>
+      <c r="FE14" s="26"/>
+      <c r="FF14" s="26"/>
+      <c r="FG14" s="26"/>
+      <c r="FH14" s="26"/>
+      <c r="FI14" s="26"/>
+      <c r="FJ14" s="26"/>
+      <c r="FK14" s="26"/>
+      <c r="FL14" s="26"/>
+      <c r="FM14" s="26"/>
+      <c r="FN14" s="26"/>
+      <c r="FO14" s="26"/>
+      <c r="FP14" s="26"/>
+      <c r="FQ14" s="26"/>
+      <c r="FR14" s="26"/>
+      <c r="FS14" s="26"/>
+      <c r="FT14" s="26"/>
+      <c r="FU14" s="26"/>
+      <c r="FV14" s="26"/>
+      <c r="FW14" s="26"/>
+      <c r="FX14" s="26"/>
+      <c r="FY14" s="26"/>
+      <c r="FZ14" s="26"/>
+      <c r="GA14" s="26"/>
+      <c r="GB14" s="26"/>
+      <c r="GC14" s="26"/>
+      <c r="GD14" s="26"/>
+      <c r="GE14" s="26"/>
+      <c r="GF14" s="26"/>
+      <c r="GG14" s="26"/>
+      <c r="GH14" s="26"/>
+      <c r="GI14" s="26"/>
+      <c r="GJ14" s="26"/>
+      <c r="GK14" s="26"/>
+      <c r="GL14" s="26"/>
+      <c r="GM14" s="26"/>
+      <c r="GN14" s="26"/>
+      <c r="GO14" s="26"/>
+      <c r="GP14" s="26"/>
+      <c r="GQ14" s="26"/>
+      <c r="GR14" s="26"/>
+      <c r="GS14" s="26"/>
+      <c r="GT14" s="26"/>
+      <c r="GU14" s="26"/>
+      <c r="GV14" s="26"/>
+      <c r="GW14" s="26"/>
+      <c r="GX14" s="26"/>
+      <c r="GY14" s="26"/>
+      <c r="GZ14" s="26"/>
+      <c r="HA14" s="26"/>
+      <c r="HB14" s="26"/>
+      <c r="HC14" s="26"/>
+      <c r="HD14" s="26"/>
+      <c r="HE14" s="26"/>
+      <c r="HF14" s="26"/>
+      <c r="HG14" s="26"/>
+      <c r="HH14" s="26"/>
+      <c r="HI14" s="26"/>
+      <c r="HJ14" s="26"/>
+      <c r="HK14" s="26"/>
+      <c r="HL14" s="26"/>
+      <c r="HM14" s="26"/>
+      <c r="HN14" s="26"/>
+      <c r="HO14" s="26"/>
+      <c r="HP14" s="26"/>
+      <c r="HQ14" s="26"/>
+      <c r="HR14" s="26"/>
+      <c r="HS14" s="26"/>
+      <c r="HT14" s="26"/>
+      <c r="HU14" s="26"/>
+      <c r="HV14" s="26"/>
+      <c r="HW14" s="26"/>
+      <c r="HX14" s="26"/>
+      <c r="HY14" s="26"/>
+      <c r="HZ14" s="26"/>
+      <c r="IA14" s="26"/>
+      <c r="IB14" s="26"/>
+      <c r="IC14" s="26"/>
+      <c r="ID14" s="26"/>
+      <c r="IE14" s="26"/>
+      <c r="IF14" s="26"/>
+      <c r="IG14" s="26"/>
+      <c r="IH14" s="26"/>
+      <c r="II14" s="26"/>
+      <c r="IJ14" s="26"/>
+      <c r="IK14" s="26"/>
+      <c r="IL14" s="26"/>
+      <c r="IM14" s="26"/>
+      <c r="IN14" s="26"/>
+      <c r="IO14" s="26"/>
+      <c r="IP14" s="26"/>
+      <c r="IQ14" s="26"/>
+      <c r="IR14" s="26"/>
+      <c r="IS14" s="26"/>
+      <c r="IT14" s="26"/>
+      <c r="IU14" s="26"/>
+      <c r="IV14" s="26"/>
+      <c r="IW14" s="26"/>
+      <c r="IX14" s="26"/>
+      <c r="IY14" s="26"/>
+      <c r="IZ14" s="26"/>
+      <c r="JA14" s="26"/>
+      <c r="JB14" s="26"/>
+      <c r="JC14" s="26"/>
+      <c r="JD14" s="26"/>
+      <c r="JE14" s="26"/>
+      <c r="JF14" s="26"/>
+      <c r="JG14" s="26"/>
+      <c r="JH14" s="26"/>
+      <c r="JI14" s="26"/>
+      <c r="JJ14" s="26"/>
+      <c r="JK14" s="26"/>
+      <c r="JL14" s="26"/>
+      <c r="JM14" s="26"/>
+      <c r="JN14" s="26"/>
     </row>
     <row r="15" s="14" customFormat="1" ht="25.5">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="27" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K15" s="9">
         <v>2010</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="N15" s="27"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="16"/>
-      <c r="AB15" s="16"/>
-      <c r="AC15" s="16"/>
-      <c r="AD15" s="16"/>
-      <c r="AE15" s="16"/>
-      <c r="AF15" s="16"/>
-      <c r="AG15" s="16"/>
-      <c r="AH15" s="16"/>
-      <c r="AI15" s="16"/>
-      <c r="AJ15" s="16"/>
-      <c r="AK15" s="16"/>
-      <c r="AL15" s="16"/>
-      <c r="AM15" s="16"/>
-      <c r="AN15" s="16"/>
-      <c r="AO15" s="16"/>
-      <c r="AP15" s="16"/>
-      <c r="AQ15" s="16"/>
-      <c r="AR15" s="16"/>
-      <c r="AS15" s="16"/>
-      <c r="AT15" s="16"/>
-      <c r="AU15" s="16"/>
-      <c r="AV15" s="16"/>
-      <c r="AW15" s="16"/>
-      <c r="AX15" s="16"/>
-      <c r="AY15" s="16"/>
-      <c r="AZ15" s="16"/>
-      <c r="BA15" s="16"/>
-      <c r="BB15" s="16"/>
-      <c r="BC15" s="16"/>
-      <c r="BD15" s="16"/>
-      <c r="BE15" s="16"/>
-      <c r="BF15" s="16"/>
-      <c r="BG15" s="16"/>
-      <c r="BH15" s="16"/>
-      <c r="BI15" s="16"/>
-      <c r="BJ15" s="16"/>
-      <c r="BK15" s="16"/>
-      <c r="BL15" s="16"/>
-      <c r="BM15" s="16"/>
-      <c r="BN15" s="16"/>
-      <c r="BO15" s="16"/>
-      <c r="BP15" s="16"/>
-      <c r="BQ15" s="16"/>
-      <c r="BR15" s="16"/>
-      <c r="BS15" s="16"/>
-      <c r="BT15" s="16"/>
-      <c r="BU15" s="16"/>
-      <c r="BV15" s="16"/>
-      <c r="BW15" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="N15" s="28"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+      <c r="Y15"/>
+      <c r="Z15"/>
+      <c r="AA15"/>
+      <c r="AB15"/>
+      <c r="AC15"/>
+      <c r="AD15"/>
+      <c r="AE15"/>
+      <c r="AF15"/>
+      <c r="AG15"/>
+      <c r="AH15"/>
+      <c r="AI15"/>
+      <c r="AJ15"/>
+      <c r="AK15"/>
+      <c r="AL15"/>
+      <c r="AM15"/>
+      <c r="AN15"/>
+      <c r="AO15"/>
+      <c r="AP15"/>
+      <c r="AQ15"/>
+      <c r="AR15"/>
+      <c r="AS15"/>
+      <c r="AT15"/>
+      <c r="AU15"/>
+      <c r="AV15"/>
+      <c r="AW15"/>
+      <c r="AX15"/>
+      <c r="AY15"/>
+      <c r="AZ15"/>
+      <c r="BA15"/>
+      <c r="BB15"/>
+      <c r="BC15"/>
+      <c r="BD15"/>
+      <c r="BE15"/>
+      <c r="BF15"/>
+      <c r="BG15"/>
+      <c r="BH15"/>
+      <c r="BI15"/>
+      <c r="BJ15"/>
+      <c r="BK15"/>
+      <c r="BL15"/>
+      <c r="BM15"/>
+      <c r="BN15"/>
+      <c r="BO15"/>
+      <c r="BP15"/>
+      <c r="BQ15"/>
+      <c r="BR15"/>
+      <c r="BS15"/>
+      <c r="BT15"/>
+      <c r="BU15"/>
+      <c r="BV15"/>
+      <c r="BW15"/>
       <c r="BX15" s="16"/>
       <c r="BY15" s="16"/>
       <c r="BZ15" s="16"/>
@@ -6370,108 +6983,108 @@
       <c r="JM15" s="16"/>
       <c r="JN15" s="16"/>
     </row>
-    <row r="16" s="6" customFormat="1" ht="51">
-      <c r="A16" s="26" t="s">
+    <row r="16" s="6" customFormat="1" ht="25.5">
+      <c r="A16" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="G16" s="28" t="s">
-        <v>131</v>
+        <v>115</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>132</v>
+        <v>136</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>137</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="K16" s="9">
-        <v>2010</v>
+        <v>119</v>
+      </c>
+      <c r="K16" s="7">
+        <v>2020</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M16" s="22" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="10"/>
-      <c r="AA16" s="10"/>
-      <c r="AB16" s="10"/>
-      <c r="AC16" s="10"/>
-      <c r="AD16" s="10"/>
-      <c r="AE16" s="10"/>
-      <c r="AF16" s="10"/>
-      <c r="AG16" s="10"/>
-      <c r="AH16" s="10"/>
-      <c r="AI16" s="10"/>
-      <c r="AJ16" s="10"/>
-      <c r="AK16" s="10"/>
-      <c r="AL16" s="10"/>
-      <c r="AM16" s="10"/>
-      <c r="AN16" s="10"/>
-      <c r="AO16" s="10"/>
-      <c r="AP16" s="10"/>
-      <c r="AQ16" s="10"/>
-      <c r="AR16" s="10"/>
-      <c r="AS16" s="10"/>
-      <c r="AT16" s="10"/>
-      <c r="AU16" s="10"/>
-      <c r="AV16" s="10"/>
-      <c r="AW16" s="10"/>
-      <c r="AX16" s="10"/>
-      <c r="AY16" s="10"/>
-      <c r="AZ16" s="10"/>
-      <c r="BA16" s="10"/>
-      <c r="BB16" s="10"/>
-      <c r="BC16" s="10"/>
-      <c r="BD16" s="10"/>
-      <c r="BE16" s="10"/>
-      <c r="BF16" s="10"/>
-      <c r="BG16" s="10"/>
-      <c r="BH16" s="10"/>
-      <c r="BI16" s="10"/>
-      <c r="BJ16" s="10"/>
-      <c r="BK16" s="10"/>
-      <c r="BL16" s="10"/>
-      <c r="BM16" s="10"/>
-      <c r="BN16" s="10"/>
-      <c r="BO16" s="10"/>
-      <c r="BP16" s="10"/>
-      <c r="BQ16" s="10"/>
-      <c r="BR16" s="10"/>
-      <c r="BS16" s="10"/>
-      <c r="BT16" s="10"/>
-      <c r="BU16" s="10"/>
-      <c r="BV16" s="10"/>
-      <c r="BW16" s="10"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16"/>
+      <c r="Z16"/>
+      <c r="AA16"/>
+      <c r="AB16"/>
+      <c r="AC16"/>
+      <c r="AD16"/>
+      <c r="AE16"/>
+      <c r="AF16"/>
+      <c r="AG16"/>
+      <c r="AH16"/>
+      <c r="AI16"/>
+      <c r="AJ16"/>
+      <c r="AK16"/>
+      <c r="AL16"/>
+      <c r="AM16"/>
+      <c r="AN16"/>
+      <c r="AO16"/>
+      <c r="AP16"/>
+      <c r="AQ16"/>
+      <c r="AR16"/>
+      <c r="AS16"/>
+      <c r="AT16"/>
+      <c r="AU16"/>
+      <c r="AV16"/>
+      <c r="AW16"/>
+      <c r="AX16"/>
+      <c r="AY16"/>
+      <c r="AZ16"/>
+      <c r="BA16"/>
+      <c r="BB16"/>
+      <c r="BC16"/>
+      <c r="BD16"/>
+      <c r="BE16"/>
+      <c r="BF16"/>
+      <c r="BG16"/>
+      <c r="BH16"/>
+      <c r="BI16"/>
+      <c r="BJ16"/>
+      <c r="BK16"/>
+      <c r="BL16"/>
+      <c r="BM16"/>
+      <c r="BN16"/>
+      <c r="BO16"/>
+      <c r="BP16"/>
+      <c r="BQ16"/>
+      <c r="BR16"/>
+      <c r="BS16"/>
+      <c r="BT16"/>
+      <c r="BU16"/>
+      <c r="BV16"/>
+      <c r="BW16"/>
       <c r="BX16" s="10"/>
       <c r="BY16" s="10"/>
       <c r="BZ16" s="10"/>
@@ -6672,152 +7285,211 @@
       <c r="JM16" s="10"/>
       <c r="JN16" s="10"/>
     </row>
-    <row r="17" s="6" customFormat="1" ht="38.25">
-      <c r="A17" s="26" t="s">
+    <row r="17" s="6" customFormat="1" ht="28.5">
+      <c r="A17" s="27" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="H17" s="7"/>
+        <v>139</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="I17" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>139</v>
+        <v>131</v>
+      </c>
+      <c r="K17" s="9">
+        <v>2010</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>141</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="M17" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="N17" s="10"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="30"/>
+      <c r="S17" s="30"/>
+      <c r="T17" s="30"/>
+      <c r="U17" s="30"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="30"/>
+      <c r="X17" s="30"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="30"/>
+      <c r="AA17" s="30"/>
+      <c r="AB17" s="30"/>
+      <c r="AC17" s="30"/>
+      <c r="AD17" s="30"/>
+      <c r="AE17" s="30"/>
+      <c r="AF17" s="30"/>
+      <c r="AG17" s="30"/>
+      <c r="AH17" s="30"/>
+      <c r="AI17" s="30"/>
+      <c r="AJ17" s="30"/>
+      <c r="AK17" s="30"/>
+      <c r="AL17" s="30"/>
+      <c r="AM17" s="30"/>
+      <c r="AN17" s="30"/>
+      <c r="AO17" s="30"/>
+      <c r="AP17" s="30"/>
+      <c r="AQ17" s="30"/>
+      <c r="AR17" s="30"/>
+      <c r="AS17" s="30"/>
+      <c r="AT17" s="30"/>
+      <c r="AU17" s="30"/>
+      <c r="AV17" s="30"/>
+      <c r="AW17" s="30"/>
+      <c r="AX17" s="30"/>
+      <c r="AY17" s="30"/>
+      <c r="AZ17" s="30"/>
+      <c r="BA17" s="30"/>
+      <c r="BB17" s="30"/>
+      <c r="BC17" s="30"/>
+      <c r="BD17" s="30"/>
+      <c r="BE17" s="30"/>
+      <c r="BF17" s="30"/>
+      <c r="BG17" s="30"/>
+      <c r="BH17" s="30"/>
+      <c r="BI17" s="30"/>
+      <c r="BJ17" s="30"/>
+      <c r="BK17" s="30"/>
+      <c r="BL17" s="30"/>
+      <c r="BM17" s="30"/>
+      <c r="BN17" s="30"/>
+      <c r="BO17" s="30"/>
+      <c r="BP17" s="30"/>
+      <c r="BQ17" s="30"/>
+      <c r="BR17" s="30"/>
+      <c r="BS17" s="30"/>
+      <c r="BT17" s="30"/>
+      <c r="BU17" s="30"/>
+      <c r="BV17" s="30"/>
+      <c r="BW17" s="30"/>
     </row>
     <row r="18" s="6" customFormat="1" ht="25.5">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="27" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="J18" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>149</v>
+      <c r="J18" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K18" s="7">
+        <v>2020</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="10"/>
-      <c r="AB18" s="10"/>
-      <c r="AC18" s="10"/>
-      <c r="AD18" s="10"/>
-      <c r="AE18" s="10"/>
-      <c r="AF18" s="10"/>
-      <c r="AG18" s="10"/>
-      <c r="AH18" s="10"/>
-      <c r="AI18" s="10"/>
-      <c r="AJ18" s="10"/>
-      <c r="AK18" s="10"/>
-      <c r="AL18" s="10"/>
-      <c r="AM18" s="10"/>
-      <c r="AN18" s="10"/>
-      <c r="AO18" s="10"/>
-      <c r="AP18" s="10"/>
-      <c r="AQ18" s="10"/>
-      <c r="AR18" s="10"/>
-      <c r="AS18" s="10"/>
-      <c r="AT18" s="10"/>
-      <c r="AU18" s="10"/>
-      <c r="AV18" s="10"/>
-      <c r="AW18" s="10"/>
-      <c r="AX18" s="10"/>
-      <c r="AY18" s="10"/>
-      <c r="AZ18" s="10"/>
-      <c r="BA18" s="10"/>
-      <c r="BB18" s="10"/>
-      <c r="BC18" s="10"/>
-      <c r="BD18" s="10"/>
-      <c r="BE18" s="10"/>
-      <c r="BF18" s="10"/>
-      <c r="BG18" s="10"/>
-      <c r="BH18" s="10"/>
-      <c r="BI18" s="10"/>
-      <c r="BJ18" s="10"/>
-      <c r="BK18" s="10"/>
-      <c r="BL18" s="10"/>
-      <c r="BM18" s="10"/>
-      <c r="BN18" s="10"/>
-      <c r="BO18" s="10"/>
-      <c r="BP18" s="10"/>
-      <c r="BQ18" s="10"/>
-      <c r="BR18" s="10"/>
-      <c r="BS18" s="10"/>
-      <c r="BT18" s="10"/>
-      <c r="BU18" s="10"/>
-      <c r="BV18" s="10"/>
-      <c r="BW18" s="10"/>
+        <v>47</v>
+      </c>
+      <c r="M18" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="N18" s="31"/>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="R18"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
+      <c r="W18"/>
+      <c r="X18"/>
+      <c r="Y18"/>
+      <c r="Z18"/>
+      <c r="AA18"/>
+      <c r="AB18"/>
+      <c r="AC18"/>
+      <c r="AD18"/>
+      <c r="AE18"/>
+      <c r="AF18"/>
+      <c r="AG18"/>
+      <c r="AH18"/>
+      <c r="AI18"/>
+      <c r="AJ18"/>
+      <c r="AK18"/>
+      <c r="AL18"/>
+      <c r="AM18"/>
+      <c r="AN18"/>
+      <c r="AO18"/>
+      <c r="AP18"/>
+      <c r="AQ18"/>
+      <c r="AR18"/>
+      <c r="AS18"/>
+      <c r="AT18"/>
+      <c r="AU18"/>
+      <c r="AV18"/>
+      <c r="AW18"/>
+      <c r="AX18"/>
+      <c r="AY18"/>
+      <c r="AZ18"/>
+      <c r="BA18"/>
+      <c r="BB18"/>
+      <c r="BC18"/>
+      <c r="BD18"/>
+      <c r="BE18"/>
+      <c r="BF18"/>
+      <c r="BG18"/>
+      <c r="BH18"/>
+      <c r="BI18"/>
+      <c r="BJ18"/>
+      <c r="BK18"/>
+      <c r="BL18"/>
+      <c r="BM18"/>
+      <c r="BN18"/>
+      <c r="BO18"/>
+      <c r="BP18"/>
+      <c r="BQ18"/>
+      <c r="BR18"/>
+      <c r="BS18"/>
+      <c r="BT18"/>
+      <c r="BU18"/>
+      <c r="BV18"/>
+      <c r="BW18"/>
       <c r="BX18" s="10"/>
       <c r="BY18" s="10"/>
       <c r="BZ18" s="10"/>
@@ -7018,110 +7690,108 @@
       <c r="JM18" s="10"/>
       <c r="JN18" s="10"/>
     </row>
-    <row r="19" s="6" customFormat="1" ht="28.5">
-      <c r="A19" s="29" t="s">
+    <row r="19" s="6" customFormat="1" ht="38.25">
+      <c r="A19" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="B19" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="29" t="s">
+      <c r="J19" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="K19" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="L19" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M19" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="30" t="s">
+      <c r="N19" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="G19" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="J19" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="K19" s="29">
-        <v>2023</v>
-      </c>
-      <c r="L19" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="M19" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="N19" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="10"/>
-      <c r="Y19" s="10"/>
-      <c r="Z19" s="10"/>
-      <c r="AA19" s="10"/>
-      <c r="AB19" s="10"/>
-      <c r="AC19" s="10"/>
-      <c r="AD19" s="10"/>
-      <c r="AE19" s="10"/>
-      <c r="AF19" s="10"/>
-      <c r="AG19" s="10"/>
-      <c r="AH19" s="10"/>
-      <c r="AI19" s="10"/>
-      <c r="AJ19" s="10"/>
-      <c r="AK19" s="10"/>
-      <c r="AL19" s="10"/>
-      <c r="AM19" s="10"/>
-      <c r="AN19" s="10"/>
-      <c r="AO19" s="10"/>
-      <c r="AP19" s="10"/>
-      <c r="AQ19" s="10"/>
-      <c r="AR19" s="10"/>
-      <c r="AS19" s="10"/>
-      <c r="AT19" s="10"/>
-      <c r="AU19" s="10"/>
-      <c r="AV19" s="10"/>
-      <c r="AW19" s="10"/>
-      <c r="AX19" s="10"/>
-      <c r="AY19" s="10"/>
-      <c r="AZ19" s="10"/>
-      <c r="BA19" s="10"/>
-      <c r="BB19" s="10"/>
-      <c r="BC19" s="10"/>
-      <c r="BD19" s="10"/>
-      <c r="BE19" s="10"/>
-      <c r="BF19" s="10"/>
-      <c r="BG19" s="10"/>
-      <c r="BH19" s="10"/>
-      <c r="BI19" s="10"/>
-      <c r="BJ19" s="10"/>
-      <c r="BK19" s="10"/>
-      <c r="BL19" s="10"/>
-      <c r="BM19" s="10"/>
-      <c r="BN19" s="10"/>
-      <c r="BO19" s="10"/>
-      <c r="BP19" s="10"/>
-      <c r="BQ19" s="10"/>
-      <c r="BR19" s="10"/>
-      <c r="BS19" s="10"/>
-      <c r="BT19" s="10"/>
-      <c r="BU19" s="10"/>
-      <c r="BV19" s="10"/>
-      <c r="BW19" s="10"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
+      <c r="Y19"/>
+      <c r="Z19"/>
+      <c r="AA19"/>
+      <c r="AB19"/>
+      <c r="AC19"/>
+      <c r="AD19"/>
+      <c r="AE19"/>
+      <c r="AF19"/>
+      <c r="AG19"/>
+      <c r="AH19"/>
+      <c r="AI19"/>
+      <c r="AJ19"/>
+      <c r="AK19"/>
+      <c r="AL19"/>
+      <c r="AM19"/>
+      <c r="AN19"/>
+      <c r="AO19"/>
+      <c r="AP19"/>
+      <c r="AQ19"/>
+      <c r="AR19"/>
+      <c r="AS19"/>
+      <c r="AT19"/>
+      <c r="AU19"/>
+      <c r="AV19"/>
+      <c r="AW19"/>
+      <c r="AX19"/>
+      <c r="AY19"/>
+      <c r="AZ19"/>
+      <c r="BA19"/>
+      <c r="BB19"/>
+      <c r="BC19"/>
+      <c r="BD19"/>
+      <c r="BE19"/>
+      <c r="BF19"/>
+      <c r="BG19"/>
+      <c r="BH19"/>
+      <c r="BI19"/>
+      <c r="BJ19"/>
+      <c r="BK19"/>
+      <c r="BL19"/>
+      <c r="BM19"/>
+      <c r="BN19"/>
+      <c r="BO19"/>
+      <c r="BP19"/>
+      <c r="BQ19"/>
+      <c r="BR19"/>
+      <c r="BS19"/>
+      <c r="BT19"/>
+      <c r="BU19"/>
+      <c r="BV19"/>
+      <c r="BW19"/>
       <c r="BX19" s="10"/>
       <c r="BY19" s="10"/>
       <c r="BZ19" s="10"/>
@@ -7322,1312 +7992,2690 @@
       <c r="JM19" s="10"/>
       <c r="JN19" s="10"/>
     </row>
-    <row r="20" s="32" customFormat="1" ht="51">
-      <c r="A20" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="29" t="s">
+    <row r="20" s="6" customFormat="1" ht="38.25">
+      <c r="A20" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="J20" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E20" s="29" t="s">
+      <c r="K20" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="F20" s="33" t="s">
+      <c r="L20" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="M20" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="H20" s="29"/>
-      <c r="I20" s="34" t="s">
+      <c r="N20" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="J20" s="35"/>
-      <c r="K20" s="29" t="s">
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="32"/>
+      <c r="AG20" s="32"/>
+      <c r="AH20" s="32"/>
+      <c r="AI20" s="32"/>
+      <c r="AJ20" s="32"/>
+      <c r="AK20" s="32"/>
+      <c r="AL20" s="32"/>
+      <c r="AM20" s="32"/>
+      <c r="AN20" s="32"/>
+      <c r="AO20" s="32"/>
+      <c r="AP20" s="32"/>
+      <c r="AQ20" s="32"/>
+      <c r="AR20" s="32"/>
+      <c r="AS20" s="32"/>
+      <c r="AT20" s="32"/>
+      <c r="AU20" s="32"/>
+      <c r="AV20" s="32"/>
+      <c r="AW20" s="32"/>
+      <c r="AX20" s="32"/>
+      <c r="AY20" s="32"/>
+      <c r="AZ20" s="32"/>
+      <c r="BA20" s="32"/>
+      <c r="BB20" s="32"/>
+      <c r="BC20" s="32"/>
+      <c r="BD20" s="32"/>
+      <c r="BE20" s="32"/>
+      <c r="BF20" s="32"/>
+      <c r="BG20" s="32"/>
+      <c r="BH20" s="32"/>
+      <c r="BI20" s="32"/>
+      <c r="BJ20" s="32"/>
+      <c r="BK20" s="32"/>
+      <c r="BL20" s="32"/>
+      <c r="BM20" s="32"/>
+      <c r="BN20" s="32"/>
+      <c r="BO20" s="32"/>
+      <c r="BP20" s="32"/>
+      <c r="BQ20" s="32"/>
+      <c r="BR20" s="32"/>
+      <c r="BS20" s="32"/>
+      <c r="BT20" s="32"/>
+      <c r="BU20" s="32"/>
+      <c r="BV20" s="32"/>
+      <c r="BW20" s="32"/>
+      <c r="BX20" s="32"/>
+      <c r="BY20" s="32"/>
+      <c r="BZ20" s="32"/>
+      <c r="CA20" s="32"/>
+      <c r="CB20" s="32"/>
+      <c r="CC20" s="32"/>
+      <c r="CD20" s="32"/>
+      <c r="CE20" s="32"/>
+      <c r="CF20" s="32"/>
+      <c r="CG20" s="32"/>
+      <c r="CH20" s="32"/>
+      <c r="CI20" s="32"/>
+      <c r="CJ20" s="32"/>
+      <c r="CK20" s="32"/>
+      <c r="CL20" s="32"/>
+      <c r="CM20" s="32"/>
+      <c r="CN20" s="32"/>
+      <c r="CO20" s="32"/>
+      <c r="CP20" s="32"/>
+      <c r="CQ20" s="32"/>
+      <c r="CR20" s="32"/>
+      <c r="CS20" s="32"/>
+      <c r="CT20" s="32"/>
+      <c r="CU20" s="32"/>
+      <c r="CV20" s="32"/>
+      <c r="CW20" s="32"/>
+      <c r="CX20" s="32"/>
+      <c r="CY20" s="32"/>
+      <c r="CZ20" s="32"/>
+      <c r="DA20" s="32"/>
+      <c r="DB20" s="32"/>
+      <c r="DC20" s="32"/>
+      <c r="DD20" s="32"/>
+      <c r="DE20" s="32"/>
+      <c r="DF20" s="32"/>
+      <c r="DG20" s="32"/>
+      <c r="DH20" s="32"/>
+      <c r="DI20" s="32"/>
+      <c r="DJ20" s="32"/>
+      <c r="DK20" s="32"/>
+      <c r="DL20" s="32"/>
+      <c r="DM20" s="32"/>
+      <c r="DN20" s="32"/>
+      <c r="DO20" s="32"/>
+      <c r="DP20" s="32"/>
+      <c r="DQ20" s="32"/>
+      <c r="DR20" s="32"/>
+      <c r="DS20" s="32"/>
+      <c r="DT20" s="32"/>
+      <c r="DU20" s="32"/>
+      <c r="DV20" s="32"/>
+      <c r="DW20" s="32"/>
+      <c r="DX20" s="32"/>
+      <c r="DY20" s="32"/>
+      <c r="DZ20" s="32"/>
+      <c r="EA20" s="32"/>
+      <c r="EB20" s="32"/>
+      <c r="EC20" s="32"/>
+      <c r="ED20" s="32"/>
+      <c r="EE20" s="32"/>
+      <c r="EF20" s="32"/>
+      <c r="EG20" s="32"/>
+      <c r="EH20" s="32"/>
+      <c r="EI20" s="32"/>
+      <c r="EJ20" s="32"/>
+      <c r="EK20" s="32"/>
+      <c r="EL20" s="32"/>
+      <c r="EM20" s="32"/>
+      <c r="EN20" s="32"/>
+      <c r="EO20" s="32"/>
+      <c r="EP20" s="32"/>
+      <c r="EQ20" s="32"/>
+      <c r="ER20" s="32"/>
+      <c r="ES20" s="32"/>
+      <c r="ET20" s="32"/>
+      <c r="EU20" s="32"/>
+      <c r="EV20" s="32"/>
+      <c r="EW20" s="32"/>
+      <c r="EX20" s="32"/>
+      <c r="EY20" s="32"/>
+      <c r="EZ20" s="32"/>
+      <c r="FA20" s="32"/>
+      <c r="FB20" s="32"/>
+      <c r="FC20" s="32"/>
+      <c r="FD20" s="32"/>
+      <c r="FE20" s="32"/>
+      <c r="FF20" s="32"/>
+      <c r="FG20" s="32"/>
+      <c r="FH20" s="32"/>
+      <c r="FI20" s="32"/>
+      <c r="FJ20" s="32"/>
+      <c r="FK20" s="32"/>
+      <c r="FL20" s="32"/>
+      <c r="FM20" s="32"/>
+      <c r="FN20" s="32"/>
+      <c r="FO20" s="32"/>
+      <c r="FP20" s="32"/>
+      <c r="FQ20" s="32"/>
+      <c r="FR20" s="32"/>
+      <c r="FS20" s="32"/>
+      <c r="FT20" s="32"/>
+      <c r="FU20" s="32"/>
+      <c r="FV20" s="32"/>
+      <c r="FW20" s="32"/>
+      <c r="FX20" s="32"/>
+      <c r="FY20" s="32"/>
+      <c r="FZ20" s="32"/>
+      <c r="GA20" s="32"/>
+      <c r="GB20" s="32"/>
+      <c r="GC20" s="32"/>
+      <c r="GD20" s="32"/>
+      <c r="GE20" s="32"/>
+      <c r="GF20" s="32"/>
+      <c r="GG20" s="32"/>
+      <c r="GH20" s="32"/>
+      <c r="GI20" s="32"/>
+      <c r="GJ20" s="32"/>
+      <c r="GK20" s="32"/>
+      <c r="GL20" s="32"/>
+      <c r="GM20" s="32"/>
+      <c r="GN20" s="32"/>
+      <c r="GO20" s="32"/>
+      <c r="GP20" s="32"/>
+      <c r="GQ20" s="32"/>
+      <c r="GR20" s="32"/>
+      <c r="GS20" s="32"/>
+      <c r="GT20" s="32"/>
+      <c r="GU20" s="32"/>
+      <c r="GV20" s="32"/>
+      <c r="GW20" s="32"/>
+      <c r="GX20" s="32"/>
+      <c r="GY20" s="32"/>
+      <c r="GZ20" s="32"/>
+      <c r="HA20" s="32"/>
+      <c r="HB20" s="32"/>
+      <c r="HC20" s="32"/>
+      <c r="HD20" s="32"/>
+      <c r="HE20" s="32"/>
+      <c r="HF20" s="32"/>
+      <c r="HG20" s="32"/>
+      <c r="HH20" s="32"/>
+      <c r="HI20" s="32"/>
+      <c r="HJ20" s="32"/>
+      <c r="HK20" s="32"/>
+      <c r="HL20" s="32"/>
+      <c r="HM20" s="32"/>
+      <c r="HN20" s="32"/>
+      <c r="HO20" s="32"/>
+      <c r="HP20" s="32"/>
+      <c r="HQ20" s="32"/>
+      <c r="HR20" s="32"/>
+      <c r="HS20" s="32"/>
+      <c r="HT20" s="32"/>
+      <c r="HU20" s="32"/>
+      <c r="HV20" s="32"/>
+      <c r="HW20" s="32"/>
+      <c r="HX20" s="32"/>
+      <c r="HY20" s="32"/>
+      <c r="HZ20" s="32"/>
+      <c r="IA20" s="32"/>
+      <c r="IB20" s="32"/>
+      <c r="IC20" s="32"/>
+      <c r="ID20" s="32"/>
+      <c r="IE20" s="32"/>
+      <c r="IF20" s="32"/>
+      <c r="IG20" s="32"/>
+      <c r="IH20" s="32"/>
+      <c r="II20" s="32"/>
+      <c r="IJ20" s="32"/>
+      <c r="IK20" s="32"/>
+      <c r="IL20" s="32"/>
+      <c r="IM20" s="32"/>
+      <c r="IN20" s="32"/>
+      <c r="IO20" s="32"/>
+      <c r="IP20" s="32"/>
+      <c r="IQ20" s="32"/>
+      <c r="IR20" s="32"/>
+      <c r="IS20" s="32"/>
+      <c r="IT20" s="32"/>
+      <c r="IU20" s="32"/>
+      <c r="IV20" s="32"/>
+      <c r="IW20" s="32"/>
+      <c r="IX20" s="32"/>
+      <c r="IY20" s="32"/>
+      <c r="IZ20" s="32"/>
+      <c r="JA20" s="32"/>
+      <c r="JB20" s="32"/>
+      <c r="JC20" s="32"/>
+      <c r="JD20" s="32"/>
+      <c r="JE20" s="32"/>
+      <c r="JF20" s="32"/>
+      <c r="JG20" s="32"/>
+      <c r="JH20" s="32"/>
+      <c r="JI20" s="32"/>
+      <c r="JJ20" s="32"/>
+      <c r="JK20" s="32"/>
+      <c r="JL20" s="32"/>
+      <c r="JM20" s="32"/>
+      <c r="JN20" s="32"/>
+    </row>
+    <row r="21" s="33" customFormat="1" ht="51">
+      <c r="A21" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="L20" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="M20" s="29"/>
-      <c r="N20" s="16" t="s">
+      <c r="D21" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
-      <c r="S20" s="36"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="36"/>
-      <c r="V20" s="36"/>
-      <c r="W20" s="36"/>
-      <c r="X20" s="36"/>
-      <c r="Y20" s="36"/>
-      <c r="Z20" s="36"/>
-      <c r="AA20" s="36"/>
-      <c r="AB20" s="36"/>
-      <c r="AC20" s="36"/>
-      <c r="AD20" s="36"/>
-      <c r="AE20" s="36"/>
-      <c r="AF20" s="36"/>
-      <c r="AG20" s="36"/>
-      <c r="AH20" s="36"/>
-      <c r="AI20" s="36"/>
-      <c r="AJ20" s="36"/>
-      <c r="AK20" s="36"/>
-      <c r="AL20" s="36"/>
-      <c r="AM20" s="36"/>
-      <c r="AN20" s="36"/>
-      <c r="AO20" s="36"/>
-      <c r="AP20" s="36"/>
-      <c r="AQ20" s="36"/>
-      <c r="AR20" s="36"/>
-      <c r="AS20" s="36"/>
-      <c r="AT20" s="36"/>
-      <c r="AU20" s="36"/>
-      <c r="AV20" s="36"/>
-      <c r="AW20" s="36"/>
-      <c r="AX20" s="36"/>
-      <c r="AY20" s="36"/>
-      <c r="AZ20" s="36"/>
-      <c r="BA20" s="36"/>
-      <c r="BB20" s="36"/>
-      <c r="BC20" s="36"/>
-      <c r="BD20" s="36"/>
-      <c r="BE20" s="36"/>
-      <c r="BF20" s="36"/>
-      <c r="BG20" s="36"/>
-      <c r="BH20" s="36"/>
-      <c r="BI20" s="36"/>
-      <c r="BJ20" s="36"/>
-      <c r="BK20" s="36"/>
-      <c r="BL20" s="36"/>
-      <c r="BM20" s="36"/>
-      <c r="BN20" s="36"/>
-      <c r="BO20" s="36"/>
-      <c r="BP20" s="36"/>
-      <c r="BQ20" s="36"/>
-      <c r="BR20" s="36"/>
-      <c r="BS20" s="36"/>
-      <c r="BT20" s="36"/>
-      <c r="BU20" s="36"/>
-      <c r="BV20" s="36"/>
-      <c r="BW20" s="36"/>
-      <c r="BX20" s="36"/>
-      <c r="BY20" s="36"/>
-      <c r="BZ20" s="36"/>
-      <c r="CA20" s="36"/>
-      <c r="CB20" s="36"/>
-      <c r="CC20" s="36"/>
-      <c r="CD20" s="36"/>
-      <c r="CE20" s="36"/>
-      <c r="CF20" s="36"/>
-      <c r="CG20" s="36"/>
-      <c r="CH20" s="36"/>
-      <c r="CI20" s="36"/>
-      <c r="CJ20" s="36"/>
-      <c r="CK20" s="36"/>
-      <c r="CL20" s="36"/>
-      <c r="CM20" s="36"/>
-      <c r="CN20" s="36"/>
-      <c r="CO20" s="36"/>
-      <c r="CP20" s="36"/>
-      <c r="CQ20" s="36"/>
-      <c r="CR20" s="36"/>
-      <c r="CS20" s="36"/>
-      <c r="CT20" s="36"/>
-      <c r="CU20" s="36"/>
-      <c r="CV20" s="36"/>
-      <c r="CW20" s="36"/>
-      <c r="CX20" s="36"/>
-      <c r="CY20" s="36"/>
-      <c r="CZ20" s="36"/>
-      <c r="DA20" s="36"/>
-      <c r="DB20" s="36"/>
-      <c r="DC20" s="36"/>
-      <c r="DD20" s="36"/>
-      <c r="DE20" s="36"/>
-      <c r="DF20" s="36"/>
-      <c r="DG20" s="36"/>
-      <c r="DH20" s="36"/>
-      <c r="DI20" s="36"/>
-      <c r="DJ20" s="36"/>
-      <c r="DK20" s="36"/>
-      <c r="DL20" s="36"/>
-      <c r="DM20" s="36"/>
-      <c r="DN20" s="36"/>
-      <c r="DO20" s="36"/>
-      <c r="DP20" s="36"/>
-      <c r="DQ20" s="36"/>
-      <c r="DR20" s="36"/>
-      <c r="DS20" s="36"/>
-      <c r="DT20" s="36"/>
-      <c r="DU20" s="36"/>
-      <c r="DV20" s="36"/>
-      <c r="DW20" s="36"/>
-      <c r="DX20" s="36"/>
-      <c r="DY20" s="36"/>
-      <c r="DZ20" s="36"/>
-      <c r="EA20" s="36"/>
-      <c r="EB20" s="36"/>
-      <c r="EC20" s="36"/>
-      <c r="ED20" s="36"/>
-      <c r="EE20" s="36"/>
-      <c r="EF20" s="36"/>
-      <c r="EG20" s="36"/>
-      <c r="EH20" s="36"/>
-      <c r="EI20" s="36"/>
-      <c r="EJ20" s="36"/>
-      <c r="EK20" s="36"/>
-      <c r="EL20" s="36"/>
-      <c r="EM20" s="36"/>
-      <c r="EN20" s="36"/>
-      <c r="EO20" s="36"/>
-      <c r="EP20" s="36"/>
-      <c r="EQ20" s="36"/>
-      <c r="ER20" s="36"/>
-      <c r="ES20" s="36"/>
-      <c r="ET20" s="36"/>
-      <c r="EU20" s="36"/>
-      <c r="EV20" s="36"/>
-      <c r="EW20" s="36"/>
-      <c r="EX20" s="36"/>
-      <c r="EY20" s="36"/>
-      <c r="EZ20" s="36"/>
-      <c r="FA20" s="36"/>
-      <c r="FB20" s="36"/>
-      <c r="FC20" s="36"/>
-      <c r="FD20" s="36"/>
-      <c r="FE20" s="36"/>
-      <c r="FF20" s="36"/>
-      <c r="FG20" s="36"/>
-      <c r="FH20" s="36"/>
-      <c r="FI20" s="36"/>
-      <c r="FJ20" s="36"/>
-      <c r="FK20" s="36"/>
-      <c r="FL20" s="36"/>
-      <c r="FM20" s="36"/>
-      <c r="FN20" s="36"/>
-      <c r="FO20" s="36"/>
-      <c r="FP20" s="36"/>
-      <c r="FQ20" s="36"/>
-      <c r="FR20" s="36"/>
-      <c r="FS20" s="36"/>
-      <c r="FT20" s="36"/>
-      <c r="FU20" s="36"/>
-      <c r="FV20" s="36"/>
-      <c r="FW20" s="36"/>
-      <c r="FX20" s="36"/>
-      <c r="FY20" s="36"/>
-      <c r="FZ20" s="36"/>
-      <c r="GA20" s="36"/>
-      <c r="GB20" s="36"/>
-      <c r="GC20" s="36"/>
-      <c r="GD20" s="36"/>
-      <c r="GE20" s="36"/>
-      <c r="GF20" s="36"/>
-      <c r="GG20" s="36"/>
-      <c r="GH20" s="36"/>
-      <c r="GI20" s="36"/>
-      <c r="GJ20" s="36"/>
-      <c r="GK20" s="36"/>
-      <c r="GL20" s="36"/>
-      <c r="GM20" s="36"/>
-      <c r="GN20" s="36"/>
-      <c r="GO20" s="36"/>
-      <c r="GP20" s="36"/>
-      <c r="GQ20" s="36"/>
-      <c r="GR20" s="36"/>
-      <c r="GS20" s="36"/>
-      <c r="GT20" s="36"/>
-      <c r="GU20" s="36"/>
-      <c r="GV20" s="36"/>
-      <c r="GW20" s="36"/>
-      <c r="GX20" s="36"/>
-      <c r="GY20" s="36"/>
-      <c r="GZ20" s="36"/>
-      <c r="HA20" s="36"/>
-      <c r="HB20" s="36"/>
-      <c r="HC20" s="36"/>
-      <c r="HD20" s="36"/>
-      <c r="HE20" s="36"/>
-      <c r="HF20" s="36"/>
-      <c r="HG20" s="36"/>
-      <c r="HH20" s="36"/>
-      <c r="HI20" s="36"/>
-      <c r="HJ20" s="36"/>
-      <c r="HK20" s="36"/>
-      <c r="HL20" s="36"/>
-      <c r="HM20" s="36"/>
-      <c r="HN20" s="36"/>
-      <c r="HO20" s="36"/>
-      <c r="HP20" s="36"/>
-      <c r="HQ20" s="36"/>
-      <c r="HR20" s="36"/>
-      <c r="HS20" s="36"/>
-      <c r="HT20" s="36"/>
-      <c r="HU20" s="36"/>
-      <c r="HV20" s="36"/>
-      <c r="HW20" s="36"/>
-      <c r="HX20" s="36"/>
-      <c r="HY20" s="36"/>
-      <c r="HZ20" s="36"/>
-      <c r="IA20" s="36"/>
-      <c r="IB20" s="36"/>
-      <c r="IC20" s="36"/>
-      <c r="ID20" s="36"/>
-      <c r="IE20" s="36"/>
-      <c r="IF20" s="36"/>
-      <c r="IG20" s="36"/>
-      <c r="IH20" s="36"/>
-      <c r="II20" s="36"/>
-      <c r="IJ20" s="36"/>
-      <c r="IK20" s="36"/>
-      <c r="IL20" s="36"/>
-      <c r="IM20" s="36"/>
-      <c r="IN20" s="36"/>
-      <c r="IO20" s="36"/>
-      <c r="IP20" s="36"/>
-      <c r="IQ20" s="36"/>
-      <c r="IR20" s="36"/>
-      <c r="IS20" s="36"/>
-      <c r="IT20" s="36"/>
-      <c r="IU20" s="36"/>
-      <c r="IV20" s="36"/>
-      <c r="IW20" s="36"/>
-      <c r="IX20" s="36"/>
-      <c r="IY20" s="36"/>
-      <c r="IZ20" s="36"/>
-      <c r="JA20" s="36"/>
-      <c r="JB20" s="36"/>
-      <c r="JC20" s="36"/>
-      <c r="JD20" s="36"/>
-      <c r="JE20" s="36"/>
-      <c r="JF20" s="36"/>
-      <c r="JG20" s="36"/>
-      <c r="JH20" s="36"/>
-      <c r="JI20" s="36"/>
-      <c r="JJ20" s="36"/>
-      <c r="JK20" s="36"/>
-      <c r="JL20" s="36"/>
-      <c r="JM20" s="36"/>
-      <c r="JN20" s="36"/>
+      <c r="E21" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="K21" s="7">
+        <v>2026</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="N21" s="10"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="33"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="33"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="33"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="33"/>
+      <c r="AB21" s="33"/>
+      <c r="AC21" s="33"/>
+      <c r="AD21" s="33"/>
+      <c r="AE21" s="33"/>
+      <c r="AF21" s="33"/>
+      <c r="AG21" s="33"/>
+      <c r="AH21" s="33"/>
+      <c r="AI21" s="33"/>
+      <c r="AJ21" s="33"/>
+      <c r="AK21" s="33"/>
+      <c r="AL21" s="33"/>
+      <c r="AM21" s="33"/>
+      <c r="AN21" s="33"/>
+      <c r="AO21" s="33"/>
+      <c r="AP21" s="33"/>
+      <c r="AQ21" s="33"/>
+      <c r="AR21" s="33"/>
+      <c r="AS21" s="33"/>
+      <c r="AT21" s="33"/>
+      <c r="AU21" s="33"/>
+      <c r="AV21" s="33"/>
+      <c r="AW21" s="33"/>
+      <c r="AX21" s="33"/>
+      <c r="AY21" s="33"/>
+      <c r="AZ21" s="33"/>
+      <c r="BA21" s="33"/>
+      <c r="BB21" s="33"/>
+      <c r="BC21" s="33"/>
+      <c r="BD21" s="33"/>
+      <c r="BE21" s="33"/>
+      <c r="BF21" s="33"/>
+      <c r="BG21" s="33"/>
+      <c r="BH21" s="33"/>
+      <c r="BI21" s="33"/>
+      <c r="BJ21" s="33"/>
+      <c r="BK21" s="33"/>
+      <c r="BL21" s="33"/>
+      <c r="BM21" s="33"/>
+      <c r="BN21" s="33"/>
+      <c r="BO21" s="33"/>
+      <c r="BP21" s="33"/>
+      <c r="BQ21" s="33"/>
+      <c r="BR21" s="33"/>
+      <c r="BS21" s="33"/>
+      <c r="BT21" s="33"/>
+      <c r="BU21" s="33"/>
+      <c r="BV21" s="33"/>
+      <c r="BW21" s="33"/>
+      <c r="BX21" s="33"/>
+      <c r="BY21" s="33"/>
+      <c r="BZ21" s="33"/>
+      <c r="CA21" s="33"/>
+      <c r="CB21" s="33"/>
+      <c r="CC21" s="33"/>
+      <c r="CD21" s="33"/>
+      <c r="CE21" s="33"/>
+      <c r="CF21" s="33"/>
+      <c r="CG21" s="33"/>
+      <c r="CH21" s="33"/>
+      <c r="CI21" s="33"/>
+      <c r="CJ21" s="33"/>
+      <c r="CK21" s="33"/>
+      <c r="CL21" s="33"/>
+      <c r="CM21" s="33"/>
+      <c r="CN21" s="33"/>
+      <c r="CO21" s="33"/>
+      <c r="CP21" s="33"/>
+      <c r="CQ21" s="33"/>
+      <c r="CR21" s="33"/>
+      <c r="CS21" s="33"/>
+      <c r="CT21" s="33"/>
+      <c r="CU21" s="33"/>
+      <c r="CV21" s="33"/>
+      <c r="CW21" s="33"/>
+      <c r="CX21" s="33"/>
+      <c r="CY21" s="33"/>
+      <c r="CZ21" s="33"/>
+      <c r="DA21" s="33"/>
+      <c r="DB21" s="33"/>
+      <c r="DC21" s="33"/>
+      <c r="DD21" s="33"/>
+      <c r="DE21" s="33"/>
+      <c r="DF21" s="33"/>
+      <c r="DG21" s="33"/>
+      <c r="DH21" s="33"/>
+      <c r="DI21" s="33"/>
+      <c r="DJ21" s="33"/>
+      <c r="DK21" s="33"/>
+      <c r="DL21" s="33"/>
+      <c r="DM21" s="33"/>
+      <c r="DN21" s="33"/>
+      <c r="DO21" s="33"/>
+      <c r="DP21" s="33"/>
+      <c r="DQ21" s="33"/>
+      <c r="DR21" s="33"/>
+      <c r="DS21" s="33"/>
+      <c r="DT21" s="33"/>
+      <c r="DU21" s="33"/>
+      <c r="DV21" s="33"/>
+      <c r="DW21" s="33"/>
+      <c r="DX21" s="33"/>
+      <c r="DY21" s="33"/>
+      <c r="DZ21" s="33"/>
+      <c r="EA21" s="33"/>
+      <c r="EB21" s="33"/>
+      <c r="EC21" s="33"/>
+      <c r="ED21" s="33"/>
+      <c r="EE21" s="33"/>
+      <c r="EF21" s="33"/>
+      <c r="EG21" s="33"/>
+      <c r="EH21" s="33"/>
+      <c r="EI21" s="33"/>
+      <c r="EJ21" s="33"/>
+      <c r="EK21" s="33"/>
+      <c r="EL21" s="33"/>
+      <c r="EM21" s="33"/>
+      <c r="EN21" s="33"/>
+      <c r="EO21" s="33"/>
+      <c r="EP21" s="33"/>
+      <c r="EQ21" s="33"/>
+      <c r="ER21" s="33"/>
+      <c r="ES21" s="33"/>
+      <c r="ET21" s="33"/>
+      <c r="EU21" s="33"/>
+      <c r="EV21" s="33"/>
+      <c r="EW21" s="33"/>
+      <c r="EX21" s="33"/>
+      <c r="EY21" s="33"/>
+      <c r="EZ21" s="33"/>
+      <c r="FA21" s="33"/>
+      <c r="FB21" s="33"/>
+      <c r="FC21" s="33"/>
+      <c r="FD21" s="33"/>
+      <c r="FE21" s="33"/>
+      <c r="FF21" s="33"/>
+      <c r="FG21" s="33"/>
+      <c r="FH21" s="33"/>
+      <c r="FI21" s="33"/>
+      <c r="FJ21" s="33"/>
+      <c r="FK21" s="33"/>
+      <c r="FL21" s="33"/>
+      <c r="FM21" s="33"/>
+      <c r="FN21" s="33"/>
+      <c r="FO21" s="33"/>
+      <c r="FP21" s="33"/>
+      <c r="FQ21" s="33"/>
+      <c r="FR21" s="33"/>
+      <c r="FS21" s="33"/>
+      <c r="FT21" s="33"/>
+      <c r="FU21" s="33"/>
+      <c r="FV21" s="33"/>
+      <c r="FW21" s="33"/>
+      <c r="FX21" s="33"/>
+      <c r="FY21" s="33"/>
+      <c r="FZ21" s="33"/>
+      <c r="GA21" s="33"/>
+      <c r="GB21" s="33"/>
+      <c r="GC21" s="33"/>
+      <c r="GD21" s="33"/>
+      <c r="GE21" s="33"/>
+      <c r="GF21" s="33"/>
+      <c r="GG21" s="33"/>
+      <c r="GH21" s="33"/>
+      <c r="GI21" s="33"/>
+      <c r="GJ21" s="33"/>
+      <c r="GK21" s="33"/>
+      <c r="GL21" s="33"/>
+      <c r="GM21" s="33"/>
+      <c r="GN21" s="33"/>
+      <c r="GO21" s="33"/>
+      <c r="GP21" s="33"/>
+      <c r="GQ21" s="33"/>
+      <c r="GR21" s="33"/>
+      <c r="GS21" s="33"/>
+      <c r="GT21" s="33"/>
+      <c r="GU21" s="33"/>
+      <c r="GV21" s="33"/>
+      <c r="GW21" s="33"/>
+      <c r="GX21" s="33"/>
+      <c r="GY21" s="33"/>
+      <c r="GZ21" s="33"/>
+      <c r="HA21" s="33"/>
+      <c r="HB21" s="33"/>
+      <c r="HC21" s="33"/>
+      <c r="HD21" s="33"/>
+      <c r="HE21" s="33"/>
+      <c r="HF21" s="33"/>
+      <c r="HG21" s="33"/>
+      <c r="HH21" s="33"/>
+      <c r="HI21" s="33"/>
+      <c r="HJ21" s="33"/>
+      <c r="HK21" s="33"/>
+      <c r="HL21" s="33"/>
+      <c r="HM21" s="33"/>
+      <c r="HN21" s="33"/>
+      <c r="HO21" s="33"/>
+      <c r="HP21" s="33"/>
+      <c r="HQ21" s="33"/>
+      <c r="HR21" s="33"/>
+      <c r="HS21" s="33"/>
+      <c r="HT21" s="33"/>
+      <c r="HU21" s="33"/>
+      <c r="HV21" s="33"/>
+      <c r="HW21" s="33"/>
+      <c r="HX21" s="33"/>
+      <c r="HY21" s="33"/>
+      <c r="HZ21" s="33"/>
+      <c r="IA21" s="33"/>
+      <c r="IB21" s="33"/>
+      <c r="IC21" s="33"/>
+      <c r="ID21" s="33"/>
+      <c r="IE21" s="33"/>
+      <c r="IF21" s="33"/>
+      <c r="IG21" s="33"/>
+      <c r="IH21" s="33"/>
+      <c r="II21" s="33"/>
+      <c r="IJ21" s="33"/>
+      <c r="IK21" s="33"/>
+      <c r="IL21" s="33"/>
+      <c r="IM21" s="33"/>
+      <c r="IN21" s="33"/>
+      <c r="IO21" s="33"/>
+      <c r="IP21" s="33"/>
+      <c r="IQ21" s="33"/>
+      <c r="IR21" s="33"/>
+      <c r="IS21" s="33"/>
+      <c r="IT21" s="33"/>
+      <c r="IU21" s="33"/>
+      <c r="IV21" s="33"/>
+      <c r="IW21" s="33"/>
+      <c r="IX21" s="33"/>
+      <c r="IY21" s="33"/>
+      <c r="IZ21" s="33"/>
+      <c r="JA21" s="33"/>
+      <c r="JB21" s="33"/>
+      <c r="JC21" s="33"/>
+      <c r="JD21" s="33"/>
+      <c r="JE21" s="33"/>
+      <c r="JF21" s="33"/>
+      <c r="JG21" s="33"/>
+      <c r="JH21" s="33"/>
+      <c r="JI21" s="33"/>
+      <c r="JJ21" s="33"/>
+      <c r="JK21" s="33"/>
+      <c r="JL21" s="33"/>
+      <c r="JM21" s="33"/>
+      <c r="JN21" s="33"/>
     </row>
-    <row r="21" s="37" customFormat="1" ht="25.5">
-      <c r="A21" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="E21" s="29" t="s">
+    <row r="22" s="34" customFormat="1" ht="42.75">
+      <c r="A22" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F21" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29" t="s">
+      <c r="G22" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H22" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="I21" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="J21" s="35"/>
-      <c r="K21" s="29">
-        <v>2025</v>
-      </c>
-      <c r="L21" s="29" t="s">
+      <c r="I22" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="J22" s="35" t="s">
         <v>176</v>
       </c>
-      <c r="M21" s="29"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="37"/>
-      <c r="S21" s="37"/>
-      <c r="T21" s="37"/>
-      <c r="U21" s="37"/>
-      <c r="V21" s="37"/>
-      <c r="W21" s="37"/>
-      <c r="X21" s="37"/>
-      <c r="Y21" s="37"/>
-      <c r="Z21" s="37"/>
-      <c r="AA21" s="37"/>
-      <c r="AB21" s="37"/>
-      <c r="AC21" s="37"/>
-      <c r="AD21" s="37"/>
-      <c r="AE21" s="37"/>
-      <c r="AF21" s="37"/>
-      <c r="AG21" s="37"/>
-      <c r="AH21" s="37"/>
-      <c r="AI21" s="37"/>
-      <c r="AJ21" s="37"/>
-      <c r="AK21" s="37"/>
-      <c r="AL21" s="37"/>
-      <c r="AM21" s="37"/>
-      <c r="AN21" s="37"/>
-      <c r="AO21" s="37"/>
-      <c r="AP21" s="37"/>
-      <c r="AQ21" s="37"/>
-      <c r="AR21" s="37"/>
-      <c r="AS21" s="37"/>
-      <c r="AT21" s="37"/>
-      <c r="AU21" s="37"/>
-      <c r="AV21" s="37"/>
-      <c r="AW21" s="37"/>
-      <c r="AX21" s="37"/>
-      <c r="AY21" s="37"/>
-      <c r="AZ21" s="37"/>
-      <c r="BA21" s="37"/>
-      <c r="BB21" s="37"/>
-      <c r="BC21" s="37"/>
-      <c r="BD21" s="37"/>
-      <c r="BE21" s="37"/>
-      <c r="BF21" s="37"/>
-      <c r="BG21" s="37"/>
-      <c r="BH21" s="37"/>
-      <c r="BI21" s="37"/>
-      <c r="BJ21" s="37"/>
-      <c r="BK21" s="37"/>
-      <c r="BL21" s="37"/>
-      <c r="BM21" s="37"/>
-      <c r="BN21" s="37"/>
-      <c r="BO21" s="37"/>
-      <c r="BP21" s="37"/>
-      <c r="BQ21" s="37"/>
-      <c r="BR21" s="37"/>
-      <c r="BS21" s="37"/>
-      <c r="BT21" s="37"/>
-      <c r="BU21" s="37"/>
-      <c r="BV21" s="37"/>
-      <c r="BW21" s="37"/>
-      <c r="BX21" s="37"/>
-      <c r="BY21" s="37"/>
-      <c r="BZ21" s="37"/>
-      <c r="CA21" s="37"/>
-      <c r="CB21" s="37"/>
-      <c r="CC21" s="37"/>
-      <c r="CD21" s="37"/>
-      <c r="CE21" s="37"/>
-      <c r="CF21" s="37"/>
-      <c r="CG21" s="37"/>
-      <c r="CH21" s="37"/>
-      <c r="CI21" s="37"/>
-      <c r="CJ21" s="37"/>
-      <c r="CK21" s="37"/>
-      <c r="CL21" s="37"/>
-      <c r="CM21" s="37"/>
-      <c r="CN21" s="37"/>
-      <c r="CO21" s="37"/>
-      <c r="CP21" s="37"/>
-      <c r="CQ21" s="37"/>
-      <c r="CR21" s="37"/>
-      <c r="CS21" s="37"/>
-      <c r="CT21" s="37"/>
-      <c r="CU21" s="37"/>
-      <c r="CV21" s="37"/>
-      <c r="CW21" s="37"/>
-      <c r="CX21" s="37"/>
-      <c r="CY21" s="37"/>
-      <c r="CZ21" s="37"/>
-      <c r="DA21" s="37"/>
-      <c r="DB21" s="37"/>
-      <c r="DC21" s="37"/>
-      <c r="DD21" s="37"/>
-      <c r="DE21" s="37"/>
-      <c r="DF21" s="37"/>
-      <c r="DG21" s="37"/>
-      <c r="DH21" s="37"/>
-      <c r="DI21" s="37"/>
-      <c r="DJ21" s="37"/>
-      <c r="DK21" s="37"/>
-      <c r="DL21" s="37"/>
-      <c r="DM21" s="37"/>
-      <c r="DN21" s="37"/>
-      <c r="DO21" s="37"/>
-      <c r="DP21" s="37"/>
-      <c r="DQ21" s="37"/>
-      <c r="DR21" s="37"/>
-      <c r="DS21" s="37"/>
-      <c r="DT21" s="37"/>
-      <c r="DU21" s="37"/>
-      <c r="DV21" s="37"/>
-      <c r="DW21" s="37"/>
-      <c r="DX21" s="37"/>
-      <c r="DY21" s="37"/>
-      <c r="DZ21" s="37"/>
-      <c r="EA21" s="37"/>
-      <c r="EB21" s="37"/>
-      <c r="EC21" s="37"/>
-      <c r="ED21" s="37"/>
-      <c r="EE21" s="37"/>
-      <c r="EF21" s="37"/>
-      <c r="EG21" s="37"/>
-      <c r="EH21" s="37"/>
-      <c r="EI21" s="37"/>
-      <c r="EJ21" s="37"/>
-      <c r="EK21" s="37"/>
-      <c r="EL21" s="37"/>
-      <c r="EM21" s="37"/>
-      <c r="EN21" s="37"/>
-      <c r="EO21" s="37"/>
-      <c r="EP21" s="37"/>
-      <c r="EQ21" s="37"/>
-      <c r="ER21" s="37"/>
-      <c r="ES21" s="37"/>
-      <c r="ET21" s="37"/>
-      <c r="EU21" s="37"/>
-      <c r="EV21" s="37"/>
-      <c r="EW21" s="37"/>
-      <c r="EX21" s="37"/>
-      <c r="EY21" s="37"/>
-      <c r="EZ21" s="37"/>
-      <c r="FA21" s="37"/>
-      <c r="FB21" s="37"/>
-      <c r="FC21" s="37"/>
-      <c r="FD21" s="37"/>
-      <c r="FE21" s="37"/>
-      <c r="FF21" s="37"/>
-      <c r="FG21" s="37"/>
-      <c r="FH21" s="37"/>
-      <c r="FI21" s="37"/>
-      <c r="FJ21" s="37"/>
-      <c r="FK21" s="37"/>
-      <c r="FL21" s="37"/>
-      <c r="FM21" s="37"/>
-      <c r="FN21" s="37"/>
-      <c r="FO21" s="37"/>
-      <c r="FP21" s="37"/>
-      <c r="FQ21" s="37"/>
-      <c r="FR21" s="37"/>
-      <c r="FS21" s="37"/>
-      <c r="FT21" s="37"/>
-      <c r="FU21" s="37"/>
-      <c r="FV21" s="37"/>
-      <c r="FW21" s="37"/>
-      <c r="FX21" s="37"/>
-      <c r="FY21" s="37"/>
-      <c r="FZ21" s="37"/>
-      <c r="GA21" s="37"/>
-      <c r="GB21" s="37"/>
-      <c r="GC21" s="37"/>
-      <c r="GD21" s="37"/>
-      <c r="GE21" s="37"/>
-      <c r="GF21" s="37"/>
-      <c r="GG21" s="37"/>
-      <c r="GH21" s="37"/>
-      <c r="GI21" s="37"/>
-      <c r="GJ21" s="37"/>
-      <c r="GK21" s="37"/>
-      <c r="GL21" s="37"/>
-      <c r="GM21" s="37"/>
-      <c r="GN21" s="37"/>
-      <c r="GO21" s="37"/>
-      <c r="GP21" s="37"/>
-      <c r="GQ21" s="37"/>
-      <c r="GR21" s="37"/>
-      <c r="GS21" s="37"/>
-      <c r="GT21" s="37"/>
-      <c r="GU21" s="37"/>
-      <c r="GV21" s="37"/>
-      <c r="GW21" s="37"/>
-      <c r="GX21" s="37"/>
-      <c r="GY21" s="37"/>
-      <c r="GZ21" s="37"/>
-      <c r="HA21" s="37"/>
-      <c r="HB21" s="37"/>
-      <c r="HC21" s="37"/>
-      <c r="HD21" s="37"/>
-      <c r="HE21" s="37"/>
-      <c r="HF21" s="37"/>
-      <c r="HG21" s="37"/>
-      <c r="HH21" s="37"/>
-      <c r="HI21" s="37"/>
-      <c r="HJ21" s="37"/>
-      <c r="HK21" s="37"/>
-      <c r="HL21" s="37"/>
-      <c r="HM21" s="37"/>
-      <c r="HN21" s="37"/>
-      <c r="HO21" s="37"/>
-      <c r="HP21" s="37"/>
-      <c r="HQ21" s="37"/>
-      <c r="HR21" s="37"/>
-      <c r="HS21" s="37"/>
-      <c r="HT21" s="37"/>
-      <c r="HU21" s="37"/>
-      <c r="HV21" s="37"/>
-      <c r="HW21" s="37"/>
-      <c r="HX21" s="37"/>
-      <c r="HY21" s="37"/>
-      <c r="HZ21" s="37"/>
-      <c r="IA21" s="37"/>
-      <c r="IB21" s="37"/>
-      <c r="IC21" s="37"/>
-      <c r="ID21" s="37"/>
-      <c r="IE21" s="37"/>
-      <c r="IF21" s="37"/>
-      <c r="IG21" s="37"/>
-      <c r="IH21" s="37"/>
-      <c r="II21" s="37"/>
-      <c r="IJ21" s="37"/>
-      <c r="IK21" s="37"/>
-      <c r="IL21" s="37"/>
-      <c r="IM21" s="37"/>
-      <c r="IN21" s="37"/>
-      <c r="IO21" s="37"/>
-      <c r="IP21" s="37"/>
-      <c r="IQ21" s="37"/>
-      <c r="IR21" s="37"/>
-      <c r="IS21" s="37"/>
-      <c r="IT21" s="37"/>
-      <c r="IU21" s="37"/>
-      <c r="IV21" s="37"/>
-      <c r="IW21" s="37"/>
-      <c r="IX21" s="37"/>
-      <c r="IY21" s="37"/>
-      <c r="IZ21" s="37"/>
-      <c r="JA21" s="37"/>
-      <c r="JB21" s="37"/>
-      <c r="JC21" s="37"/>
-      <c r="JD21" s="37"/>
-      <c r="JE21" s="37"/>
-      <c r="JF21" s="37"/>
-      <c r="JG21" s="37"/>
-      <c r="JH21" s="37"/>
-      <c r="JI21" s="37"/>
-      <c r="JJ21" s="37"/>
-      <c r="JK21" s="37"/>
-      <c r="JL21" s="37"/>
-      <c r="JM21" s="37"/>
-      <c r="JN21" s="37"/>
-    </row>
-    <row r="22" ht="42.75">
-      <c r="A22" s="39" t="s">
+      <c r="K22" s="7">
+        <v>2026</v>
+      </c>
+      <c r="L22" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B22" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" s="39" t="s">
+      <c r="M22" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E22" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="F22" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="H22" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="J22" s="39" t="s">
-        <v>182</v>
-      </c>
-      <c r="K22" s="42">
-        <v>2010</v>
-      </c>
-      <c r="L22" s="42" t="s">
-        <v>183</v>
-      </c>
-      <c r="M22" s="39"/>
-      <c r="N22" s="43" t="s">
-        <v>184</v>
-      </c>
+      <c r="N22" s="10"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="34"/>
+      <c r="Z22" s="34"/>
+      <c r="AA22" s="34"/>
+      <c r="AB22" s="34"/>
+      <c r="AC22" s="34"/>
+      <c r="AD22" s="34"/>
+      <c r="AE22" s="34"/>
+      <c r="AF22" s="34"/>
+      <c r="AG22" s="34"/>
+      <c r="AH22" s="34"/>
+      <c r="AI22" s="34"/>
+      <c r="AJ22" s="34"/>
+      <c r="AK22" s="34"/>
+      <c r="AL22" s="34"/>
+      <c r="AM22" s="34"/>
+      <c r="AN22" s="34"/>
+      <c r="AO22" s="34"/>
+      <c r="AP22" s="34"/>
+      <c r="AQ22" s="34"/>
+      <c r="AR22" s="34"/>
+      <c r="AS22" s="34"/>
+      <c r="AT22" s="34"/>
+      <c r="AU22" s="34"/>
+      <c r="AV22" s="34"/>
+      <c r="AW22" s="34"/>
+      <c r="AX22" s="34"/>
+      <c r="AY22" s="34"/>
+      <c r="AZ22" s="34"/>
+      <c r="BA22" s="34"/>
+      <c r="BB22" s="34"/>
+      <c r="BC22" s="34"/>
+      <c r="BD22" s="34"/>
+      <c r="BE22" s="34"/>
+      <c r="BF22" s="34"/>
+      <c r="BG22" s="34"/>
+      <c r="BH22" s="34"/>
+      <c r="BI22" s="34"/>
+      <c r="BJ22" s="34"/>
+      <c r="BK22" s="34"/>
+      <c r="BL22" s="34"/>
+      <c r="BM22" s="34"/>
+      <c r="BN22" s="34"/>
+      <c r="BO22" s="34"/>
+      <c r="BP22" s="34"/>
+      <c r="BQ22" s="34"/>
+      <c r="BR22" s="34"/>
+      <c r="BS22" s="34"/>
+      <c r="BT22" s="34"/>
+      <c r="BU22" s="34"/>
+      <c r="BV22" s="34"/>
+      <c r="BW22" s="34"/>
     </row>
     <row r="23" s="16" customFormat="1" ht="25.5">
-      <c r="A23" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="D23" s="39" t="s">
+      <c r="A23" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B23" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="E23" s="42" t="s">
+      <c r="C23" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="F23" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="44" t="s">
+      <c r="D23" s="36" t="s">
         <v>187</v>
       </c>
-      <c r="J23" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="K23" s="42">
-        <v>2010</v>
-      </c>
-      <c r="L23" s="42" t="s">
-        <v>183</v>
-      </c>
-      <c r="M23" s="39"/>
-      <c r="N23" s="45" t="s">
+      <c r="E23" s="36" t="s">
         <v>188</v>
       </c>
+      <c r="F23" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="37" t="s">
+        <v>190</v>
+      </c>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="38" t="s">
+        <v>191</v>
+      </c>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Y23"/>
+      <c r="Z23"/>
+      <c r="AA23"/>
+      <c r="AB23"/>
+      <c r="AC23"/>
+      <c r="AD23"/>
+      <c r="AE23"/>
+      <c r="AF23"/>
+      <c r="AG23"/>
+      <c r="AH23"/>
+      <c r="AI23"/>
+      <c r="AJ23"/>
+      <c r="AK23"/>
+      <c r="AL23"/>
+      <c r="AM23"/>
+      <c r="AN23"/>
+      <c r="AO23"/>
+      <c r="AP23"/>
+      <c r="AQ23"/>
+      <c r="AR23"/>
+      <c r="AS23"/>
+      <c r="AT23"/>
+      <c r="AU23"/>
+      <c r="AV23"/>
+      <c r="AW23"/>
+      <c r="AX23"/>
+      <c r="AY23"/>
+      <c r="AZ23"/>
+      <c r="BA23"/>
+      <c r="BB23"/>
+      <c r="BC23"/>
+      <c r="BD23"/>
+      <c r="BE23"/>
+      <c r="BF23"/>
+      <c r="BG23"/>
+      <c r="BH23"/>
+      <c r="BI23"/>
+      <c r="BJ23"/>
+      <c r="BK23"/>
+      <c r="BL23"/>
+      <c r="BM23"/>
+      <c r="BN23"/>
+      <c r="BO23"/>
+      <c r="BP23"/>
+      <c r="BQ23"/>
+      <c r="BR23"/>
+      <c r="BS23"/>
+      <c r="BT23"/>
+      <c r="BU23"/>
+      <c r="BV23"/>
+      <c r="BW23"/>
     </row>
-    <row r="24" ht="28.5">
-      <c r="A24" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>189</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>189</v>
-      </c>
-      <c r="F24" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="46" t="s">
+    <row r="24" ht="25.5">
+      <c r="A24" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="I24" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="J24" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="K24" s="42">
-        <v>2010</v>
-      </c>
-      <c r="L24" s="42" t="s">
-        <v>183</v>
-      </c>
-      <c r="M24" s="39"/>
-      <c r="N24" s="43" t="s">
-        <v>184</v>
-      </c>
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
     </row>
     <row r="25" ht="25.5">
-      <c r="A25" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="B25" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>192</v>
-      </c>
-      <c r="D25" s="47" t="s">
-        <v>193</v>
-      </c>
-      <c r="E25" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="F25" s="48" t="s">
+      <c r="A25" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="F25" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47">
-        <v>2016</v>
-      </c>
-      <c r="L25" s="47" t="s">
-        <v>197</v>
-      </c>
-      <c r="M25" s="47"/>
-      <c r="N25" s="25"/>
+      <c r="G25" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="H25" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
     </row>
     <row r="26" ht="25.5">
-      <c r="A26" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="B26" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>192</v>
-      </c>
-      <c r="D26" s="47" t="s">
-        <v>198</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="F26" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="25"/>
+      <c r="A26" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>205</v>
+      </c>
+      <c r="F26" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="G26" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="H26" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="J26" s="36"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
     </row>
     <row r="27" ht="25.5">
-      <c r="A27" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="B27" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" s="47" t="s">
-        <v>201</v>
-      </c>
-      <c r="E27" s="47" t="s">
+      <c r="A27" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="F27" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="G27" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="H27" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="I27" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="J27" s="36"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="J27" s="52"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="25"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
     </row>
-    <row r="28" ht="38.25">
-      <c r="A28" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="B28" s="47" t="s">
+    <row r="28" ht="42.75">
+      <c r="A28" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B28" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="F28" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="G28" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="H28" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="J28" s="36"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+    </row>
+    <row r="29" ht="28.5">
+      <c r="A29" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="F29" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="G29" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="H29" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="J29" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="K29" s="38">
+        <v>2010</v>
+      </c>
+      <c r="L29" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="M29" s="36"/>
+      <c r="N29" s="41" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" ht="38.25">
+      <c r="A30" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="F30" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="J30" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="K30" s="38">
+        <v>2010</v>
+      </c>
+      <c r="L30" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="M30" s="36"/>
+      <c r="N30" s="41" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="31" s="10" customFormat="1" ht="38.25">
+      <c r="A31" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="E31" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="F31" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="J31" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="K31" s="38">
+        <v>2010</v>
+      </c>
+      <c r="L31" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="M31" s="36"/>
+      <c r="N31" s="44" t="s">
+        <v>231</v>
+      </c>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10"/>
+      <c r="V31" s="10"/>
+      <c r="W31" s="10"/>
+      <c r="X31" s="10"/>
+      <c r="Y31" s="10"/>
+      <c r="Z31" s="10"/>
+      <c r="AA31" s="10"/>
+      <c r="AB31" s="10"/>
+      <c r="AC31" s="10"/>
+      <c r="AD31" s="10"/>
+      <c r="AE31" s="10"/>
+      <c r="AF31" s="10"/>
+      <c r="AG31" s="10"/>
+      <c r="AH31" s="10"/>
+      <c r="AI31" s="10"/>
+      <c r="AJ31" s="10"/>
+      <c r="AK31" s="10"/>
+      <c r="AL31" s="10"/>
+      <c r="AM31" s="10"/>
+      <c r="AN31" s="10"/>
+      <c r="AO31" s="10"/>
+      <c r="AP31" s="10"/>
+      <c r="AQ31" s="10"/>
+      <c r="AR31" s="10"/>
+      <c r="AS31" s="10"/>
+      <c r="AT31" s="10"/>
+      <c r="AU31" s="10"/>
+      <c r="AV31" s="10"/>
+      <c r="AW31" s="10"/>
+      <c r="AX31" s="10"/>
+      <c r="AY31" s="10"/>
+      <c r="AZ31" s="10"/>
+      <c r="BA31" s="10"/>
+      <c r="BB31" s="10"/>
+      <c r="BC31" s="10"/>
+      <c r="BD31" s="10"/>
+      <c r="BE31" s="10"/>
+      <c r="BF31" s="10"/>
+      <c r="BG31" s="10"/>
+      <c r="BH31" s="10"/>
+      <c r="BI31" s="10"/>
+      <c r="BJ31" s="10"/>
+      <c r="BK31" s="10"/>
+      <c r="BL31" s="10"/>
+      <c r="BM31" s="10"/>
+      <c r="BN31" s="10"/>
+      <c r="BO31" s="10"/>
+      <c r="BP31" s="10"/>
+      <c r="BQ31" s="10"/>
+      <c r="BR31" s="10"/>
+      <c r="BS31" s="10"/>
+      <c r="BT31" s="10"/>
+      <c r="BU31" s="10"/>
+      <c r="BV31" s="10"/>
+      <c r="BW31" s="10"/>
+    </row>
+    <row r="32" ht="51">
+      <c r="A32" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>232</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="F32" s="39" t="s">
+        <v>235</v>
+      </c>
+      <c r="G32" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="H32" s="36"/>
+      <c r="I32" s="46" t="s">
+        <v>237</v>
+      </c>
+      <c r="J32" s="47"/>
+      <c r="K32" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="L32" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="M32" s="36"/>
+      <c r="N32" s="34" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" s="26" customFormat="1" ht="42.75">
+      <c r="A33" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="F33" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="G33" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="H33" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="I33" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="J33" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="K33" s="36">
+        <v>2020</v>
+      </c>
+      <c r="L33" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="M33" s="36"/>
+      <c r="N33" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
+      <c r="S33" s="26"/>
+      <c r="T33" s="26"/>
+      <c r="U33" s="26"/>
+      <c r="V33" s="26"/>
+      <c r="W33" s="26"/>
+      <c r="X33" s="26"/>
+      <c r="Y33" s="26"/>
+      <c r="Z33" s="26"/>
+      <c r="AA33" s="26"/>
+      <c r="AB33" s="26"/>
+      <c r="AC33" s="26"/>
+      <c r="AD33" s="26"/>
+      <c r="AE33" s="26"/>
+      <c r="AF33" s="26"/>
+      <c r="AG33" s="26"/>
+      <c r="AH33" s="26"/>
+      <c r="AI33" s="26"/>
+      <c r="AJ33" s="26"/>
+      <c r="AK33" s="26"/>
+      <c r="AL33" s="26"/>
+      <c r="AM33" s="26"/>
+      <c r="AN33" s="26"/>
+      <c r="AO33" s="26"/>
+      <c r="AP33" s="26"/>
+      <c r="AQ33" s="26"/>
+      <c r="AR33" s="26"/>
+      <c r="AS33" s="26"/>
+      <c r="AT33" s="26"/>
+      <c r="AU33" s="26"/>
+      <c r="AV33" s="26"/>
+      <c r="AW33" s="26"/>
+      <c r="AX33" s="26"/>
+      <c r="AY33" s="26"/>
+      <c r="AZ33" s="26"/>
+      <c r="BA33" s="26"/>
+      <c r="BB33" s="26"/>
+      <c r="BC33" s="26"/>
+      <c r="BD33" s="26"/>
+      <c r="BE33" s="26"/>
+      <c r="BF33" s="26"/>
+      <c r="BG33" s="26"/>
+      <c r="BH33" s="26"/>
+      <c r="BI33" s="26"/>
+      <c r="BJ33" s="26"/>
+      <c r="BK33" s="26"/>
+      <c r="BL33" s="26"/>
+      <c r="BM33" s="26"/>
+      <c r="BN33" s="26"/>
+      <c r="BO33" s="26"/>
+      <c r="BP33" s="26"/>
+      <c r="BQ33" s="26"/>
+      <c r="BR33" s="26"/>
+      <c r="BS33" s="26"/>
+      <c r="BT33" s="26"/>
+      <c r="BU33" s="26"/>
+      <c r="BV33" s="26"/>
+      <c r="BW33" s="26"/>
+    </row>
+    <row r="34" ht="38.25">
+      <c r="A34" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="E34" s="49"/>
+      <c r="F34" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="G34" s="50" t="s">
+        <v>253</v>
+      </c>
+      <c r="H34" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="52" t="s">
+        <v>254</v>
+      </c>
+      <c r="J34" s="51" t="s">
+        <v>255</v>
+      </c>
+      <c r="K34" s="51"/>
+      <c r="L34" s="51"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="34"/>
+    </row>
+    <row r="35" s="34" customFormat="1" ht="76.5">
+      <c r="A35" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B35" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>257</v>
+      </c>
+      <c r="D35" s="54" t="s">
+        <v>258</v>
+      </c>
+      <c r="E35" s="55" t="s">
+        <v>259</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>260</v>
+      </c>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="56" t="s">
+        <v>261</v>
+      </c>
+      <c r="J35" s="54" t="s">
+        <v>262</v>
+      </c>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="N35" s="54"/>
+      <c r="O35" s="34"/>
+      <c r="P35" s="34"/>
+      <c r="Q35" s="34"/>
+      <c r="R35" s="34"/>
+      <c r="S35" s="34"/>
+      <c r="T35" s="34"/>
+      <c r="U35" s="34"/>
+      <c r="V35" s="34"/>
+      <c r="W35" s="34"/>
+      <c r="X35" s="34"/>
+      <c r="Y35" s="34"/>
+      <c r="Z35" s="34"/>
+      <c r="AA35" s="34"/>
+      <c r="AB35" s="34"/>
+      <c r="AC35" s="34"/>
+      <c r="AD35" s="34"/>
+      <c r="AE35" s="34"/>
+      <c r="AF35" s="34"/>
+      <c r="AG35" s="34"/>
+      <c r="AH35" s="34"/>
+      <c r="AI35" s="34"/>
+      <c r="AJ35" s="34"/>
+      <c r="AK35" s="34"/>
+      <c r="AL35" s="34"/>
+      <c r="AM35" s="34"/>
+      <c r="AN35" s="34"/>
+      <c r="AO35" s="34"/>
+      <c r="AP35" s="34"/>
+      <c r="AQ35" s="34"/>
+      <c r="AR35" s="34"/>
+      <c r="AS35" s="34"/>
+      <c r="AT35" s="34"/>
+      <c r="AU35" s="34"/>
+      <c r="AV35" s="34"/>
+      <c r="AW35" s="34"/>
+      <c r="AX35" s="34"/>
+      <c r="AY35" s="34"/>
+      <c r="AZ35" s="34"/>
+      <c r="BA35" s="34"/>
+      <c r="BB35" s="34"/>
+      <c r="BC35" s="34"/>
+      <c r="BD35" s="34"/>
+      <c r="BE35" s="34"/>
+      <c r="BF35" s="34"/>
+      <c r="BG35" s="34"/>
+      <c r="BH35" s="34"/>
+      <c r="BI35" s="34"/>
+      <c r="BJ35" s="34"/>
+      <c r="BK35" s="34"/>
+      <c r="BL35" s="34"/>
+      <c r="BM35" s="34"/>
+      <c r="BN35" s="34"/>
+      <c r="BO35" s="34"/>
+      <c r="BP35" s="34"/>
+      <c r="BQ35" s="34"/>
+      <c r="BR35" s="34"/>
+      <c r="BS35" s="34"/>
+      <c r="BT35" s="34"/>
+      <c r="BU35" s="34"/>
+      <c r="BV35" s="34"/>
+      <c r="BW35" s="34"/>
+    </row>
+    <row r="36" ht="51">
+      <c r="A36" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B36" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="C36" s="54" t="s">
+        <v>186</v>
+      </c>
+      <c r="D36" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="E36" s="54" t="s">
+        <v>265</v>
+      </c>
+      <c r="F36" s="54" t="s">
+        <v>266</v>
+      </c>
+      <c r="G36" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="H36" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="56" t="s">
+        <v>268</v>
+      </c>
+      <c r="J36" s="54" t="s">
+        <v>269</v>
+      </c>
+      <c r="K36" s="54"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="54"/>
+      <c r="N36" s="54"/>
+    </row>
+    <row r="37" ht="38.25">
+      <c r="A37" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B37" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="D37" s="54" t="s">
+        <v>271</v>
+      </c>
+      <c r="E37" s="54"/>
+      <c r="F37" s="55" t="s">
+        <v>272</v>
+      </c>
+      <c r="G37" s="54"/>
+      <c r="H37" s="54"/>
+      <c r="I37" s="56" t="s">
+        <v>273</v>
+      </c>
+      <c r="J37" s="54"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="54"/>
+      <c r="N37" s="54"/>
+    </row>
+    <row r="38" ht="25.5">
+      <c r="A38" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B38" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" s="54" t="s">
+        <v>208</v>
+      </c>
+      <c r="D38" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="E38" s="54" t="s">
+        <v>275</v>
+      </c>
+      <c r="F38" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="G38" s="26"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="58" t="s">
+        <v>277</v>
+      </c>
+      <c r="J38" s="54"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="54"/>
+      <c r="N38" s="54"/>
+    </row>
+    <row r="39" s="10" customFormat="1" ht="51">
+      <c r="A39" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B39" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="D39" s="54" t="s">
+        <v>279</v>
+      </c>
+      <c r="E39" s="54" t="s">
+        <v>280</v>
+      </c>
+      <c r="F39" s="59" t="s">
+        <v>281</v>
+      </c>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="56" t="s">
+        <v>282</v>
+      </c>
+      <c r="J39" s="54"/>
+      <c r="K39" s="54">
+        <v>2016</v>
+      </c>
+      <c r="L39" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="M39" s="54"/>
+      <c r="N39" s="26"/>
+      <c r="O39"/>
+      <c r="P39"/>
+      <c r="Q39"/>
+      <c r="R39"/>
+      <c r="S39"/>
+      <c r="T39"/>
+      <c r="U39"/>
+      <c r="V39"/>
+      <c r="W39"/>
+      <c r="X39"/>
+      <c r="Y39"/>
+      <c r="Z39"/>
+      <c r="AA39"/>
+      <c r="AB39"/>
+      <c r="AC39"/>
+      <c r="AD39"/>
+      <c r="AE39"/>
+      <c r="AF39"/>
+      <c r="AG39"/>
+      <c r="AH39"/>
+      <c r="AI39"/>
+      <c r="AJ39"/>
+      <c r="AK39"/>
+      <c r="AL39"/>
+      <c r="AM39"/>
+      <c r="AN39"/>
+      <c r="AO39"/>
+      <c r="AP39"/>
+      <c r="AQ39"/>
+      <c r="AR39"/>
+      <c r="AS39"/>
+      <c r="AT39"/>
+      <c r="AU39"/>
+      <c r="AV39"/>
+      <c r="AW39"/>
+      <c r="AX39"/>
+      <c r="AY39"/>
+      <c r="AZ39"/>
+      <c r="BA39"/>
+      <c r="BB39"/>
+      <c r="BC39"/>
+      <c r="BD39"/>
+      <c r="BE39"/>
+      <c r="BF39"/>
+      <c r="BG39"/>
+      <c r="BH39"/>
+      <c r="BI39"/>
+      <c r="BJ39"/>
+      <c r="BK39"/>
+      <c r="BL39"/>
+      <c r="BM39"/>
+      <c r="BN39"/>
+      <c r="BO39"/>
+      <c r="BP39"/>
+      <c r="BQ39"/>
+      <c r="BR39"/>
+      <c r="BS39"/>
+      <c r="BT39"/>
+      <c r="BU39"/>
+      <c r="BV39"/>
+      <c r="BW39"/>
+    </row>
+    <row r="40" ht="25.5">
+      <c r="A40" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B40" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="D40" s="54" t="s">
+        <v>284</v>
+      </c>
+      <c r="E40" s="54" t="s">
+        <v>280</v>
+      </c>
+      <c r="F40" s="59" t="s">
+        <v>285</v>
+      </c>
+      <c r="G40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="54"/>
+      <c r="L40" s="54"/>
+      <c r="M40" s="54"/>
+      <c r="N40" s="26"/>
+    </row>
+    <row r="41" ht="25.5">
+      <c r="A41" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B41" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C41" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="47" t="s">
-        <v>205</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="F28" s="53" t="s">
-        <v>207</v>
-      </c>
-      <c r="G28" s="47" t="s">
-        <v>208</v>
-      </c>
-      <c r="H28" s="47" t="s">
+      <c r="D41" s="54" t="s">
+        <v>286</v>
+      </c>
+      <c r="E41" s="54" t="s">
+        <v>287</v>
+      </c>
+      <c r="F41" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="G41" s="54" t="s">
+        <v>288</v>
+      </c>
+      <c r="H41" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="I28" s="54" t="s">
-        <v>209</v>
-      </c>
-      <c r="J28" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="M28" s="47"/>
-      <c r="N28" s="55" t="s">
-        <v>211</v>
+      <c r="I41" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J41" s="54" t="s">
+        <v>289</v>
+      </c>
+      <c r="K41" s="54" t="s">
+        <v>290</v>
+      </c>
+      <c r="L41" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="M41" s="54"/>
+      <c r="N41" s="63" t="s">
+        <v>291</v>
       </c>
     </row>
-    <row r="29" ht="89.25">
-      <c r="A29" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="B29" s="47" t="s">
+    <row r="42" s="10" customFormat="1" ht="25.5">
+      <c r="A42" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B42" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" s="47" t="s">
-        <v>212</v>
-      </c>
-      <c r="E29" s="47" t="s">
-        <v>213</v>
-      </c>
-      <c r="F29" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="47" t="s">
-        <v>214</v>
-      </c>
-      <c r="H29" s="47" t="s">
+      <c r="C42" s="54" t="s">
+        <v>292</v>
+      </c>
+      <c r="D42" s="54" t="s">
+        <v>293</v>
+      </c>
+      <c r="E42" s="54" t="s">
+        <v>294</v>
+      </c>
+      <c r="F42" s="55" t="s">
+        <v>295</v>
+      </c>
+      <c r="G42" s="54" t="s">
+        <v>296</v>
+      </c>
+      <c r="H42" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="54" t="s">
-        <v>85</v>
-      </c>
-      <c r="J29" s="47" t="s">
-        <v>215</v>
-      </c>
-      <c r="K29" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="L29" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="M29" s="47"/>
-      <c r="N29" s="55" t="s">
-        <v>211</v>
-      </c>
+      <c r="I42" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="J42" s="54" t="s">
+        <v>298</v>
+      </c>
+      <c r="K42" s="54"/>
+      <c r="L42" s="54" t="s">
+        <v>34</v>
+      </c>
+      <c r="M42" s="54"/>
+      <c r="N42" s="63" t="s">
+        <v>291</v>
+      </c>
+      <c r="O42" s="10"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="10"/>
+      <c r="T42" s="10"/>
+      <c r="U42" s="10"/>
+      <c r="V42" s="10"/>
+      <c r="W42" s="10"/>
+      <c r="X42" s="10"/>
+      <c r="Y42" s="10"/>
+      <c r="Z42" s="10"/>
+      <c r="AA42" s="10"/>
+      <c r="AB42" s="10"/>
+      <c r="AC42" s="10"/>
+      <c r="AD42" s="10"/>
+      <c r="AE42" s="10"/>
+      <c r="AF42" s="10"/>
+      <c r="AG42" s="10"/>
+      <c r="AH42" s="10"/>
+      <c r="AI42" s="10"/>
+      <c r="AJ42" s="10"/>
+      <c r="AK42" s="10"/>
+      <c r="AL42" s="10"/>
+      <c r="AM42" s="10"/>
+      <c r="AN42" s="10"/>
+      <c r="AO42" s="10"/>
+      <c r="AP42" s="10"/>
+      <c r="AQ42" s="10"/>
+      <c r="AR42" s="10"/>
+      <c r="AS42" s="10"/>
+      <c r="AT42" s="10"/>
+      <c r="AU42" s="10"/>
+      <c r="AV42" s="10"/>
+      <c r="AW42" s="10"/>
+      <c r="AX42" s="10"/>
+      <c r="AY42" s="10"/>
+      <c r="AZ42" s="10"/>
+      <c r="BA42" s="10"/>
+      <c r="BB42" s="10"/>
+      <c r="BC42" s="10"/>
+      <c r="BD42" s="10"/>
+      <c r="BE42" s="10"/>
+      <c r="BF42" s="10"/>
+      <c r="BG42" s="10"/>
+      <c r="BH42" s="10"/>
+      <c r="BI42" s="10"/>
+      <c r="BJ42" s="10"/>
+      <c r="BK42" s="10"/>
+      <c r="BL42" s="10"/>
+      <c r="BM42" s="10"/>
+      <c r="BN42" s="10"/>
+      <c r="BO42" s="10"/>
+      <c r="BP42" s="10"/>
+      <c r="BQ42" s="10"/>
+      <c r="BR42" s="10"/>
+      <c r="BS42" s="10"/>
+      <c r="BT42" s="10"/>
+      <c r="BU42" s="10"/>
+      <c r="BV42" s="10"/>
+      <c r="BW42" s="10"/>
     </row>
-    <row r="30" ht="25.5">
-      <c r="A30" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="B30" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="D30" s="56" t="s">
-        <v>217</v>
-      </c>
-      <c r="E30" s="56" t="s">
-        <v>218</v>
-      </c>
-      <c r="F30" s="57"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="58" t="s">
-        <v>219</v>
-      </c>
-      <c r="J30" s="59"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="56" t="s">
-        <v>220</v>
-      </c>
-      <c r="M30" s="56"/>
-      <c r="N30" s="60"/>
+    <row r="43" ht="89.25">
+      <c r="A43" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B43" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="D43" s="54" t="s">
+        <v>300</v>
+      </c>
+      <c r="E43" s="55" t="s">
+        <v>301</v>
+      </c>
+      <c r="F43" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="G43" s="54" t="s">
+        <v>302</v>
+      </c>
+      <c r="H43" s="54"/>
+      <c r="I43" s="64" t="s">
+        <v>303</v>
+      </c>
+      <c r="J43" s="54"/>
+      <c r="K43" s="54" t="s">
+        <v>304</v>
+      </c>
+      <c r="L43" s="54" t="s">
+        <v>305</v>
+      </c>
+      <c r="M43" s="54"/>
+      <c r="N43" s="65" t="s">
+        <v>306</v>
+      </c>
     </row>
-    <row r="31" ht="25.5">
-      <c r="A31" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="B31" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" s="56" t="s">
-        <v>221</v>
-      </c>
-      <c r="E31" s="56" t="s">
-        <v>218</v>
-      </c>
-      <c r="F31" s="57"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="58" t="s">
-        <v>222</v>
-      </c>
-      <c r="J31" s="56"/>
-      <c r="K31" s="56"/>
-      <c r="L31" s="56"/>
-      <c r="M31" s="56"/>
-      <c r="N31" s="60"/>
-    </row>
-    <row r="32" ht="25.5">
-      <c r="A32" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="B32" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" s="56" t="s">
-        <v>223</v>
-      </c>
-      <c r="E32" s="56" t="s">
-        <v>218</v>
-      </c>
-      <c r="F32" s="57"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="58" t="s">
-        <v>219</v>
-      </c>
-      <c r="J32" s="59"/>
-      <c r="K32" s="56"/>
-      <c r="L32" s="56" t="s">
-        <v>220</v>
-      </c>
-      <c r="M32" s="56"/>
-      <c r="N32" s="60"/>
-    </row>
-    <row r="33" ht="25.5">
-      <c r="A33" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="B33" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" s="56" t="s">
-        <v>224</v>
-      </c>
-      <c r="E33" s="56"/>
-      <c r="F33" s="57" t="s">
-        <v>225</v>
-      </c>
-      <c r="G33" s="56"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="61"/>
-      <c r="J33" s="56"/>
-      <c r="K33" s="56"/>
-      <c r="L33" s="56"/>
-      <c r="M33" s="56"/>
-      <c r="N33" s="60"/>
-    </row>
-    <row r="34" ht="25.5">
-      <c r="A34" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="B34" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" s="56" t="s">
-        <v>200</v>
-      </c>
-      <c r="D34" s="56" t="s">
-        <v>226</v>
-      </c>
-      <c r="E34" s="56" t="s">
-        <v>218</v>
-      </c>
-      <c r="F34" s="57"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="62"/>
-      <c r="J34" s="56"/>
-      <c r="K34" s="56"/>
-      <c r="L34" s="56"/>
-      <c r="M34" s="56"/>
-      <c r="N34" s="60"/>
-    </row>
-    <row r="35" ht="38.25">
-      <c r="A35" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="B35" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="56" t="s">
-        <v>200</v>
-      </c>
-      <c r="D35" s="56" t="s">
-        <v>227</v>
-      </c>
-      <c r="E35" s="56" t="s">
-        <v>218</v>
-      </c>
-      <c r="F35" s="57" t="s">
-        <v>228</v>
-      </c>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="58" t="s">
-        <v>229</v>
-      </c>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="56"/>
-      <c r="M35" s="56"/>
-      <c r="N35" s="60"/>
-    </row>
-    <row r="36" ht="38.25">
-      <c r="A36" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="B36" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="56" t="s">
-        <v>230</v>
-      </c>
-      <c r="D36" s="56" t="s">
-        <v>231</v>
-      </c>
-      <c r="E36" s="56" t="s">
-        <v>232</v>
-      </c>
-      <c r="F36" s="57" t="s">
-        <v>233</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="58" t="s">
-        <v>234</v>
-      </c>
-      <c r="J36" s="56"/>
-      <c r="K36" s="56"/>
-      <c r="L36" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="M36" s="56"/>
-      <c r="N36" s="60"/>
-    </row>
-    <row r="37" ht="14.25">
-      <c r="A37" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="B37" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37" s="56" t="s">
-        <v>235</v>
-      </c>
-      <c r="D37" s="56" t="s">
-        <v>236</v>
-      </c>
-      <c r="E37" s="56" t="s">
-        <v>218</v>
-      </c>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="63"/>
-      <c r="J37" s="56"/>
-      <c r="K37" s="56"/>
-      <c r="L37" s="56"/>
-      <c r="M37" s="56"/>
-      <c r="N37" s="56" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="38" ht="51">
-      <c r="A38" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="B38" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" s="56" t="s">
-        <v>235</v>
-      </c>
-      <c r="D38" s="56" t="s">
-        <v>238</v>
-      </c>
-      <c r="E38" s="56" t="s">
-        <v>218</v>
-      </c>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="63"/>
-      <c r="J38" s="56"/>
-      <c r="K38" s="56"/>
-      <c r="L38" s="56"/>
-      <c r="M38" s="56"/>
-      <c r="N38" s="56" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="39" ht="51">
-      <c r="A39" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="B39" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39" s="56" t="s">
-        <v>239</v>
-      </c>
-      <c r="D39" s="56" t="s">
-        <v>240</v>
-      </c>
-      <c r="E39" s="56" t="s">
-        <v>241</v>
-      </c>
-      <c r="F39" s="64" t="s">
-        <v>242</v>
-      </c>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="63"/>
-      <c r="J39" s="56"/>
-      <c r="K39" s="56"/>
-      <c r="L39" s="56"/>
-      <c r="M39" s="56"/>
-      <c r="N39" s="56" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="40" s="10" customFormat="1" ht="25.5">
-      <c r="A40" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="B40" s="56" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" s="56" t="s">
-        <v>243</v>
-      </c>
-      <c r="E40" s="56" t="s">
-        <v>218</v>
-      </c>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="63"/>
-      <c r="J40" s="56"/>
-      <c r="K40" s="56"/>
-      <c r="L40" s="56"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="56" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25">
-      <c r="A41" s="65" t="s">
-        <v>244</v>
-      </c>
-      <c r="B41" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="65" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41" s="65" t="s">
-        <v>245</v>
-      </c>
-      <c r="E41" s="65" t="s">
-        <v>246</v>
-      </c>
-      <c r="F41" s="65"/>
-      <c r="G41" s="65" t="s">
-        <v>247</v>
-      </c>
-      <c r="H41" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="I41" s="66"/>
-      <c r="J41" s="65"/>
-      <c r="K41" s="65"/>
-      <c r="L41" s="65"/>
-      <c r="M41" s="65" t="s">
-        <v>161</v>
-      </c>
-      <c r="N41" s="65"/>
-    </row>
-    <row r="42" ht="14.25">
-      <c r="A42" s="1"/>
-      <c r="M42" s="67"/>
-      <c r="N42" s="67"/>
-    </row>
-    <row r="43" ht="14.25">
-      <c r="M43" s="67"/>
-      <c r="N43" s="67"/>
-    </row>
-    <row r="44" ht="14.25">
-      <c r="M44" s="67"/>
-      <c r="N44" s="67"/>
+    <row r="44" ht="51">
+      <c r="A44" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B44" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="66" t="s">
+        <v>307</v>
+      </c>
+      <c r="E44" s="55" t="s">
+        <v>259</v>
+      </c>
+      <c r="F44" s="55" t="s">
+        <v>260</v>
+      </c>
+      <c r="G44" s="66"/>
+      <c r="H44" s="66"/>
+      <c r="I44" s="62" t="s">
+        <v>308</v>
+      </c>
+      <c r="J44" s="66"/>
+      <c r="K44" s="66"/>
+      <c r="L44" s="66"/>
+      <c r="M44" s="66"/>
+      <c r="N44" s="26"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="M45" s="67"/>
-      <c r="N45" s="67"/>
+      <c r="A45" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B45" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" s="54" t="s">
+        <v>309</v>
+      </c>
+      <c r="E45" s="67" t="s">
+        <v>310</v>
+      </c>
+      <c r="F45" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="62" t="s">
+        <v>312</v>
+      </c>
+      <c r="J45" s="54"/>
+      <c r="K45" s="54"/>
+      <c r="L45" s="54"/>
+      <c r="M45" s="54"/>
+      <c r="N45" s="26"/>
     </row>
-    <row r="46" ht="14.25">
-      <c r="M46" s="67"/>
-      <c r="N46" s="67"/>
+    <row r="46" ht="38.25">
+      <c r="A46" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B46" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="D46" s="54" t="s">
+        <v>313</v>
+      </c>
+      <c r="E46" s="69" t="s">
+        <v>314</v>
+      </c>
+      <c r="F46" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="G46" s="26"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="62" t="s">
+        <v>315</v>
+      </c>
+      <c r="J46" s="54"/>
+      <c r="K46" s="54">
+        <v>2010</v>
+      </c>
+      <c r="L46" s="54" t="s">
+        <v>316</v>
+      </c>
+      <c r="M46" s="54"/>
+      <c r="N46" s="26"/>
     </row>
-    <row r="47" ht="14.25">
-      <c r="M47" s="67"/>
-      <c r="N47" s="67"/>
+    <row r="47" ht="38.25">
+      <c r="A47" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B47" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="C47" s="54" t="s">
+        <v>317</v>
+      </c>
+      <c r="D47" s="54" t="s">
+        <v>318</v>
+      </c>
+      <c r="E47" s="54" t="s">
+        <v>319</v>
+      </c>
+      <c r="F47" s="54"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="56" t="s">
+        <v>320</v>
+      </c>
+      <c r="J47" s="54"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="54" t="s">
+        <v>321</v>
+      </c>
+      <c r="M47" s="54"/>
+      <c r="N47" s="70" t="s">
+        <v>322</v>
+      </c>
     </row>
-    <row r="48" ht="14.25">
-      <c r="M48" s="67"/>
-      <c r="N48" s="67"/>
+    <row r="48" ht="85.5">
+      <c r="A48" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B48" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="54" t="s">
+        <v>317</v>
+      </c>
+      <c r="D48" s="54" t="s">
+        <v>323</v>
+      </c>
+      <c r="E48" s="69" t="s">
+        <v>324</v>
+      </c>
+      <c r="F48" s="54" t="s">
+        <v>325</v>
+      </c>
+      <c r="G48" s="71"/>
+      <c r="H48" s="72"/>
+      <c r="I48" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J48" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="K48" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="L48" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="M48" s="57"/>
+      <c r="N48" s="26"/>
     </row>
-    <row r="49" ht="14.25">
-      <c r="M49" s="67"/>
-      <c r="N49" s="67"/>
+    <row r="49" ht="42.75">
+      <c r="A49" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" s="74" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" s="74" t="s">
+        <v>271</v>
+      </c>
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="74"/>
+      <c r="H49" s="74"/>
+      <c r="I49" s="75" t="s">
+        <v>327</v>
+      </c>
+      <c r="J49" s="74"/>
+      <c r="K49" s="74"/>
+      <c r="L49" s="74" t="s">
+        <v>328</v>
+      </c>
+      <c r="M49" s="74" t="s">
+        <v>329</v>
+      </c>
+      <c r="N49" s="76"/>
     </row>
-    <row r="50" ht="14.25">
-      <c r="M50" s="67"/>
-      <c r="N50" s="67"/>
+    <row r="50" ht="89.25">
+      <c r="A50" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B50" s="74" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" s="74" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" s="74" t="s">
+        <v>330</v>
+      </c>
+      <c r="E50" s="74" t="s">
+        <v>331</v>
+      </c>
+      <c r="F50" s="77"/>
+      <c r="G50" s="74"/>
+      <c r="H50" s="74"/>
+      <c r="I50" s="78" t="s">
+        <v>332</v>
+      </c>
+      <c r="J50" s="79"/>
+      <c r="K50" s="74"/>
+      <c r="L50" s="74" t="s">
+        <v>305</v>
+      </c>
+      <c r="M50" s="74"/>
+      <c r="N50" s="76"/>
     </row>
     <row r="51" ht="14.25">
-      <c r="M51" s="67"/>
-      <c r="N51" s="67"/>
+      <c r="A51" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B51" s="74" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="74" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" s="74" t="s">
+        <v>333</v>
+      </c>
+      <c r="E51" s="74" t="s">
+        <v>331</v>
+      </c>
+      <c r="F51" s="77"/>
+      <c r="G51" s="74"/>
+      <c r="H51" s="74"/>
+      <c r="I51" s="78" t="s">
+        <v>334</v>
+      </c>
+      <c r="J51" s="74"/>
+      <c r="K51" s="74"/>
+      <c r="L51" s="74"/>
+      <c r="M51" s="74"/>
+      <c r="N51" s="76"/>
     </row>
-    <row r="52" ht="14.25">
-      <c r="M52" s="67"/>
-      <c r="N52" s="67"/>
+    <row r="52" ht="25.5">
+      <c r="A52" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B52" s="74" t="s">
+        <v>111</v>
+      </c>
+      <c r="C52" s="74" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="74" t="s">
+        <v>335</v>
+      </c>
+      <c r="E52" s="74" t="s">
+        <v>331</v>
+      </c>
+      <c r="F52" s="77"/>
+      <c r="G52" s="74"/>
+      <c r="H52" s="74"/>
+      <c r="I52" s="78" t="s">
+        <v>332</v>
+      </c>
+      <c r="J52" s="79"/>
+      <c r="K52" s="74"/>
+      <c r="L52" s="74" t="s">
+        <v>305</v>
+      </c>
+      <c r="M52" s="74"/>
+      <c r="N52" s="76"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="M53" s="67"/>
-      <c r="N53" s="67"/>
+      <c r="A53" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B53" s="74" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="D53" s="74" t="s">
+        <v>336</v>
+      </c>
+      <c r="E53" s="74"/>
+      <c r="F53" s="77" t="s">
+        <v>337</v>
+      </c>
+      <c r="G53" s="74"/>
+      <c r="H53" s="74"/>
+      <c r="I53" s="80"/>
+      <c r="J53" s="74"/>
+      <c r="K53" s="74"/>
+      <c r="L53" s="74"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="76"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="M54" s="67"/>
-      <c r="N54" s="67"/>
+      <c r="A54" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B54" s="74" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" s="74" t="s">
+        <v>169</v>
+      </c>
+      <c r="D54" s="74" t="s">
+        <v>338</v>
+      </c>
+      <c r="E54" s="74" t="s">
+        <v>331</v>
+      </c>
+      <c r="F54" s="77"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="74"/>
+      <c r="L54" s="74"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="76"/>
     </row>
-    <row r="55" ht="14.25">
-      <c r="M55" s="67"/>
-      <c r="N55" s="67"/>
+    <row r="55" ht="25.5">
+      <c r="A55" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B55" s="74" t="s">
+        <v>111</v>
+      </c>
+      <c r="C55" s="74" t="s">
+        <v>169</v>
+      </c>
+      <c r="D55" s="74" t="s">
+        <v>339</v>
+      </c>
+      <c r="E55" s="74" t="s">
+        <v>331</v>
+      </c>
+      <c r="F55" s="77" t="s">
+        <v>340</v>
+      </c>
+      <c r="G55" s="74"/>
+      <c r="H55" s="74"/>
+      <c r="I55" s="78" t="s">
+        <v>341</v>
+      </c>
+      <c r="J55" s="74"/>
+      <c r="K55" s="74"/>
+      <c r="L55" s="74"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="76"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="M56" s="67"/>
-      <c r="N56" s="67"/>
+      <c r="A56" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B56" s="74" t="s">
+        <v>111</v>
+      </c>
+      <c r="C56" s="74" t="s">
+        <v>342</v>
+      </c>
+      <c r="D56" s="74" t="s">
+        <v>343</v>
+      </c>
+      <c r="E56" s="74" t="s">
+        <v>344</v>
+      </c>
+      <c r="F56" s="77" t="s">
+        <v>345</v>
+      </c>
+      <c r="G56" s="74"/>
+      <c r="H56" s="74"/>
+      <c r="I56" s="78" t="s">
+        <v>346</v>
+      </c>
+      <c r="J56" s="74"/>
+      <c r="K56" s="74"/>
+      <c r="L56" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="M56" s="74"/>
+      <c r="N56" s="76"/>
+    </row>
+    <row r="57" ht="38.25">
+      <c r="A57" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B57" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" s="74" t="s">
+        <v>347</v>
+      </c>
+      <c r="D57" s="74" t="s">
+        <v>348</v>
+      </c>
+      <c r="E57" s="74" t="s">
+        <v>331</v>
+      </c>
+      <c r="F57" s="74"/>
+      <c r="G57" s="74"/>
+      <c r="H57" s="74"/>
+      <c r="I57" s="82"/>
+      <c r="J57" s="74"/>
+      <c r="K57" s="74"/>
+      <c r="L57" s="74"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="74" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="58" ht="14.25">
+      <c r="A58" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B58" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" s="74" t="s">
+        <v>347</v>
+      </c>
+      <c r="D58" s="74" t="s">
+        <v>350</v>
+      </c>
+      <c r="E58" s="74" t="s">
+        <v>331</v>
+      </c>
+      <c r="F58" s="74"/>
+      <c r="G58" s="74"/>
+      <c r="H58" s="74"/>
+      <c r="I58" s="82"/>
+      <c r="J58" s="74"/>
+      <c r="K58" s="74"/>
+      <c r="L58" s="74"/>
+      <c r="M58" s="74"/>
+      <c r="N58" s="74" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="59" ht="14.25">
+      <c r="A59" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B59" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" s="74" t="s">
+        <v>351</v>
+      </c>
+      <c r="D59" s="74" t="s">
+        <v>352</v>
+      </c>
+      <c r="E59" s="74" t="s">
+        <v>353</v>
+      </c>
+      <c r="F59" s="83" t="s">
+        <v>354</v>
+      </c>
+      <c r="G59" s="74"/>
+      <c r="H59" s="74"/>
+      <c r="I59" s="82"/>
+      <c r="J59" s="74"/>
+      <c r="K59" s="74"/>
+      <c r="L59" s="74"/>
+      <c r="M59" s="74"/>
+      <c r="N59" s="74" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="60" ht="51">
+      <c r="A60" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B60" s="74" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="D60" s="74" t="s">
+        <v>355</v>
+      </c>
+      <c r="E60" s="74" t="s">
+        <v>331</v>
+      </c>
+      <c r="F60" s="74"/>
+      <c r="G60" s="74"/>
+      <c r="H60" s="74"/>
+      <c r="I60" s="82"/>
+      <c r="J60" s="74"/>
+      <c r="K60" s="74"/>
+      <c r="L60" s="74"/>
+      <c r="M60" s="74"/>
+      <c r="N60" s="74" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="61" ht="38.25">
+      <c r="A61" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B61" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C61" s="74" t="s">
+        <v>107</v>
+      </c>
+      <c r="D61" s="74" t="s">
+        <v>356</v>
+      </c>
+      <c r="E61" s="74"/>
+      <c r="F61" s="74"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="74"/>
+      <c r="I61" s="82"/>
+      <c r="J61" s="74"/>
+      <c r="K61" s="74"/>
+      <c r="L61" s="74"/>
+      <c r="M61" s="74"/>
+      <c r="N61" s="76"/>
+    </row>
+    <row r="62" ht="14.25">
+      <c r="A62" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B62" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" s="74" t="s">
+        <v>143</v>
+      </c>
+      <c r="D62" s="74" t="s">
+        <v>357</v>
+      </c>
+      <c r="E62" s="74"/>
+      <c r="F62" s="74"/>
+      <c r="G62" s="74"/>
+      <c r="H62" s="74"/>
+      <c r="I62" s="82"/>
+      <c r="J62" s="74"/>
+      <c r="K62" s="74"/>
+      <c r="L62" s="74"/>
+      <c r="M62" s="74"/>
+      <c r="N62" s="76"/>
+    </row>
+    <row r="63" ht="14.25">
+      <c r="A63" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B63" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" s="74" t="s">
+        <v>143</v>
+      </c>
+      <c r="D63" s="74" t="s">
+        <v>358</v>
+      </c>
+      <c r="E63" s="74"/>
+      <c r="F63" s="74"/>
+      <c r="G63" s="74"/>
+      <c r="H63" s="74"/>
+      <c r="I63" s="82"/>
+      <c r="J63" s="74"/>
+      <c r="K63" s="74"/>
+      <c r="L63" s="74"/>
+      <c r="M63" s="74"/>
+      <c r="N63" s="76"/>
+    </row>
+    <row r="64" ht="14.25">
+      <c r="A64" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B64" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C64" s="74" t="s">
+        <v>143</v>
+      </c>
+      <c r="D64" s="74" t="s">
+        <v>333</v>
+      </c>
+      <c r="E64" s="74" t="s">
+        <v>331</v>
+      </c>
+      <c r="F64" s="74"/>
+      <c r="G64" s="74"/>
+      <c r="H64" s="74"/>
+      <c r="I64" s="82"/>
+      <c r="J64" s="74"/>
+      <c r="K64" s="74"/>
+      <c r="L64" s="74"/>
+      <c r="M64" s="74"/>
+      <c r="N64" s="76"/>
+    </row>
+    <row r="65" ht="14.25">
+      <c r="A65" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B65" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C65" s="74" t="s">
+        <v>317</v>
+      </c>
+      <c r="D65" s="74" t="s">
+        <v>359</v>
+      </c>
+      <c r="E65" s="74"/>
+      <c r="F65" s="74"/>
+      <c r="G65" s="74"/>
+      <c r="H65" s="74"/>
+      <c r="I65" s="82"/>
+      <c r="J65" s="74"/>
+      <c r="K65" s="74"/>
+      <c r="L65" s="74"/>
+      <c r="M65" s="74"/>
+      <c r="N65" s="76"/>
+    </row>
+    <row r="66" ht="14.25">
+      <c r="A66" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B66" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" s="74" t="s">
+        <v>360</v>
+      </c>
+      <c r="D66" s="74" t="s">
+        <v>361</v>
+      </c>
+      <c r="E66" s="74"/>
+      <c r="F66" s="74"/>
+      <c r="G66" s="74"/>
+      <c r="H66" s="74"/>
+      <c r="I66" s="82"/>
+      <c r="J66" s="74"/>
+      <c r="K66" s="74"/>
+      <c r="L66" s="74"/>
+      <c r="M66" s="74"/>
+      <c r="N66" s="76"/>
+    </row>
+    <row r="67" ht="14.25">
+      <c r="A67" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B67" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" s="74" t="s">
+        <v>360</v>
+      </c>
+      <c r="D67" s="74" t="s">
+        <v>362</v>
+      </c>
+      <c r="E67" s="84" t="s">
+        <v>331</v>
+      </c>
+      <c r="F67" s="74"/>
+      <c r="G67" s="74"/>
+      <c r="H67" s="74"/>
+      <c r="I67" s="82"/>
+      <c r="J67" s="74"/>
+      <c r="K67" s="74"/>
+      <c r="L67" s="74"/>
+      <c r="M67" s="74"/>
+      <c r="N67" s="76"/>
+    </row>
+    <row r="68" ht="14.25">
+      <c r="A68" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B68" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C68" s="74" t="s">
+        <v>360</v>
+      </c>
+      <c r="D68" s="74" t="s">
+        <v>361</v>
+      </c>
+      <c r="E68" s="84" t="s">
+        <v>331</v>
+      </c>
+      <c r="F68" s="74"/>
+      <c r="G68" s="74"/>
+      <c r="H68" s="74"/>
+      <c r="I68" s="82"/>
+      <c r="J68" s="74"/>
+      <c r="K68" s="74"/>
+      <c r="L68" s="74"/>
+      <c r="M68" s="74"/>
+      <c r="N68" s="76"/>
+    </row>
+    <row r="69" ht="14.25">
+      <c r="A69" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B69" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C69" s="74" t="s">
+        <v>360</v>
+      </c>
+      <c r="D69" s="74" t="s">
+        <v>335</v>
+      </c>
+      <c r="E69" s="84" t="s">
+        <v>331</v>
+      </c>
+      <c r="F69" s="74"/>
+      <c r="G69" s="74"/>
+      <c r="H69" s="74"/>
+      <c r="I69" s="75" t="s">
+        <v>363</v>
+      </c>
+      <c r="J69" s="79"/>
+      <c r="K69" s="74"/>
+      <c r="L69" s="74" t="s">
+        <v>305</v>
+      </c>
+      <c r="M69" s="74"/>
+      <c r="N69" s="76"/>
+    </row>
+    <row r="70" ht="14.25">
+      <c r="A70" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B70" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" s="74" t="s">
+        <v>360</v>
+      </c>
+      <c r="D70" s="74" t="s">
+        <v>330</v>
+      </c>
+      <c r="E70" s="84" t="s">
+        <v>331</v>
+      </c>
+      <c r="F70" s="74"/>
+      <c r="G70" s="74"/>
+      <c r="H70" s="74"/>
+      <c r="I70" s="75" t="s">
+        <v>332</v>
+      </c>
+      <c r="J70" s="79"/>
+      <c r="K70" s="74"/>
+      <c r="L70" s="74" t="s">
+        <v>305</v>
+      </c>
+      <c r="M70" s="74"/>
+      <c r="N70" s="76"/>
+    </row>
+    <row r="71" ht="14.25">
+      <c r="A71" s="85" t="s">
+        <v>364</v>
+      </c>
+      <c r="B71" s="85" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" s="85" t="s">
+        <v>365</v>
+      </c>
+      <c r="D71" s="85" t="s">
+        <v>366</v>
+      </c>
+      <c r="E71" s="85" t="s">
+        <v>367</v>
+      </c>
+      <c r="F71" s="86" t="s">
+        <v>368</v>
+      </c>
+      <c r="G71" s="85" t="s">
+        <v>369</v>
+      </c>
+      <c r="H71" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" s="87" t="s">
+        <v>370</v>
+      </c>
+      <c r="J71" s="86" t="s">
+        <v>226</v>
+      </c>
+      <c r="K71" s="85">
+        <v>2023</v>
+      </c>
+      <c r="L71" s="85" t="s">
+        <v>24</v>
+      </c>
+      <c r="M71" s="85" t="s">
+        <v>371</v>
+      </c>
+      <c r="N71" s="86" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="72" ht="14.25">
+      <c r="A72" s="85" t="s">
+        <v>364</v>
+      </c>
+      <c r="B72" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="85" t="s">
+        <v>373</v>
+      </c>
+      <c r="D72" s="85" t="s">
+        <v>374</v>
+      </c>
+      <c r="E72" s="85" t="s">
+        <v>375</v>
+      </c>
+      <c r="F72" s="85"/>
+      <c r="G72" s="85" t="s">
+        <v>376</v>
+      </c>
+      <c r="H72" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="88"/>
+      <c r="J72" s="85"/>
+      <c r="K72" s="85"/>
+      <c r="L72" s="85"/>
+      <c r="M72" s="85" t="s">
+        <v>371</v>
+      </c>
+      <c r="N72" s="85"/>
+    </row>
+    <row r="73" ht="14.25">
+      <c r="A73" s="1"/>
+      <c r="I73" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N41">
-    <sortState ref="A2:N41" columnSort="0">
-      <sortCondition sortBy="value" descending="0" ref="A2:A41"/>
-      <sortCondition sortBy="value" descending="0" ref="M2:M41"/>
-      <sortCondition sortBy="value" descending="0" ref="B2:B41"/>
-      <sortCondition sortBy="value" descending="0" ref="C2:C41"/>
+  <autoFilter ref="A1:N72">
+    <sortState ref="A2:N72" columnSort="0">
+      <sortCondition sortBy="value" descending="0" ref="A2:A72"/>
+      <sortCondition sortBy="value" descending="0" ref="M2:M72"/>
+      <sortCondition sortBy="value" descending="0" ref="B2:B72"/>
+      <sortCondition sortBy="value" descending="0" ref="C2:C72"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
@@ -8641,27 +10689,51 @@
     <hyperlink r:id="rId7" ref="I9"/>
     <hyperlink r:id="rId7" ref="I10"/>
     <hyperlink r:id="rId7" ref="I11"/>
-    <hyperlink r:id="rId8" ref="I12"/>
-    <hyperlink r:id="rId9" ref="I13"/>
-    <hyperlink r:id="rId10" location="c=indicator&amp;i=stru_2020_1.pbs20&amp;t=A02&amp;view=map11" ref="I14"/>
-    <hyperlink r:id="rId11" ref="I15"/>
-    <hyperlink r:id="rId12" ref="I16"/>
-    <hyperlink r:id="rId13" ref="I17"/>
-    <hyperlink r:id="rId14" ref="I18"/>
-    <hyperlink r:id="rId15" ref="I20"/>
-    <hyperlink r:id="rId16" ref="I21"/>
-    <hyperlink r:id="rId17" ref="I22"/>
-    <hyperlink r:id="rId10" location="c=indicator&amp;i=stru2.partssucnb10&amp;t=A01&amp;view=map2" ref="I23"/>
-    <hyperlink r:id="rId18" ref="I24"/>
-    <hyperlink r:id="rId19" ref="I25"/>
-    <hyperlink r:id="rId20" ref="I27"/>
-    <hyperlink r:id="rId21" ref="I28"/>
-    <hyperlink r:id="rId7" ref="I29"/>
-    <hyperlink r:id="rId22" ref="I30"/>
-    <hyperlink r:id="rId23" ref="I31"/>
-    <hyperlink r:id="rId22" ref="I32"/>
+    <hyperlink r:id="rId7" ref="I12"/>
+    <hyperlink r:id="rId8" ref="I13"/>
+    <hyperlink r:id="rId9" ref="I14"/>
+    <hyperlink r:id="rId10" ref="I15"/>
+    <hyperlink r:id="rId11" location="c=indicator&amp;i=stru_2020_1.pbs20&amp;t=A02&amp;view=map11" ref="I16"/>
+    <hyperlink r:id="rId12" ref="I17"/>
+    <hyperlink r:id="rId11" location="c=indicator&amp;i=cult_2020_2.partirrig20_&amp;t=A02&amp;view=map11" ref="I18"/>
+    <hyperlink r:id="rId13" ref="I19"/>
+    <hyperlink r:id="rId14" ref="I20"/>
+    <hyperlink r:id="rId15" ref="I21"/>
+    <hyperlink r:id="rId16" ref="I22"/>
+    <hyperlink r:id="rId17" ref="I23"/>
+    <hyperlink r:id="rId17" ref="I24"/>
+    <hyperlink r:id="rId18" ref="I25"/>
+    <hyperlink r:id="rId18" ref="I26"/>
+    <hyperlink r:id="rId18" ref="I27"/>
+    <hyperlink r:id="rId18" ref="I28"/>
+    <hyperlink r:id="rId19" ref="I29"/>
+    <hyperlink r:id="rId20" ref="I30"/>
+    <hyperlink r:id="rId11" location="c=indicator&amp;i=stru2.partssucnb10&amp;t=A01&amp;view=map2" ref="I31"/>
+    <hyperlink r:id="rId21" ref="I32"/>
+    <hyperlink r:id="rId22" ref="I33"/>
+    <hyperlink r:id="rId23" ref="I34"/>
     <hyperlink r:id="rId24" ref="I35"/>
-    <hyperlink r:id="rId25" ref="I36"/>
+    <hyperlink r:id="rId25" ref="M35"/>
+    <hyperlink r:id="rId26" ref="I36"/>
+    <hyperlink r:id="rId27" ref="I37"/>
+    <hyperlink r:id="rId28" ref="I38"/>
+    <hyperlink r:id="rId29" ref="I39"/>
+    <hyperlink r:id="rId7" ref="I41"/>
+    <hyperlink r:id="rId30" ref="I42"/>
+    <hyperlink r:id="rId31" ref="I43"/>
+    <hyperlink r:id="rId16" ref="I44"/>
+    <hyperlink r:id="rId30" ref="I45"/>
+    <hyperlink r:id="rId32" ref="I46"/>
+    <hyperlink r:id="rId33" ref="I47"/>
+    <hyperlink r:id="rId7" ref="I48"/>
+    <hyperlink r:id="rId34" location="export" ref="I49"/>
+    <hyperlink r:id="rId35" ref="I50"/>
+    <hyperlink r:id="rId36" ref="I51"/>
+    <hyperlink r:id="rId35" ref="I52"/>
+    <hyperlink r:id="rId37" ref="I55"/>
+    <hyperlink r:id="rId38" ref="I56"/>
+    <hyperlink r:id="rId35" ref="I69"/>
+    <hyperlink r:id="rId35" ref="I70"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -8679,60 +10751,60 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="68" t="s">
-        <v>248</v>
-      </c>
-      <c r="B1" s="68" t="s">
-        <v>249</v>
+      <c r="A1" s="89" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1" s="89" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="2" s="0" customFormat="1" ht="14.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="70" t="s">
-        <v>250</v>
+      <c r="B2" s="91" t="s">
+        <v>379</v>
       </c>
       <c r="C2"/>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="29" t="s">
-        <v>153</v>
+      <c r="A3" s="92" t="s">
+        <v>380</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="39" t="s">
-        <v>177</v>
+      <c r="A4" s="36" t="s">
+        <v>184</v>
       </c>
       <c r="B4" t="s">
-        <v>252</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="47" t="s">
-        <v>191</v>
+      <c r="A5" s="54" t="s">
+        <v>256</v>
       </c>
       <c r="B5" t="s">
-        <v>253</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="56" t="s">
-        <v>216</v>
+      <c r="A6" s="74" t="s">
+        <v>326</v>
       </c>
       <c r="B6" t="s">
-        <v>254</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="65" t="s">
-        <v>244</v>
+      <c r="A7" s="85" t="s">
+        <v>364</v>
       </c>
       <c r="B7" t="s">
-        <v>255</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -8755,20 +10827,20 @@
     <col customWidth="1" min="6" max="6" width="12.8515625"/>
     <col bestFit="1" customWidth="1" min="7" max="7" width="25.78125"/>
     <col bestFit="1" customWidth="1" min="8" max="8" width="21.3515625"/>
-    <col customWidth="1" min="9" max="9" style="71" width="32.7109375"/>
+    <col customWidth="1" min="9" max="9" style="93" width="32.7109375"/>
     <col customWidth="1" min="10" max="10" width="23.57421875"/>
     <col customWidth="1" min="11" max="11" width="44.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" s="68" customFormat="1" ht="25.5">
-      <c r="A1" s="68" t="s">
+    <row r="1" s="89" customFormat="1" ht="25.5">
+      <c r="A1" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="68" t="s">
-        <v>256</v>
-      </c>
-      <c r="C1" s="68" t="s">
-        <v>257</v>
+      <c r="B1" s="89" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" s="89" t="s">
+        <v>387</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>9</v>
@@ -8785,49 +10857,49 @@
       <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="72" t="s">
-        <v>258</v>
-      </c>
-      <c r="J1" s="68" t="s">
-        <v>259</v>
-      </c>
-      <c r="K1" s="68" t="s">
+      <c r="I1" s="94" t="s">
+        <v>388</v>
+      </c>
+      <c r="J1" s="89" t="s">
+        <v>389</v>
+      </c>
+      <c r="K1" s="89" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="73" customFormat="1" ht="28.5">
-      <c r="A2" s="74" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="75" t="s">
-        <v>260</v>
-      </c>
-      <c r="C2" s="74" t="s">
-        <v>261</v>
-      </c>
-      <c r="D2" s="75" t="s">
-        <v>262</v>
-      </c>
-      <c r="E2" s="75" t="s">
-        <v>263</v>
-      </c>
-      <c r="F2" s="75" t="s">
-        <v>264</v>
-      </c>
-      <c r="G2" s="73" t="s">
-        <v>265</v>
-      </c>
-      <c r="H2" s="74" t="s">
-        <v>266</v>
-      </c>
-      <c r="I2" s="76" t="s">
-        <v>267</v>
-      </c>
-      <c r="J2" s="73" t="s">
-        <v>268</v>
-      </c>
-      <c r="K2" s="77" t="s">
-        <v>269</v>
+    <row r="2" s="95" customFormat="1" ht="28.5">
+      <c r="A2" s="96" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="97" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" s="96" t="s">
+        <v>391</v>
+      </c>
+      <c r="D2" s="97" t="s">
+        <v>392</v>
+      </c>
+      <c r="E2" s="97" t="s">
+        <v>393</v>
+      </c>
+      <c r="F2" s="97" t="s">
+        <v>394</v>
+      </c>
+      <c r="G2" s="95" t="s">
+        <v>395</v>
+      </c>
+      <c r="H2" s="96" t="s">
+        <v>396</v>
+      </c>
+      <c r="I2" s="98" t="s">
+        <v>397</v>
+      </c>
+      <c r="J2" s="95" t="s">
+        <v>398</v>
+      </c>
+      <c r="K2" s="99" t="s">
+        <v>399</v>
       </c>
     </row>
   </sheetData>
